--- a/IG/7日版/AI Native-生成AI_IG.xlsx
+++ b/IG/7日版/AI Native-生成AI_IG.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C09084C-BF9C-4FF5-9386-ED8F2B890F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE5D25A-86F4-453F-87D6-2BEC4DFBC80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -351,16 +351,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>オリエンテーション用資材</t>
-    <rPh sb="9" eb="10">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シザイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>【AI Native研修】 生成ＡＩの衝撃.pptx</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -2024,15 +2014,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>・教材のダウンロード
-・本科目の概要説明
-　科目の位置づけや目的、全体スケジュールの説明</t>
-    <rPh sb="1" eb="3">
-      <t>キョウザイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">・共通1
 </t>
     <rPh sb="1" eb="3">
@@ -2417,6 +2398,31 @@
     </rPh>
     <rPh sb="20" eb="22">
       <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>【AI Native研修-生成AI】研修の概要.pptx</t>
+    <rPh sb="10" eb="12">
+      <t>ケンシュウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ケンシュウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>・教材のダウンロード
+・本科目の概要説明
+　科目の位置づけや目的、全体の説明</t>
+    <rPh sb="1" eb="3">
+      <t>キョウザイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -3171,6 +3177,42 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3179,42 +3221,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3961,7 +3967,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D40" s="56"/>
       <c r="E40" s="53"/>
@@ -3992,7 +3998,7 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="C43" s="85" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D43" s="57"/>
       <c r="E43" s="55"/>
@@ -4126,7 +4132,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>34</v>
+        <v>204</v>
       </c>
       <c r="D8" s="45" t="s">
         <v>20</v>
@@ -4192,12 +4198,12 @@
         <v>3</v>
       </c>
       <c r="D12" s="100" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="E12" s="101"/>
       <c r="F12" s="102"/>
       <c r="G12" s="90" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H12" s="20"/>
       <c r="I12" s="50" t="s">
@@ -4310,18 +4316,18 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="110" t="s">
-        <v>205</v>
-      </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="110"/>
+      <c r="B5" s="122" t="s">
+        <v>203</v>
+      </c>
+      <c r="C5" s="122"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="122"/>
+      <c r="I5" s="122"/>
+      <c r="J5" s="122"/>
+      <c r="K5" s="122"/>
       <c r="L5" s="29"/>
       <c r="M5" s="30"/>
     </row>
@@ -4360,10 +4366,10 @@
     </row>
     <row r="8" spans="1:14">
       <c r="B8" s="34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="45" t="s">
         <v>20</v>
@@ -4399,10 +4405,10 @@
       <c r="H10" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="108" t="s">
+      <c r="I10" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="109"/>
+      <c r="J10" s="121"/>
       <c r="K10" s="98" t="s">
         <v>33</v>
       </c>
@@ -4432,7 +4438,7 @@
     </row>
     <row r="12" spans="1:14" ht="75.599999999999994">
       <c r="A12" s="10"/>
-      <c r="B12" s="118" t="str">
+      <c r="B12" s="108" t="str">
         <f>master!B3</f>
         <v>自己紹介</v>
       </c>
@@ -4440,13 +4446,13 @@
         <f>master!C3</f>
         <v>ー</v>
       </c>
-      <c r="D12" s="111" t="s">
-        <v>177</v>
-      </c>
-      <c r="E12" s="112"/>
-      <c r="F12" s="113"/>
+      <c r="D12" s="116" t="s">
+        <v>176</v>
+      </c>
+      <c r="E12" s="117"/>
+      <c r="F12" s="118"/>
       <c r="G12" s="51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="49" t="s">
@@ -4462,15 +4468,15 @@
     </row>
     <row r="13" spans="1:14" ht="88.2">
       <c r="A13" s="10"/>
-      <c r="B13" s="119"/>
+      <c r="B13" s="109"/>
       <c r="C13" s="68"/>
-      <c r="D13" s="114" t="s">
-        <v>179</v>
-      </c>
-      <c r="E13" s="115"/>
-      <c r="F13" s="116"/>
+      <c r="D13" s="113" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="114"/>
+      <c r="F13" s="115"/>
       <c r="G13" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H13" s="69"/>
       <c r="I13" s="70" t="s">
@@ -4486,7 +4492,7 @@
     </row>
     <row r="14" spans="1:14" ht="138.6">
       <c r="A14" s="10"/>
-      <c r="B14" s="117" t="str">
+      <c r="B14" s="119" t="str">
         <f>master!B4</f>
         <v>導入編</v>
       </c>
@@ -4494,13 +4500,13 @@
         <f>master!C4</f>
         <v>あなたはもう生成ＡＩを使っていますか？</v>
       </c>
-      <c r="D14" s="111" t="s">
-        <v>152</v>
-      </c>
-      <c r="E14" s="112"/>
-      <c r="F14" s="113"/>
+      <c r="D14" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="E14" s="117"/>
+      <c r="F14" s="118"/>
       <c r="G14" s="51" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="49" t="s">
@@ -4516,18 +4522,18 @@
     </row>
     <row r="15" spans="1:14" ht="75.599999999999994">
       <c r="A15" s="11"/>
-      <c r="B15" s="117"/>
+      <c r="B15" s="119"/>
       <c r="C15" s="51" t="str">
         <f>master!C5</f>
         <v>FYI：システム開発SaaS　「GEAR.indigo」</v>
       </c>
-      <c r="D15" s="111" t="s">
-        <v>153</v>
-      </c>
-      <c r="E15" s="112"/>
-      <c r="F15" s="113"/>
+      <c r="D15" s="116" t="s">
+        <v>152</v>
+      </c>
+      <c r="E15" s="117"/>
+      <c r="F15" s="118"/>
       <c r="G15" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="49" t="s">
@@ -4543,18 +4549,18 @@
     </row>
     <row r="16" spans="1:14" ht="37.799999999999997">
       <c r="A16" s="11"/>
-      <c r="B16" s="117"/>
+      <c r="B16" s="119"/>
       <c r="C16" s="51" t="str">
         <f>master!C6</f>
         <v>FYI：GEAR.indigo　「業務要件一覧」</v>
       </c>
-      <c r="D16" s="111" t="s">
-        <v>154</v>
-      </c>
-      <c r="E16" s="112"/>
-      <c r="F16" s="113"/>
+      <c r="D16" s="116" t="s">
+        <v>153</v>
+      </c>
+      <c r="E16" s="117"/>
+      <c r="F16" s="118"/>
       <c r="G16" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="49" t="s">
@@ -4570,18 +4576,18 @@
     </row>
     <row r="17" spans="1:14" ht="37.799999999999997">
       <c r="A17" s="11"/>
-      <c r="B17" s="117"/>
+      <c r="B17" s="119"/>
       <c r="C17" s="51" t="str">
         <f>master!C7</f>
         <v>FYI：GEAR.indigo　「システム化業務フロー」</v>
       </c>
-      <c r="D17" s="111" t="s">
-        <v>155</v>
-      </c>
-      <c r="E17" s="112"/>
-      <c r="F17" s="113"/>
+      <c r="D17" s="116" t="s">
+        <v>154</v>
+      </c>
+      <c r="E17" s="117"/>
+      <c r="F17" s="118"/>
       <c r="G17" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="49" t="s">
@@ -4597,18 +4603,18 @@
     </row>
     <row r="18" spans="1:14" ht="37.799999999999997">
       <c r="A18" s="11"/>
-      <c r="B18" s="117"/>
+      <c r="B18" s="119"/>
       <c r="C18" s="51" t="str">
         <f>master!C8</f>
         <v>FYI：GEAR.indigo　「テーブル定義書」</v>
       </c>
-      <c r="D18" s="111" t="s">
-        <v>156</v>
-      </c>
-      <c r="E18" s="112"/>
-      <c r="F18" s="113"/>
+      <c r="D18" s="116" t="s">
+        <v>155</v>
+      </c>
+      <c r="E18" s="117"/>
+      <c r="F18" s="118"/>
       <c r="G18" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="49" t="s">
@@ -4624,18 +4630,18 @@
     </row>
     <row r="19" spans="1:14" ht="37.799999999999997">
       <c r="A19" s="11"/>
-      <c r="B19" s="117"/>
+      <c r="B19" s="119"/>
       <c r="C19" s="51" t="str">
         <f>master!C9</f>
         <v>FYI：GEAR.indigo　「画面定義書」</v>
       </c>
-      <c r="D19" s="111" t="s">
-        <v>157</v>
-      </c>
-      <c r="E19" s="112"/>
-      <c r="F19" s="113"/>
+      <c r="D19" s="116" t="s">
+        <v>156</v>
+      </c>
+      <c r="E19" s="117"/>
+      <c r="F19" s="118"/>
       <c r="G19" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H19" s="12"/>
       <c r="I19" s="49" t="s">
@@ -4651,18 +4657,18 @@
     </row>
     <row r="20" spans="1:14" ht="50.4">
       <c r="A20" s="11"/>
-      <c r="B20" s="117"/>
+      <c r="B20" s="119"/>
       <c r="C20" s="51" t="str">
         <f>master!C10</f>
         <v>GEAR.indigo が （いずれ）見せてくれるもの</v>
       </c>
-      <c r="D20" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="E20" s="112"/>
-      <c r="F20" s="113"/>
+      <c r="D20" s="116" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" s="117"/>
+      <c r="F20" s="118"/>
       <c r="G20" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="49" t="s">
@@ -4678,18 +4684,18 @@
     </row>
     <row r="21" spans="1:14" ht="37.799999999999997">
       <c r="A21" s="11"/>
-      <c r="B21" s="117"/>
+      <c r="B21" s="119"/>
       <c r="C21" s="51" t="str">
         <f>master!C11</f>
         <v>あなたはどちらになりたいですか？</v>
       </c>
-      <c r="D21" s="111" t="s">
-        <v>130</v>
-      </c>
-      <c r="E21" s="112"/>
-      <c r="F21" s="113"/>
+      <c r="D21" s="116" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="117"/>
+      <c r="F21" s="118"/>
       <c r="G21" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="49" t="s">
@@ -4705,18 +4711,18 @@
     </row>
     <row r="22" spans="1:14" ht="37.799999999999997">
       <c r="A22" s="11"/>
-      <c r="B22" s="117"/>
+      <c r="B22" s="119"/>
       <c r="C22" s="51" t="str">
         <f>master!C12</f>
         <v>いま、生成AIができること　（システム開発関連）</v>
       </c>
-      <c r="D22" s="111" t="s">
-        <v>132</v>
-      </c>
-      <c r="E22" s="112"/>
-      <c r="F22" s="113"/>
+      <c r="D22" s="116" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" s="117"/>
+      <c r="F22" s="118"/>
       <c r="G22" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="49" t="s">
@@ -4732,18 +4738,18 @@
     </row>
     <row r="23" spans="1:14" ht="75.599999999999994">
       <c r="A23" s="11"/>
-      <c r="B23" s="117"/>
+      <c r="B23" s="119"/>
       <c r="C23" s="51" t="str">
         <f>master!C13</f>
         <v>いま、生成ＡＩができないこと</v>
       </c>
-      <c r="D23" s="111" t="s">
-        <v>203</v>
-      </c>
-      <c r="E23" s="112"/>
-      <c r="F23" s="113"/>
+      <c r="D23" s="116" t="s">
+        <v>201</v>
+      </c>
+      <c r="E23" s="117"/>
+      <c r="F23" s="118"/>
       <c r="G23" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="49" t="s">
@@ -4759,18 +4765,18 @@
     </row>
     <row r="24" spans="1:14" ht="226.8">
       <c r="A24" s="11"/>
-      <c r="B24" s="117"/>
+      <c r="B24" s="119"/>
       <c r="C24" s="51" t="str">
         <f>master!C14</f>
         <v>生成ＡＩを使う心得８条</v>
       </c>
-      <c r="D24" s="111" t="s">
-        <v>135</v>
-      </c>
-      <c r="E24" s="112"/>
-      <c r="F24" s="113"/>
+      <c r="D24" s="116" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="117"/>
+      <c r="F24" s="118"/>
       <c r="G24" s="51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="49" t="s">
@@ -4786,7 +4792,7 @@
     </row>
     <row r="25" spans="1:14" ht="25.2">
       <c r="A25" s="11"/>
-      <c r="B25" s="117" t="str">
+      <c r="B25" s="119" t="str">
         <f>master!B15</f>
         <v>復習編</v>
       </c>
@@ -4794,13 +4800,13 @@
         <f>master!C15</f>
         <v>NTTDATAが目指す方向性</v>
       </c>
-      <c r="D25" s="111" t="s">
-        <v>204</v>
-      </c>
-      <c r="E25" s="112"/>
-      <c r="F25" s="113"/>
+      <c r="D25" s="116" t="s">
+        <v>202</v>
+      </c>
+      <c r="E25" s="117"/>
+      <c r="F25" s="118"/>
       <c r="G25" s="51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="49" t="s">
@@ -4810,7 +4816,7 @@
         <v>6.9444444444444447E-4</v>
       </c>
       <c r="K25" s="43" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
@@ -4818,18 +4824,18 @@
     </row>
     <row r="26" spans="1:14" ht="25.2">
       <c r="A26" s="11"/>
-      <c r="B26" s="117"/>
+      <c r="B26" s="119"/>
       <c r="C26" s="51" t="str">
         <f>master!C16</f>
         <v>NTTデータ新入社員向け生成AI基礎講座</v>
       </c>
-      <c r="D26" s="111" t="s">
-        <v>204</v>
-      </c>
-      <c r="E26" s="112"/>
-      <c r="F26" s="113"/>
+      <c r="D26" s="116" t="s">
+        <v>202</v>
+      </c>
+      <c r="E26" s="117"/>
+      <c r="F26" s="118"/>
       <c r="G26" s="51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="49" t="s">
@@ -4839,7 +4845,7 @@
         <v>6.9444444444444447E-4</v>
       </c>
       <c r="K26" s="43" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
@@ -4847,18 +4853,18 @@
     </row>
     <row r="27" spans="1:14" ht="25.2">
       <c r="A27" s="11"/>
-      <c r="B27" s="117"/>
+      <c r="B27" s="119"/>
       <c r="C27" s="51" t="str">
         <f>master!C17</f>
         <v>プロンプト設計の基本</v>
       </c>
-      <c r="D27" s="111" t="s">
-        <v>148</v>
-      </c>
-      <c r="E27" s="112"/>
-      <c r="F27" s="113"/>
+      <c r="D27" s="116" t="s">
+        <v>147</v>
+      </c>
+      <c r="E27" s="117"/>
+      <c r="F27" s="118"/>
       <c r="G27" s="51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="49" t="s">
@@ -4874,18 +4880,18 @@
     </row>
     <row r="28" spans="1:14" ht="75.599999999999994">
       <c r="A28" s="11"/>
-      <c r="B28" s="117"/>
+      <c r="B28" s="119"/>
       <c r="C28" s="51" t="str">
         <f>master!C18</f>
         <v>プロンプト設計の基本を踏まえた構造型プロンプト</v>
       </c>
-      <c r="D28" s="111" t="s">
-        <v>149</v>
-      </c>
-      <c r="E28" s="112"/>
-      <c r="F28" s="113"/>
+      <c r="D28" s="116" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" s="117"/>
+      <c r="F28" s="118"/>
       <c r="G28" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="49" t="s">
@@ -4901,16 +4907,16 @@
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1">
       <c r="A29" s="11"/>
-      <c r="B29" s="117"/>
+      <c r="B29" s="119"/>
       <c r="C29" s="51" t="str">
         <f>master!C19</f>
         <v>本セクションで学ぶこと</v>
       </c>
-      <c r="D29" s="111"/>
-      <c r="E29" s="112"/>
-      <c r="F29" s="113"/>
+      <c r="D29" s="116"/>
+      <c r="E29" s="117"/>
+      <c r="F29" s="118"/>
       <c r="G29" s="51" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="49" t="s">
@@ -4926,18 +4932,18 @@
     </row>
     <row r="30" spans="1:14" ht="50.4">
       <c r="A30" s="11"/>
-      <c r="B30" s="117"/>
+      <c r="B30" s="119"/>
       <c r="C30" s="51" t="str">
         <f>master!C20</f>
         <v>エージェントAIとは何か？</v>
       </c>
-      <c r="D30" s="111" t="s">
-        <v>158</v>
-      </c>
-      <c r="E30" s="112"/>
-      <c r="F30" s="113"/>
+      <c r="D30" s="116" t="s">
+        <v>157</v>
+      </c>
+      <c r="E30" s="117"/>
+      <c r="F30" s="118"/>
       <c r="G30" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="49" t="s">
@@ -4953,18 +4959,18 @@
     </row>
     <row r="31" spans="1:14" ht="25.2">
       <c r="A31" s="11"/>
-      <c r="B31" s="117"/>
+      <c r="B31" s="119"/>
       <c r="C31" s="51" t="str">
         <f>master!C21</f>
         <v>エージェントの処理</v>
       </c>
-      <c r="D31" s="111" t="s">
-        <v>150</v>
-      </c>
-      <c r="E31" s="112"/>
-      <c r="F31" s="113"/>
+      <c r="D31" s="116" t="s">
+        <v>149</v>
+      </c>
+      <c r="E31" s="117"/>
+      <c r="F31" s="118"/>
       <c r="G31" s="51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="49" t="s">
@@ -4980,18 +4986,18 @@
     </row>
     <row r="32" spans="1:14" ht="37.799999999999997">
       <c r="A32" s="11"/>
-      <c r="B32" s="117"/>
+      <c r="B32" s="119"/>
       <c r="C32" s="51" t="str">
         <f>master!C22</f>
         <v>AIエージェントのアーキテクチャ</v>
       </c>
-      <c r="D32" s="111" t="s">
-        <v>136</v>
-      </c>
-      <c r="E32" s="112"/>
-      <c r="F32" s="113"/>
+      <c r="D32" s="116" t="s">
+        <v>135</v>
+      </c>
+      <c r="E32" s="117"/>
+      <c r="F32" s="118"/>
       <c r="G32" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="49" t="s">
@@ -5007,18 +5013,18 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="117"/>
+      <c r="B33" s="119"/>
       <c r="C33" s="51" t="str">
         <f>master!C23</f>
         <v>AIの強みを生かすポイント</v>
       </c>
-      <c r="D33" s="111" t="s">
-        <v>137</v>
-      </c>
-      <c r="E33" s="112"/>
-      <c r="F33" s="113"/>
+      <c r="D33" s="116" t="s">
+        <v>136</v>
+      </c>
+      <c r="E33" s="117"/>
+      <c r="F33" s="118"/>
       <c r="G33" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="49" t="s">
@@ -5034,7 +5040,7 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="11"/>
-      <c r="B34" s="117" t="str">
+      <c r="B34" s="119" t="str">
         <f>master!B24</f>
         <v>AI-Native研修の目的</v>
       </c>
@@ -5042,15 +5048,15 @@
         <f>master!C24</f>
         <v>1.研修概要</v>
       </c>
-      <c r="D34" s="111"/>
-      <c r="E34" s="112"/>
-      <c r="F34" s="113"/>
+      <c r="D34" s="116"/>
+      <c r="E34" s="117"/>
+      <c r="F34" s="118"/>
       <c r="G34" s="51" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J34" s="47">
         <v>0</v>
@@ -5062,18 +5068,18 @@
     </row>
     <row r="35" spans="1:14" ht="25.2">
       <c r="A35" s="11"/>
-      <c r="B35" s="117"/>
+      <c r="B35" s="119"/>
       <c r="C35" s="51" t="str">
         <f>master!C25</f>
         <v>2-1　背景目的</v>
       </c>
-      <c r="D35" s="111" t="s">
-        <v>138</v>
-      </c>
-      <c r="E35" s="112"/>
-      <c r="F35" s="113"/>
+      <c r="D35" s="116" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" s="117"/>
+      <c r="F35" s="118"/>
       <c r="G35" s="51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="49" t="s">
@@ -5089,18 +5095,18 @@
     </row>
     <row r="36" spans="1:14" ht="151.19999999999999">
       <c r="A36" s="11"/>
-      <c r="B36" s="117"/>
+      <c r="B36" s="119"/>
       <c r="C36" s="51" t="str">
         <f>master!C26</f>
         <v>2-3　研修のゴールと獲得可能な経験</v>
       </c>
-      <c r="D36" s="111" t="s">
-        <v>197</v>
-      </c>
-      <c r="E36" s="112"/>
-      <c r="F36" s="113"/>
+      <c r="D36" s="116" t="s">
+        <v>195</v>
+      </c>
+      <c r="E36" s="117"/>
+      <c r="F36" s="118"/>
       <c r="G36" s="51" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="49" t="s">
@@ -5116,18 +5122,18 @@
     </row>
     <row r="37" spans="1:14" ht="37.799999999999997">
       <c r="A37" s="11"/>
-      <c r="B37" s="117"/>
+      <c r="B37" s="119"/>
       <c r="C37" s="51" t="str">
         <f>master!C27</f>
         <v>AIエージェントを用いたシステム開発タスクの実行の大まかな流れ</v>
       </c>
-      <c r="D37" s="111" t="s">
-        <v>151</v>
-      </c>
-      <c r="E37" s="112"/>
-      <c r="F37" s="113"/>
+      <c r="D37" s="116" t="s">
+        <v>150</v>
+      </c>
+      <c r="E37" s="117"/>
+      <c r="F37" s="118"/>
       <c r="G37" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="49" t="s">
@@ -5143,18 +5149,18 @@
     </row>
     <row r="38" spans="1:14" ht="37.799999999999997">
       <c r="A38" s="11"/>
-      <c r="B38" s="117"/>
+      <c r="B38" s="119"/>
       <c r="C38" s="51" t="str">
         <f>master!C28</f>
         <v>学ぶ範囲</v>
       </c>
-      <c r="D38" s="111" t="s">
-        <v>159</v>
-      </c>
-      <c r="E38" s="112"/>
-      <c r="F38" s="113"/>
+      <c r="D38" s="116" t="s">
+        <v>158</v>
+      </c>
+      <c r="E38" s="117"/>
+      <c r="F38" s="118"/>
       <c r="G38" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="49" t="s">
@@ -5170,7 +5176,7 @@
     </row>
     <row r="39" spans="1:14" ht="50.4">
       <c r="A39" s="11"/>
-      <c r="B39" s="117" t="str">
+      <c r="B39" s="119" t="str">
         <f>master!B29</f>
         <v>キャリア編</v>
       </c>
@@ -5178,13 +5184,13 @@
         <f>master!C29</f>
         <v>おまけ：新人の仕事はどうなるか？ これまで</v>
       </c>
-      <c r="D39" s="111" t="s">
-        <v>161</v>
-      </c>
-      <c r="E39" s="112"/>
-      <c r="F39" s="113"/>
+      <c r="D39" s="116" t="s">
+        <v>160</v>
+      </c>
+      <c r="E39" s="117"/>
+      <c r="F39" s="118"/>
       <c r="G39" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="49" t="s">
@@ -5194,7 +5200,7 @@
         <v>1.3888888888888889E-3</v>
       </c>
       <c r="K39" s="43" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
@@ -5202,18 +5208,18 @@
     </row>
     <row r="40" spans="1:14" ht="63">
       <c r="A40" s="11"/>
-      <c r="B40" s="117"/>
+      <c r="B40" s="119"/>
       <c r="C40" s="51" t="str">
         <f>master!C30</f>
         <v>おまけ：生成AI before/after</v>
       </c>
-      <c r="D40" s="111" t="s">
-        <v>162</v>
-      </c>
-      <c r="E40" s="112"/>
-      <c r="F40" s="113"/>
+      <c r="D40" s="116" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40" s="117"/>
+      <c r="F40" s="118"/>
       <c r="G40" s="51" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="49" t="s">
@@ -5223,7 +5229,7 @@
         <v>1.3888888888888889E-3</v>
       </c>
       <c r="K40" s="43" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
@@ -5231,18 +5237,18 @@
     </row>
     <row r="41" spans="1:14" ht="50.4">
       <c r="A41" s="11"/>
-      <c r="B41" s="117"/>
+      <c r="B41" s="119"/>
       <c r="C41" s="51" t="str">
         <f>master!C31</f>
         <v>おまけ：新人の仕事はどうなるか？　これから</v>
       </c>
-      <c r="D41" s="111" t="s">
-        <v>160</v>
-      </c>
-      <c r="E41" s="112"/>
-      <c r="F41" s="113"/>
+      <c r="D41" s="116" t="s">
+        <v>159</v>
+      </c>
+      <c r="E41" s="117"/>
+      <c r="F41" s="118"/>
       <c r="G41" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="49" t="s">
@@ -5252,7 +5258,7 @@
         <v>1.3888888888888889E-3</v>
       </c>
       <c r="K41" s="43" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
@@ -5260,18 +5266,18 @@
     </row>
     <row r="42" spans="1:14" ht="100.8">
       <c r="A42" s="11"/>
-      <c r="B42" s="117"/>
+      <c r="B42" s="119"/>
       <c r="C42" s="51" t="str">
         <f>master!C32</f>
         <v>代表的な若手の仕事</v>
       </c>
-      <c r="D42" s="111" t="s">
-        <v>198</v>
-      </c>
-      <c r="E42" s="112"/>
-      <c r="F42" s="113"/>
+      <c r="D42" s="116" t="s">
+        <v>196</v>
+      </c>
+      <c r="E42" s="117"/>
+      <c r="F42" s="118"/>
       <c r="G42" s="51" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="49" t="s">
@@ -5281,7 +5287,7 @@
         <v>2.0833333333333333E-3</v>
       </c>
       <c r="K42" s="43" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
@@ -5289,18 +5295,18 @@
     </row>
     <row r="43" spans="1:14" ht="88.2">
       <c r="A43" s="11"/>
-      <c r="B43" s="117"/>
+      <c r="B43" s="119"/>
       <c r="C43" s="51" t="str">
         <f>master!C33</f>
         <v>そもそも</v>
       </c>
-      <c r="D43" s="111" t="s">
-        <v>199</v>
-      </c>
-      <c r="E43" s="112"/>
-      <c r="F43" s="113"/>
+      <c r="D43" s="116" t="s">
+        <v>197</v>
+      </c>
+      <c r="E43" s="117"/>
+      <c r="F43" s="118"/>
       <c r="G43" s="51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H43" s="12"/>
       <c r="I43" s="49" t="s">
@@ -5310,7 +5316,7 @@
         <v>6.9444444444444447E-4</v>
       </c>
       <c r="K43" s="43" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
@@ -5318,18 +5324,18 @@
     </row>
     <row r="44" spans="1:14" ht="37.799999999999997">
       <c r="A44" s="11"/>
-      <c r="B44" s="117"/>
+      <c r="B44" s="119"/>
       <c r="C44" s="51" t="str">
         <f>master!C34</f>
         <v>2040年の就業構造推計（改定版）の概要</v>
       </c>
-      <c r="D44" s="111" t="s">
-        <v>163</v>
-      </c>
-      <c r="E44" s="112"/>
-      <c r="F44" s="113"/>
+      <c r="D44" s="116" t="s">
+        <v>162</v>
+      </c>
+      <c r="E44" s="117"/>
+      <c r="F44" s="118"/>
       <c r="G44" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="49" t="s">
@@ -5339,7 +5345,7 @@
         <v>2.0833333333333333E-3</v>
       </c>
       <c r="K44" s="43" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
@@ -5347,18 +5353,18 @@
     </row>
     <row r="45" spans="1:14" ht="50.4">
       <c r="A45" s="11"/>
-      <c r="B45" s="117"/>
+      <c r="B45" s="119"/>
       <c r="C45" s="51" t="str">
         <f>master!C35</f>
         <v>全国版就業構造推計（改定版）・職業間ミスマッチ</v>
       </c>
-      <c r="D45" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="E45" s="112"/>
-      <c r="F45" s="113"/>
+      <c r="D45" s="116" t="s">
+        <v>163</v>
+      </c>
+      <c r="E45" s="117"/>
+      <c r="F45" s="118"/>
       <c r="G45" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H45" s="12"/>
       <c r="I45" s="49" t="s">
@@ -5368,7 +5374,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="K45" s="43" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
@@ -5376,18 +5382,18 @@
     </row>
     <row r="46" spans="1:14" ht="50.4">
       <c r="A46" s="11"/>
-      <c r="B46" s="117"/>
+      <c r="B46" s="119"/>
       <c r="C46" s="51" t="str">
         <f>master!C36</f>
         <v>（参考）将来の産業構造は・・・</v>
       </c>
-      <c r="D46" s="111" t="s">
-        <v>165</v>
-      </c>
-      <c r="E46" s="112"/>
-      <c r="F46" s="113"/>
+      <c r="D46" s="116" t="s">
+        <v>164</v>
+      </c>
+      <c r="E46" s="117"/>
+      <c r="F46" s="118"/>
       <c r="G46" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H46" s="12"/>
       <c r="I46" s="49" t="s">
@@ -5397,7 +5403,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="K46" s="43" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
@@ -5405,18 +5411,18 @@
     </row>
     <row r="47" spans="1:14" ht="63">
       <c r="A47" s="11"/>
-      <c r="B47" s="117"/>
+      <c r="B47" s="119"/>
       <c r="C47" s="51" t="str">
         <f>master!C37</f>
         <v>ヒント１：生成ＡＩと原理原則</v>
       </c>
-      <c r="D47" s="111" t="s">
-        <v>139</v>
-      </c>
-      <c r="E47" s="112"/>
-      <c r="F47" s="113"/>
+      <c r="D47" s="116" t="s">
+        <v>138</v>
+      </c>
+      <c r="E47" s="117"/>
+      <c r="F47" s="118"/>
       <c r="G47" s="51" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H47" s="12"/>
       <c r="I47" s="49" t="s">
@@ -5432,18 +5438,18 @@
     </row>
     <row r="48" spans="1:14" ht="50.4">
       <c r="A48" s="11"/>
-      <c r="B48" s="117"/>
+      <c r="B48" s="119"/>
       <c r="C48" s="51" t="str">
         <f>master!C38</f>
         <v>ヒント2：プロンプトによる生成AIの挙動の違い</v>
       </c>
-      <c r="D48" s="111" t="s">
-        <v>191</v>
-      </c>
-      <c r="E48" s="112"/>
-      <c r="F48" s="113"/>
+      <c r="D48" s="116" t="s">
+        <v>189</v>
+      </c>
+      <c r="E48" s="117"/>
+      <c r="F48" s="118"/>
       <c r="G48" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H48" s="12"/>
       <c r="I48" s="49" t="s">
@@ -5459,18 +5465,18 @@
     </row>
     <row r="49" spans="1:14" ht="189">
       <c r="A49" s="11"/>
-      <c r="B49" s="117"/>
+      <c r="B49" s="119"/>
       <c r="C49" s="51" t="str">
         <f>master!C39</f>
         <v>ヒント３：それでも生成AIを積極的に使うしかない</v>
       </c>
-      <c r="D49" s="111" t="s">
-        <v>192</v>
-      </c>
-      <c r="E49" s="112"/>
-      <c r="F49" s="113"/>
+      <c r="D49" s="116" t="s">
+        <v>190</v>
+      </c>
+      <c r="E49" s="117"/>
+      <c r="F49" s="118"/>
       <c r="G49" s="51" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H49" s="12"/>
       <c r="I49" s="49" t="s">
@@ -5486,20 +5492,20 @@
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="11"/>
-      <c r="B50" s="117"/>
+      <c r="B50" s="119"/>
       <c r="C50" s="51" t="str">
         <f>master!C40</f>
         <v>1. 研修概要</v>
       </c>
-      <c r="D50" s="111"/>
-      <c r="E50" s="112"/>
-      <c r="F50" s="113"/>
+      <c r="D50" s="116"/>
+      <c r="E50" s="117"/>
+      <c r="F50" s="118"/>
       <c r="G50" s="51" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H50" s="12"/>
       <c r="I50" s="49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J50" s="47">
         <v>0</v>
@@ -5511,16 +5517,16 @@
     </row>
     <row r="51" spans="1:14" ht="15" customHeight="1">
       <c r="A51" s="11"/>
-      <c r="B51" s="117"/>
+      <c r="B51" s="119"/>
       <c r="C51" s="51" t="str">
         <f>master!C41</f>
         <v>デジタルブートキャンプの目的</v>
       </c>
-      <c r="D51" s="111"/>
-      <c r="E51" s="112"/>
-      <c r="F51" s="113"/>
+      <c r="D51" s="116"/>
+      <c r="E51" s="117"/>
+      <c r="F51" s="118"/>
       <c r="G51" s="51" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H51" s="12"/>
       <c r="I51" s="49" t="s">
@@ -5536,18 +5542,18 @@
     </row>
     <row r="52" spans="1:14" ht="50.4">
       <c r="A52" s="11"/>
-      <c r="B52" s="117"/>
+      <c r="B52" s="119"/>
       <c r="C52" s="51" t="str">
         <f>master!C42</f>
         <v>まとめ</v>
       </c>
-      <c r="D52" s="111" t="s">
-        <v>166</v>
-      </c>
-      <c r="E52" s="112"/>
-      <c r="F52" s="113"/>
+      <c r="D52" s="116" t="s">
+        <v>165</v>
+      </c>
+      <c r="E52" s="117"/>
+      <c r="F52" s="118"/>
       <c r="G52" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H52" s="12"/>
       <c r="I52" s="49" t="s">
@@ -5563,7 +5569,7 @@
     </row>
     <row r="53" spans="1:14" ht="25.2">
       <c r="A53" s="11"/>
-      <c r="B53" s="117" t="str">
+      <c r="B53" s="119" t="str">
         <f>master!B43</f>
         <v>NTTデータの強み編</v>
       </c>
@@ -5571,13 +5577,13 @@
         <f>master!C43</f>
         <v>2025年の変動</v>
       </c>
-      <c r="D53" s="111" t="s">
-        <v>142</v>
-      </c>
-      <c r="E53" s="112"/>
-      <c r="F53" s="113"/>
+      <c r="D53" s="116" t="s">
+        <v>141</v>
+      </c>
+      <c r="E53" s="117"/>
+      <c r="F53" s="118"/>
       <c r="G53" s="51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H53" s="12"/>
       <c r="I53" s="49" t="s">
@@ -5593,18 +5599,18 @@
     </row>
     <row r="54" spans="1:14" ht="50.4">
       <c r="A54" s="11"/>
-      <c r="B54" s="117"/>
+      <c r="B54" s="119"/>
       <c r="C54" s="51" t="str">
         <f>master!C44</f>
         <v>2025年の変動　AIエージェントの台頭</v>
       </c>
-      <c r="D54" s="111" t="s">
-        <v>172</v>
-      </c>
-      <c r="E54" s="112"/>
-      <c r="F54" s="113"/>
+      <c r="D54" s="116" t="s">
+        <v>171</v>
+      </c>
+      <c r="E54" s="117"/>
+      <c r="F54" s="118"/>
       <c r="G54" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H54" s="12"/>
       <c r="I54" s="49" t="s">
@@ -5620,18 +5626,18 @@
     </row>
     <row r="55" spans="1:14" ht="50.4">
       <c r="A55" s="11"/>
-      <c r="B55" s="117"/>
+      <c r="B55" s="119"/>
       <c r="C55" s="51" t="str">
         <f>master!C45</f>
         <v>2025年の変動　Vibe Coding</v>
       </c>
-      <c r="D55" s="111" t="s">
-        <v>171</v>
-      </c>
-      <c r="E55" s="112"/>
-      <c r="F55" s="113"/>
+      <c r="D55" s="116" t="s">
+        <v>170</v>
+      </c>
+      <c r="E55" s="117"/>
+      <c r="F55" s="118"/>
       <c r="G55" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H55" s="12"/>
       <c r="I55" s="49" t="s">
@@ -5647,18 +5653,18 @@
     </row>
     <row r="56" spans="1:14" ht="88.2">
       <c r="A56" s="11"/>
-      <c r="B56" s="117"/>
+      <c r="B56" s="119"/>
       <c r="C56" s="51" t="str">
         <f>master!C46</f>
         <v>2025年の変動　Spec Driven Development</v>
       </c>
-      <c r="D56" s="111" t="s">
-        <v>200</v>
-      </c>
-      <c r="E56" s="112"/>
-      <c r="F56" s="113"/>
+      <c r="D56" s="116" t="s">
+        <v>198</v>
+      </c>
+      <c r="E56" s="117"/>
+      <c r="F56" s="118"/>
       <c r="G56" s="51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H56" s="12"/>
       <c r="I56" s="49" t="s">
@@ -5674,18 +5680,18 @@
     </row>
     <row r="57" spans="1:14" ht="50.4">
       <c r="A57" s="11"/>
-      <c r="B57" s="117"/>
+      <c r="B57" s="119"/>
       <c r="C57" s="51" t="str">
         <f>master!C47</f>
         <v>2025年の変動　ハーネスエンジニアリング</v>
       </c>
-      <c r="D57" s="111" t="s">
-        <v>201</v>
-      </c>
-      <c r="E57" s="112"/>
-      <c r="F57" s="113"/>
+      <c r="D57" s="116" t="s">
+        <v>199</v>
+      </c>
+      <c r="E57" s="117"/>
+      <c r="F57" s="118"/>
       <c r="G57" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H57" s="12"/>
       <c r="I57" s="49" t="s">
@@ -5701,18 +5707,18 @@
     </row>
     <row r="58" spans="1:14" ht="75.599999999999994">
       <c r="A58" s="11"/>
-      <c r="B58" s="117"/>
+      <c r="B58" s="119"/>
       <c r="C58" s="51" t="str">
         <f>master!C48</f>
         <v>2025年の変動　動向まとめ</v>
       </c>
-      <c r="D58" s="111" t="s">
-        <v>173</v>
-      </c>
-      <c r="E58" s="112"/>
-      <c r="F58" s="113"/>
+      <c r="D58" s="116" t="s">
+        <v>172</v>
+      </c>
+      <c r="E58" s="117"/>
+      <c r="F58" s="118"/>
       <c r="G58" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H58" s="12"/>
       <c r="I58" s="49" t="s">
@@ -5728,18 +5734,18 @@
     </row>
     <row r="59" spans="1:14" ht="113.4">
       <c r="A59" s="11"/>
-      <c r="B59" s="117"/>
+      <c r="B59" s="119"/>
       <c r="C59" s="51" t="str">
         <f>master!C49</f>
         <v>2026年 ソフトウェア開発における課題とNTTDグループの強み</v>
       </c>
-      <c r="D59" s="111" t="s">
-        <v>175</v>
-      </c>
-      <c r="E59" s="112"/>
-      <c r="F59" s="113"/>
+      <c r="D59" s="116" t="s">
+        <v>174</v>
+      </c>
+      <c r="E59" s="117"/>
+      <c r="F59" s="118"/>
       <c r="G59" s="51" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H59" s="12"/>
       <c r="I59" s="49" t="s">
@@ -5755,18 +5761,18 @@
     </row>
     <row r="60" spans="1:14" ht="37.799999999999997">
       <c r="A60" s="11"/>
-      <c r="B60" s="117"/>
+      <c r="B60" s="119"/>
       <c r="C60" s="51" t="str">
         <f>master!C50</f>
         <v>2025年の変動</v>
       </c>
-      <c r="D60" s="111" t="s">
-        <v>176</v>
-      </c>
-      <c r="E60" s="112"/>
-      <c r="F60" s="113"/>
+      <c r="D60" s="116" t="s">
+        <v>175</v>
+      </c>
+      <c r="E60" s="117"/>
+      <c r="F60" s="118"/>
       <c r="G60" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H60" s="12"/>
       <c r="I60" s="49" t="s">
@@ -5790,15 +5796,15 @@
         <f>master!C51</f>
         <v>ー</v>
       </c>
-      <c r="D61" s="111"/>
-      <c r="E61" s="112"/>
-      <c r="F61" s="113"/>
+      <c r="D61" s="116"/>
+      <c r="E61" s="117"/>
+      <c r="F61" s="118"/>
       <c r="G61" s="51" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H61" s="12"/>
       <c r="I61" s="49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J61" s="47">
         <v>0</v>
@@ -5810,7 +5816,7 @@
     </row>
     <row r="62" spans="1:14" ht="50.4" customHeight="1">
       <c r="A62" s="11"/>
-      <c r="B62" s="120" t="str">
+      <c r="B62" s="110" t="str">
         <f>master!B52</f>
         <v>ハンズオン編:ChatGPT</v>
       </c>
@@ -5818,11 +5824,11 @@
         <f>master!C52</f>
         <v>生成ＡＩハンズオン</v>
       </c>
-      <c r="D62" s="114"/>
-      <c r="E62" s="115"/>
-      <c r="F62" s="116"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="114"/>
+      <c r="F62" s="115"/>
       <c r="G62" s="68" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H62" s="69"/>
       <c r="I62" s="70" t="s">
@@ -5838,16 +5844,16 @@
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="11"/>
-      <c r="B63" s="121"/>
+      <c r="B63" s="111"/>
       <c r="C63" s="68" t="str">
         <f>master!C53</f>
         <v>ChatGPTの使い方（一般チャット）</v>
       </c>
-      <c r="D63" s="114"/>
-      <c r="E63" s="115"/>
-      <c r="F63" s="116"/>
+      <c r="D63" s="113"/>
+      <c r="E63" s="114"/>
+      <c r="F63" s="115"/>
       <c r="G63" s="68" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H63" s="69"/>
       <c r="I63" s="70" t="s">
@@ -5863,18 +5869,18 @@
     </row>
     <row r="64" spans="1:14" ht="50.4">
       <c r="A64" s="11"/>
-      <c r="B64" s="121"/>
+      <c r="B64" s="111"/>
       <c r="C64" s="68" t="str">
         <f>master!C54</f>
         <v>プロンプトを入れてみる</v>
       </c>
-      <c r="D64" s="114" t="s">
-        <v>170</v>
-      </c>
-      <c r="E64" s="115"/>
-      <c r="F64" s="116"/>
+      <c r="D64" s="113" t="s">
+        <v>169</v>
+      </c>
+      <c r="E64" s="114"/>
+      <c r="F64" s="115"/>
       <c r="G64" s="68" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H64" s="69"/>
       <c r="I64" s="70" t="s">
@@ -5890,18 +5896,18 @@
     </row>
     <row r="65" spans="1:14" ht="63">
       <c r="A65" s="11"/>
-      <c r="B65" s="121"/>
+      <c r="B65" s="111"/>
       <c r="C65" s="68" t="str">
         <f>master!C55</f>
         <v>ハンズオン例</v>
       </c>
-      <c r="D65" s="114" t="s">
-        <v>144</v>
-      </c>
-      <c r="E65" s="115"/>
-      <c r="F65" s="116"/>
+      <c r="D65" s="113" t="s">
+        <v>143</v>
+      </c>
+      <c r="E65" s="114"/>
+      <c r="F65" s="115"/>
       <c r="G65" s="68" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H65" s="69"/>
       <c r="I65" s="70" t="s">
@@ -5917,18 +5923,18 @@
     </row>
     <row r="66" spans="1:14" ht="126">
       <c r="A66" s="11"/>
-      <c r="B66" s="121"/>
+      <c r="B66" s="111"/>
       <c r="C66" s="68" t="str">
         <f>master!C56</f>
         <v>例１：【レポート作成】　佐々木社長の調査を行う</v>
       </c>
-      <c r="D66" s="114" t="s">
-        <v>167</v>
-      </c>
-      <c r="E66" s="115"/>
-      <c r="F66" s="116"/>
+      <c r="D66" s="113" t="s">
+        <v>166</v>
+      </c>
+      <c r="E66" s="114"/>
+      <c r="F66" s="115"/>
       <c r="G66" s="68" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H66" s="69"/>
       <c r="I66" s="70" t="s">
@@ -5944,18 +5950,18 @@
     </row>
     <row r="67" spans="1:14" ht="126" customHeight="1">
       <c r="A67" s="11"/>
-      <c r="B67" s="121"/>
+      <c r="B67" s="111"/>
       <c r="C67" s="68" t="str">
         <f>master!C57</f>
         <v>例２：顧客提案向けの企画書を作りたい</v>
       </c>
-      <c r="D67" s="114" t="s">
-        <v>167</v>
-      </c>
-      <c r="E67" s="115"/>
-      <c r="F67" s="116"/>
+      <c r="D67" s="113" t="s">
+        <v>166</v>
+      </c>
+      <c r="E67" s="114"/>
+      <c r="F67" s="115"/>
       <c r="G67" s="68" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H67" s="69"/>
       <c r="I67" s="70" t="s">
@@ -5971,18 +5977,18 @@
     </row>
     <row r="68" spans="1:14" ht="126" customHeight="1">
       <c r="A68" s="11"/>
-      <c r="B68" s="121"/>
+      <c r="B68" s="111"/>
       <c r="C68" s="68" t="str">
         <f>master!C58</f>
         <v>例３：１００本ノックを作ってみる</v>
       </c>
-      <c r="D68" s="114" t="s">
-        <v>167</v>
-      </c>
-      <c r="E68" s="115"/>
-      <c r="F68" s="116"/>
+      <c r="D68" s="113" t="s">
+        <v>166</v>
+      </c>
+      <c r="E68" s="114"/>
+      <c r="F68" s="115"/>
       <c r="G68" s="68" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H68" s="69"/>
       <c r="I68" s="70" t="s">
@@ -5998,16 +6004,16 @@
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="11"/>
-      <c r="B69" s="122"/>
+      <c r="B69" s="112"/>
       <c r="C69" s="68" t="str">
         <f>master!C59</f>
         <v>ChatGPT まとめ</v>
       </c>
-      <c r="D69" s="114"/>
-      <c r="E69" s="115"/>
-      <c r="F69" s="116"/>
+      <c r="D69" s="113"/>
+      <c r="E69" s="114"/>
+      <c r="F69" s="115"/>
       <c r="G69" s="68" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H69" s="69"/>
       <c r="I69" s="70" t="s">
@@ -6023,7 +6029,7 @@
     </row>
     <row r="70" spans="1:14" ht="15" customHeight="1">
       <c r="A70" s="11"/>
-      <c r="B70" s="120" t="str">
+      <c r="B70" s="110" t="str">
         <f>master!B60</f>
         <v xml:space="preserve">ハンズオン編:GitHub Copilot </v>
       </c>
@@ -6031,11 +6037,11 @@
         <f>master!C60</f>
         <v>生成ＡＩハンズオン</v>
       </c>
-      <c r="D70" s="114"/>
-      <c r="E70" s="115"/>
-      <c r="F70" s="116"/>
+      <c r="D70" s="113"/>
+      <c r="E70" s="114"/>
+      <c r="F70" s="115"/>
       <c r="G70" s="68" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H70" s="69"/>
       <c r="I70" s="70" t="s">
@@ -6051,18 +6057,18 @@
     </row>
     <row r="71" spans="1:14" ht="25.2">
       <c r="A71" s="11"/>
-      <c r="B71" s="121"/>
+      <c r="B71" s="111"/>
       <c r="C71" s="68" t="str">
         <f>master!C61</f>
         <v>Visual Studio Code を開く</v>
       </c>
-      <c r="D71" s="114" t="s">
-        <v>168</v>
-      </c>
-      <c r="E71" s="115"/>
-      <c r="F71" s="116"/>
+      <c r="D71" s="113" t="s">
+        <v>167</v>
+      </c>
+      <c r="E71" s="114"/>
+      <c r="F71" s="115"/>
       <c r="G71" s="68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H71" s="69"/>
       <c r="I71" s="70" t="s">
@@ -6078,18 +6084,18 @@
     </row>
     <row r="72" spans="1:14" ht="37.799999999999997">
       <c r="A72" s="11"/>
-      <c r="B72" s="121"/>
+      <c r="B72" s="111"/>
       <c r="C72" s="68" t="str">
         <f>master!C62</f>
         <v>コード補完機能</v>
       </c>
-      <c r="D72" s="114" t="s">
-        <v>169</v>
-      </c>
-      <c r="E72" s="115"/>
-      <c r="F72" s="116"/>
+      <c r="D72" s="113" t="s">
+        <v>168</v>
+      </c>
+      <c r="E72" s="114"/>
+      <c r="F72" s="115"/>
       <c r="G72" s="68" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H72" s="69"/>
       <c r="I72" s="70" t="s">
@@ -6105,18 +6111,18 @@
     </row>
     <row r="73" spans="1:14" ht="100.8">
       <c r="A73" s="11"/>
-      <c r="B73" s="121"/>
+      <c r="B73" s="111"/>
       <c r="C73" s="68" t="str">
         <f>master!C63</f>
         <v>チャット機能</v>
       </c>
-      <c r="D73" s="114" t="s">
-        <v>202</v>
-      </c>
-      <c r="E73" s="115"/>
-      <c r="F73" s="116"/>
+      <c r="D73" s="113" t="s">
+        <v>200</v>
+      </c>
+      <c r="E73" s="114"/>
+      <c r="F73" s="115"/>
       <c r="G73" s="68" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H73" s="69"/>
       <c r="I73" s="70" t="s">
@@ -6132,16 +6138,16 @@
     </row>
     <row r="74" spans="1:14" ht="15" customHeight="1">
       <c r="A74" s="11"/>
-      <c r="B74" s="121"/>
+      <c r="B74" s="111"/>
       <c r="C74" s="68" t="str">
         <f>master!C64</f>
         <v>ChatGPT で 簡単なアプリやゲームを作ってみましょう</v>
       </c>
-      <c r="D74" s="114"/>
-      <c r="E74" s="115"/>
-      <c r="F74" s="116"/>
+      <c r="D74" s="113"/>
+      <c r="E74" s="114"/>
+      <c r="F74" s="115"/>
       <c r="G74" s="68" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H74" s="69"/>
       <c r="I74" s="70" t="s">
@@ -6157,18 +6163,18 @@
     </row>
     <row r="75" spans="1:14" ht="25.2">
       <c r="A75" s="11"/>
-      <c r="B75" s="121"/>
+      <c r="B75" s="111"/>
       <c r="C75" s="68" t="str">
         <f>master!C65</f>
         <v>例１　高級志向テトリス</v>
       </c>
-      <c r="D75" s="114" t="s">
-        <v>141</v>
-      </c>
-      <c r="E75" s="115"/>
-      <c r="F75" s="116"/>
+      <c r="D75" s="113" t="s">
+        <v>140</v>
+      </c>
+      <c r="E75" s="114"/>
+      <c r="F75" s="115"/>
       <c r="G75" s="68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H75" s="69"/>
       <c r="I75" s="70" t="s">
@@ -6184,18 +6190,18 @@
     </row>
     <row r="76" spans="1:14" ht="25.2">
       <c r="A76" s="11"/>
-      <c r="B76" s="121"/>
+      <c r="B76" s="111"/>
       <c r="C76" s="68" t="str">
         <f>master!C66</f>
         <v>例）わくわく！にっぽんダーツの旅</v>
       </c>
-      <c r="D76" s="114" t="s">
-        <v>141</v>
-      </c>
-      <c r="E76" s="115"/>
-      <c r="F76" s="116"/>
+      <c r="D76" s="113" t="s">
+        <v>140</v>
+      </c>
+      <c r="E76" s="114"/>
+      <c r="F76" s="115"/>
       <c r="G76" s="68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H76" s="69"/>
       <c r="I76" s="70" t="s">
@@ -6211,18 +6217,18 @@
     </row>
     <row r="77" spans="1:14" ht="25.2">
       <c r="A77" s="11"/>
-      <c r="B77" s="121"/>
+      <c r="B77" s="111"/>
       <c r="C77" s="68" t="str">
         <f>master!C67</f>
         <v>例）タスク管理ツール</v>
       </c>
-      <c r="D77" s="114" t="s">
-        <v>141</v>
-      </c>
-      <c r="E77" s="115"/>
-      <c r="F77" s="116"/>
+      <c r="D77" s="113" t="s">
+        <v>140</v>
+      </c>
+      <c r="E77" s="114"/>
+      <c r="F77" s="115"/>
       <c r="G77" s="68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H77" s="69"/>
       <c r="I77" s="70" t="s">
@@ -6238,15 +6244,15 @@
     </row>
     <row r="78" spans="1:14" ht="126">
       <c r="A78" s="11"/>
-      <c r="B78" s="121"/>
+      <c r="B78" s="111"/>
       <c r="C78" s="68"/>
-      <c r="D78" s="114" t="s">
-        <v>146</v>
-      </c>
-      <c r="E78" s="115"/>
-      <c r="F78" s="116"/>
+      <c r="D78" s="113" t="s">
+        <v>145</v>
+      </c>
+      <c r="E78" s="114"/>
+      <c r="F78" s="115"/>
       <c r="G78" s="68" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H78" s="69"/>
       <c r="I78" s="70" t="s">
@@ -6262,18 +6268,18 @@
     </row>
     <row r="79" spans="1:14" ht="63">
       <c r="A79" s="11"/>
-      <c r="B79" s="121"/>
+      <c r="B79" s="111"/>
       <c r="C79" s="68" t="str">
         <f>master!C68</f>
         <v>ディレクトリ作成とファイル配置</v>
       </c>
-      <c r="D79" s="114" t="s">
-        <v>147</v>
-      </c>
-      <c r="E79" s="115"/>
-      <c r="F79" s="116"/>
+      <c r="D79" s="113" t="s">
+        <v>146</v>
+      </c>
+      <c r="E79" s="114"/>
+      <c r="F79" s="115"/>
       <c r="G79" s="68" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H79" s="69"/>
       <c r="I79" s="70" t="s">
@@ -6289,18 +6295,18 @@
     </row>
     <row r="80" spans="1:14" ht="25.2">
       <c r="A80" s="11"/>
-      <c r="B80" s="121"/>
+      <c r="B80" s="111"/>
       <c r="C80" s="68" t="str">
         <f>master!C69</f>
         <v>チャット機能：Aｓｋ</v>
       </c>
-      <c r="D80" s="114" t="s">
-        <v>141</v>
-      </c>
-      <c r="E80" s="115"/>
-      <c r="F80" s="116"/>
+      <c r="D80" s="113" t="s">
+        <v>140</v>
+      </c>
+      <c r="E80" s="114"/>
+      <c r="F80" s="115"/>
       <c r="G80" s="68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H80" s="69"/>
       <c r="I80" s="70" t="s">
@@ -6316,18 +6322,18 @@
     </row>
     <row r="81" spans="1:14" ht="50.4">
       <c r="A81" s="11"/>
-      <c r="B81" s="121"/>
+      <c r="B81" s="111"/>
       <c r="C81" s="68" t="str">
         <f>master!C70</f>
         <v>Askモードについて</v>
       </c>
-      <c r="D81" s="114" t="s">
-        <v>174</v>
-      </c>
-      <c r="E81" s="115"/>
-      <c r="F81" s="116"/>
+      <c r="D81" s="113" t="s">
+        <v>173</v>
+      </c>
+      <c r="E81" s="114"/>
+      <c r="F81" s="115"/>
       <c r="G81" s="68" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H81" s="69"/>
       <c r="I81" s="70" t="s">
@@ -6343,18 +6349,18 @@
     </row>
     <row r="82" spans="1:14" ht="25.2">
       <c r="A82" s="11"/>
-      <c r="B82" s="121"/>
+      <c r="B82" s="111"/>
       <c r="C82" s="87" t="str">
         <f>master!C71</f>
         <v>実行例</v>
       </c>
-      <c r="D82" s="114" t="s">
-        <v>141</v>
-      </c>
-      <c r="E82" s="115"/>
-      <c r="F82" s="116"/>
+      <c r="D82" s="113" t="s">
+        <v>140</v>
+      </c>
+      <c r="E82" s="114"/>
+      <c r="F82" s="115"/>
       <c r="G82" s="68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H82" s="69"/>
       <c r="I82" s="70" t="s">
@@ -6370,15 +6376,15 @@
     </row>
     <row r="83" spans="1:14" ht="37.799999999999997">
       <c r="A83" s="11"/>
-      <c r="B83" s="121"/>
+      <c r="B83" s="111"/>
       <c r="C83" s="88"/>
-      <c r="D83" s="114" t="s">
-        <v>193</v>
-      </c>
-      <c r="E83" s="115"/>
-      <c r="F83" s="116"/>
+      <c r="D83" s="113" t="s">
+        <v>191</v>
+      </c>
+      <c r="E83" s="114"/>
+      <c r="F83" s="115"/>
       <c r="G83" s="68" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H83" s="69"/>
       <c r="I83" s="70" t="s">
@@ -6394,18 +6400,18 @@
     </row>
     <row r="84" spans="1:14" ht="25.2">
       <c r="A84" s="11"/>
-      <c r="B84" s="121"/>
+      <c r="B84" s="111"/>
       <c r="C84" s="68" t="str">
         <f>master!C72</f>
         <v>Askモードまとめ</v>
       </c>
-      <c r="D84" s="114" t="s">
-        <v>141</v>
-      </c>
-      <c r="E84" s="115"/>
-      <c r="F84" s="116"/>
+      <c r="D84" s="113" t="s">
+        <v>140</v>
+      </c>
+      <c r="E84" s="114"/>
+      <c r="F84" s="115"/>
       <c r="G84" s="68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H84" s="69"/>
       <c r="I84" s="70" t="s">
@@ -6421,18 +6427,18 @@
     </row>
     <row r="85" spans="1:14" ht="25.2">
       <c r="A85" s="11"/>
-      <c r="B85" s="121"/>
+      <c r="B85" s="111"/>
       <c r="C85" s="68" t="str">
         <f>master!C73</f>
         <v>チャット機能：Agent</v>
       </c>
-      <c r="D85" s="114" t="s">
-        <v>141</v>
-      </c>
-      <c r="E85" s="115"/>
-      <c r="F85" s="116"/>
+      <c r="D85" s="113" t="s">
+        <v>140</v>
+      </c>
+      <c r="E85" s="114"/>
+      <c r="F85" s="115"/>
       <c r="G85" s="68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H85" s="69"/>
       <c r="I85" s="70" t="s">
@@ -6448,18 +6454,18 @@
     </row>
     <row r="86" spans="1:14" ht="25.2">
       <c r="A86" s="11"/>
-      <c r="B86" s="121"/>
+      <c r="B86" s="111"/>
       <c r="C86" s="68" t="str">
         <f>master!C74</f>
         <v>Agentモード</v>
       </c>
-      <c r="D86" s="114" t="s">
-        <v>141</v>
-      </c>
-      <c r="E86" s="115"/>
-      <c r="F86" s="116"/>
+      <c r="D86" s="113" t="s">
+        <v>140</v>
+      </c>
+      <c r="E86" s="114"/>
+      <c r="F86" s="115"/>
       <c r="G86" s="68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H86" s="69"/>
       <c r="I86" s="70" t="s">
@@ -6475,18 +6481,18 @@
     </row>
     <row r="87" spans="1:14" ht="37.799999999999997">
       <c r="A87" s="11"/>
-      <c r="B87" s="121"/>
+      <c r="B87" s="111"/>
       <c r="C87" s="68" t="str">
         <f>master!C75</f>
         <v>実行例</v>
       </c>
-      <c r="D87" s="114" t="s">
-        <v>174</v>
-      </c>
-      <c r="E87" s="115"/>
-      <c r="F87" s="116"/>
+      <c r="D87" s="113" t="s">
+        <v>173</v>
+      </c>
+      <c r="E87" s="114"/>
+      <c r="F87" s="115"/>
       <c r="G87" s="68" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H87" s="69"/>
       <c r="I87" s="70" t="s">
@@ -6502,18 +6508,18 @@
     </row>
     <row r="88" spans="1:14" ht="37.799999999999997">
       <c r="A88" s="11"/>
-      <c r="B88" s="121"/>
+      <c r="B88" s="111"/>
       <c r="C88" s="68" t="str">
         <f>master!C76</f>
         <v>READMEの内容を確認しましょう</v>
       </c>
-      <c r="D88" s="114" t="s">
-        <v>174</v>
-      </c>
-      <c r="E88" s="115"/>
-      <c r="F88" s="116"/>
+      <c r="D88" s="113" t="s">
+        <v>173</v>
+      </c>
+      <c r="E88" s="114"/>
+      <c r="F88" s="115"/>
       <c r="G88" s="68" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H88" s="69"/>
       <c r="I88" s="70" t="s">
@@ -6529,18 +6535,18 @@
     </row>
     <row r="89" spans="1:14" ht="37.799999999999997">
       <c r="A89" s="11"/>
-      <c r="B89" s="121"/>
+      <c r="B89" s="111"/>
       <c r="C89" s="87" t="str">
         <f>master!C77</f>
         <v>Changeログを作ってみましょう</v>
       </c>
-      <c r="D89" s="114" t="s">
-        <v>174</v>
-      </c>
-      <c r="E89" s="115"/>
-      <c r="F89" s="116"/>
+      <c r="D89" s="113" t="s">
+        <v>173</v>
+      </c>
+      <c r="E89" s="114"/>
+      <c r="F89" s="115"/>
       <c r="G89" s="68" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H89" s="69"/>
       <c r="I89" s="70" t="s">
@@ -6556,15 +6562,15 @@
     </row>
     <row r="90" spans="1:14" ht="37.799999999999997">
       <c r="A90" s="11"/>
-      <c r="B90" s="121"/>
+      <c r="B90" s="111"/>
       <c r="C90" s="88"/>
-      <c r="D90" s="114" t="s">
-        <v>189</v>
-      </c>
-      <c r="E90" s="115"/>
-      <c r="F90" s="116"/>
+      <c r="D90" s="113" t="s">
+        <v>187</v>
+      </c>
+      <c r="E90" s="114"/>
+      <c r="F90" s="115"/>
       <c r="G90" s="68" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H90" s="69"/>
       <c r="I90" s="70" t="s">
@@ -6580,18 +6586,18 @@
     </row>
     <row r="91" spans="1:14" ht="25.2">
       <c r="A91" s="11"/>
-      <c r="B91" s="121"/>
+      <c r="B91" s="111"/>
       <c r="C91" s="68" t="str">
         <f>master!C78</f>
         <v>チャット機能：Plan</v>
       </c>
-      <c r="D91" s="114" t="s">
-        <v>141</v>
-      </c>
-      <c r="E91" s="115"/>
-      <c r="F91" s="116"/>
+      <c r="D91" s="113" t="s">
+        <v>140</v>
+      </c>
+      <c r="E91" s="114"/>
+      <c r="F91" s="115"/>
       <c r="G91" s="68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H91" s="69"/>
       <c r="I91" s="70" t="s">
@@ -6607,18 +6613,18 @@
     </row>
     <row r="92" spans="1:14" ht="37.799999999999997">
       <c r="A92" s="11"/>
-      <c r="B92" s="121"/>
+      <c r="B92" s="111"/>
       <c r="C92" s="68" t="str">
         <f>master!C79</f>
         <v>Planモードで機能追加してみましょう</v>
       </c>
-      <c r="D92" s="114" t="s">
-        <v>174</v>
-      </c>
-      <c r="E92" s="115"/>
-      <c r="F92" s="116"/>
+      <c r="D92" s="113" t="s">
+        <v>173</v>
+      </c>
+      <c r="E92" s="114"/>
+      <c r="F92" s="115"/>
       <c r="G92" s="68" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H92" s="69"/>
       <c r="I92" s="70" t="s">
@@ -6634,18 +6640,18 @@
     </row>
     <row r="93" spans="1:14" ht="25.2">
       <c r="A93" s="11"/>
-      <c r="B93" s="121"/>
+      <c r="B93" s="111"/>
       <c r="C93" s="68" t="str">
         <f>master!C80</f>
         <v>実行例</v>
       </c>
-      <c r="D93" s="114" t="s">
-        <v>141</v>
-      </c>
-      <c r="E93" s="115"/>
-      <c r="F93" s="116"/>
+      <c r="D93" s="113" t="s">
+        <v>140</v>
+      </c>
+      <c r="E93" s="114"/>
+      <c r="F93" s="115"/>
       <c r="G93" s="68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H93" s="69"/>
       <c r="I93" s="70" t="s">
@@ -6661,18 +6667,18 @@
     </row>
     <row r="94" spans="1:14" ht="25.2">
       <c r="A94" s="11"/>
-      <c r="B94" s="121"/>
+      <c r="B94" s="111"/>
       <c r="C94" s="87" t="str">
         <f>master!C81</f>
         <v>実行結果</v>
       </c>
-      <c r="D94" s="114" t="s">
-        <v>141</v>
-      </c>
-      <c r="E94" s="115"/>
-      <c r="F94" s="116"/>
+      <c r="D94" s="113" t="s">
+        <v>140</v>
+      </c>
+      <c r="E94" s="114"/>
+      <c r="F94" s="115"/>
       <c r="G94" s="68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H94" s="69"/>
       <c r="I94" s="70" t="s">
@@ -6688,15 +6694,15 @@
     </row>
     <row r="95" spans="1:14" ht="37.799999999999997">
       <c r="A95" s="11"/>
-      <c r="B95" s="121"/>
+      <c r="B95" s="111"/>
       <c r="C95" s="88"/>
-      <c r="D95" s="114" t="s">
-        <v>189</v>
-      </c>
-      <c r="E95" s="115"/>
-      <c r="F95" s="116"/>
+      <c r="D95" s="113" t="s">
+        <v>187</v>
+      </c>
+      <c r="E95" s="114"/>
+      <c r="F95" s="115"/>
       <c r="G95" s="68" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H95" s="69"/>
       <c r="I95" s="70" t="s">
@@ -6712,18 +6718,18 @@
     </row>
     <row r="96" spans="1:14" ht="25.2">
       <c r="A96" s="11"/>
-      <c r="B96" s="121"/>
+      <c r="B96" s="111"/>
       <c r="C96" s="68" t="str">
         <f>master!C82</f>
         <v>Planモード＆Agentモードまとめ</v>
       </c>
-      <c r="D96" s="114" t="s">
-        <v>141</v>
-      </c>
-      <c r="E96" s="115"/>
-      <c r="F96" s="116"/>
+      <c r="D96" s="113" t="s">
+        <v>140</v>
+      </c>
+      <c r="E96" s="114"/>
+      <c r="F96" s="115"/>
       <c r="G96" s="68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H96" s="69"/>
       <c r="I96" s="70" t="s">
@@ -6747,13 +6753,13 @@
         <f>master!C83</f>
         <v>開発したゲームやアプリをプレゼン</v>
       </c>
-      <c r="D97" s="114" t="s">
-        <v>188</v>
-      </c>
-      <c r="E97" s="115"/>
-      <c r="F97" s="116"/>
+      <c r="D97" s="113" t="s">
+        <v>186</v>
+      </c>
+      <c r="E97" s="114"/>
+      <c r="F97" s="115"/>
       <c r="G97" s="68" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H97" s="69"/>
       <c r="I97" s="70" t="s">
@@ -6763,7 +6769,7 @@
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="K97" s="72" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
@@ -6775,6 +6781,86 @@
     <row r="99" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="B14:B24"/>
+    <mergeCell ref="B25:B33"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="B39:B52"/>
+    <mergeCell ref="B53:B60"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="B62:B69"/>
     <mergeCell ref="B70:B96"/>
@@ -6799,86 +6885,6 @@
     <mergeCell ref="D80:F80"/>
     <mergeCell ref="D81:F81"/>
     <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="B39:B52"/>
-    <mergeCell ref="B53:B60"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="B14:B24"/>
-    <mergeCell ref="B25:B33"/>
-    <mergeCell ref="B34:B38"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="D7:E7"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6911,7 +6917,7 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="2:3">
@@ -6924,437 +6930,437 @@
     </row>
     <row r="3" spans="2:3">
       <c r="B3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="C5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="C6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="C8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="C9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="C10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="C13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="C14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="B15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="C16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="2:3">
       <c r="C17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="C18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="C19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="C20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="C21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="C22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="C23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="2:3">
       <c r="B24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="C25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="C26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="2:3">
       <c r="C27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="2:3">
       <c r="C28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="B29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="2:3">
       <c r="C30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="2:3">
       <c r="C31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="2:3">
       <c r="C32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="C33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="2:3">
       <c r="C34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="2:3">
       <c r="C35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="2:3">
       <c r="C36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="2:3">
       <c r="C37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="2:3">
       <c r="C38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="2:3">
       <c r="C39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="2:3">
       <c r="C40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="2:3">
       <c r="C41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="C42" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="2:3">
       <c r="B43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="2:3">
       <c r="C44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="2:3">
       <c r="C45" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="2:3">
       <c r="C46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="2:3">
       <c r="C47" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="2:3">
       <c r="C48" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="2:3">
       <c r="C49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="2:3">
       <c r="C50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" spans="2:3">
       <c r="B51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C51" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="2:3">
       <c r="B52" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C52" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="2:3">
       <c r="C53" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="2:3">
       <c r="C54" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="2:3">
       <c r="C55" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="56" spans="2:3">
       <c r="C56" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="2:3">
       <c r="C57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="2:3">
       <c r="C58" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="2:3">
       <c r="C59" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="60" spans="2:3">
       <c r="B60" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="2:3">
       <c r="C61" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62" spans="2:3">
       <c r="C62" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63" spans="2:3">
       <c r="C63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64" spans="2:3">
       <c r="C64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="3:3">
       <c r="C65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66" spans="3:3">
       <c r="C66" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="67" spans="3:3">
       <c r="C67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="3:3">
       <c r="C68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" spans="3:3">
       <c r="C69" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="70" spans="3:3">
       <c r="C70" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="71" spans="3:3">
       <c r="C71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="72" spans="3:3">
       <c r="C72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73" spans="3:3">
       <c r="C73" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="74" spans="3:3">
       <c r="C74" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="75" spans="3:3">
       <c r="C75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="76" spans="3:3">
       <c r="C76" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="77" spans="3:3">
       <c r="C77" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="78" spans="3:3">
       <c r="C78" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79" spans="3:3">
       <c r="C79" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="3:3">
       <c r="C80" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="81" spans="2:3">
       <c r="C81" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="82" spans="2:3">
       <c r="C82" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="83" spans="2:3">
       <c r="B83" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C83" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/IG/7日版/AI Native-生成AI_IG.xlsx
+++ b/IG/7日版/AI Native-生成AI_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5579D88C-28AE-406B-9ED6-921440EC8913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B871136D-AF45-44BC-BB83-4FA66C07F3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1302,34 +1302,6 @@
   </si>
   <si>
     <t>以下の内容を説明する。
-■実行結果の永続化や取り消し方法</t>
-    <rPh sb="13" eb="15">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ケッカ</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>エイゾクカ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>ケ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ホウホウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>以下の内容を説明する。
-■mdファイルのプレビュー方法</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>以下の内容を説明する。
 ■実行例の説明
 　②ディレクトリの詳細な説明</t>
     <rPh sb="17" eb="19">
@@ -2102,30 +2074,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>以下の内容を実施してもらう。
-■実施内容
-　1. ディレクトリを作成する
-　2. 成果物を配置する
-　3. Visual Studio Codeで成果物を参照する
-※一緒に実施する。</t>
-    <rPh sb="6" eb="8">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="41" eb="44">
-      <t>セイカブツ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="73" eb="76">
-      <t>セイカブツ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>以下の内容を説明する。
 ■実施概要
 　1. ディレクトリを作成する
@@ -2329,16 +2277,7 @@
 　・/tests：指定範囲のテストコードを提示する等
 　・/{プロンプトファイル名}：指定したプロンプトファイルの実行を行う</t>
     <rPh sb="18" eb="20">
-      <t>ガイヨウ</t>
-    </rPh>
-    <rPh sb="129" eb="131">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="132" eb="134">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="138" eb="140">
-      <t>フヨウ</t>
+      <t>ガイヨウショウサイセツメイフヨウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -2351,6 +2290,70 @@
     <rPh sb="17" eb="19">
       <t>ガイヨウ</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">以下の内容を実施してもらう。
+■実施内容
+　1. ディレクトリを作成する
+　2. 成果物を配置する
+　3. Visual Studio Codeで成果物を参照する
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※ハンズオンとして実施する。</t>
+    </r>
+    <rPh sb="6" eb="8">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="41" eb="44">
+      <t>セイカブツ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="73" eb="76">
+      <t>セイカブツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■実行結果の採用や取り消しの方法</t>
+    <rPh sb="13" eb="15">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サイヨウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■mdファイルのプレビューの方法</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -3016,6 +3019,27 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="20" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -3067,14 +3091,20 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3085,6 +3115,27 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3094,15 +3145,6 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -3111,45 +3153,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3523,15 +3526,15 @@
   <sheetData>
     <row r="2" spans="1:8" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="85" t="str">
+      <c r="B2" s="92" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!B1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-生成AI_IG」</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
     </row>
     <row r="3" spans="1:8" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -3544,10 +3547,10 @@
     </row>
     <row r="4" spans="1:8" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="87"/>
+      <c r="C4" s="94"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -3555,18 +3558,18 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="88"/>
-      <c r="C5" s="89"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="96"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
     <row r="7" spans="1:8" ht="16.2">
-      <c r="B7" s="90" t="s">
+      <c r="B7" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="90"/>
+      <c r="C7" s="97"/>
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="24"/>
@@ -3626,7 +3629,7 @@
         <f>master!B5</f>
         <v>モジュール1：オリエンテーションとマインドセット変革</v>
       </c>
-      <c r="F14" s="84"/>
+      <c r="F14" s="91"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8">
@@ -3635,7 +3638,7 @@
         <v>30</v>
       </c>
       <c r="C15" s="74"/>
-      <c r="F15" s="84"/>
+      <c r="F15" s="91"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8">
@@ -3647,7 +3650,7 @@
         <f>master!B8</f>
         <v>モジュール2：AI・LLMの基礎理解</v>
       </c>
-      <c r="F16" s="84"/>
+      <c r="F16" s="91"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8">
@@ -3659,14 +3662,14 @@
         <f>master!B13</f>
         <v>モジュール3：NTTデータが目指すAIビジネス（Vision）</v>
       </c>
-      <c r="F17" s="84"/>
+      <c r="F17" s="91"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="38"/>
       <c r="B18" s="41"/>
       <c r="C18" s="75"/>
-      <c r="F18" s="84"/>
+      <c r="F18" s="91"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8">
@@ -3678,7 +3681,7 @@
         <f>master!B28</f>
         <v>モジュール4：プロンプトエンジニアリング</v>
       </c>
-      <c r="F19" s="84"/>
+      <c r="F19" s="91"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8">
@@ -3687,14 +3690,14 @@
       </c>
       <c r="B20" s="42"/>
       <c r="C20" s="74"/>
-      <c r="F20" s="84"/>
+      <c r="F20" s="91"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="57"/>
       <c r="B21" s="41"/>
       <c r="C21" s="75"/>
-      <c r="F21" s="84"/>
+      <c r="F21" s="91"/>
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8">
@@ -3750,7 +3753,7 @@
         <f>master!B35</f>
         <v>モジュール5：ハンズオン（ChatGPT）</v>
       </c>
-      <c r="F26" s="84"/>
+      <c r="F26" s="91"/>
       <c r="G26" s="14"/>
       <c r="H26" s="6"/>
     </row>
@@ -3758,7 +3761,7 @@
       <c r="A27" s="39"/>
       <c r="B27" s="42"/>
       <c r="C27" s="59"/>
-      <c r="F27" s="84"/>
+      <c r="F27" s="91"/>
       <c r="G27" s="14"/>
       <c r="H27" s="6"/>
     </row>
@@ -3768,7 +3771,7 @@
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="59"/>
-      <c r="F28" s="84"/>
+      <c r="F28" s="91"/>
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8">
@@ -3777,7 +3780,7 @@
       <c r="C29" s="60"/>
       <c r="D29" s="56"/>
       <c r="E29" s="53"/>
-      <c r="F29" s="84"/>
+      <c r="F29" s="91"/>
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8">
@@ -3791,7 +3794,7 @@
       </c>
       <c r="D30" s="56"/>
       <c r="E30" s="53"/>
-      <c r="F30" s="84"/>
+      <c r="F30" s="91"/>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8">
@@ -3800,7 +3803,7 @@
       <c r="C31" s="59"/>
       <c r="D31" s="56"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="84"/>
+      <c r="F31" s="91"/>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8">
@@ -3811,7 +3814,7 @@
       <c r="C32" s="59"/>
       <c r="D32" s="56"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="84"/>
+      <c r="F32" s="91"/>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8">
@@ -3820,7 +3823,7 @@
       <c r="C33" s="59"/>
       <c r="D33" s="56"/>
       <c r="E33" s="53"/>
-      <c r="F33" s="84"/>
+      <c r="F33" s="91"/>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8">
@@ -3829,7 +3832,7 @@
       <c r="C34" s="59"/>
       <c r="D34" s="56"/>
       <c r="E34" s="53"/>
-      <c r="F34" s="84"/>
+      <c r="F34" s="91"/>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8">
@@ -3838,7 +3841,7 @@
       <c r="C35" s="59"/>
       <c r="D35" s="56"/>
       <c r="E35" s="53"/>
-      <c r="F35" s="84"/>
+      <c r="F35" s="91"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8">
@@ -3849,7 +3852,7 @@
       <c r="C36" s="59"/>
       <c r="D36" s="56"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="84"/>
+      <c r="F36" s="91"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8">
@@ -3858,7 +3861,7 @@
       <c r="C37" s="59"/>
       <c r="D37" s="56"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="84"/>
+      <c r="F37" s="91"/>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8">
@@ -3867,7 +3870,7 @@
       <c r="C38" s="59"/>
       <c r="D38" s="56"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="84"/>
+      <c r="F38" s="91"/>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8">
@@ -3876,7 +3879,7 @@
       <c r="C39" s="59"/>
       <c r="D39" s="56"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="84"/>
+      <c r="F39" s="91"/>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8">
@@ -3887,7 +3890,7 @@
       <c r="C40" s="60"/>
       <c r="D40" s="56"/>
       <c r="E40" s="53"/>
-      <c r="F40" s="84"/>
+      <c r="F40" s="91"/>
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8">
@@ -3901,7 +3904,7 @@
       </c>
       <c r="D41" s="58"/>
       <c r="E41" s="54"/>
-      <c r="F41" s="84"/>
+      <c r="F41" s="91"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8">
@@ -3910,7 +3913,7 @@
       <c r="C42" s="60"/>
       <c r="D42" s="56"/>
       <c r="E42" s="54"/>
-      <c r="F42" s="84"/>
+      <c r="F42" s="91"/>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1">
@@ -3997,10 +4000,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="96"/>
+      <c r="C4" s="103"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -4011,16 +4014,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -4035,10 +4038,10 @@
       <c r="C7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="98" t="s">
+      <c r="D7" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="98"/>
+      <c r="E7" s="105"/>
       <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
@@ -4070,46 +4073,46 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="10"/>
-      <c r="B10" s="92"/>
-      <c r="C10" s="92" t="s">
+      <c r="B10" s="99"/>
+      <c r="C10" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="92" t="s">
+      <c r="D10" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92" t="s">
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="99" t="s">
+      <c r="H10" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="91" t="s">
+      <c r="I10" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="91"/>
-      <c r="K10" s="91" t="s">
+      <c r="J10" s="98"/>
+      <c r="K10" s="98" t="s">
         <v>31</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="92"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="92"/>
-      <c r="H11" s="100"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="107"/>
       <c r="I11" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J11" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="92"/>
+      <c r="K11" s="99"/>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="63">
@@ -4118,11 +4121,11 @@
       <c r="C12" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="93" t="s">
+      <c r="D12" s="100" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="94"/>
-      <c r="F12" s="95"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="102"/>
       <c r="G12" s="83" t="s">
         <v>50</v>
       </c>
@@ -4221,12 +4224,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -4237,18 +4240,18 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="103" t="s">
-        <v>205</v>
-      </c>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
+      <c r="B5" s="108" t="s">
+        <v>202</v>
+      </c>
+      <c r="C5" s="108"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
       <c r="L5" s="29"/>
       <c r="M5" s="30"/>
     </row>
@@ -4268,10 +4271,10 @@
       <c r="C7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="98" t="s">
+      <c r="D7" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="98"/>
+      <c r="E7" s="105"/>
       <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
@@ -4290,7 +4293,7 @@
         <v>34</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D8" s="45" t="s">
         <v>20</v>
@@ -4309,28 +4312,28 @@
     </row>
     <row r="10" spans="1:14" ht="24" customHeight="1">
       <c r="A10" s="10"/>
-      <c r="B10" s="92" t="s">
+      <c r="B10" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="92" t="s">
+      <c r="C10" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="92" t="s">
+      <c r="D10" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92" t="s">
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="91" t="s">
+      <c r="H10" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="101" t="s">
+      <c r="I10" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="102"/>
-      <c r="K10" s="91" t="s">
+      <c r="J10" s="110"/>
+      <c r="K10" s="98" t="s">
         <v>33</v>
       </c>
       <c r="L10" s="6"/>
@@ -4339,20 +4342,20 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="10"/>
-      <c r="B11" s="92"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="92"/>
-      <c r="H11" s="91"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="98"/>
       <c r="I11" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J11" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="92"/>
+      <c r="K11" s="99"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
@@ -4367,11 +4370,11 @@
         <f>master!C3</f>
         <v>講師の自己紹介</v>
       </c>
-      <c r="D12" s="104" t="s">
+      <c r="D12" s="113" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="105"/>
-      <c r="F12" s="106"/>
+      <c r="E12" s="114"/>
+      <c r="F12" s="115"/>
       <c r="G12" s="51" t="s">
         <v>49</v>
       </c>
@@ -4390,27 +4393,27 @@
     <row r="13" spans="1:14" ht="100.8">
       <c r="A13" s="10"/>
       <c r="B13" s="112"/>
-      <c r="C13" s="120" t="str">
+      <c r="C13" s="85" t="str">
         <f>master!C4</f>
         <v>受講生の自己紹介</v>
       </c>
-      <c r="D13" s="121" t="s">
-        <v>179</v>
-      </c>
-      <c r="E13" s="122"/>
-      <c r="F13" s="123"/>
-      <c r="G13" s="120" t="s">
+      <c r="D13" s="116" t="s">
+        <v>177</v>
+      </c>
+      <c r="E13" s="117"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="85" t="s">
         <v>152</v>
       </c>
-      <c r="H13" s="124"/>
-      <c r="I13" s="125" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="126">
+      <c r="H13" s="86"/>
+      <c r="I13" s="87" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="88">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K13" s="127" t="s">
-        <v>174</v>
+      <c r="K13" s="89" t="s">
+        <v>172</v>
       </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
@@ -4418,7 +4421,7 @@
     </row>
     <row r="14" spans="1:14" ht="163.80000000000001">
       <c r="A14" s="11"/>
-      <c r="B14" s="110" t="str">
+      <c r="B14" s="119" t="str">
         <f>master!B5</f>
         <v>モジュール1：オリエンテーションとマインドセット変革</v>
       </c>
@@ -4426,11 +4429,11 @@
         <f>master!C5</f>
         <v>1-1. 研修概要</v>
       </c>
-      <c r="D14" s="104" t="s">
+      <c r="D14" s="113" t="s">
         <v>136</v>
       </c>
-      <c r="E14" s="105"/>
-      <c r="F14" s="106"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="115"/>
       <c r="G14" s="51" t="s">
         <v>104</v>
       </c>
@@ -4448,16 +4451,16 @@
     </row>
     <row r="15" spans="1:14" ht="100.8">
       <c r="A15" s="11"/>
-      <c r="B15" s="110"/>
+      <c r="B15" s="119"/>
       <c r="C15" s="51" t="str">
         <f>master!C6</f>
         <v>1-2. 背景・目的</v>
       </c>
-      <c r="D15" s="104" t="s">
+      <c r="D15" s="113" t="s">
         <v>135</v>
       </c>
-      <c r="E15" s="105"/>
-      <c r="F15" s="106"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="115"/>
       <c r="G15" s="51" t="s">
         <v>47</v>
       </c>
@@ -4475,16 +4478,16 @@
     </row>
     <row r="16" spans="1:14" ht="214.2">
       <c r="A16" s="11"/>
-      <c r="B16" s="110"/>
+      <c r="B16" s="119"/>
       <c r="C16" s="51" t="str">
         <f>master!C7</f>
         <v>1-3. 研修ゴールと獲得可能な経験背景・目的</v>
       </c>
-      <c r="D16" s="104" t="s">
-        <v>180</v>
-      </c>
-      <c r="E16" s="105"/>
-      <c r="F16" s="106"/>
+      <c r="D16" s="113" t="s">
+        <v>178</v>
+      </c>
+      <c r="E16" s="114"/>
+      <c r="F16" s="115"/>
       <c r="G16" s="51" t="s">
         <v>137</v>
       </c>
@@ -4502,7 +4505,7 @@
     </row>
     <row r="17" spans="1:14" ht="88.2">
       <c r="A17" s="11"/>
-      <c r="B17" s="117" t="str">
+      <c r="B17" s="120" t="str">
         <f>master!B8</f>
         <v>モジュール2：AI・LLMの基礎理解</v>
       </c>
@@ -4510,11 +4513,11 @@
         <f>master!C8</f>
         <v>2-1. 生成AI（Generative AI）とは？</v>
       </c>
-      <c r="D17" s="104" t="s">
+      <c r="D17" s="113" t="s">
         <v>138</v>
       </c>
-      <c r="E17" s="105"/>
-      <c r="F17" s="106"/>
+      <c r="E17" s="114"/>
+      <c r="F17" s="115"/>
       <c r="G17" s="51" t="s">
         <v>45</v>
       </c>
@@ -4532,16 +4535,16 @@
     </row>
     <row r="18" spans="1:14" ht="113.4">
       <c r="A18" s="11"/>
-      <c r="B18" s="118"/>
+      <c r="B18" s="121"/>
       <c r="C18" s="51" t="str">
         <f>master!C9</f>
         <v>2-2. AIの変化</v>
       </c>
-      <c r="D18" s="104" t="s">
+      <c r="D18" s="113" t="s">
         <v>139</v>
       </c>
-      <c r="E18" s="105"/>
-      <c r="F18" s="106"/>
+      <c r="E18" s="114"/>
+      <c r="F18" s="115"/>
       <c r="G18" s="51" t="s">
         <v>43</v>
       </c>
@@ -4559,16 +4562,16 @@
     </row>
     <row r="19" spans="1:14" ht="113.4">
       <c r="A19" s="11"/>
-      <c r="B19" s="118"/>
+      <c r="B19" s="121"/>
       <c r="C19" s="51" t="str">
         <f>master!C10</f>
         <v>2-3. LLM（大規模言語モデル）の仕組み</v>
       </c>
-      <c r="D19" s="104" t="s">
+      <c r="D19" s="113" t="s">
         <v>140</v>
       </c>
-      <c r="E19" s="105"/>
-      <c r="F19" s="106"/>
+      <c r="E19" s="114"/>
+      <c r="F19" s="115"/>
       <c r="G19" s="51" t="s">
         <v>43</v>
       </c>
@@ -4586,16 +4589,16 @@
     </row>
     <row r="20" spans="1:14" ht="126">
       <c r="A20" s="11"/>
-      <c r="B20" s="118"/>
+      <c r="B20" s="121"/>
       <c r="C20" s="51" t="str">
         <f>master!C11</f>
         <v>2-4. 生成AIの「苦手なこと」（弱み）</v>
       </c>
-      <c r="D20" s="104" t="s">
+      <c r="D20" s="113" t="s">
         <v>141</v>
       </c>
-      <c r="E20" s="105"/>
-      <c r="F20" s="106"/>
+      <c r="E20" s="114"/>
+      <c r="F20" s="115"/>
       <c r="G20" s="51" t="s">
         <v>44</v>
       </c>
@@ -4613,16 +4616,16 @@
     </row>
     <row r="21" spans="1:14" ht="239.4">
       <c r="A21" s="11"/>
-      <c r="B21" s="119"/>
+      <c r="B21" s="122"/>
       <c r="C21" s="51" t="str">
         <f>master!C12</f>
         <v>2-5. 生成AIを使う心得８条</v>
       </c>
-      <c r="D21" s="104" t="s">
-        <v>181</v>
-      </c>
-      <c r="E21" s="105"/>
-      <c r="F21" s="106"/>
+      <c r="D21" s="113" t="s">
+        <v>179</v>
+      </c>
+      <c r="E21" s="114"/>
+      <c r="F21" s="115"/>
       <c r="G21" s="51" t="s">
         <v>142</v>
       </c>
@@ -4640,7 +4643,7 @@
     </row>
     <row r="22" spans="1:14" ht="25.2">
       <c r="A22" s="11"/>
-      <c r="B22" s="110" t="str">
+      <c r="B22" s="119" t="str">
         <f>master!B13</f>
         <v>モジュール3：NTTデータが目指すAIビジネス（Vision）</v>
       </c>
@@ -4648,9 +4651,9 @@
         <f>master!C13</f>
         <v>3-1. 本モジュールで学ぶこと①</v>
       </c>
-      <c r="D22" s="104"/>
-      <c r="E22" s="105"/>
-      <c r="F22" s="106"/>
+      <c r="D22" s="113"/>
+      <c r="E22" s="114"/>
+      <c r="F22" s="115"/>
       <c r="G22" s="51" t="s">
         <v>46</v>
       </c>
@@ -4668,14 +4671,14 @@
     </row>
     <row r="23" spans="1:14" ht="25.2">
       <c r="A23" s="11"/>
-      <c r="B23" s="110"/>
+      <c r="B23" s="119"/>
       <c r="C23" s="51" t="str">
         <f>master!C14</f>
         <v>3-2. NTTデータのAI戦略：Quality Growthとは</v>
       </c>
-      <c r="D23" s="104"/>
-      <c r="E23" s="105"/>
-      <c r="F23" s="106"/>
+      <c r="D23" s="113"/>
+      <c r="E23" s="114"/>
+      <c r="F23" s="115"/>
       <c r="G23" s="51" t="s">
         <v>46</v>
       </c>
@@ -4693,14 +4696,14 @@
     </row>
     <row r="24" spans="1:14" ht="25.2">
       <c r="A24" s="11"/>
-      <c r="B24" s="110"/>
+      <c r="B24" s="119"/>
       <c r="C24" s="51" t="str">
         <f>master!C15</f>
         <v>3-3. なぜ今、AIが重要なのか</v>
       </c>
-      <c r="D24" s="104"/>
-      <c r="E24" s="105"/>
-      <c r="F24" s="106"/>
+      <c r="D24" s="113"/>
+      <c r="E24" s="114"/>
+      <c r="F24" s="115"/>
       <c r="G24" s="51" t="s">
         <v>46</v>
       </c>
@@ -4718,14 +4721,14 @@
     </row>
     <row r="25" spans="1:14" ht="25.2">
       <c r="A25" s="11"/>
-      <c r="B25" s="110"/>
+      <c r="B25" s="119"/>
       <c r="C25" s="51" t="str">
         <f>master!C16</f>
         <v>3-4. 生成AIの進化：今、どこにいるか</v>
       </c>
-      <c r="D25" s="104"/>
-      <c r="E25" s="105"/>
-      <c r="F25" s="106"/>
+      <c r="D25" s="113"/>
+      <c r="E25" s="114"/>
+      <c r="F25" s="115"/>
       <c r="G25" s="51" t="s">
         <v>46</v>
       </c>
@@ -4743,14 +4746,14 @@
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
       <c r="A26" s="11"/>
-      <c r="B26" s="110"/>
+      <c r="B26" s="119"/>
       <c r="C26" s="51" t="str">
         <f>master!C17</f>
         <v>3-5. 本モジュールで学ぶこと②</v>
       </c>
-      <c r="D26" s="104"/>
-      <c r="E26" s="105"/>
-      <c r="F26" s="106"/>
+      <c r="D26" s="113"/>
+      <c r="E26" s="114"/>
+      <c r="F26" s="115"/>
       <c r="G26" s="51" t="s">
         <v>37</v>
       </c>
@@ -4768,16 +4771,16 @@
     </row>
     <row r="27" spans="1:14" ht="63">
       <c r="A27" s="11"/>
-      <c r="B27" s="110"/>
+      <c r="B27" s="119"/>
       <c r="C27" s="51" t="str">
         <f>master!C18</f>
         <v>3-6. エージェントAI（Agentic AI）とは何か</v>
       </c>
-      <c r="D27" s="104" t="s">
-        <v>182</v>
-      </c>
-      <c r="E27" s="105"/>
-      <c r="F27" s="106"/>
+      <c r="D27" s="113" t="s">
+        <v>180</v>
+      </c>
+      <c r="E27" s="114"/>
+      <c r="F27" s="115"/>
       <c r="G27" s="51" t="s">
         <v>39</v>
       </c>
@@ -4795,16 +4798,16 @@
     </row>
     <row r="28" spans="1:14" ht="63">
       <c r="A28" s="11"/>
-      <c r="B28" s="110"/>
+      <c r="B28" s="119"/>
       <c r="C28" s="51" t="str">
         <f>master!C19</f>
         <v>3-7. エージェントの処理</v>
       </c>
-      <c r="D28" s="104" t="s">
+      <c r="D28" s="113" t="s">
         <v>143</v>
       </c>
-      <c r="E28" s="105"/>
-      <c r="F28" s="106"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="115"/>
       <c r="G28" s="51" t="s">
         <v>39</v>
       </c>
@@ -4822,14 +4825,14 @@
     </row>
     <row r="29" spans="1:14" ht="37.799999999999997">
       <c r="A29" s="11"/>
-      <c r="B29" s="110"/>
+      <c r="B29" s="119"/>
       <c r="C29" s="51" t="str">
         <f>master!C20</f>
         <v>3-8. 本モジュールで学ぶこと③</v>
       </c>
-      <c r="D29" s="104"/>
-      <c r="E29" s="105"/>
-      <c r="F29" s="106"/>
+      <c r="D29" s="113"/>
+      <c r="E29" s="114"/>
+      <c r="F29" s="115"/>
       <c r="G29" s="51" t="s">
         <v>40</v>
       </c>
@@ -4847,14 +4850,14 @@
     </row>
     <row r="30" spans="1:14" ht="37.799999999999997">
       <c r="A30" s="11"/>
-      <c r="B30" s="110"/>
+      <c r="B30" s="119"/>
       <c r="C30" s="51" t="str">
         <f>master!C21</f>
         <v>3-9. NTTデータが描く未来：Smart AI Agent®</v>
       </c>
-      <c r="D30" s="104"/>
-      <c r="E30" s="105"/>
-      <c r="F30" s="106"/>
+      <c r="D30" s="113"/>
+      <c r="E30" s="114"/>
+      <c r="F30" s="115"/>
       <c r="G30" s="51" t="s">
         <v>40</v>
       </c>
@@ -4872,14 +4875,14 @@
     </row>
     <row r="31" spans="1:14" ht="37.799999999999997">
       <c r="A31" s="11"/>
-      <c r="B31" s="110"/>
+      <c r="B31" s="119"/>
       <c r="C31" s="51" t="str">
         <f>master!C22</f>
         <v>3-10. AIの強みを生かした業務変革の進め方</v>
       </c>
-      <c r="D31" s="104"/>
-      <c r="E31" s="105"/>
-      <c r="F31" s="106"/>
+      <c r="D31" s="113"/>
+      <c r="E31" s="114"/>
+      <c r="F31" s="115"/>
       <c r="G31" s="51" t="s">
         <v>40</v>
       </c>
@@ -4897,14 +4900,14 @@
     </row>
     <row r="32" spans="1:14" ht="37.799999999999997">
       <c r="A32" s="11"/>
-      <c r="B32" s="110"/>
+      <c r="B32" s="119"/>
       <c r="C32" s="51" t="str">
         <f>master!C23</f>
         <v>3-11. AIの強みを生かすポイント：人とAIとの役割分担</v>
       </c>
-      <c r="D32" s="104"/>
-      <c r="E32" s="105"/>
-      <c r="F32" s="106"/>
+      <c r="D32" s="113"/>
+      <c r="E32" s="114"/>
+      <c r="F32" s="115"/>
       <c r="G32" s="51" t="s">
         <v>40</v>
       </c>
@@ -4922,14 +4925,14 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="110"/>
+      <c r="B33" s="119"/>
       <c r="C33" s="51" t="str">
         <f>master!C24</f>
         <v>3-12. AIの強みを生かすポイント：プロセス自体をAI前提で再設計</v>
       </c>
-      <c r="D33" s="104"/>
-      <c r="E33" s="105"/>
-      <c r="F33" s="106"/>
+      <c r="D33" s="113"/>
+      <c r="E33" s="114"/>
+      <c r="F33" s="115"/>
       <c r="G33" s="51" t="s">
         <v>40</v>
       </c>
@@ -4947,14 +4950,14 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="110"/>
+      <c r="B34" s="119"/>
       <c r="C34" s="51" t="str">
         <f>master!C25</f>
         <v>3-13. JALカード様 -  AIバーチャル顧客を活用したマーケティング高度化</v>
       </c>
-      <c r="D34" s="104"/>
-      <c r="E34" s="105"/>
-      <c r="F34" s="106"/>
+      <c r="D34" s="113"/>
+      <c r="E34" s="114"/>
+      <c r="F34" s="115"/>
       <c r="G34" s="51" t="s">
         <v>40</v>
       </c>
@@ -4972,14 +4975,14 @@
     </row>
     <row r="35" spans="1:14" ht="37.799999999999997">
       <c r="A35" s="11"/>
-      <c r="B35" s="110"/>
+      <c r="B35" s="119"/>
       <c r="C35" s="51" t="str">
         <f>master!C26</f>
         <v>3-14. 大手メディアサービス会社 - AI-BPOによるオペレーション変革</v>
       </c>
-      <c r="D35" s="104"/>
-      <c r="E35" s="105"/>
-      <c r="F35" s="106"/>
+      <c r="D35" s="113"/>
+      <c r="E35" s="114"/>
+      <c r="F35" s="115"/>
       <c r="G35" s="51" t="s">
         <v>40</v>
       </c>
@@ -4997,14 +5000,14 @@
     </row>
     <row r="36" spans="1:14" ht="37.799999999999997">
       <c r="A36" s="11"/>
-      <c r="B36" s="110"/>
+      <c r="B36" s="119"/>
       <c r="C36" s="51" t="str">
         <f>master!C27</f>
         <v>Appendix：りそな様 - AI CoEと生成AI人財育成アカデミーの推進</v>
       </c>
-      <c r="D36" s="104"/>
-      <c r="E36" s="105"/>
-      <c r="F36" s="106"/>
+      <c r="D36" s="113"/>
+      <c r="E36" s="114"/>
+      <c r="F36" s="115"/>
       <c r="G36" s="51" t="s">
         <v>40</v>
       </c>
@@ -5022,7 +5025,7 @@
     </row>
     <row r="37" spans="1:14" ht="88.2">
       <c r="A37" s="11"/>
-      <c r="B37" s="117" t="str">
+      <c r="B37" s="120" t="str">
         <f>master!B28</f>
         <v>モジュール4：プロンプトエンジニアリング</v>
       </c>
@@ -5030,11 +5033,11 @@
         <f>master!C28</f>
         <v>4-1. プロンプトとは?</v>
       </c>
-      <c r="D37" s="104" t="s">
-        <v>183</v>
-      </c>
-      <c r="E37" s="105"/>
-      <c r="F37" s="106"/>
+      <c r="D37" s="113" t="s">
+        <v>181</v>
+      </c>
+      <c r="E37" s="114"/>
+      <c r="F37" s="115"/>
       <c r="G37" s="51" t="s">
         <v>45</v>
       </c>
@@ -5052,16 +5055,16 @@
     </row>
     <row r="38" spans="1:14" ht="37.799999999999997">
       <c r="A38" s="11"/>
-      <c r="B38" s="118"/>
+      <c r="B38" s="121"/>
       <c r="C38" s="51" t="str">
         <f>master!C29</f>
         <v>4-2. プロンプトを構成する4つの要素</v>
       </c>
-      <c r="D38" s="104" t="s">
+      <c r="D38" s="113" t="s">
         <v>144</v>
       </c>
-      <c r="E38" s="105"/>
-      <c r="F38" s="106"/>
+      <c r="E38" s="114"/>
+      <c r="F38" s="115"/>
       <c r="G38" s="51" t="s">
         <v>40</v>
       </c>
@@ -5079,16 +5082,16 @@
     </row>
     <row r="39" spans="1:14" ht="63">
       <c r="A39" s="11"/>
-      <c r="B39" s="118"/>
+      <c r="B39" s="121"/>
       <c r="C39" s="51" t="str">
         <f>master!C30</f>
         <v>4-3. 悪いプロンプト vs 良いプロンプト</v>
       </c>
-      <c r="D39" s="104" t="s">
+      <c r="D39" s="113" t="s">
         <v>145</v>
       </c>
-      <c r="E39" s="105"/>
-      <c r="F39" s="106"/>
+      <c r="E39" s="114"/>
+      <c r="F39" s="115"/>
       <c r="G39" s="51" t="s">
         <v>39</v>
       </c>
@@ -5106,14 +5109,14 @@
     </row>
     <row r="40" spans="1:14" ht="37.799999999999997">
       <c r="A40" s="11"/>
-      <c r="B40" s="118"/>
+      <c r="B40" s="121"/>
       <c r="C40" s="51" t="str">
         <f>master!C31</f>
         <v>4-4. テクニック①：Role Prompting（役割の付与）</v>
       </c>
-      <c r="D40" s="104"/>
-      <c r="E40" s="105"/>
-      <c r="F40" s="106"/>
+      <c r="D40" s="113"/>
+      <c r="E40" s="114"/>
+      <c r="F40" s="115"/>
       <c r="G40" s="51" t="s">
         <v>40</v>
       </c>
@@ -5131,14 +5134,14 @@
     </row>
     <row r="41" spans="1:14" ht="37.799999999999997">
       <c r="A41" s="11"/>
-      <c r="B41" s="118"/>
+      <c r="B41" s="121"/>
       <c r="C41" s="51" t="str">
         <f>master!C32</f>
         <v>4-5. テクニック②：区切り文字の活用</v>
       </c>
-      <c r="D41" s="104"/>
-      <c r="E41" s="105"/>
-      <c r="F41" s="106"/>
+      <c r="D41" s="113"/>
+      <c r="E41" s="114"/>
+      <c r="F41" s="115"/>
       <c r="G41" s="51" t="s">
         <v>40</v>
       </c>
@@ -5156,14 +5159,14 @@
     </row>
     <row r="42" spans="1:14" ht="37.799999999999997">
       <c r="A42" s="11"/>
-      <c r="B42" s="118"/>
+      <c r="B42" s="121"/>
       <c r="C42" s="51" t="str">
         <f>master!C33</f>
         <v>4-6. テクニック③：Zero-shot vs Few-shot</v>
       </c>
-      <c r="D42" s="104"/>
-      <c r="E42" s="105"/>
-      <c r="F42" s="106"/>
+      <c r="D42" s="113"/>
+      <c r="E42" s="114"/>
+      <c r="F42" s="115"/>
       <c r="G42" s="51" t="s">
         <v>40</v>
       </c>
@@ -5181,14 +5184,14 @@
     </row>
     <row r="43" spans="1:14" ht="50.4">
       <c r="A43" s="11"/>
-      <c r="B43" s="119"/>
+      <c r="B43" s="122"/>
       <c r="C43" s="51" t="str">
         <f>master!C34</f>
         <v>4-7. テクニック④：Chain of Thought（思考の連鎖）</v>
       </c>
-      <c r="D43" s="104"/>
-      <c r="E43" s="105"/>
-      <c r="F43" s="106"/>
+      <c r="D43" s="113"/>
+      <c r="E43" s="114"/>
+      <c r="F43" s="115"/>
       <c r="G43" s="51" t="s">
         <v>41</v>
       </c>
@@ -5206,7 +5209,7 @@
     </row>
     <row r="44" spans="1:14" ht="75.599999999999994">
       <c r="A44" s="11"/>
-      <c r="B44" s="113" t="str">
+      <c r="B44" s="126" t="str">
         <f>master!B35</f>
         <v>モジュール5：ハンズオン（ChatGPT）</v>
       </c>
@@ -5214,11 +5217,11 @@
         <f>master!C35</f>
         <v>5-1. ChatGPTの使い方（一般チャット）</v>
       </c>
-      <c r="D44" s="107" t="s">
-        <v>184</v>
-      </c>
-      <c r="E44" s="108"/>
-      <c r="F44" s="109"/>
+      <c r="D44" s="123" t="s">
+        <v>182</v>
+      </c>
+      <c r="E44" s="124"/>
+      <c r="F44" s="125"/>
       <c r="G44" s="65" t="s">
         <v>42</v>
       </c>
@@ -5236,16 +5239,16 @@
     </row>
     <row r="45" spans="1:14" ht="126">
       <c r="A45" s="11"/>
-      <c r="B45" s="114"/>
+      <c r="B45" s="127"/>
       <c r="C45" s="65" t="str">
         <f>master!C36</f>
         <v>5-2. 例①：顧客提案向けの企画提案書を作りたい</v>
       </c>
-      <c r="D45" s="107" t="s">
-        <v>192</v>
-      </c>
-      <c r="E45" s="108"/>
-      <c r="F45" s="109"/>
+      <c r="D45" s="123" t="s">
+        <v>190</v>
+      </c>
+      <c r="E45" s="124"/>
+      <c r="F45" s="125"/>
       <c r="G45" s="65" t="s">
         <v>44</v>
       </c>
@@ -5263,16 +5266,16 @@
     </row>
     <row r="46" spans="1:14" ht="126">
       <c r="A46" s="11"/>
-      <c r="B46" s="114"/>
+      <c r="B46" s="127"/>
       <c r="C46" s="65" t="str">
         <f>master!C37</f>
         <v>5-3. 例①：顧客提案向けの企画提案書を作りたい - プロンプト例</v>
       </c>
-      <c r="D46" s="107" t="s">
+      <c r="D46" s="123" t="s">
         <v>147</v>
       </c>
-      <c r="E46" s="108"/>
-      <c r="F46" s="109"/>
+      <c r="E46" s="124"/>
+      <c r="F46" s="125"/>
       <c r="G46" s="65" t="s">
         <v>44</v>
       </c>
@@ -5290,16 +5293,16 @@
     </row>
     <row r="47" spans="1:14" ht="37.799999999999997">
       <c r="A47" s="11"/>
-      <c r="B47" s="114"/>
+      <c r="B47" s="127"/>
       <c r="C47" s="65" t="str">
         <f>master!C38</f>
         <v>5-4. 例①：顧客提案向けの企画提案書を作りたい - 実行例</v>
       </c>
-      <c r="D47" s="107" t="s">
+      <c r="D47" s="123" t="s">
         <v>146</v>
       </c>
-      <c r="E47" s="108"/>
-      <c r="F47" s="109"/>
+      <c r="E47" s="124"/>
+      <c r="F47" s="125"/>
       <c r="G47" s="65" t="s">
         <v>40</v>
       </c>
@@ -5317,24 +5320,24 @@
     </row>
     <row r="48" spans="1:14" ht="88.2">
       <c r="A48" s="11"/>
-      <c r="B48" s="114"/>
-      <c r="C48" s="120"/>
-      <c r="D48" s="121" t="s">
-        <v>191</v>
-      </c>
-      <c r="E48" s="122"/>
-      <c r="F48" s="123"/>
-      <c r="G48" s="120" t="s">
+      <c r="B48" s="127"/>
+      <c r="C48" s="85"/>
+      <c r="D48" s="116" t="s">
+        <v>189</v>
+      </c>
+      <c r="E48" s="117"/>
+      <c r="F48" s="118"/>
+      <c r="G48" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="H48" s="124"/>
-      <c r="I48" s="125" t="s">
-        <v>25</v>
-      </c>
-      <c r="J48" s="126">
+      <c r="H48" s="86"/>
+      <c r="I48" s="87" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" s="88">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="K48" s="127" t="s">
+      <c r="K48" s="89" t="s">
         <v>130</v>
       </c>
       <c r="L48" s="6"/>
@@ -5343,16 +5346,16 @@
     </row>
     <row r="49" spans="1:14" ht="50.4">
       <c r="A49" s="11"/>
-      <c r="B49" s="114"/>
+      <c r="B49" s="127"/>
       <c r="C49" s="65" t="str">
         <f>master!C39</f>
         <v>5-5. 例②：100本ノックを作ってみる</v>
       </c>
-      <c r="D49" s="107" t="s">
-        <v>200</v>
-      </c>
-      <c r="E49" s="108"/>
-      <c r="F49" s="109"/>
+      <c r="D49" s="123" t="s">
+        <v>197</v>
+      </c>
+      <c r="E49" s="124"/>
+      <c r="F49" s="125"/>
       <c r="G49" s="65" t="s">
         <v>41</v>
       </c>
@@ -5370,16 +5373,16 @@
     </row>
     <row r="50" spans="1:14" ht="75.599999999999994">
       <c r="A50" s="11"/>
-      <c r="B50" s="114"/>
+      <c r="B50" s="127"/>
       <c r="C50" s="65" t="str">
         <f>master!C40</f>
         <v>5-6. 例②：100本ノックを作ってみる -プロンプト例</v>
       </c>
-      <c r="D50" s="107" t="s">
-        <v>185</v>
-      </c>
-      <c r="E50" s="108"/>
-      <c r="F50" s="109"/>
+      <c r="D50" s="123" t="s">
+        <v>183</v>
+      </c>
+      <c r="E50" s="124"/>
+      <c r="F50" s="125"/>
       <c r="G50" s="65" t="s">
         <v>42</v>
       </c>
@@ -5397,24 +5400,24 @@
     </row>
     <row r="51" spans="1:14" ht="88.2">
       <c r="A51" s="11"/>
-      <c r="B51" s="114"/>
-      <c r="C51" s="120"/>
-      <c r="D51" s="121" t="s">
-        <v>193</v>
-      </c>
-      <c r="E51" s="122"/>
-      <c r="F51" s="123"/>
-      <c r="G51" s="120" t="s">
+      <c r="B51" s="127"/>
+      <c r="C51" s="85"/>
+      <c r="D51" s="116" t="s">
+        <v>191</v>
+      </c>
+      <c r="E51" s="117"/>
+      <c r="F51" s="118"/>
+      <c r="G51" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="H51" s="124"/>
-      <c r="I51" s="125" t="s">
-        <v>199</v>
-      </c>
-      <c r="J51" s="126">
+      <c r="H51" s="86"/>
+      <c r="I51" s="87" t="s">
+        <v>196</v>
+      </c>
+      <c r="J51" s="88">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="K51" s="127" t="s">
+      <c r="K51" s="89" t="s">
         <v>130</v>
       </c>
       <c r="L51" s="6"/>
@@ -5423,16 +5426,16 @@
     </row>
     <row r="52" spans="1:14" ht="50.4">
       <c r="A52" s="11"/>
-      <c r="B52" s="114"/>
+      <c r="B52" s="127"/>
       <c r="C52" s="65" t="str">
         <f>master!C41</f>
         <v>5-7. 例②：100本ノックを作ってみる - 実行結果①</v>
       </c>
-      <c r="D52" s="107" t="s">
-        <v>161</v>
-      </c>
-      <c r="E52" s="108"/>
-      <c r="F52" s="109"/>
+      <c r="D52" s="123" t="s">
+        <v>159</v>
+      </c>
+      <c r="E52" s="124"/>
+      <c r="F52" s="125"/>
       <c r="G52" s="65" t="s">
         <v>41</v>
       </c>
@@ -5450,16 +5453,16 @@
     </row>
     <row r="53" spans="1:14" ht="50.4">
       <c r="A53" s="11"/>
-      <c r="B53" s="114"/>
+      <c r="B53" s="127"/>
       <c r="C53" s="65" t="str">
         <f>master!C42</f>
         <v>5-8. 例②：100本ノックを作ってみる - 実行結果②</v>
       </c>
-      <c r="D53" s="107" t="s">
-        <v>162</v>
-      </c>
-      <c r="E53" s="108"/>
-      <c r="F53" s="109"/>
+      <c r="D53" s="123" t="s">
+        <v>160</v>
+      </c>
+      <c r="E53" s="124"/>
+      <c r="F53" s="125"/>
       <c r="G53" s="65" t="s">
         <v>41</v>
       </c>
@@ -5477,16 +5480,16 @@
     </row>
     <row r="54" spans="1:14" ht="50.4">
       <c r="A54" s="11"/>
-      <c r="B54" s="114"/>
+      <c r="B54" s="127"/>
       <c r="C54" s="65" t="str">
         <f>master!C43</f>
         <v>5-9. 例②：100本ノックを作ってみる - 実行結果③</v>
       </c>
-      <c r="D54" s="107" t="s">
-        <v>163</v>
-      </c>
-      <c r="E54" s="108"/>
-      <c r="F54" s="109"/>
+      <c r="D54" s="123" t="s">
+        <v>161</v>
+      </c>
+      <c r="E54" s="124"/>
+      <c r="F54" s="125"/>
       <c r="G54" s="65" t="s">
         <v>41</v>
       </c>
@@ -5504,16 +5507,16 @@
     </row>
     <row r="55" spans="1:14" ht="63">
       <c r="A55" s="11"/>
-      <c r="B55" s="115"/>
+      <c r="B55" s="128"/>
       <c r="C55" s="65" t="str">
         <f>master!C44</f>
         <v>5-10. ChatGPT まとめ</v>
       </c>
-      <c r="D55" s="107" t="s">
+      <c r="D55" s="123" t="s">
         <v>148</v>
       </c>
-      <c r="E55" s="108"/>
-      <c r="F55" s="109"/>
+      <c r="E55" s="124"/>
+      <c r="F55" s="125"/>
       <c r="G55" s="65" t="s">
         <v>39</v>
       </c>
@@ -5531,7 +5534,7 @@
     </row>
     <row r="56" spans="1:14" ht="50.4" customHeight="1">
       <c r="A56" s="11"/>
-      <c r="B56" s="114" t="str">
+      <c r="B56" s="127" t="str">
         <f>master!B45</f>
         <v>モジュール6：ハンズオン（ GitHub Copilot ）</v>
       </c>
@@ -5539,11 +5542,11 @@
         <f>master!C45</f>
         <v>6-1. Visual Studio Code を開く</v>
       </c>
-      <c r="D56" s="107" t="s">
+      <c r="D56" s="123" t="s">
         <v>149</v>
       </c>
-      <c r="E56" s="108"/>
-      <c r="F56" s="109"/>
+      <c r="E56" s="124"/>
+      <c r="F56" s="125"/>
       <c r="G56" s="65" t="s">
         <v>41</v>
       </c>
@@ -5561,16 +5564,16 @@
     </row>
     <row r="57" spans="1:14" ht="63">
       <c r="A57" s="11"/>
-      <c r="B57" s="114"/>
+      <c r="B57" s="127"/>
       <c r="C57" s="65" t="str">
         <f>master!C46</f>
         <v>6-2. コード補完機能</v>
       </c>
-      <c r="D57" s="107" t="s">
+      <c r="D57" s="123" t="s">
         <v>150</v>
       </c>
-      <c r="E57" s="108"/>
-      <c r="F57" s="109"/>
+      <c r="E57" s="124"/>
+      <c r="F57" s="125"/>
       <c r="G57" s="65" t="s">
         <v>39</v>
       </c>
@@ -5588,16 +5591,16 @@
     </row>
     <row r="58" spans="1:14" ht="75.599999999999994">
       <c r="A58" s="11"/>
-      <c r="B58" s="114"/>
+      <c r="B58" s="127"/>
       <c r="C58" s="65" t="str">
         <f>master!C47</f>
         <v>6-3. チャット機能</v>
       </c>
-      <c r="D58" s="107" t="s">
-        <v>210</v>
-      </c>
-      <c r="E58" s="108"/>
-      <c r="F58" s="109"/>
+      <c r="D58" s="123" t="s">
+        <v>207</v>
+      </c>
+      <c r="E58" s="124"/>
+      <c r="F58" s="125"/>
       <c r="G58" s="65" t="s">
         <v>42</v>
       </c>
@@ -5615,16 +5618,16 @@
     </row>
     <row r="59" spans="1:14" ht="88.2">
       <c r="A59" s="11"/>
-      <c r="B59" s="114"/>
+      <c r="B59" s="127"/>
       <c r="C59" s="65" t="str">
         <f>master!C48</f>
         <v>6-4. チャット機能 - コマンド</v>
       </c>
-      <c r="D59" s="107" t="s">
-        <v>209</v>
-      </c>
-      <c r="E59" s="108"/>
-      <c r="F59" s="109"/>
+      <c r="D59" s="123" t="s">
+        <v>206</v>
+      </c>
+      <c r="E59" s="124"/>
+      <c r="F59" s="125"/>
       <c r="G59" s="65" t="s">
         <v>45</v>
       </c>
@@ -5642,16 +5645,16 @@
     </row>
     <row r="60" spans="1:14" ht="50.4">
       <c r="A60" s="11"/>
-      <c r="B60" s="114"/>
+      <c r="B60" s="127"/>
       <c r="C60" s="65" t="str">
         <f>master!C49</f>
         <v>6-5. 簡単なアプリやゲームを作ってみましょう</v>
       </c>
-      <c r="D60" s="107" t="s">
-        <v>175</v>
-      </c>
-      <c r="E60" s="108"/>
-      <c r="F60" s="109"/>
+      <c r="D60" s="123" t="s">
+        <v>173</v>
+      </c>
+      <c r="E60" s="124"/>
+      <c r="F60" s="125"/>
       <c r="G60" s="65" t="s">
         <v>41</v>
       </c>
@@ -5669,16 +5672,16 @@
     </row>
     <row r="61" spans="1:14" ht="50.4">
       <c r="A61" s="11"/>
-      <c r="B61" s="114"/>
+      <c r="B61" s="127"/>
       <c r="C61" s="65" t="str">
         <f>master!C50</f>
         <v>6-6. 例①：高級志向テトリス</v>
       </c>
-      <c r="D61" s="107" t="s">
-        <v>178</v>
-      </c>
-      <c r="E61" s="108"/>
-      <c r="F61" s="109"/>
+      <c r="D61" s="123" t="s">
+        <v>176</v>
+      </c>
+      <c r="E61" s="124"/>
+      <c r="F61" s="125"/>
       <c r="G61" s="65" t="s">
         <v>41</v>
       </c>
@@ -5696,16 +5699,16 @@
     </row>
     <row r="62" spans="1:14" ht="50.4">
       <c r="A62" s="11"/>
-      <c r="B62" s="114"/>
+      <c r="B62" s="127"/>
       <c r="C62" s="65" t="str">
         <f>master!C51</f>
         <v>6-7. 例②：わくわく！にっぽんダーツの旅</v>
       </c>
-      <c r="D62" s="107" t="s">
-        <v>176</v>
-      </c>
-      <c r="E62" s="108"/>
-      <c r="F62" s="109"/>
+      <c r="D62" s="123" t="s">
+        <v>174</v>
+      </c>
+      <c r="E62" s="124"/>
+      <c r="F62" s="125"/>
       <c r="G62" s="65" t="s">
         <v>41</v>
       </c>
@@ -5723,16 +5726,16 @@
     </row>
     <row r="63" spans="1:14" ht="50.4">
       <c r="A63" s="11"/>
-      <c r="B63" s="114"/>
+      <c r="B63" s="127"/>
       <c r="C63" s="65" t="str">
         <f>master!C52</f>
         <v>6-8. 例③：タスク管理ツール</v>
       </c>
-      <c r="D63" s="107" t="s">
-        <v>177</v>
-      </c>
-      <c r="E63" s="108"/>
-      <c r="F63" s="109"/>
+      <c r="D63" s="123" t="s">
+        <v>175</v>
+      </c>
+      <c r="E63" s="124"/>
+      <c r="F63" s="125"/>
       <c r="G63" s="65" t="s">
         <v>41</v>
       </c>
@@ -5750,40 +5753,40 @@
     </row>
     <row r="64" spans="1:14" ht="138.6">
       <c r="A64" s="11"/>
-      <c r="B64" s="114"/>
-      <c r="C64" s="120"/>
-      <c r="D64" s="121" t="s">
-        <v>190</v>
-      </c>
-      <c r="E64" s="122"/>
-      <c r="F64" s="123"/>
-      <c r="G64" s="120" t="s">
+      <c r="B64" s="127"/>
+      <c r="C64" s="85"/>
+      <c r="D64" s="116" t="s">
+        <v>188</v>
+      </c>
+      <c r="E64" s="117"/>
+      <c r="F64" s="118"/>
+      <c r="G64" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="H64" s="124"/>
-      <c r="I64" s="125" t="s">
+      <c r="H64" s="86"/>
+      <c r="I64" s="87" t="s">
         <v>131</v>
       </c>
-      <c r="J64" s="126">
+      <c r="J64" s="88">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K64" s="127"/>
+      <c r="K64" s="89"/>
       <c r="L64" s="6"/>
       <c r="M64" s="6"/>
       <c r="N64" s="6"/>
     </row>
     <row r="65" spans="1:14" ht="75.599999999999994">
       <c r="A65" s="11"/>
-      <c r="B65" s="114"/>
+      <c r="B65" s="127"/>
       <c r="C65" s="65" t="str">
         <f>master!C53</f>
         <v>6-9. ディレクトリ作成とファイル配置</v>
       </c>
-      <c r="D65" s="107" t="s">
-        <v>195</v>
-      </c>
-      <c r="E65" s="108"/>
-      <c r="F65" s="109"/>
+      <c r="D65" s="123" t="s">
+        <v>192</v>
+      </c>
+      <c r="E65" s="124"/>
+      <c r="F65" s="125"/>
       <c r="G65" s="65" t="s">
         <v>42</v>
       </c>
@@ -5801,40 +5804,40 @@
     </row>
     <row r="66" spans="1:14" ht="88.2">
       <c r="A66" s="11"/>
-      <c r="B66" s="114"/>
-      <c r="C66" s="120"/>
-      <c r="D66" s="121" t="s">
-        <v>194</v>
-      </c>
-      <c r="E66" s="122"/>
-      <c r="F66" s="123"/>
-      <c r="G66" s="120" t="s">
+      <c r="B66" s="127"/>
+      <c r="C66" s="85"/>
+      <c r="D66" s="116" t="s">
+        <v>208</v>
+      </c>
+      <c r="E66" s="117"/>
+      <c r="F66" s="118"/>
+      <c r="G66" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="H66" s="124"/>
-      <c r="I66" s="125" t="s">
+      <c r="H66" s="86"/>
+      <c r="I66" s="87" t="s">
         <v>131</v>
       </c>
-      <c r="J66" s="126">
+      <c r="J66" s="88">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K66" s="127"/>
+      <c r="K66" s="89"/>
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
     </row>
     <row r="67" spans="1:14" ht="50.4">
       <c r="A67" s="11"/>
-      <c r="B67" s="114"/>
+      <c r="B67" s="127"/>
       <c r="C67" s="65" t="str">
         <f>master!C54</f>
         <v>6-10. チャット機能 - Askモード</v>
       </c>
-      <c r="D67" s="107" t="s">
-        <v>206</v>
-      </c>
-      <c r="E67" s="108"/>
-      <c r="F67" s="109"/>
+      <c r="D67" s="123" t="s">
+        <v>203</v>
+      </c>
+      <c r="E67" s="124"/>
+      <c r="F67" s="125"/>
       <c r="G67" s="65" t="s">
         <v>41</v>
       </c>
@@ -5852,16 +5855,16 @@
     </row>
     <row r="68" spans="1:14" ht="100.8">
       <c r="A68" s="11"/>
-      <c r="B68" s="114"/>
+      <c r="B68" s="127"/>
       <c r="C68" s="65" t="str">
         <f>master!C55</f>
         <v>6-11. Askモードについて</v>
       </c>
-      <c r="D68" s="107" t="s">
+      <c r="D68" s="123" t="s">
         <v>154</v>
       </c>
-      <c r="E68" s="108"/>
-      <c r="F68" s="109"/>
+      <c r="E68" s="124"/>
+      <c r="F68" s="125"/>
       <c r="G68" s="65" t="s">
         <v>47</v>
       </c>
@@ -5879,16 +5882,16 @@
     </row>
     <row r="69" spans="1:14" ht="50.4">
       <c r="A69" s="11"/>
-      <c r="B69" s="114"/>
+      <c r="B69" s="127"/>
       <c r="C69" s="65" t="str">
         <f>master!C56</f>
         <v>6-12. 実行例①</v>
       </c>
-      <c r="D69" s="107" t="s">
-        <v>160</v>
-      </c>
-      <c r="E69" s="108"/>
-      <c r="F69" s="109"/>
+      <c r="D69" s="123" t="s">
+        <v>158</v>
+      </c>
+      <c r="E69" s="124"/>
+      <c r="F69" s="125"/>
       <c r="G69" s="65" t="s">
         <v>41</v>
       </c>
@@ -5906,16 +5909,16 @@
     </row>
     <row r="70" spans="1:14" ht="50.4">
       <c r="A70" s="11"/>
-      <c r="B70" s="114"/>
+      <c r="B70" s="127"/>
       <c r="C70" s="65" t="str">
         <f>master!C57</f>
         <v>6-13. 実行例②</v>
       </c>
-      <c r="D70" s="107" t="s">
-        <v>158</v>
-      </c>
-      <c r="E70" s="108"/>
-      <c r="F70" s="109"/>
+      <c r="D70" s="123" t="s">
+        <v>156</v>
+      </c>
+      <c r="E70" s="124"/>
+      <c r="F70" s="125"/>
       <c r="G70" s="65" t="s">
         <v>41</v>
       </c>
@@ -5933,16 +5936,16 @@
     </row>
     <row r="71" spans="1:14" ht="50.4">
       <c r="A71" s="11"/>
-      <c r="B71" s="114"/>
+      <c r="B71" s="127"/>
       <c r="C71" s="65" t="str">
         <f>master!C58</f>
         <v>6-14. 実行例③</v>
       </c>
-      <c r="D71" s="107" t="s">
-        <v>159</v>
-      </c>
-      <c r="E71" s="108"/>
-      <c r="F71" s="109"/>
+      <c r="D71" s="123" t="s">
+        <v>157</v>
+      </c>
+      <c r="E71" s="124"/>
+      <c r="F71" s="125"/>
       <c r="G71" s="65" t="s">
         <v>41</v>
       </c>
@@ -5960,40 +5963,40 @@
     </row>
     <row r="72" spans="1:14" ht="138.6">
       <c r="A72" s="11"/>
-      <c r="B72" s="114"/>
-      <c r="C72" s="120"/>
-      <c r="D72" s="121" t="s">
-        <v>189</v>
-      </c>
-      <c r="E72" s="122"/>
-      <c r="F72" s="123"/>
-      <c r="G72" s="120" t="s">
+      <c r="B72" s="127"/>
+      <c r="C72" s="85"/>
+      <c r="D72" s="116" t="s">
+        <v>187</v>
+      </c>
+      <c r="E72" s="117"/>
+      <c r="F72" s="118"/>
+      <c r="G72" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="H72" s="124"/>
-      <c r="I72" s="125" t="s">
+      <c r="H72" s="86"/>
+      <c r="I72" s="87" t="s">
         <v>131</v>
       </c>
-      <c r="J72" s="126">
+      <c r="J72" s="88">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K72" s="127"/>
+      <c r="K72" s="89"/>
       <c r="L72" s="6"/>
       <c r="M72" s="6"/>
       <c r="N72" s="6"/>
     </row>
     <row r="73" spans="1:14" ht="63">
       <c r="A73" s="11"/>
-      <c r="B73" s="114"/>
+      <c r="B73" s="127"/>
       <c r="C73" s="65" t="str">
         <f>master!C59</f>
         <v>6-15. Askモードまとめ</v>
       </c>
-      <c r="D73" s="107" t="s">
+      <c r="D73" s="123" t="s">
         <v>153</v>
       </c>
-      <c r="E73" s="108"/>
-      <c r="F73" s="109"/>
+      <c r="E73" s="124"/>
+      <c r="F73" s="125"/>
       <c r="G73" s="65" t="s">
         <v>39</v>
       </c>
@@ -6011,16 +6014,16 @@
     </row>
     <row r="74" spans="1:14" ht="50.4">
       <c r="A74" s="11"/>
-      <c r="B74" s="114"/>
+      <c r="B74" s="127"/>
       <c r="C74" s="65" t="str">
         <f>master!C60</f>
         <v>6-16. チャット機能 - Agentモード</v>
       </c>
-      <c r="D74" s="107" t="s">
-        <v>207</v>
-      </c>
-      <c r="E74" s="108"/>
-      <c r="F74" s="109"/>
+      <c r="D74" s="123" t="s">
+        <v>204</v>
+      </c>
+      <c r="E74" s="124"/>
+      <c r="F74" s="125"/>
       <c r="G74" s="65" t="s">
         <v>41</v>
       </c>
@@ -6038,16 +6041,16 @@
     </row>
     <row r="75" spans="1:14" ht="63">
       <c r="A75" s="11"/>
-      <c r="B75" s="114"/>
+      <c r="B75" s="127"/>
       <c r="C75" s="65" t="str">
         <f>master!C61</f>
         <v>6-17. Agentモード</v>
       </c>
-      <c r="D75" s="107" t="s">
-        <v>164</v>
-      </c>
-      <c r="E75" s="108"/>
-      <c r="F75" s="109"/>
+      <c r="D75" s="123" t="s">
+        <v>162</v>
+      </c>
+      <c r="E75" s="124"/>
+      <c r="F75" s="125"/>
       <c r="G75" s="65" t="s">
         <v>39</v>
       </c>
@@ -6065,16 +6068,16 @@
     </row>
     <row r="76" spans="1:14" ht="50.4">
       <c r="A76" s="11"/>
-      <c r="B76" s="114"/>
+      <c r="B76" s="127"/>
       <c r="C76" s="65" t="str">
         <f>master!C62</f>
         <v>6-18. 実行例</v>
       </c>
-      <c r="D76" s="107" t="s">
-        <v>165</v>
-      </c>
-      <c r="E76" s="108"/>
-      <c r="F76" s="109"/>
+      <c r="D76" s="123" t="s">
+        <v>163</v>
+      </c>
+      <c r="E76" s="124"/>
+      <c r="F76" s="125"/>
       <c r="G76" s="65" t="s">
         <v>41</v>
       </c>
@@ -6092,16 +6095,16 @@
     </row>
     <row r="77" spans="1:14" ht="37.799999999999997">
       <c r="A77" s="11"/>
-      <c r="B77" s="114"/>
+      <c r="B77" s="127"/>
       <c r="C77" s="65" t="str">
         <f>master!C63</f>
         <v>6-19. READMEの内容を確認しましょう①</v>
       </c>
-      <c r="D77" s="107" t="s">
-        <v>157</v>
-      </c>
-      <c r="E77" s="108"/>
-      <c r="F77" s="109"/>
+      <c r="D77" s="123" t="s">
+        <v>210</v>
+      </c>
+      <c r="E77" s="124"/>
+      <c r="F77" s="125"/>
       <c r="G77" s="65" t="s">
         <v>40</v>
       </c>
@@ -6119,16 +6122,16 @@
     </row>
     <row r="78" spans="1:14" ht="37.799999999999997">
       <c r="A78" s="11"/>
-      <c r="B78" s="114"/>
+      <c r="B78" s="127"/>
       <c r="C78" s="65" t="str">
         <f>master!C64</f>
         <v>6-20. READMEの内容を確認しましょう②</v>
       </c>
-      <c r="D78" s="107" t="s">
-        <v>156</v>
-      </c>
-      <c r="E78" s="108"/>
-      <c r="F78" s="109"/>
+      <c r="D78" s="123" t="s">
+        <v>209</v>
+      </c>
+      <c r="E78" s="124"/>
+      <c r="F78" s="125"/>
       <c r="G78" s="65" t="s">
         <v>40</v>
       </c>
@@ -6146,24 +6149,24 @@
     </row>
     <row r="79" spans="1:14" ht="126">
       <c r="A79" s="11"/>
-      <c r="B79" s="114"/>
-      <c r="C79" s="120"/>
-      <c r="D79" s="121" t="s">
-        <v>188</v>
-      </c>
-      <c r="E79" s="122"/>
-      <c r="F79" s="123"/>
-      <c r="G79" s="120" t="s">
+      <c r="B79" s="127"/>
+      <c r="C79" s="85"/>
+      <c r="D79" s="116" t="s">
+        <v>186</v>
+      </c>
+      <c r="E79" s="117"/>
+      <c r="F79" s="118"/>
+      <c r="G79" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="H79" s="124"/>
-      <c r="I79" s="125" t="s">
+      <c r="H79" s="86"/>
+      <c r="I79" s="87" t="s">
         <v>131</v>
       </c>
-      <c r="J79" s="126">
+      <c r="J79" s="88">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="K79" s="127" t="s">
+      <c r="K79" s="89" t="s">
         <v>155</v>
       </c>
       <c r="L79" s="6"/>
@@ -6172,16 +6175,16 @@
     </row>
     <row r="80" spans="1:14" ht="50.4">
       <c r="A80" s="11"/>
-      <c r="B80" s="114"/>
+      <c r="B80" s="127"/>
       <c r="C80" s="65" t="str">
         <f>master!C65</f>
         <v>6-21. Changeログを作ってみましょう</v>
       </c>
-      <c r="D80" s="107" t="s">
-        <v>166</v>
-      </c>
-      <c r="E80" s="108"/>
-      <c r="F80" s="109"/>
+      <c r="D80" s="123" t="s">
+        <v>164</v>
+      </c>
+      <c r="E80" s="124"/>
+      <c r="F80" s="125"/>
       <c r="G80" s="65" t="s">
         <v>41</v>
       </c>
@@ -6199,24 +6202,24 @@
     </row>
     <row r="81" spans="1:14" ht="113.4">
       <c r="A81" s="11"/>
-      <c r="B81" s="114"/>
-      <c r="C81" s="128"/>
-      <c r="D81" s="121" t="s">
-        <v>187</v>
-      </c>
-      <c r="E81" s="122"/>
-      <c r="F81" s="123"/>
-      <c r="G81" s="120" t="s">
+      <c r="B81" s="127"/>
+      <c r="C81" s="90"/>
+      <c r="D81" s="116" t="s">
+        <v>185</v>
+      </c>
+      <c r="E81" s="117"/>
+      <c r="F81" s="118"/>
+      <c r="G81" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="H81" s="124"/>
-      <c r="I81" s="125" t="s">
-        <v>199</v>
-      </c>
-      <c r="J81" s="126">
+      <c r="H81" s="86"/>
+      <c r="I81" s="87" t="s">
+        <v>196</v>
+      </c>
+      <c r="J81" s="88">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K81" s="127" t="s">
+      <c r="K81" s="89" t="s">
         <v>130</v>
       </c>
       <c r="L81" s="6"/>
@@ -6225,16 +6228,16 @@
     </row>
     <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="114"/>
+      <c r="B82" s="127"/>
       <c r="C82" s="65" t="str">
         <f>master!C66</f>
         <v>6-22. チャット機能 - Planモード</v>
       </c>
-      <c r="D82" s="107" t="s">
-        <v>208</v>
-      </c>
-      <c r="E82" s="108"/>
-      <c r="F82" s="109"/>
+      <c r="D82" s="123" t="s">
+        <v>205</v>
+      </c>
+      <c r="E82" s="124"/>
+      <c r="F82" s="125"/>
       <c r="G82" s="65" t="s">
         <v>41</v>
       </c>
@@ -6252,16 +6255,16 @@
     </row>
     <row r="83" spans="1:14" ht="63">
       <c r="A83" s="11"/>
-      <c r="B83" s="114"/>
+      <c r="B83" s="127"/>
       <c r="C83" s="65" t="str">
         <f>master!C67</f>
         <v>6-23. Planモードで機能追加してみましょう</v>
       </c>
-      <c r="D83" s="107" t="s">
-        <v>170</v>
-      </c>
-      <c r="E83" s="108"/>
-      <c r="F83" s="109"/>
+      <c r="D83" s="123" t="s">
+        <v>168</v>
+      </c>
+      <c r="E83" s="124"/>
+      <c r="F83" s="125"/>
       <c r="G83" s="65" t="s">
         <v>39</v>
       </c>
@@ -6279,16 +6282,16 @@
     </row>
     <row r="84" spans="1:14" ht="63">
       <c r="A84" s="11"/>
-      <c r="B84" s="114"/>
+      <c r="B84" s="127"/>
       <c r="C84" s="65" t="str">
         <f>master!C68</f>
         <v>6-24. 実行例①</v>
       </c>
-      <c r="D84" s="107" t="s">
-        <v>167</v>
-      </c>
-      <c r="E84" s="108"/>
-      <c r="F84" s="109"/>
+      <c r="D84" s="123" t="s">
+        <v>165</v>
+      </c>
+      <c r="E84" s="124"/>
+      <c r="F84" s="125"/>
       <c r="G84" s="65" t="s">
         <v>39</v>
       </c>
@@ -6306,16 +6309,16 @@
     </row>
     <row r="85" spans="1:14" ht="50.4">
       <c r="A85" s="11"/>
-      <c r="B85" s="114"/>
+      <c r="B85" s="127"/>
       <c r="C85" s="65" t="str">
         <f>master!C69</f>
         <v>6-25. 実行例②</v>
       </c>
-      <c r="D85" s="107" t="s">
-        <v>168</v>
-      </c>
-      <c r="E85" s="108"/>
-      <c r="F85" s="109"/>
+      <c r="D85" s="123" t="s">
+        <v>166</v>
+      </c>
+      <c r="E85" s="124"/>
+      <c r="F85" s="125"/>
       <c r="G85" s="65" t="s">
         <v>41</v>
       </c>
@@ -6333,16 +6336,16 @@
     </row>
     <row r="86" spans="1:14" ht="50.4">
       <c r="A86" s="11"/>
-      <c r="B86" s="114"/>
+      <c r="B86" s="127"/>
       <c r="C86" s="65" t="str">
         <f>master!C70</f>
         <v>6-26. 実行例③</v>
       </c>
-      <c r="D86" s="107" t="s">
-        <v>169</v>
-      </c>
-      <c r="E86" s="108"/>
-      <c r="F86" s="109"/>
+      <c r="D86" s="123" t="s">
+        <v>167</v>
+      </c>
+      <c r="E86" s="124"/>
+      <c r="F86" s="125"/>
       <c r="G86" s="65" t="s">
         <v>41</v>
       </c>
@@ -6360,40 +6363,40 @@
     </row>
     <row r="87" spans="1:14" ht="126">
       <c r="A87" s="11"/>
-      <c r="B87" s="114"/>
-      <c r="C87" s="120"/>
-      <c r="D87" s="121" t="s">
-        <v>186</v>
-      </c>
-      <c r="E87" s="122"/>
-      <c r="F87" s="123"/>
-      <c r="G87" s="120" t="s">
+      <c r="B87" s="127"/>
+      <c r="C87" s="85"/>
+      <c r="D87" s="116" t="s">
+        <v>184</v>
+      </c>
+      <c r="E87" s="117"/>
+      <c r="F87" s="118"/>
+      <c r="G87" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="H87" s="124"/>
-      <c r="I87" s="125" t="s">
-        <v>25</v>
-      </c>
-      <c r="J87" s="126">
+      <c r="H87" s="86"/>
+      <c r="I87" s="87" t="s">
+        <v>25</v>
+      </c>
+      <c r="J87" s="88">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="K87" s="127"/>
+      <c r="K87" s="89"/>
       <c r="L87" s="6"/>
       <c r="M87" s="6"/>
       <c r="N87" s="6"/>
     </row>
     <row r="88" spans="1:14" ht="50.4">
       <c r="A88" s="11"/>
-      <c r="B88" s="114"/>
+      <c r="B88" s="127"/>
       <c r="C88" s="65" t="str">
         <f>master!C71</f>
         <v>6-27. 実行結果①</v>
       </c>
-      <c r="D88" s="107" t="s">
-        <v>171</v>
-      </c>
-      <c r="E88" s="108"/>
-      <c r="F88" s="109"/>
+      <c r="D88" s="123" t="s">
+        <v>169</v>
+      </c>
+      <c r="E88" s="124"/>
+      <c r="F88" s="125"/>
       <c r="G88" s="65" t="s">
         <v>41</v>
       </c>
@@ -6411,16 +6414,16 @@
     </row>
     <row r="89" spans="1:14" ht="50.4">
       <c r="A89" s="11"/>
-      <c r="B89" s="114"/>
+      <c r="B89" s="127"/>
       <c r="C89" s="65" t="str">
         <f>master!C72</f>
         <v>6-28. 実行結果②</v>
       </c>
-      <c r="D89" s="107" t="s">
-        <v>172</v>
-      </c>
-      <c r="E89" s="108"/>
-      <c r="F89" s="109"/>
+      <c r="D89" s="123" t="s">
+        <v>170</v>
+      </c>
+      <c r="E89" s="124"/>
+      <c r="F89" s="125"/>
       <c r="G89" s="65" t="s">
         <v>41</v>
       </c>
@@ -6438,16 +6441,16 @@
     </row>
     <row r="90" spans="1:14" ht="113.4">
       <c r="A90" s="11"/>
-      <c r="B90" s="115"/>
+      <c r="B90" s="128"/>
       <c r="C90" s="65" t="str">
         <f>master!C73</f>
         <v>6-29. Planモード＆Agentモードまとめ</v>
       </c>
-      <c r="D90" s="107" t="s">
-        <v>173</v>
-      </c>
-      <c r="E90" s="108"/>
-      <c r="F90" s="109"/>
+      <c r="D90" s="123" t="s">
+        <v>171</v>
+      </c>
+      <c r="E90" s="124"/>
+      <c r="F90" s="125"/>
       <c r="G90" s="65" t="s">
         <v>43</v>
       </c>
@@ -6465,58 +6468,58 @@
     </row>
     <row r="91" spans="1:14" ht="102" customHeight="1">
       <c r="A91" s="11"/>
-      <c r="B91" s="113" t="str">
+      <c r="B91" s="126" t="str">
         <f>master!B74</f>
         <v>成果物のプレゼン</v>
       </c>
-      <c r="C91" s="120" t="str">
+      <c r="C91" s="85" t="str">
         <f>master!C74</f>
         <v>開発した成果物のプレゼン（グループ）</v>
       </c>
-      <c r="D91" s="121" t="s">
-        <v>203</v>
-      </c>
-      <c r="E91" s="122"/>
-      <c r="F91" s="123"/>
-      <c r="G91" s="120" t="s">
+      <c r="D91" s="116" t="s">
+        <v>200</v>
+      </c>
+      <c r="E91" s="117"/>
+      <c r="F91" s="118"/>
+      <c r="G91" s="85" t="s">
         <v>47</v>
       </c>
-      <c r="H91" s="124"/>
-      <c r="I91" s="125" t="s">
-        <v>25</v>
-      </c>
-      <c r="J91" s="126">
+      <c r="H91" s="86"/>
+      <c r="I91" s="87" t="s">
+        <v>25</v>
+      </c>
+      <c r="J91" s="88">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K91" s="127"/>
+      <c r="K91" s="89"/>
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
       <c r="N91" s="6"/>
     </row>
     <row r="92" spans="1:14" ht="88.2">
       <c r="A92" s="11"/>
-      <c r="B92" s="115"/>
-      <c r="C92" s="120" t="str">
+      <c r="B92" s="128"/>
+      <c r="C92" s="85" t="str">
         <f>master!C75</f>
         <v>開発した成果物のプレゼン（全体）</v>
       </c>
-      <c r="D92" s="121" t="s">
-        <v>198</v>
-      </c>
-      <c r="E92" s="122"/>
-      <c r="F92" s="123"/>
-      <c r="G92" s="120" t="s">
+      <c r="D92" s="116" t="s">
+        <v>195</v>
+      </c>
+      <c r="E92" s="117"/>
+      <c r="F92" s="118"/>
+      <c r="G92" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="H92" s="124"/>
-      <c r="I92" s="125" t="s">
+      <c r="H92" s="86"/>
+      <c r="I92" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="J92" s="126" t="s">
+      <c r="J92" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="K92" s="127" t="s">
-        <v>202</v>
+      <c r="K92" s="89" t="s">
+        <v>199</v>
       </c>
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
@@ -6528,40 +6531,38 @@
     <row r="94" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="B56:B90"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
     <mergeCell ref="D92:F92"/>
     <mergeCell ref="B91:B92"/>
     <mergeCell ref="D80:F80"/>
     <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D91:F91"/>
     <mergeCell ref="D90:F90"/>
     <mergeCell ref="D89:F89"/>
     <mergeCell ref="D79:F79"/>
     <mergeCell ref="D50:F50"/>
     <mergeCell ref="D52:F52"/>
     <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D68:F68"/>
     <mergeCell ref="B37:B43"/>
     <mergeCell ref="D60:F60"/>
     <mergeCell ref="D78:F78"/>
     <mergeCell ref="D64:F64"/>
     <mergeCell ref="D66:F66"/>
     <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D85:F85"/>
     <mergeCell ref="D71:F71"/>
     <mergeCell ref="D73:F73"/>
     <mergeCell ref="D74:F74"/>
@@ -6569,26 +6570,28 @@
     <mergeCell ref="D76:F76"/>
     <mergeCell ref="D77:F77"/>
     <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="B56:B90"/>
     <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D54:F54"/>
     <mergeCell ref="D56:F56"/>
     <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D34:F34"/>
     <mergeCell ref="D46:F46"/>
     <mergeCell ref="D53:F53"/>
     <mergeCell ref="B44:B55"/>
     <mergeCell ref="D44:F44"/>
     <mergeCell ref="D45:F45"/>
     <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D54:F54"/>
     <mergeCell ref="D42:F42"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="D27:F27"/>
@@ -6683,7 +6686,7 @@
       </c>
     </row>
     <row r="5" spans="2:3">
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="84" t="s">
         <v>57</v>
       </c>
       <c r="C5" t="s">
@@ -6701,7 +6704,7 @@
       </c>
     </row>
     <row r="8" spans="2:3">
-      <c r="B8" s="116" t="s">
+      <c r="B8" s="84" t="s">
         <v>103</v>
       </c>
       <c r="C8" t="s">
@@ -6729,8 +6732,8 @@
       </c>
     </row>
     <row r="13" spans="2:3">
-      <c r="B13" s="116" t="s">
-        <v>201</v>
+      <c r="B13" s="84" t="s">
+        <v>198</v>
       </c>
       <c r="C13" t="s">
         <v>63</v>
@@ -6807,7 +6810,7 @@
       </c>
     </row>
     <row r="28" spans="2:3">
-      <c r="B28" s="116" t="s">
+      <c r="B28" s="84" t="s">
         <v>81</v>
       </c>
       <c r="C28" t="s">
@@ -6845,7 +6848,7 @@
       </c>
     </row>
     <row r="35" spans="2:3">
-      <c r="B35" s="116" t="s">
+      <c r="B35" s="84" t="s">
         <v>80</v>
       </c>
       <c r="C35" t="s">
@@ -6898,7 +6901,7 @@
       </c>
     </row>
     <row r="45" spans="2:3">
-      <c r="B45" s="116" t="s">
+      <c r="B45" s="84" t="s">
         <v>84</v>
       </c>
       <c r="C45" t="s">
@@ -7050,12 +7053,12 @@
         <v>132</v>
       </c>
       <c r="C74" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="75" spans="2:3">
       <c r="C75" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/IG/7日版/AI Native-生成AI_IG.xlsx
+++ b/IG/7日版/AI Native-生成AI_IG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B871136D-AF45-44BC-BB83-4FA66C07F3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3D6FD9-0D6B-4144-A7AC-ED8B039FDDBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール（1日）" sheetId="33" r:id="rId1"/>
@@ -1188,62 +1188,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>以下の内容を実施する。
-■講師による自己紹介 (3分)
-　・氏名
-　・経歴
-　・その他
-　※生成AIを使った、自己紹介文を読む（１分）</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>コウシ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ジコ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ショウカイ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>プン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ケイレキ</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="55" eb="59">
-      <t>ジコショウカイ</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="61" eb="62">
-      <t>ヨ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>以下の内容を説明する。
 ■Askモードのまとめ
 　・実際のファイル編集などを伴わずに、安全に内容の確認や分析を行うことができる。
@@ -1666,61 +1610,6 @@
     </rPh>
     <rPh sb="26" eb="27">
       <t>ヨ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>以下の内容を実施してもらう。
-■グループ内での自己紹介
-　1. 生成AIを使って自己紹介文を作成する（5分）
-　　・部署
-　　・氏名
-　　・その他の特徴
-　2. 生成AIで作った自己紹介文を読む（5分*人数）</t>
-    <rPh sb="20" eb="21">
-      <t>ナイ</t>
-    </rPh>
-    <rPh sb="23" eb="27">
-      <t>ジコショウカイ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="40" eb="44">
-      <t>ジコショウカイ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>フン</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>ブショ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>シメイ</t>
-    </rPh>
-    <rPh sb="72" eb="73">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="74" eb="76">
-      <t>トクチョウ</t>
-    </rPh>
-    <rPh sb="86" eb="87">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="95" eb="96">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="101" eb="103">
-      <t>ニンズウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -2354,6 +2243,127 @@
   <si>
     <t>以下の内容を説明する。
 ■mdファイルのプレビューの方法</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を実施する。
+■講師による自己紹介 (3分)
+　・氏名
+　・経歴
+　・その他
+　※生成AIを使った、自己紹介文を読む（1分）</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウシ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジコ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>プン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ケイレキ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="55" eb="59">
+      <t>ジコショウカイ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">以下の内容を実施してもらう。
+■グループ内での自己紹介（5分*人数）
+　1. 生成AIを使って自己紹介文を作成する（2分）
+　　・部署
+　　・氏名
+　　・その他の特徴
+　2. 生成AIで作った自己紹介文を読む（2分）
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※「1分以内」や「簡潔に」といった、分量や長さを具体的に指定するキーワードを指定した方が良いかもしれません。</t>
+    </r>
+    <rPh sb="20" eb="21">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>ジコショウカイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="50" eb="54">
+      <t>ジコショウカイ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>ブショ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="82" eb="83">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>ツク</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -2923,9 +2933,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3091,6 +3098,60 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3100,59 +3161,8 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3526,15 +3536,15 @@
   <sheetData>
     <row r="2" spans="1:8" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="92" t="str">
+      <c r="B2" s="91" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!B1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-生成AI_IG」</v>
       </c>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
     </row>
     <row r="3" spans="1:8" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -3547,10 +3557,10 @@
     </row>
     <row r="4" spans="1:8" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="93" t="s">
+      <c r="B4" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="94"/>
+      <c r="C4" s="93"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -3558,18 +3568,18 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="95"/>
-      <c r="C5" s="96"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="95"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
     <row r="7" spans="1:8" ht="16.2">
-      <c r="B7" s="97" t="s">
+      <c r="B7" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="97"/>
+      <c r="C7" s="96"/>
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="24"/>
@@ -3585,7 +3595,7 @@
       <c r="B10" s="17">
         <v>0.39583333333333331</v>
       </c>
-      <c r="C10" s="76" t="s">
+      <c r="C10" s="75" t="s">
         <v>3</v>
       </c>
       <c r="G10" s="14" t="s">
@@ -3594,10 +3604,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="39"/>
-      <c r="B11" s="63">
+      <c r="B11" s="62">
         <v>0.40625</v>
       </c>
-      <c r="C11" s="73" t="str">
+      <c r="C11" s="72" t="str">
         <f>master!B3</f>
         <v>自己紹介</v>
       </c>
@@ -3607,16 +3617,16 @@
       <c r="A12" s="37">
         <v>0.41666666666666669</v>
       </c>
-      <c r="B12" s="70"/>
-      <c r="C12" s="74"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="73"/>
       <c r="G12" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="38"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="75"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="74"/>
       <c r="F13" s="23"/>
       <c r="H13" s="6"/>
     </row>
@@ -3625,51 +3635,51 @@
       <c r="B14" s="37">
         <v>0.4375</v>
       </c>
-      <c r="C14" s="73" t="str">
+      <c r="C14" s="72" t="str">
         <f>master!B5</f>
         <v>モジュール1：オリエンテーションとマインドセット変革</v>
       </c>
-      <c r="F14" s="91"/>
+      <c r="F14" s="90"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="39"/>
-      <c r="B15" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="74"/>
-      <c r="F15" s="91"/>
+      <c r="B15" s="37">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="C15" s="71" t="str">
+        <f>master!B8</f>
+        <v>モジュール2：AI・LLMの基礎理解</v>
+      </c>
+      <c r="F15" s="90"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="37">
         <v>0.45833333333333331</v>
       </c>
-      <c r="B16" s="41"/>
+      <c r="B16" s="62">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="C16" s="72" t="str">
-        <f>master!B8</f>
-        <v>モジュール2：AI・LLMの基礎理解</v>
-      </c>
-      <c r="F16" s="91"/>
+        <f>master!B13</f>
+        <v>モジュール3：NTTデータが目指すAIビジネス（Vision）</v>
+      </c>
+      <c r="F16" s="90"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="38"/>
-      <c r="B17" s="40">
-        <v>0.46875</v>
-      </c>
-      <c r="C17" s="73" t="str">
-        <f>master!B13</f>
-        <v>モジュール3：NTTデータが目指すAIビジネス（Vision）</v>
-      </c>
-      <c r="F17" s="91"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="73"/>
+      <c r="F17" s="90"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="38"/>
       <c r="B18" s="41"/>
-      <c r="C18" s="75"/>
-      <c r="F18" s="91"/>
+      <c r="C18" s="74"/>
+      <c r="F18" s="90"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8">
@@ -3677,27 +3687,31 @@
       <c r="B19" s="40">
         <v>0.48958333333333331</v>
       </c>
-      <c r="C19" s="73" t="str">
+      <c r="C19" s="72" t="str">
         <f>master!B28</f>
         <v>モジュール4：プロンプトエンジニアリング</v>
       </c>
-      <c r="F19" s="91"/>
+      <c r="F19" s="90"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="62">
+      <c r="A20" s="61">
         <v>0.5</v>
       </c>
       <c r="B20" s="42"/>
       <c r="C20" s="74"/>
-      <c r="F20" s="91"/>
+      <c r="F20" s="90"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="57"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="75"/>
-      <c r="F21" s="91"/>
+      <c r="A21" s="56"/>
+      <c r="B21" s="17">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="C21" s="128" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" s="90"/>
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8">
@@ -3705,7 +3719,7 @@
       <c r="B22" s="38">
         <v>0.52083333333333337</v>
       </c>
-      <c r="C22" s="77" t="s">
+      <c r="C22" s="76" t="s">
         <v>1</v>
       </c>
       <c r="F22" s="22"/>
@@ -3717,7 +3731,7 @@
       <c r="B23" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="78"/>
+      <c r="C23" s="77"/>
       <c r="F23" s="22"/>
       <c r="G23" s="10"/>
       <c r="H23" s="6"/>
@@ -3729,7 +3743,7 @@
       <c r="B24" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="78"/>
+      <c r="C24" s="77"/>
       <c r="F24" s="22"/>
       <c r="G24" s="10"/>
       <c r="H24" s="6"/>
@@ -3739,7 +3753,7 @@
       <c r="B25" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="79"/>
+      <c r="C25" s="78"/>
       <c r="F25" s="22"/>
       <c r="G25" s="10"/>
       <c r="H25" s="6"/>
@@ -3749,19 +3763,19 @@
       <c r="B26" s="40">
         <v>0.5625</v>
       </c>
-      <c r="C26" s="59" t="str">
+      <c r="C26" s="58" t="str">
         <f>master!B35</f>
         <v>モジュール5：ハンズオン（ChatGPT）</v>
       </c>
-      <c r="F26" s="91"/>
+      <c r="F26" s="90"/>
       <c r="G26" s="14"/>
       <c r="H26" s="6"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="39"/>
       <c r="B27" s="42"/>
-      <c r="C27" s="59"/>
-      <c r="F27" s="91"/>
+      <c r="C27" s="58"/>
+      <c r="F27" s="90"/>
       <c r="G27" s="14"/>
       <c r="H27" s="6"/>
     </row>
@@ -3770,17 +3784,17 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="B28" s="42"/>
-      <c r="C28" s="59"/>
-      <c r="F28" s="91"/>
+      <c r="C28" s="58"/>
+      <c r="F28" s="90"/>
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="38"/>
       <c r="B29" s="41"/>
-      <c r="C29" s="60"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="91"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="90"/>
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8">
@@ -3788,60 +3802,60 @@
       <c r="B30" s="42">
         <v>0.60416666666666663</v>
       </c>
-      <c r="C30" s="59" t="str">
+      <c r="C30" s="58" t="str">
         <f>master!B45</f>
         <v>モジュール6：ハンズオン（ GitHub Copilot ）</v>
       </c>
-      <c r="D30" s="56"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="91"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="90"/>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="39"/>
       <c r="B31" s="42"/>
-      <c r="C31" s="59"/>
-      <c r="D31" s="56"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="55"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="91"/>
+      <c r="F31" s="90"/>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="62">
+      <c r="A32" s="61">
         <v>0.625</v>
       </c>
       <c r="B32" s="42"/>
-      <c r="C32" s="59"/>
-      <c r="D32" s="56"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="55"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="91"/>
+      <c r="F32" s="90"/>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="57"/>
+      <c r="A33" s="56"/>
       <c r="B33" s="42"/>
-      <c r="C33" s="59"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="91"/>
+      <c r="C33" s="58"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="90"/>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="57"/>
+      <c r="A34" s="56"/>
       <c r="B34" s="42"/>
-      <c r="C34" s="59"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="91"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="55"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="90"/>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="39"/>
       <c r="B35" s="42"/>
-      <c r="C35" s="59"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="53"/>
-      <c r="F35" s="91"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="55"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="90"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8">
@@ -3849,37 +3863,37 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="B36" s="42"/>
-      <c r="C36" s="59"/>
-      <c r="D36" s="56"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="55"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="91"/>
+      <c r="F36" s="90"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="38"/>
       <c r="B37" s="42"/>
-      <c r="C37" s="59"/>
-      <c r="D37" s="56"/>
+      <c r="C37" s="58"/>
+      <c r="D37" s="55"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="91"/>
+      <c r="F37" s="90"/>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="38"/>
       <c r="B38" s="42"/>
-      <c r="C38" s="59"/>
-      <c r="D38" s="56"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="55"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="91"/>
+      <c r="F38" s="90"/>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="38"/>
       <c r="B39" s="42"/>
-      <c r="C39" s="59"/>
-      <c r="D39" s="56"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="55"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="91"/>
+      <c r="F39" s="90"/>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8">
@@ -3887,10 +3901,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="B40" s="41"/>
-      <c r="C40" s="60"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="53"/>
-      <c r="F40" s="91"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="90"/>
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8">
@@ -3898,34 +3912,34 @@
       <c r="B41" s="40">
         <v>0.71875</v>
       </c>
-      <c r="C41" s="59" t="str">
+      <c r="C41" s="58" t="str">
         <f>master!B74</f>
         <v>成果物のプレゼン</v>
       </c>
-      <c r="D41" s="58"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="91"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="90"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="42"/>
       <c r="B42" s="41"/>
-      <c r="C42" s="60"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="54"/>
-      <c r="F42" s="91"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="55"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="90"/>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1">
       <c r="A43" s="41"/>
-      <c r="B43" s="81">
+      <c r="B43" s="80">
         <v>0.73958333333333337</v>
       </c>
-      <c r="C43" s="80" t="s">
+      <c r="C43" s="79" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="57"/>
-      <c r="E43" s="55"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="54"/>
       <c r="F43" s="22"/>
       <c r="G43" s="14" t="s">
         <v>12</v>
@@ -4000,10 +4014,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="103" t="s">
+      <c r="B4" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="103"/>
+      <c r="C4" s="102"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -4014,16 +4028,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="104"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -4038,10 +4052,10 @@
       <c r="C7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="105" t="s">
+      <c r="D7" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="105"/>
+      <c r="E7" s="104"/>
       <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
@@ -4073,46 +4087,46 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="10"/>
-      <c r="B10" s="99"/>
-      <c r="C10" s="99" t="s">
+      <c r="B10" s="98"/>
+      <c r="C10" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="99" t="s">
+      <c r="D10" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99" t="s">
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="106" t="s">
+      <c r="H10" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="98" t="s">
+      <c r="I10" s="97" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="98"/>
-      <c r="K10" s="98" t="s">
+      <c r="J10" s="97"/>
+      <c r="K10" s="97" t="s">
         <v>31</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="107"/>
+      <c r="B11" s="98"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="106"/>
       <c r="I11" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J11" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="99"/>
+      <c r="K11" s="98"/>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="63">
@@ -4121,19 +4135,19 @@
       <c r="C12" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="100" t="s">
+      <c r="D12" s="99" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="101"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="83" t="s">
+      <c r="E12" s="100"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="82" t="s">
         <v>50</v>
       </c>
       <c r="H12" s="20"/>
       <c r="I12" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="J12" s="61">
+      <c r="J12" s="60">
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="K12" s="20"/>
@@ -4224,12 +4238,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="103" t="s">
+      <c r="B4" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -4240,18 +4254,18 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="108" t="s">
-        <v>202</v>
-      </c>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
+      <c r="B5" s="125" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
       <c r="L5" s="29"/>
       <c r="M5" s="30"/>
     </row>
@@ -4271,10 +4285,10 @@
       <c r="C7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="105" t="s">
+      <c r="D7" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="105"/>
+      <c r="E7" s="104"/>
       <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
@@ -4292,8 +4306,8 @@
       <c r="B8" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="64" t="s">
-        <v>201</v>
+      <c r="C8" s="63" t="s">
+        <v>198</v>
       </c>
       <c r="D8" s="45" t="s">
         <v>20</v>
@@ -4312,28 +4326,28 @@
     </row>
     <row r="10" spans="1:14" ht="24" customHeight="1">
       <c r="A10" s="10"/>
-      <c r="B10" s="99" t="s">
+      <c r="B10" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="99" t="s">
+      <c r="C10" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="99" t="s">
+      <c r="D10" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99" t="s">
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="98" t="s">
+      <c r="H10" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="109" t="s">
+      <c r="I10" s="126" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="110"/>
-      <c r="K10" s="98" t="s">
+      <c r="J10" s="127"/>
+      <c r="K10" s="97" t="s">
         <v>33</v>
       </c>
       <c r="L10" s="6"/>
@@ -4342,27 +4356,27 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="10"/>
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="98"/>
+      <c r="B11" s="98"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="97"/>
       <c r="I11" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J11" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="99"/>
+      <c r="K11" s="98"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
     </row>
     <row r="12" spans="1:14" ht="88.2">
       <c r="A12" s="10"/>
-      <c r="B12" s="111" t="str">
+      <c r="B12" s="123" t="str">
         <f>master!B3</f>
         <v>自己紹介</v>
       </c>
@@ -4370,11 +4384,11 @@
         <f>master!C3</f>
         <v>講師の自己紹介</v>
       </c>
-      <c r="D12" s="113" t="s">
-        <v>151</v>
-      </c>
-      <c r="E12" s="114"/>
-      <c r="F12" s="115"/>
+      <c r="D12" s="119" t="s">
+        <v>208</v>
+      </c>
+      <c r="E12" s="120"/>
+      <c r="F12" s="121"/>
       <c r="G12" s="51" t="s">
         <v>49</v>
       </c>
@@ -4390,30 +4404,30 @@
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
     </row>
-    <row r="13" spans="1:14" ht="100.8">
+    <row r="13" spans="1:14" ht="126">
       <c r="A13" s="10"/>
-      <c r="B13" s="112"/>
-      <c r="C13" s="85" t="str">
+      <c r="B13" s="124"/>
+      <c r="C13" s="84" t="str">
         <f>master!C4</f>
         <v>受講生の自己紹介</v>
       </c>
-      <c r="D13" s="116" t="s">
-        <v>177</v>
-      </c>
-      <c r="E13" s="117"/>
-      <c r="F13" s="118"/>
-      <c r="G13" s="85" t="s">
-        <v>152</v>
-      </c>
-      <c r="H13" s="86"/>
-      <c r="I13" s="87" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="88">
+      <c r="D13" s="110" t="s">
+        <v>210</v>
+      </c>
+      <c r="E13" s="111"/>
+      <c r="F13" s="112"/>
+      <c r="G13" s="84" t="s">
+        <v>209</v>
+      </c>
+      <c r="H13" s="85"/>
+      <c r="I13" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="87">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K13" s="89" t="s">
-        <v>172</v>
+      <c r="K13" s="88" t="s">
+        <v>170</v>
       </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
@@ -4421,7 +4435,7 @@
     </row>
     <row r="14" spans="1:14" ht="163.80000000000001">
       <c r="A14" s="11"/>
-      <c r="B14" s="119" t="str">
+      <c r="B14" s="122" t="str">
         <f>master!B5</f>
         <v>モジュール1：オリエンテーションとマインドセット変革</v>
       </c>
@@ -4429,11 +4443,11 @@
         <f>master!C5</f>
         <v>1-1. 研修概要</v>
       </c>
-      <c r="D14" s="113" t="s">
+      <c r="D14" s="119" t="s">
         <v>136</v>
       </c>
-      <c r="E14" s="114"/>
-      <c r="F14" s="115"/>
+      <c r="E14" s="120"/>
+      <c r="F14" s="121"/>
       <c r="G14" s="51" t="s">
         <v>104</v>
       </c>
@@ -4451,16 +4465,16 @@
     </row>
     <row r="15" spans="1:14" ht="100.8">
       <c r="A15" s="11"/>
-      <c r="B15" s="119"/>
+      <c r="B15" s="122"/>
       <c r="C15" s="51" t="str">
         <f>master!C6</f>
         <v>1-2. 背景・目的</v>
       </c>
-      <c r="D15" s="113" t="s">
+      <c r="D15" s="119" t="s">
         <v>135</v>
       </c>
-      <c r="E15" s="114"/>
-      <c r="F15" s="115"/>
+      <c r="E15" s="120"/>
+      <c r="F15" s="121"/>
       <c r="G15" s="51" t="s">
         <v>47</v>
       </c>
@@ -4478,16 +4492,16 @@
     </row>
     <row r="16" spans="1:14" ht="214.2">
       <c r="A16" s="11"/>
-      <c r="B16" s="119"/>
+      <c r="B16" s="122"/>
       <c r="C16" s="51" t="str">
         <f>master!C7</f>
         <v>1-3. 研修ゴールと獲得可能な経験背景・目的</v>
       </c>
-      <c r="D16" s="113" t="s">
-        <v>178</v>
-      </c>
-      <c r="E16" s="114"/>
-      <c r="F16" s="115"/>
+      <c r="D16" s="119" t="s">
+        <v>175</v>
+      </c>
+      <c r="E16" s="120"/>
+      <c r="F16" s="121"/>
       <c r="G16" s="51" t="s">
         <v>137</v>
       </c>
@@ -4505,7 +4519,7 @@
     </row>
     <row r="17" spans="1:14" ht="88.2">
       <c r="A17" s="11"/>
-      <c r="B17" s="120" t="str">
+      <c r="B17" s="115" t="str">
         <f>master!B8</f>
         <v>モジュール2：AI・LLMの基礎理解</v>
       </c>
@@ -4513,11 +4527,11 @@
         <f>master!C8</f>
         <v>2-1. 生成AI（Generative AI）とは？</v>
       </c>
-      <c r="D17" s="113" t="s">
+      <c r="D17" s="119" t="s">
         <v>138</v>
       </c>
-      <c r="E17" s="114"/>
-      <c r="F17" s="115"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="121"/>
       <c r="G17" s="51" t="s">
         <v>45</v>
       </c>
@@ -4535,16 +4549,16 @@
     </row>
     <row r="18" spans="1:14" ht="113.4">
       <c r="A18" s="11"/>
-      <c r="B18" s="121"/>
+      <c r="B18" s="116"/>
       <c r="C18" s="51" t="str">
         <f>master!C9</f>
         <v>2-2. AIの変化</v>
       </c>
-      <c r="D18" s="113" t="s">
+      <c r="D18" s="119" t="s">
         <v>139</v>
       </c>
-      <c r="E18" s="114"/>
-      <c r="F18" s="115"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="121"/>
       <c r="G18" s="51" t="s">
         <v>43</v>
       </c>
@@ -4562,16 +4576,16 @@
     </row>
     <row r="19" spans="1:14" ht="113.4">
       <c r="A19" s="11"/>
-      <c r="B19" s="121"/>
+      <c r="B19" s="116"/>
       <c r="C19" s="51" t="str">
         <f>master!C10</f>
         <v>2-3. LLM（大規模言語モデル）の仕組み</v>
       </c>
-      <c r="D19" s="113" t="s">
+      <c r="D19" s="119" t="s">
         <v>140</v>
       </c>
-      <c r="E19" s="114"/>
-      <c r="F19" s="115"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="121"/>
       <c r="G19" s="51" t="s">
         <v>43</v>
       </c>
@@ -4589,16 +4603,16 @@
     </row>
     <row r="20" spans="1:14" ht="126">
       <c r="A20" s="11"/>
-      <c r="B20" s="121"/>
+      <c r="B20" s="116"/>
       <c r="C20" s="51" t="str">
         <f>master!C11</f>
         <v>2-4. 生成AIの「苦手なこと」（弱み）</v>
       </c>
-      <c r="D20" s="113" t="s">
+      <c r="D20" s="119" t="s">
         <v>141</v>
       </c>
-      <c r="E20" s="114"/>
-      <c r="F20" s="115"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="121"/>
       <c r="G20" s="51" t="s">
         <v>44</v>
       </c>
@@ -4616,16 +4630,16 @@
     </row>
     <row r="21" spans="1:14" ht="239.4">
       <c r="A21" s="11"/>
-      <c r="B21" s="122"/>
+      <c r="B21" s="117"/>
       <c r="C21" s="51" t="str">
         <f>master!C12</f>
         <v>2-5. 生成AIを使う心得８条</v>
       </c>
-      <c r="D21" s="113" t="s">
-        <v>179</v>
-      </c>
-      <c r="E21" s="114"/>
-      <c r="F21" s="115"/>
+      <c r="D21" s="119" t="s">
+        <v>176</v>
+      </c>
+      <c r="E21" s="120"/>
+      <c r="F21" s="121"/>
       <c r="G21" s="51" t="s">
         <v>142</v>
       </c>
@@ -4643,7 +4657,7 @@
     </row>
     <row r="22" spans="1:14" ht="25.2">
       <c r="A22" s="11"/>
-      <c r="B22" s="119" t="str">
+      <c r="B22" s="122" t="str">
         <f>master!B13</f>
         <v>モジュール3：NTTデータが目指すAIビジネス（Vision）</v>
       </c>
@@ -4651,9 +4665,9 @@
         <f>master!C13</f>
         <v>3-1. 本モジュールで学ぶこと①</v>
       </c>
-      <c r="D22" s="113"/>
-      <c r="E22" s="114"/>
-      <c r="F22" s="115"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="120"/>
+      <c r="F22" s="121"/>
       <c r="G22" s="51" t="s">
         <v>46</v>
       </c>
@@ -4671,14 +4685,14 @@
     </row>
     <row r="23" spans="1:14" ht="25.2">
       <c r="A23" s="11"/>
-      <c r="B23" s="119"/>
+      <c r="B23" s="122"/>
       <c r="C23" s="51" t="str">
         <f>master!C14</f>
         <v>3-2. NTTデータのAI戦略：Quality Growthとは</v>
       </c>
-      <c r="D23" s="113"/>
-      <c r="E23" s="114"/>
-      <c r="F23" s="115"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="120"/>
+      <c r="F23" s="121"/>
       <c r="G23" s="51" t="s">
         <v>46</v>
       </c>
@@ -4696,14 +4710,14 @@
     </row>
     <row r="24" spans="1:14" ht="25.2">
       <c r="A24" s="11"/>
-      <c r="B24" s="119"/>
+      <c r="B24" s="122"/>
       <c r="C24" s="51" t="str">
         <f>master!C15</f>
         <v>3-3. なぜ今、AIが重要なのか</v>
       </c>
-      <c r="D24" s="113"/>
-      <c r="E24" s="114"/>
-      <c r="F24" s="115"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="120"/>
+      <c r="F24" s="121"/>
       <c r="G24" s="51" t="s">
         <v>46</v>
       </c>
@@ -4721,14 +4735,14 @@
     </row>
     <row r="25" spans="1:14" ht="25.2">
       <c r="A25" s="11"/>
-      <c r="B25" s="119"/>
+      <c r="B25" s="122"/>
       <c r="C25" s="51" t="str">
         <f>master!C16</f>
         <v>3-4. 生成AIの進化：今、どこにいるか</v>
       </c>
-      <c r="D25" s="113"/>
-      <c r="E25" s="114"/>
-      <c r="F25" s="115"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="120"/>
+      <c r="F25" s="121"/>
       <c r="G25" s="51" t="s">
         <v>46</v>
       </c>
@@ -4746,14 +4760,14 @@
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
       <c r="A26" s="11"/>
-      <c r="B26" s="119"/>
+      <c r="B26" s="122"/>
       <c r="C26" s="51" t="str">
         <f>master!C17</f>
         <v>3-5. 本モジュールで学ぶこと②</v>
       </c>
-      <c r="D26" s="113"/>
-      <c r="E26" s="114"/>
-      <c r="F26" s="115"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="120"/>
+      <c r="F26" s="121"/>
       <c r="G26" s="51" t="s">
         <v>37</v>
       </c>
@@ -4771,16 +4785,16 @@
     </row>
     <row r="27" spans="1:14" ht="63">
       <c r="A27" s="11"/>
-      <c r="B27" s="119"/>
+      <c r="B27" s="122"/>
       <c r="C27" s="51" t="str">
         <f>master!C18</f>
         <v>3-6. エージェントAI（Agentic AI）とは何か</v>
       </c>
-      <c r="D27" s="113" t="s">
-        <v>180</v>
-      </c>
-      <c r="E27" s="114"/>
-      <c r="F27" s="115"/>
+      <c r="D27" s="119" t="s">
+        <v>177</v>
+      </c>
+      <c r="E27" s="120"/>
+      <c r="F27" s="121"/>
       <c r="G27" s="51" t="s">
         <v>39</v>
       </c>
@@ -4798,16 +4812,16 @@
     </row>
     <row r="28" spans="1:14" ht="63">
       <c r="A28" s="11"/>
-      <c r="B28" s="119"/>
+      <c r="B28" s="122"/>
       <c r="C28" s="51" t="str">
         <f>master!C19</f>
         <v>3-7. エージェントの処理</v>
       </c>
-      <c r="D28" s="113" t="s">
+      <c r="D28" s="119" t="s">
         <v>143</v>
       </c>
-      <c r="E28" s="114"/>
-      <c r="F28" s="115"/>
+      <c r="E28" s="120"/>
+      <c r="F28" s="121"/>
       <c r="G28" s="51" t="s">
         <v>39</v>
       </c>
@@ -4825,14 +4839,14 @@
     </row>
     <row r="29" spans="1:14" ht="37.799999999999997">
       <c r="A29" s="11"/>
-      <c r="B29" s="119"/>
+      <c r="B29" s="122"/>
       <c r="C29" s="51" t="str">
         <f>master!C20</f>
         <v>3-8. 本モジュールで学ぶこと③</v>
       </c>
-      <c r="D29" s="113"/>
-      <c r="E29" s="114"/>
-      <c r="F29" s="115"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="120"/>
+      <c r="F29" s="121"/>
       <c r="G29" s="51" t="s">
         <v>40</v>
       </c>
@@ -4850,14 +4864,14 @@
     </row>
     <row r="30" spans="1:14" ht="37.799999999999997">
       <c r="A30" s="11"/>
-      <c r="B30" s="119"/>
+      <c r="B30" s="122"/>
       <c r="C30" s="51" t="str">
         <f>master!C21</f>
         <v>3-9. NTTデータが描く未来：Smart AI Agent®</v>
       </c>
-      <c r="D30" s="113"/>
-      <c r="E30" s="114"/>
-      <c r="F30" s="115"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="120"/>
+      <c r="F30" s="121"/>
       <c r="G30" s="51" t="s">
         <v>40</v>
       </c>
@@ -4875,14 +4889,14 @@
     </row>
     <row r="31" spans="1:14" ht="37.799999999999997">
       <c r="A31" s="11"/>
-      <c r="B31" s="119"/>
+      <c r="B31" s="122"/>
       <c r="C31" s="51" t="str">
         <f>master!C22</f>
         <v>3-10. AIの強みを生かした業務変革の進め方</v>
       </c>
-      <c r="D31" s="113"/>
-      <c r="E31" s="114"/>
-      <c r="F31" s="115"/>
+      <c r="D31" s="119"/>
+      <c r="E31" s="120"/>
+      <c r="F31" s="121"/>
       <c r="G31" s="51" t="s">
         <v>40</v>
       </c>
@@ -4900,14 +4914,14 @@
     </row>
     <row r="32" spans="1:14" ht="37.799999999999997">
       <c r="A32" s="11"/>
-      <c r="B32" s="119"/>
+      <c r="B32" s="122"/>
       <c r="C32" s="51" t="str">
         <f>master!C23</f>
         <v>3-11. AIの強みを生かすポイント：人とAIとの役割分担</v>
       </c>
-      <c r="D32" s="113"/>
-      <c r="E32" s="114"/>
-      <c r="F32" s="115"/>
+      <c r="D32" s="119"/>
+      <c r="E32" s="120"/>
+      <c r="F32" s="121"/>
       <c r="G32" s="51" t="s">
         <v>40</v>
       </c>
@@ -4925,14 +4939,14 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="119"/>
+      <c r="B33" s="122"/>
       <c r="C33" s="51" t="str">
         <f>master!C24</f>
         <v>3-12. AIの強みを生かすポイント：プロセス自体をAI前提で再設計</v>
       </c>
-      <c r="D33" s="113"/>
-      <c r="E33" s="114"/>
-      <c r="F33" s="115"/>
+      <c r="D33" s="119"/>
+      <c r="E33" s="120"/>
+      <c r="F33" s="121"/>
       <c r="G33" s="51" t="s">
         <v>40</v>
       </c>
@@ -4950,14 +4964,14 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="119"/>
+      <c r="B34" s="122"/>
       <c r="C34" s="51" t="str">
         <f>master!C25</f>
         <v>3-13. JALカード様 -  AIバーチャル顧客を活用したマーケティング高度化</v>
       </c>
-      <c r="D34" s="113"/>
-      <c r="E34" s="114"/>
-      <c r="F34" s="115"/>
+      <c r="D34" s="119"/>
+      <c r="E34" s="120"/>
+      <c r="F34" s="121"/>
       <c r="G34" s="51" t="s">
         <v>40</v>
       </c>
@@ -4975,14 +4989,14 @@
     </row>
     <row r="35" spans="1:14" ht="37.799999999999997">
       <c r="A35" s="11"/>
-      <c r="B35" s="119"/>
+      <c r="B35" s="122"/>
       <c r="C35" s="51" t="str">
         <f>master!C26</f>
         <v>3-14. 大手メディアサービス会社 - AI-BPOによるオペレーション変革</v>
       </c>
-      <c r="D35" s="113"/>
-      <c r="E35" s="114"/>
-      <c r="F35" s="115"/>
+      <c r="D35" s="119"/>
+      <c r="E35" s="120"/>
+      <c r="F35" s="121"/>
       <c r="G35" s="51" t="s">
         <v>40</v>
       </c>
@@ -5000,14 +5014,14 @@
     </row>
     <row r="36" spans="1:14" ht="37.799999999999997">
       <c r="A36" s="11"/>
-      <c r="B36" s="119"/>
+      <c r="B36" s="122"/>
       <c r="C36" s="51" t="str">
         <f>master!C27</f>
         <v>Appendix：りそな様 - AI CoEと生成AI人財育成アカデミーの推進</v>
       </c>
-      <c r="D36" s="113"/>
-      <c r="E36" s="114"/>
-      <c r="F36" s="115"/>
+      <c r="D36" s="119"/>
+      <c r="E36" s="120"/>
+      <c r="F36" s="121"/>
       <c r="G36" s="51" t="s">
         <v>40</v>
       </c>
@@ -5025,7 +5039,7 @@
     </row>
     <row r="37" spans="1:14" ht="88.2">
       <c r="A37" s="11"/>
-      <c r="B37" s="120" t="str">
+      <c r="B37" s="115" t="str">
         <f>master!B28</f>
         <v>モジュール4：プロンプトエンジニアリング</v>
       </c>
@@ -5033,11 +5047,11 @@
         <f>master!C28</f>
         <v>4-1. プロンプトとは?</v>
       </c>
-      <c r="D37" s="113" t="s">
-        <v>181</v>
-      </c>
-      <c r="E37" s="114"/>
-      <c r="F37" s="115"/>
+      <c r="D37" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="E37" s="120"/>
+      <c r="F37" s="121"/>
       <c r="G37" s="51" t="s">
         <v>45</v>
       </c>
@@ -5055,16 +5069,16 @@
     </row>
     <row r="38" spans="1:14" ht="37.799999999999997">
       <c r="A38" s="11"/>
-      <c r="B38" s="121"/>
+      <c r="B38" s="116"/>
       <c r="C38" s="51" t="str">
         <f>master!C29</f>
         <v>4-2. プロンプトを構成する4つの要素</v>
       </c>
-      <c r="D38" s="113" t="s">
+      <c r="D38" s="119" t="s">
         <v>144</v>
       </c>
-      <c r="E38" s="114"/>
-      <c r="F38" s="115"/>
+      <c r="E38" s="120"/>
+      <c r="F38" s="121"/>
       <c r="G38" s="51" t="s">
         <v>40</v>
       </c>
@@ -5082,16 +5096,16 @@
     </row>
     <row r="39" spans="1:14" ht="63">
       <c r="A39" s="11"/>
-      <c r="B39" s="121"/>
+      <c r="B39" s="116"/>
       <c r="C39" s="51" t="str">
         <f>master!C30</f>
         <v>4-3. 悪いプロンプト vs 良いプロンプト</v>
       </c>
-      <c r="D39" s="113" t="s">
+      <c r="D39" s="119" t="s">
         <v>145</v>
       </c>
-      <c r="E39" s="114"/>
-      <c r="F39" s="115"/>
+      <c r="E39" s="120"/>
+      <c r="F39" s="121"/>
       <c r="G39" s="51" t="s">
         <v>39</v>
       </c>
@@ -5109,14 +5123,14 @@
     </row>
     <row r="40" spans="1:14" ht="37.799999999999997">
       <c r="A40" s="11"/>
-      <c r="B40" s="121"/>
+      <c r="B40" s="116"/>
       <c r="C40" s="51" t="str">
         <f>master!C31</f>
         <v>4-4. テクニック①：Role Prompting（役割の付与）</v>
       </c>
-      <c r="D40" s="113"/>
-      <c r="E40" s="114"/>
-      <c r="F40" s="115"/>
+      <c r="D40" s="119"/>
+      <c r="E40" s="120"/>
+      <c r="F40" s="121"/>
       <c r="G40" s="51" t="s">
         <v>40</v>
       </c>
@@ -5134,14 +5148,14 @@
     </row>
     <row r="41" spans="1:14" ht="37.799999999999997">
       <c r="A41" s="11"/>
-      <c r="B41" s="121"/>
+      <c r="B41" s="116"/>
       <c r="C41" s="51" t="str">
         <f>master!C32</f>
         <v>4-5. テクニック②：区切り文字の活用</v>
       </c>
-      <c r="D41" s="113"/>
-      <c r="E41" s="114"/>
-      <c r="F41" s="115"/>
+      <c r="D41" s="119"/>
+      <c r="E41" s="120"/>
+      <c r="F41" s="121"/>
       <c r="G41" s="51" t="s">
         <v>40</v>
       </c>
@@ -5159,14 +5173,14 @@
     </row>
     <row r="42" spans="1:14" ht="37.799999999999997">
       <c r="A42" s="11"/>
-      <c r="B42" s="121"/>
+      <c r="B42" s="116"/>
       <c r="C42" s="51" t="str">
         <f>master!C33</f>
         <v>4-6. テクニック③：Zero-shot vs Few-shot</v>
       </c>
-      <c r="D42" s="113"/>
-      <c r="E42" s="114"/>
-      <c r="F42" s="115"/>
+      <c r="D42" s="119"/>
+      <c r="E42" s="120"/>
+      <c r="F42" s="121"/>
       <c r="G42" s="51" t="s">
         <v>40</v>
       </c>
@@ -5184,14 +5198,14 @@
     </row>
     <row r="43" spans="1:14" ht="50.4">
       <c r="A43" s="11"/>
-      <c r="B43" s="122"/>
+      <c r="B43" s="117"/>
       <c r="C43" s="51" t="str">
         <f>master!C34</f>
         <v>4-7. テクニック④：Chain of Thought（思考の連鎖）</v>
       </c>
-      <c r="D43" s="113"/>
-      <c r="E43" s="114"/>
-      <c r="F43" s="115"/>
+      <c r="D43" s="119"/>
+      <c r="E43" s="120"/>
+      <c r="F43" s="121"/>
       <c r="G43" s="51" t="s">
         <v>41</v>
       </c>
@@ -5209,135 +5223,135 @@
     </row>
     <row r="44" spans="1:14" ht="75.599999999999994">
       <c r="A44" s="11"/>
-      <c r="B44" s="126" t="str">
+      <c r="B44" s="113" t="str">
         <f>master!B35</f>
         <v>モジュール5：ハンズオン（ChatGPT）</v>
       </c>
-      <c r="C44" s="65" t="str">
+      <c r="C44" s="64" t="str">
         <f>master!C35</f>
         <v>5-1. ChatGPTの使い方（一般チャット）</v>
       </c>
-      <c r="D44" s="123" t="s">
-        <v>182</v>
-      </c>
-      <c r="E44" s="124"/>
-      <c r="F44" s="125"/>
-      <c r="G44" s="65" t="s">
+      <c r="D44" s="107" t="s">
+        <v>179</v>
+      </c>
+      <c r="E44" s="108"/>
+      <c r="F44" s="109"/>
+      <c r="G44" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="H44" s="66"/>
-      <c r="I44" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J44" s="68">
+      <c r="H44" s="65"/>
+      <c r="I44" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" s="67">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K44" s="69"/>
+      <c r="K44" s="68"/>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
     </row>
     <row r="45" spans="1:14" ht="126">
       <c r="A45" s="11"/>
-      <c r="B45" s="127"/>
-      <c r="C45" s="65" t="str">
+      <c r="B45" s="118"/>
+      <c r="C45" s="64" t="str">
         <f>master!C36</f>
         <v>5-2. 例①：顧客提案向けの企画提案書を作りたい</v>
       </c>
-      <c r="D45" s="123" t="s">
-        <v>190</v>
-      </c>
-      <c r="E45" s="124"/>
-      <c r="F45" s="125"/>
-      <c r="G45" s="65" t="s">
+      <c r="D45" s="107" t="s">
+        <v>187</v>
+      </c>
+      <c r="E45" s="108"/>
+      <c r="F45" s="109"/>
+      <c r="G45" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="H45" s="66"/>
-      <c r="I45" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J45" s="68">
+      <c r="H45" s="65"/>
+      <c r="I45" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J45" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K45" s="69"/>
+      <c r="K45" s="68"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
     </row>
     <row r="46" spans="1:14" ht="126">
       <c r="A46" s="11"/>
-      <c r="B46" s="127"/>
-      <c r="C46" s="65" t="str">
+      <c r="B46" s="118"/>
+      <c r="C46" s="64" t="str">
         <f>master!C37</f>
         <v>5-3. 例①：顧客提案向けの企画提案書を作りたい - プロンプト例</v>
       </c>
-      <c r="D46" s="123" t="s">
+      <c r="D46" s="107" t="s">
         <v>147</v>
       </c>
-      <c r="E46" s="124"/>
-      <c r="F46" s="125"/>
-      <c r="G46" s="65" t="s">
+      <c r="E46" s="108"/>
+      <c r="F46" s="109"/>
+      <c r="G46" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="H46" s="66"/>
-      <c r="I46" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J46" s="68">
+      <c r="H46" s="65"/>
+      <c r="I46" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J46" s="67">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K46" s="69"/>
+      <c r="K46" s="68"/>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
     <row r="47" spans="1:14" ht="37.799999999999997">
       <c r="A47" s="11"/>
-      <c r="B47" s="127"/>
-      <c r="C47" s="65" t="str">
+      <c r="B47" s="118"/>
+      <c r="C47" s="64" t="str">
         <f>master!C38</f>
         <v>5-4. 例①：顧客提案向けの企画提案書を作りたい - 実行例</v>
       </c>
-      <c r="D47" s="123" t="s">
+      <c r="D47" s="107" t="s">
         <v>146</v>
       </c>
-      <c r="E47" s="124"/>
-      <c r="F47" s="125"/>
-      <c r="G47" s="65" t="s">
+      <c r="E47" s="108"/>
+      <c r="F47" s="109"/>
+      <c r="G47" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="H47" s="66"/>
-      <c r="I47" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J47" s="68">
+      <c r="H47" s="65"/>
+      <c r="I47" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J47" s="67">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K47" s="69"/>
+      <c r="K47" s="68"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
     <row r="48" spans="1:14" ht="88.2">
       <c r="A48" s="11"/>
-      <c r="B48" s="127"/>
-      <c r="C48" s="85"/>
-      <c r="D48" s="116" t="s">
-        <v>189</v>
-      </c>
-      <c r="E48" s="117"/>
-      <c r="F48" s="118"/>
-      <c r="G48" s="85" t="s">
+      <c r="B48" s="118"/>
+      <c r="C48" s="84"/>
+      <c r="D48" s="110" t="s">
+        <v>186</v>
+      </c>
+      <c r="E48" s="111"/>
+      <c r="F48" s="112"/>
+      <c r="G48" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="H48" s="86"/>
-      <c r="I48" s="87" t="s">
-        <v>25</v>
-      </c>
-      <c r="J48" s="88">
+      <c r="H48" s="85"/>
+      <c r="I48" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" s="87">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="K48" s="89" t="s">
+      <c r="K48" s="88" t="s">
         <v>130</v>
       </c>
       <c r="L48" s="6"/>
@@ -5346,78 +5360,78 @@
     </row>
     <row r="49" spans="1:14" ht="50.4">
       <c r="A49" s="11"/>
-      <c r="B49" s="127"/>
-      <c r="C49" s="65" t="str">
+      <c r="B49" s="118"/>
+      <c r="C49" s="64" t="str">
         <f>master!C39</f>
         <v>5-5. 例②：100本ノックを作ってみる</v>
       </c>
-      <c r="D49" s="123" t="s">
-        <v>197</v>
-      </c>
-      <c r="E49" s="124"/>
-      <c r="F49" s="125"/>
-      <c r="G49" s="65" t="s">
+      <c r="D49" s="107" t="s">
+        <v>194</v>
+      </c>
+      <c r="E49" s="108"/>
+      <c r="F49" s="109"/>
+      <c r="G49" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H49" s="66"/>
-      <c r="I49" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J49" s="68">
+      <c r="H49" s="65"/>
+      <c r="I49" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J49" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K49" s="69"/>
+      <c r="K49" s="68"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
     <row r="50" spans="1:14" ht="75.599999999999994">
       <c r="A50" s="11"/>
-      <c r="B50" s="127"/>
-      <c r="C50" s="65" t="str">
+      <c r="B50" s="118"/>
+      <c r="C50" s="64" t="str">
         <f>master!C40</f>
         <v>5-6. 例②：100本ノックを作ってみる -プロンプト例</v>
       </c>
-      <c r="D50" s="123" t="s">
-        <v>183</v>
-      </c>
-      <c r="E50" s="124"/>
-      <c r="F50" s="125"/>
-      <c r="G50" s="65" t="s">
+      <c r="D50" s="107" t="s">
+        <v>180</v>
+      </c>
+      <c r="E50" s="108"/>
+      <c r="F50" s="109"/>
+      <c r="G50" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="H50" s="66"/>
-      <c r="I50" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J50" s="68">
+      <c r="H50" s="65"/>
+      <c r="I50" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J50" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K50" s="69"/>
+      <c r="K50" s="68"/>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
     <row r="51" spans="1:14" ht="88.2">
       <c r="A51" s="11"/>
-      <c r="B51" s="127"/>
-      <c r="C51" s="85"/>
-      <c r="D51" s="116" t="s">
-        <v>191</v>
-      </c>
-      <c r="E51" s="117"/>
-      <c r="F51" s="118"/>
-      <c r="G51" s="85" t="s">
+      <c r="B51" s="118"/>
+      <c r="C51" s="84"/>
+      <c r="D51" s="110" t="s">
+        <v>188</v>
+      </c>
+      <c r="E51" s="111"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="H51" s="86"/>
-      <c r="I51" s="87" t="s">
-        <v>196</v>
-      </c>
-      <c r="J51" s="88">
+      <c r="H51" s="85"/>
+      <c r="I51" s="86" t="s">
+        <v>193</v>
+      </c>
+      <c r="J51" s="87">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="K51" s="89" t="s">
+      <c r="K51" s="88" t="s">
         <v>130</v>
       </c>
       <c r="L51" s="6"/>
@@ -5426,748 +5440,748 @@
     </row>
     <row r="52" spans="1:14" ht="50.4">
       <c r="A52" s="11"/>
-      <c r="B52" s="127"/>
-      <c r="C52" s="65" t="str">
+      <c r="B52" s="118"/>
+      <c r="C52" s="64" t="str">
         <f>master!C41</f>
         <v>5-7. 例②：100本ノックを作ってみる - 実行結果①</v>
       </c>
-      <c r="D52" s="123" t="s">
-        <v>159</v>
-      </c>
-      <c r="E52" s="124"/>
-      <c r="F52" s="125"/>
-      <c r="G52" s="65" t="s">
+      <c r="D52" s="107" t="s">
+        <v>157</v>
+      </c>
+      <c r="E52" s="108"/>
+      <c r="F52" s="109"/>
+      <c r="G52" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H52" s="66"/>
-      <c r="I52" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J52" s="68">
+      <c r="H52" s="65"/>
+      <c r="I52" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J52" s="67">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K52" s="69"/>
+      <c r="K52" s="68"/>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
     <row r="53" spans="1:14" ht="50.4">
       <c r="A53" s="11"/>
-      <c r="B53" s="127"/>
-      <c r="C53" s="65" t="str">
+      <c r="B53" s="118"/>
+      <c r="C53" s="64" t="str">
         <f>master!C42</f>
         <v>5-8. 例②：100本ノックを作ってみる - 実行結果②</v>
       </c>
-      <c r="D53" s="123" t="s">
-        <v>160</v>
-      </c>
-      <c r="E53" s="124"/>
-      <c r="F53" s="125"/>
-      <c r="G53" s="65" t="s">
+      <c r="D53" s="107" t="s">
+        <v>158</v>
+      </c>
+      <c r="E53" s="108"/>
+      <c r="F53" s="109"/>
+      <c r="G53" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H53" s="66"/>
-      <c r="I53" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J53" s="68">
+      <c r="H53" s="65"/>
+      <c r="I53" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J53" s="67">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K53" s="69"/>
+      <c r="K53" s="68"/>
       <c r="L53" s="6"/>
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
     </row>
     <row r="54" spans="1:14" ht="50.4">
       <c r="A54" s="11"/>
-      <c r="B54" s="127"/>
-      <c r="C54" s="65" t="str">
+      <c r="B54" s="118"/>
+      <c r="C54" s="64" t="str">
         <f>master!C43</f>
         <v>5-9. 例②：100本ノックを作ってみる - 実行結果③</v>
       </c>
-      <c r="D54" s="123" t="s">
-        <v>161</v>
-      </c>
-      <c r="E54" s="124"/>
-      <c r="F54" s="125"/>
-      <c r="G54" s="65" t="s">
+      <c r="D54" s="107" t="s">
+        <v>159</v>
+      </c>
+      <c r="E54" s="108"/>
+      <c r="F54" s="109"/>
+      <c r="G54" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H54" s="66"/>
-      <c r="I54" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J54" s="68">
+      <c r="H54" s="65"/>
+      <c r="I54" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J54" s="67">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K54" s="69"/>
+      <c r="K54" s="68"/>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
     </row>
     <row r="55" spans="1:14" ht="63">
       <c r="A55" s="11"/>
-      <c r="B55" s="128"/>
-      <c r="C55" s="65" t="str">
+      <c r="B55" s="114"/>
+      <c r="C55" s="64" t="str">
         <f>master!C44</f>
         <v>5-10. ChatGPT まとめ</v>
       </c>
-      <c r="D55" s="123" t="s">
+      <c r="D55" s="107" t="s">
         <v>148</v>
       </c>
-      <c r="E55" s="124"/>
-      <c r="F55" s="125"/>
-      <c r="G55" s="65" t="s">
+      <c r="E55" s="108"/>
+      <c r="F55" s="109"/>
+      <c r="G55" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="H55" s="66"/>
-      <c r="I55" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J55" s="68">
+      <c r="H55" s="65"/>
+      <c r="I55" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J55" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K55" s="69"/>
+      <c r="K55" s="68"/>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
     <row r="56" spans="1:14" ht="50.4" customHeight="1">
       <c r="A56" s="11"/>
-      <c r="B56" s="127" t="str">
+      <c r="B56" s="118" t="str">
         <f>master!B45</f>
         <v>モジュール6：ハンズオン（ GitHub Copilot ）</v>
       </c>
-      <c r="C56" s="65" t="str">
+      <c r="C56" s="64" t="str">
         <f>master!C45</f>
         <v>6-1. Visual Studio Code を開く</v>
       </c>
-      <c r="D56" s="123" t="s">
+      <c r="D56" s="107" t="s">
         <v>149</v>
       </c>
-      <c r="E56" s="124"/>
-      <c r="F56" s="125"/>
-      <c r="G56" s="65" t="s">
+      <c r="E56" s="108"/>
+      <c r="F56" s="109"/>
+      <c r="G56" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H56" s="66"/>
-      <c r="I56" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J56" s="68">
+      <c r="H56" s="65"/>
+      <c r="I56" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J56" s="67">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K56" s="69"/>
+      <c r="K56" s="68"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
     <row r="57" spans="1:14" ht="63">
       <c r="A57" s="11"/>
-      <c r="B57" s="127"/>
-      <c r="C57" s="65" t="str">
+      <c r="B57" s="118"/>
+      <c r="C57" s="64" t="str">
         <f>master!C46</f>
         <v>6-2. コード補完機能</v>
       </c>
-      <c r="D57" s="123" t="s">
+      <c r="D57" s="107" t="s">
         <v>150</v>
       </c>
-      <c r="E57" s="124"/>
-      <c r="F57" s="125"/>
-      <c r="G57" s="65" t="s">
+      <c r="E57" s="108"/>
+      <c r="F57" s="109"/>
+      <c r="G57" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="H57" s="66"/>
-      <c r="I57" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J57" s="68">
+      <c r="H57" s="65"/>
+      <c r="I57" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J57" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K57" s="69"/>
+      <c r="K57" s="68"/>
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
     <row r="58" spans="1:14" ht="75.599999999999994">
       <c r="A58" s="11"/>
-      <c r="B58" s="127"/>
-      <c r="C58" s="65" t="str">
+      <c r="B58" s="118"/>
+      <c r="C58" s="64" t="str">
         <f>master!C47</f>
         <v>6-3. チャット機能</v>
       </c>
-      <c r="D58" s="123" t="s">
-        <v>207</v>
-      </c>
-      <c r="E58" s="124"/>
-      <c r="F58" s="125"/>
-      <c r="G58" s="65" t="s">
+      <c r="D58" s="107" t="s">
+        <v>204</v>
+      </c>
+      <c r="E58" s="108"/>
+      <c r="F58" s="109"/>
+      <c r="G58" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="H58" s="66"/>
-      <c r="I58" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J58" s="68">
+      <c r="H58" s="65"/>
+      <c r="I58" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J58" s="67">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K58" s="69"/>
+      <c r="K58" s="68"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
     <row r="59" spans="1:14" ht="88.2">
       <c r="A59" s="11"/>
-      <c r="B59" s="127"/>
-      <c r="C59" s="65" t="str">
+      <c r="B59" s="118"/>
+      <c r="C59" s="64" t="str">
         <f>master!C48</f>
         <v>6-4. チャット機能 - コマンド</v>
       </c>
-      <c r="D59" s="123" t="s">
-        <v>206</v>
-      </c>
-      <c r="E59" s="124"/>
-      <c r="F59" s="125"/>
-      <c r="G59" s="65" t="s">
+      <c r="D59" s="107" t="s">
+        <v>203</v>
+      </c>
+      <c r="E59" s="108"/>
+      <c r="F59" s="109"/>
+      <c r="G59" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="H59" s="66"/>
-      <c r="I59" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J59" s="68">
+      <c r="H59" s="65"/>
+      <c r="I59" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J59" s="67">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K59" s="69"/>
+      <c r="K59" s="68"/>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
     <row r="60" spans="1:14" ht="50.4">
       <c r="A60" s="11"/>
-      <c r="B60" s="127"/>
-      <c r="C60" s="65" t="str">
+      <c r="B60" s="118"/>
+      <c r="C60" s="64" t="str">
         <f>master!C49</f>
         <v>6-5. 簡単なアプリやゲームを作ってみましょう</v>
       </c>
-      <c r="D60" s="123" t="s">
-        <v>173</v>
-      </c>
-      <c r="E60" s="124"/>
-      <c r="F60" s="125"/>
-      <c r="G60" s="65" t="s">
+      <c r="D60" s="107" t="s">
+        <v>171</v>
+      </c>
+      <c r="E60" s="108"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H60" s="66"/>
-      <c r="I60" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J60" s="68">
+      <c r="H60" s="65"/>
+      <c r="I60" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J60" s="67">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K60" s="69"/>
+      <c r="K60" s="68"/>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
     </row>
     <row r="61" spans="1:14" ht="50.4">
       <c r="A61" s="11"/>
-      <c r="B61" s="127"/>
-      <c r="C61" s="65" t="str">
+      <c r="B61" s="118"/>
+      <c r="C61" s="64" t="str">
         <f>master!C50</f>
         <v>6-6. 例①：高級志向テトリス</v>
       </c>
-      <c r="D61" s="123" t="s">
-        <v>176</v>
-      </c>
-      <c r="E61" s="124"/>
-      <c r="F61" s="125"/>
-      <c r="G61" s="65" t="s">
+      <c r="D61" s="107" t="s">
+        <v>174</v>
+      </c>
+      <c r="E61" s="108"/>
+      <c r="F61" s="109"/>
+      <c r="G61" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H61" s="66"/>
-      <c r="I61" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J61" s="68">
+      <c r="H61" s="65"/>
+      <c r="I61" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J61" s="67">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K61" s="69"/>
+      <c r="K61" s="68"/>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
     </row>
     <row r="62" spans="1:14" ht="50.4">
       <c r="A62" s="11"/>
-      <c r="B62" s="127"/>
-      <c r="C62" s="65" t="str">
+      <c r="B62" s="118"/>
+      <c r="C62" s="64" t="str">
         <f>master!C51</f>
         <v>6-7. 例②：わくわく！にっぽんダーツの旅</v>
       </c>
-      <c r="D62" s="123" t="s">
-        <v>174</v>
-      </c>
-      <c r="E62" s="124"/>
-      <c r="F62" s="125"/>
-      <c r="G62" s="65" t="s">
+      <c r="D62" s="107" t="s">
+        <v>172</v>
+      </c>
+      <c r="E62" s="108"/>
+      <c r="F62" s="109"/>
+      <c r="G62" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H62" s="66"/>
-      <c r="I62" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J62" s="68">
+      <c r="H62" s="65"/>
+      <c r="I62" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J62" s="67">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K62" s="69"/>
+      <c r="K62" s="68"/>
       <c r="L62" s="6"/>
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
     </row>
     <row r="63" spans="1:14" ht="50.4">
       <c r="A63" s="11"/>
-      <c r="B63" s="127"/>
-      <c r="C63" s="65" t="str">
+      <c r="B63" s="118"/>
+      <c r="C63" s="64" t="str">
         <f>master!C52</f>
         <v>6-8. 例③：タスク管理ツール</v>
       </c>
-      <c r="D63" s="123" t="s">
-        <v>175</v>
-      </c>
-      <c r="E63" s="124"/>
-      <c r="F63" s="125"/>
-      <c r="G63" s="65" t="s">
+      <c r="D63" s="107" t="s">
+        <v>173</v>
+      </c>
+      <c r="E63" s="108"/>
+      <c r="F63" s="109"/>
+      <c r="G63" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H63" s="66"/>
-      <c r="I63" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J63" s="68">
+      <c r="H63" s="65"/>
+      <c r="I63" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J63" s="67">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K63" s="69"/>
+      <c r="K63" s="68"/>
       <c r="L63" s="6"/>
       <c r="M63" s="6"/>
       <c r="N63" s="6"/>
     </row>
     <row r="64" spans="1:14" ht="138.6">
       <c r="A64" s="11"/>
-      <c r="B64" s="127"/>
-      <c r="C64" s="85"/>
-      <c r="D64" s="116" t="s">
-        <v>188</v>
-      </c>
-      <c r="E64" s="117"/>
-      <c r="F64" s="118"/>
-      <c r="G64" s="85" t="s">
+      <c r="B64" s="118"/>
+      <c r="C64" s="84"/>
+      <c r="D64" s="110" t="s">
+        <v>185</v>
+      </c>
+      <c r="E64" s="111"/>
+      <c r="F64" s="112"/>
+      <c r="G64" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="H64" s="86"/>
-      <c r="I64" s="87" t="s">
+      <c r="H64" s="85"/>
+      <c r="I64" s="86" t="s">
         <v>131</v>
       </c>
-      <c r="J64" s="88">
+      <c r="J64" s="87">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K64" s="89"/>
+      <c r="K64" s="88"/>
       <c r="L64" s="6"/>
       <c r="M64" s="6"/>
       <c r="N64" s="6"/>
     </row>
     <row r="65" spans="1:14" ht="75.599999999999994">
       <c r="A65" s="11"/>
-      <c r="B65" s="127"/>
-      <c r="C65" s="65" t="str">
+      <c r="B65" s="118"/>
+      <c r="C65" s="64" t="str">
         <f>master!C53</f>
         <v>6-9. ディレクトリ作成とファイル配置</v>
       </c>
-      <c r="D65" s="123" t="s">
-        <v>192</v>
-      </c>
-      <c r="E65" s="124"/>
-      <c r="F65" s="125"/>
-      <c r="G65" s="65" t="s">
+      <c r="D65" s="107" t="s">
+        <v>189</v>
+      </c>
+      <c r="E65" s="108"/>
+      <c r="F65" s="109"/>
+      <c r="G65" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="H65" s="66"/>
-      <c r="I65" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J65" s="68">
+      <c r="H65" s="65"/>
+      <c r="I65" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J65" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K65" s="69"/>
+      <c r="K65" s="68"/>
       <c r="L65" s="6"/>
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
     </row>
     <row r="66" spans="1:14" ht="88.2">
       <c r="A66" s="11"/>
-      <c r="B66" s="127"/>
-      <c r="C66" s="85"/>
-      <c r="D66" s="116" t="s">
-        <v>208</v>
-      </c>
-      <c r="E66" s="117"/>
-      <c r="F66" s="118"/>
-      <c r="G66" s="85" t="s">
+      <c r="B66" s="118"/>
+      <c r="C66" s="84"/>
+      <c r="D66" s="110" t="s">
+        <v>205</v>
+      </c>
+      <c r="E66" s="111"/>
+      <c r="F66" s="112"/>
+      <c r="G66" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="H66" s="86"/>
-      <c r="I66" s="87" t="s">
+      <c r="H66" s="85"/>
+      <c r="I66" s="86" t="s">
         <v>131</v>
       </c>
-      <c r="J66" s="88">
+      <c r="J66" s="87">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K66" s="89"/>
+      <c r="K66" s="88"/>
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
     </row>
     <row r="67" spans="1:14" ht="50.4">
       <c r="A67" s="11"/>
-      <c r="B67" s="127"/>
-      <c r="C67" s="65" t="str">
+      <c r="B67" s="118"/>
+      <c r="C67" s="64" t="str">
         <f>master!C54</f>
         <v>6-10. チャット機能 - Askモード</v>
       </c>
-      <c r="D67" s="123" t="s">
-        <v>203</v>
-      </c>
-      <c r="E67" s="124"/>
-      <c r="F67" s="125"/>
-      <c r="G67" s="65" t="s">
+      <c r="D67" s="107" t="s">
+        <v>200</v>
+      </c>
+      <c r="E67" s="108"/>
+      <c r="F67" s="109"/>
+      <c r="G67" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H67" s="66"/>
-      <c r="I67" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J67" s="68">
+      <c r="H67" s="65"/>
+      <c r="I67" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J67" s="67">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K67" s="69"/>
+      <c r="K67" s="68"/>
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
     </row>
     <row r="68" spans="1:14" ht="100.8">
       <c r="A68" s="11"/>
-      <c r="B68" s="127"/>
-      <c r="C68" s="65" t="str">
+      <c r="B68" s="118"/>
+      <c r="C68" s="64" t="str">
         <f>master!C55</f>
         <v>6-11. Askモードについて</v>
       </c>
-      <c r="D68" s="123" t="s">
-        <v>154</v>
-      </c>
-      <c r="E68" s="124"/>
-      <c r="F68" s="125"/>
-      <c r="G68" s="65" t="s">
+      <c r="D68" s="107" t="s">
+        <v>152</v>
+      </c>
+      <c r="E68" s="108"/>
+      <c r="F68" s="109"/>
+      <c r="G68" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="H68" s="66"/>
-      <c r="I68" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J68" s="68">
+      <c r="H68" s="65"/>
+      <c r="I68" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J68" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K68" s="69"/>
+      <c r="K68" s="68"/>
       <c r="L68" s="6"/>
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
     </row>
     <row r="69" spans="1:14" ht="50.4">
       <c r="A69" s="11"/>
-      <c r="B69" s="127"/>
-      <c r="C69" s="65" t="str">
+      <c r="B69" s="118"/>
+      <c r="C69" s="64" t="str">
         <f>master!C56</f>
         <v>6-12. 実行例①</v>
       </c>
-      <c r="D69" s="123" t="s">
-        <v>158</v>
-      </c>
-      <c r="E69" s="124"/>
-      <c r="F69" s="125"/>
-      <c r="G69" s="65" t="s">
+      <c r="D69" s="107" t="s">
+        <v>156</v>
+      </c>
+      <c r="E69" s="108"/>
+      <c r="F69" s="109"/>
+      <c r="G69" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H69" s="66"/>
-      <c r="I69" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J69" s="68">
+      <c r="H69" s="65"/>
+      <c r="I69" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J69" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K69" s="69"/>
+      <c r="K69" s="68"/>
       <c r="L69" s="6"/>
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
     </row>
     <row r="70" spans="1:14" ht="50.4">
       <c r="A70" s="11"/>
-      <c r="B70" s="127"/>
-      <c r="C70" s="65" t="str">
+      <c r="B70" s="118"/>
+      <c r="C70" s="64" t="str">
         <f>master!C57</f>
         <v>6-13. 実行例②</v>
       </c>
-      <c r="D70" s="123" t="s">
-        <v>156</v>
-      </c>
-      <c r="E70" s="124"/>
-      <c r="F70" s="125"/>
-      <c r="G70" s="65" t="s">
+      <c r="D70" s="107" t="s">
+        <v>154</v>
+      </c>
+      <c r="E70" s="108"/>
+      <c r="F70" s="109"/>
+      <c r="G70" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H70" s="66"/>
-      <c r="I70" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J70" s="68">
+      <c r="H70" s="65"/>
+      <c r="I70" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J70" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K70" s="69"/>
+      <c r="K70" s="68"/>
       <c r="L70" s="6"/>
       <c r="M70" s="6"/>
       <c r="N70" s="6"/>
     </row>
     <row r="71" spans="1:14" ht="50.4">
       <c r="A71" s="11"/>
-      <c r="B71" s="127"/>
-      <c r="C71" s="65" t="str">
+      <c r="B71" s="118"/>
+      <c r="C71" s="64" t="str">
         <f>master!C58</f>
         <v>6-14. 実行例③</v>
       </c>
-      <c r="D71" s="123" t="s">
-        <v>157</v>
-      </c>
-      <c r="E71" s="124"/>
-      <c r="F71" s="125"/>
-      <c r="G71" s="65" t="s">
+      <c r="D71" s="107" t="s">
+        <v>155</v>
+      </c>
+      <c r="E71" s="108"/>
+      <c r="F71" s="109"/>
+      <c r="G71" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H71" s="66"/>
-      <c r="I71" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J71" s="68">
+      <c r="H71" s="65"/>
+      <c r="I71" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J71" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K71" s="69"/>
+      <c r="K71" s="68"/>
       <c r="L71" s="6"/>
       <c r="M71" s="6"/>
       <c r="N71" s="6"/>
     </row>
     <row r="72" spans="1:14" ht="138.6">
       <c r="A72" s="11"/>
-      <c r="B72" s="127"/>
-      <c r="C72" s="85"/>
-      <c r="D72" s="116" t="s">
-        <v>187</v>
-      </c>
-      <c r="E72" s="117"/>
-      <c r="F72" s="118"/>
-      <c r="G72" s="85" t="s">
+      <c r="B72" s="118"/>
+      <c r="C72" s="84"/>
+      <c r="D72" s="110" t="s">
+        <v>184</v>
+      </c>
+      <c r="E72" s="111"/>
+      <c r="F72" s="112"/>
+      <c r="G72" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="H72" s="86"/>
-      <c r="I72" s="87" t="s">
+      <c r="H72" s="85"/>
+      <c r="I72" s="86" t="s">
         <v>131</v>
       </c>
-      <c r="J72" s="88">
+      <c r="J72" s="87">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K72" s="89"/>
+      <c r="K72" s="88"/>
       <c r="L72" s="6"/>
       <c r="M72" s="6"/>
       <c r="N72" s="6"/>
     </row>
     <row r="73" spans="1:14" ht="63">
       <c r="A73" s="11"/>
-      <c r="B73" s="127"/>
-      <c r="C73" s="65" t="str">
+      <c r="B73" s="118"/>
+      <c r="C73" s="64" t="str">
         <f>master!C59</f>
         <v>6-15. Askモードまとめ</v>
       </c>
-      <c r="D73" s="123" t="s">
-        <v>153</v>
-      </c>
-      <c r="E73" s="124"/>
-      <c r="F73" s="125"/>
-      <c r="G73" s="65" t="s">
+      <c r="D73" s="107" t="s">
+        <v>151</v>
+      </c>
+      <c r="E73" s="108"/>
+      <c r="F73" s="109"/>
+      <c r="G73" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="H73" s="66"/>
-      <c r="I73" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J73" s="68">
+      <c r="H73" s="65"/>
+      <c r="I73" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J73" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K73" s="69"/>
+      <c r="K73" s="68"/>
       <c r="L73" s="6"/>
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
     </row>
     <row r="74" spans="1:14" ht="50.4">
       <c r="A74" s="11"/>
-      <c r="B74" s="127"/>
-      <c r="C74" s="65" t="str">
+      <c r="B74" s="118"/>
+      <c r="C74" s="64" t="str">
         <f>master!C60</f>
         <v>6-16. チャット機能 - Agentモード</v>
       </c>
-      <c r="D74" s="123" t="s">
-        <v>204</v>
-      </c>
-      <c r="E74" s="124"/>
-      <c r="F74" s="125"/>
-      <c r="G74" s="65" t="s">
+      <c r="D74" s="107" t="s">
+        <v>201</v>
+      </c>
+      <c r="E74" s="108"/>
+      <c r="F74" s="109"/>
+      <c r="G74" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H74" s="66"/>
-      <c r="I74" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J74" s="68">
+      <c r="H74" s="65"/>
+      <c r="I74" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J74" s="67">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K74" s="69"/>
+      <c r="K74" s="68"/>
       <c r="L74" s="6"/>
       <c r="M74" s="6"/>
       <c r="N74" s="6"/>
     </row>
     <row r="75" spans="1:14" ht="63">
       <c r="A75" s="11"/>
-      <c r="B75" s="127"/>
-      <c r="C75" s="65" t="str">
+      <c r="B75" s="118"/>
+      <c r="C75" s="64" t="str">
         <f>master!C61</f>
         <v>6-17. Agentモード</v>
       </c>
-      <c r="D75" s="123" t="s">
-        <v>162</v>
-      </c>
-      <c r="E75" s="124"/>
-      <c r="F75" s="125"/>
-      <c r="G75" s="65" t="s">
+      <c r="D75" s="107" t="s">
+        <v>160</v>
+      </c>
+      <c r="E75" s="108"/>
+      <c r="F75" s="109"/>
+      <c r="G75" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="H75" s="66"/>
-      <c r="I75" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J75" s="68">
+      <c r="H75" s="65"/>
+      <c r="I75" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J75" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K75" s="69"/>
+      <c r="K75" s="68"/>
       <c r="L75" s="6"/>
       <c r="M75" s="6"/>
       <c r="N75" s="6"/>
     </row>
     <row r="76" spans="1:14" ht="50.4">
       <c r="A76" s="11"/>
-      <c r="B76" s="127"/>
-      <c r="C76" s="65" t="str">
+      <c r="B76" s="118"/>
+      <c r="C76" s="64" t="str">
         <f>master!C62</f>
         <v>6-18. 実行例</v>
       </c>
-      <c r="D76" s="123" t="s">
-        <v>163</v>
-      </c>
-      <c r="E76" s="124"/>
-      <c r="F76" s="125"/>
-      <c r="G76" s="65" t="s">
+      <c r="D76" s="107" t="s">
+        <v>161</v>
+      </c>
+      <c r="E76" s="108"/>
+      <c r="F76" s="109"/>
+      <c r="G76" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H76" s="66"/>
-      <c r="I76" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J76" s="68">
+      <c r="H76" s="65"/>
+      <c r="I76" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J76" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K76" s="69"/>
+      <c r="K76" s="68"/>
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
     </row>
     <row r="77" spans="1:14" ht="37.799999999999997">
       <c r="A77" s="11"/>
-      <c r="B77" s="127"/>
-      <c r="C77" s="65" t="str">
+      <c r="B77" s="118"/>
+      <c r="C77" s="64" t="str">
         <f>master!C63</f>
         <v>6-19. READMEの内容を確認しましょう①</v>
       </c>
-      <c r="D77" s="123" t="s">
-        <v>210</v>
-      </c>
-      <c r="E77" s="124"/>
-      <c r="F77" s="125"/>
-      <c r="G77" s="65" t="s">
+      <c r="D77" s="107" t="s">
+        <v>207</v>
+      </c>
+      <c r="E77" s="108"/>
+      <c r="F77" s="109"/>
+      <c r="G77" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="H77" s="66"/>
-      <c r="I77" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J77" s="68">
+      <c r="H77" s="65"/>
+      <c r="I77" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J77" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K77" s="69"/>
+      <c r="K77" s="68"/>
       <c r="L77" s="6"/>
       <c r="M77" s="6"/>
       <c r="N77" s="6"/>
     </row>
     <row r="78" spans="1:14" ht="37.799999999999997">
       <c r="A78" s="11"/>
-      <c r="B78" s="127"/>
-      <c r="C78" s="65" t="str">
+      <c r="B78" s="118"/>
+      <c r="C78" s="64" t="str">
         <f>master!C64</f>
         <v>6-20. READMEの内容を確認しましょう②</v>
       </c>
-      <c r="D78" s="123" t="s">
-        <v>209</v>
-      </c>
-      <c r="E78" s="124"/>
-      <c r="F78" s="125"/>
-      <c r="G78" s="65" t="s">
+      <c r="D78" s="107" t="s">
+        <v>206</v>
+      </c>
+      <c r="E78" s="108"/>
+      <c r="F78" s="109"/>
+      <c r="G78" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="H78" s="66"/>
-      <c r="I78" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J78" s="68">
+      <c r="H78" s="65"/>
+      <c r="I78" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J78" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K78" s="69"/>
+      <c r="K78" s="68"/>
       <c r="L78" s="6"/>
       <c r="M78" s="6"/>
       <c r="N78" s="6"/>
     </row>
     <row r="79" spans="1:14" ht="126">
       <c r="A79" s="11"/>
-      <c r="B79" s="127"/>
-      <c r="C79" s="85"/>
-      <c r="D79" s="116" t="s">
-        <v>186</v>
-      </c>
-      <c r="E79" s="117"/>
-      <c r="F79" s="118"/>
-      <c r="G79" s="85" t="s">
+      <c r="B79" s="118"/>
+      <c r="C79" s="84"/>
+      <c r="D79" s="110" t="s">
+        <v>183</v>
+      </c>
+      <c r="E79" s="111"/>
+      <c r="F79" s="112"/>
+      <c r="G79" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="H79" s="86"/>
-      <c r="I79" s="87" t="s">
+      <c r="H79" s="85"/>
+      <c r="I79" s="86" t="s">
         <v>131</v>
       </c>
-      <c r="J79" s="88">
+      <c r="J79" s="87">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="K79" s="89" t="s">
-        <v>155</v>
+      <c r="K79" s="88" t="s">
+        <v>153</v>
       </c>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
@@ -6175,51 +6189,51 @@
     </row>
     <row r="80" spans="1:14" ht="50.4">
       <c r="A80" s="11"/>
-      <c r="B80" s="127"/>
-      <c r="C80" s="65" t="str">
+      <c r="B80" s="118"/>
+      <c r="C80" s="64" t="str">
         <f>master!C65</f>
         <v>6-21. Changeログを作ってみましょう</v>
       </c>
-      <c r="D80" s="123" t="s">
-        <v>164</v>
-      </c>
-      <c r="E80" s="124"/>
-      <c r="F80" s="125"/>
-      <c r="G80" s="65" t="s">
+      <c r="D80" s="107" t="s">
+        <v>162</v>
+      </c>
+      <c r="E80" s="108"/>
+      <c r="F80" s="109"/>
+      <c r="G80" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H80" s="66"/>
-      <c r="I80" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J80" s="68">
+      <c r="H80" s="65"/>
+      <c r="I80" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J80" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K80" s="69"/>
+      <c r="K80" s="68"/>
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
       <c r="N80" s="6"/>
     </row>
     <row r="81" spans="1:14" ht="113.4">
       <c r="A81" s="11"/>
-      <c r="B81" s="127"/>
-      <c r="C81" s="90"/>
-      <c r="D81" s="116" t="s">
-        <v>185</v>
-      </c>
-      <c r="E81" s="117"/>
-      <c r="F81" s="118"/>
-      <c r="G81" s="85" t="s">
+      <c r="B81" s="118"/>
+      <c r="C81" s="89"/>
+      <c r="D81" s="110" t="s">
+        <v>182</v>
+      </c>
+      <c r="E81" s="111"/>
+      <c r="F81" s="112"/>
+      <c r="G81" s="84" t="s">
         <v>43</v>
       </c>
-      <c r="H81" s="86"/>
-      <c r="I81" s="87" t="s">
-        <v>196</v>
-      </c>
-      <c r="J81" s="88">
+      <c r="H81" s="85"/>
+      <c r="I81" s="86" t="s">
+        <v>193</v>
+      </c>
+      <c r="J81" s="87">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K81" s="89" t="s">
+      <c r="K81" s="88" t="s">
         <v>130</v>
       </c>
       <c r="L81" s="6"/>
@@ -6228,298 +6242,298 @@
     </row>
     <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="127"/>
-      <c r="C82" s="65" t="str">
+      <c r="B82" s="118"/>
+      <c r="C82" s="64" t="str">
         <f>master!C66</f>
         <v>6-22. チャット機能 - Planモード</v>
       </c>
-      <c r="D82" s="123" t="s">
-        <v>205</v>
-      </c>
-      <c r="E82" s="124"/>
-      <c r="F82" s="125"/>
-      <c r="G82" s="65" t="s">
+      <c r="D82" s="107" t="s">
+        <v>202</v>
+      </c>
+      <c r="E82" s="108"/>
+      <c r="F82" s="109"/>
+      <c r="G82" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H82" s="66"/>
-      <c r="I82" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J82" s="68">
+      <c r="H82" s="65"/>
+      <c r="I82" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J82" s="67">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K82" s="69"/>
+      <c r="K82" s="68"/>
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
       <c r="N82" s="6"/>
     </row>
     <row r="83" spans="1:14" ht="63">
       <c r="A83" s="11"/>
-      <c r="B83" s="127"/>
-      <c r="C83" s="65" t="str">
+      <c r="B83" s="118"/>
+      <c r="C83" s="64" t="str">
         <f>master!C67</f>
         <v>6-23. Planモードで機能追加してみましょう</v>
       </c>
-      <c r="D83" s="123" t="s">
-        <v>168</v>
-      </c>
-      <c r="E83" s="124"/>
-      <c r="F83" s="125"/>
-      <c r="G83" s="65" t="s">
+      <c r="D83" s="107" t="s">
+        <v>166</v>
+      </c>
+      <c r="E83" s="108"/>
+      <c r="F83" s="109"/>
+      <c r="G83" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="H83" s="66"/>
-      <c r="I83" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J83" s="68">
+      <c r="H83" s="65"/>
+      <c r="I83" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J83" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K83" s="69"/>
+      <c r="K83" s="68"/>
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
       <c r="N83" s="6"/>
     </row>
     <row r="84" spans="1:14" ht="63">
       <c r="A84" s="11"/>
-      <c r="B84" s="127"/>
-      <c r="C84" s="65" t="str">
+      <c r="B84" s="118"/>
+      <c r="C84" s="64" t="str">
         <f>master!C68</f>
         <v>6-24. 実行例①</v>
       </c>
-      <c r="D84" s="123" t="s">
-        <v>165</v>
-      </c>
-      <c r="E84" s="124"/>
-      <c r="F84" s="125"/>
-      <c r="G84" s="65" t="s">
+      <c r="D84" s="107" t="s">
+        <v>163</v>
+      </c>
+      <c r="E84" s="108"/>
+      <c r="F84" s="109"/>
+      <c r="G84" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="H84" s="66"/>
-      <c r="I84" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J84" s="68">
+      <c r="H84" s="65"/>
+      <c r="I84" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J84" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K84" s="69"/>
+      <c r="K84" s="68"/>
       <c r="L84" s="6"/>
       <c r="M84" s="6"/>
       <c r="N84" s="6"/>
     </row>
     <row r="85" spans="1:14" ht="50.4">
       <c r="A85" s="11"/>
-      <c r="B85" s="127"/>
-      <c r="C85" s="65" t="str">
+      <c r="B85" s="118"/>
+      <c r="C85" s="64" t="str">
         <f>master!C69</f>
         <v>6-25. 実行例②</v>
       </c>
-      <c r="D85" s="123" t="s">
-        <v>166</v>
-      </c>
-      <c r="E85" s="124"/>
-      <c r="F85" s="125"/>
-      <c r="G85" s="65" t="s">
+      <c r="D85" s="107" t="s">
+        <v>164</v>
+      </c>
+      <c r="E85" s="108"/>
+      <c r="F85" s="109"/>
+      <c r="G85" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H85" s="66"/>
-      <c r="I85" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J85" s="68">
+      <c r="H85" s="65"/>
+      <c r="I85" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J85" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K85" s="69"/>
+      <c r="K85" s="68"/>
       <c r="L85" s="6"/>
       <c r="M85" s="6"/>
       <c r="N85" s="6"/>
     </row>
     <row r="86" spans="1:14" ht="50.4">
       <c r="A86" s="11"/>
-      <c r="B86" s="127"/>
-      <c r="C86" s="65" t="str">
+      <c r="B86" s="118"/>
+      <c r="C86" s="64" t="str">
         <f>master!C70</f>
         <v>6-26. 実行例③</v>
       </c>
-      <c r="D86" s="123" t="s">
-        <v>167</v>
-      </c>
-      <c r="E86" s="124"/>
-      <c r="F86" s="125"/>
-      <c r="G86" s="65" t="s">
+      <c r="D86" s="107" t="s">
+        <v>165</v>
+      </c>
+      <c r="E86" s="108"/>
+      <c r="F86" s="109"/>
+      <c r="G86" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H86" s="66"/>
-      <c r="I86" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J86" s="68">
+      <c r="H86" s="65"/>
+      <c r="I86" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J86" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K86" s="69"/>
+      <c r="K86" s="68"/>
       <c r="L86" s="6"/>
       <c r="M86" s="6"/>
       <c r="N86" s="6"/>
     </row>
     <row r="87" spans="1:14" ht="126">
       <c r="A87" s="11"/>
-      <c r="B87" s="127"/>
-      <c r="C87" s="85"/>
-      <c r="D87" s="116" t="s">
-        <v>184</v>
-      </c>
-      <c r="E87" s="117"/>
-      <c r="F87" s="118"/>
-      <c r="G87" s="85" t="s">
+      <c r="B87" s="118"/>
+      <c r="C87" s="84"/>
+      <c r="D87" s="110" t="s">
+        <v>181</v>
+      </c>
+      <c r="E87" s="111"/>
+      <c r="F87" s="112"/>
+      <c r="G87" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="H87" s="86"/>
-      <c r="I87" s="87" t="s">
-        <v>25</v>
-      </c>
-      <c r="J87" s="88">
+      <c r="H87" s="85"/>
+      <c r="I87" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="J87" s="87">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="K87" s="89"/>
+      <c r="K87" s="88"/>
       <c r="L87" s="6"/>
       <c r="M87" s="6"/>
       <c r="N87" s="6"/>
     </row>
     <row r="88" spans="1:14" ht="50.4">
       <c r="A88" s="11"/>
-      <c r="B88" s="127"/>
-      <c r="C88" s="65" t="str">
+      <c r="B88" s="118"/>
+      <c r="C88" s="64" t="str">
         <f>master!C71</f>
         <v>6-27. 実行結果①</v>
       </c>
-      <c r="D88" s="123" t="s">
-        <v>169</v>
-      </c>
-      <c r="E88" s="124"/>
-      <c r="F88" s="125"/>
-      <c r="G88" s="65" t="s">
+      <c r="D88" s="107" t="s">
+        <v>167</v>
+      </c>
+      <c r="E88" s="108"/>
+      <c r="F88" s="109"/>
+      <c r="G88" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H88" s="66"/>
-      <c r="I88" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J88" s="68">
+      <c r="H88" s="65"/>
+      <c r="I88" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J88" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K88" s="69"/>
+      <c r="K88" s="68"/>
       <c r="L88" s="6"/>
       <c r="M88" s="6"/>
       <c r="N88" s="6"/>
     </row>
     <row r="89" spans="1:14" ht="50.4">
       <c r="A89" s="11"/>
-      <c r="B89" s="127"/>
-      <c r="C89" s="65" t="str">
+      <c r="B89" s="118"/>
+      <c r="C89" s="64" t="str">
         <f>master!C72</f>
         <v>6-28. 実行結果②</v>
       </c>
-      <c r="D89" s="123" t="s">
-        <v>170</v>
-      </c>
-      <c r="E89" s="124"/>
-      <c r="F89" s="125"/>
-      <c r="G89" s="65" t="s">
+      <c r="D89" s="107" t="s">
+        <v>168</v>
+      </c>
+      <c r="E89" s="108"/>
+      <c r="F89" s="109"/>
+      <c r="G89" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="H89" s="66"/>
-      <c r="I89" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J89" s="68">
+      <c r="H89" s="65"/>
+      <c r="I89" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J89" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K89" s="69"/>
+      <c r="K89" s="68"/>
       <c r="L89" s="6"/>
       <c r="M89" s="6"/>
       <c r="N89" s="6"/>
     </row>
     <row r="90" spans="1:14" ht="113.4">
       <c r="A90" s="11"/>
-      <c r="B90" s="128"/>
-      <c r="C90" s="65" t="str">
+      <c r="B90" s="114"/>
+      <c r="C90" s="64" t="str">
         <f>master!C73</f>
         <v>6-29. Planモード＆Agentモードまとめ</v>
       </c>
-      <c r="D90" s="123" t="s">
-        <v>171</v>
-      </c>
-      <c r="E90" s="124"/>
-      <c r="F90" s="125"/>
-      <c r="G90" s="65" t="s">
+      <c r="D90" s="107" t="s">
+        <v>169</v>
+      </c>
+      <c r="E90" s="108"/>
+      <c r="F90" s="109"/>
+      <c r="G90" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="H90" s="66"/>
-      <c r="I90" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="J90" s="68">
+      <c r="H90" s="65"/>
+      <c r="I90" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J90" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K90" s="69"/>
+      <c r="K90" s="68"/>
       <c r="L90" s="6"/>
       <c r="M90" s="6"/>
       <c r="N90" s="6"/>
     </row>
     <row r="91" spans="1:14" ht="102" customHeight="1">
       <c r="A91" s="11"/>
-      <c r="B91" s="126" t="str">
+      <c r="B91" s="113" t="str">
         <f>master!B74</f>
         <v>成果物のプレゼン</v>
       </c>
-      <c r="C91" s="85" t="str">
+      <c r="C91" s="84" t="str">
         <f>master!C74</f>
         <v>開発した成果物のプレゼン（グループ）</v>
       </c>
-      <c r="D91" s="116" t="s">
-        <v>200</v>
-      </c>
-      <c r="E91" s="117"/>
-      <c r="F91" s="118"/>
-      <c r="G91" s="85" t="s">
+      <c r="D91" s="110" t="s">
+        <v>197</v>
+      </c>
+      <c r="E91" s="111"/>
+      <c r="F91" s="112"/>
+      <c r="G91" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="H91" s="86"/>
-      <c r="I91" s="87" t="s">
-        <v>25</v>
-      </c>
-      <c r="J91" s="88">
+      <c r="H91" s="85"/>
+      <c r="I91" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="J91" s="87">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K91" s="89"/>
+      <c r="K91" s="88"/>
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
       <c r="N91" s="6"/>
     </row>
     <row r="92" spans="1:14" ht="88.2">
       <c r="A92" s="11"/>
-      <c r="B92" s="128"/>
-      <c r="C92" s="85" t="str">
+      <c r="B92" s="114"/>
+      <c r="C92" s="84" t="str">
         <f>master!C75</f>
         <v>開発した成果物のプレゼン（全体）</v>
       </c>
-      <c r="D92" s="116" t="s">
-        <v>195</v>
-      </c>
-      <c r="E92" s="117"/>
-      <c r="F92" s="118"/>
-      <c r="G92" s="85" t="s">
+      <c r="D92" s="110" t="s">
+        <v>192</v>
+      </c>
+      <c r="E92" s="111"/>
+      <c r="F92" s="112"/>
+      <c r="G92" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="H92" s="86"/>
-      <c r="I92" s="87" t="s">
+      <c r="H92" s="85"/>
+      <c r="I92" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="J92" s="88" t="s">
+      <c r="J92" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="K92" s="89" t="s">
-        <v>199</v>
+      <c r="K92" s="88" t="s">
+        <v>196</v>
       </c>
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
@@ -6531,32 +6545,61 @@
     <row r="94" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="B22:B36"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="B44:B55"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
     <mergeCell ref="B37:B43"/>
     <mergeCell ref="D60:F60"/>
     <mergeCell ref="D78:F78"/>
@@ -6573,63 +6616,34 @@
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="B56:B90"/>
     <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D68:F68"/>
     <mergeCell ref="D56:F56"/>
     <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="B44:B55"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="B22:B36"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6665,10 +6679,10 @@
       </c>
     </row>
     <row r="2" spans="2:3">
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="C2" s="81" t="s">
         <v>14</v>
       </c>
     </row>
@@ -6686,7 +6700,7 @@
       </c>
     </row>
     <row r="5" spans="2:3">
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="83" t="s">
         <v>57</v>
       </c>
       <c r="C5" t="s">
@@ -6704,7 +6718,7 @@
       </c>
     </row>
     <row r="8" spans="2:3">
-      <c r="B8" s="84" t="s">
+      <c r="B8" s="83" t="s">
         <v>103</v>
       </c>
       <c r="C8" t="s">
@@ -6732,8 +6746,8 @@
       </c>
     </row>
     <row r="13" spans="2:3">
-      <c r="B13" s="84" t="s">
-        <v>198</v>
+      <c r="B13" s="83" t="s">
+        <v>195</v>
       </c>
       <c r="C13" t="s">
         <v>63</v>
@@ -6810,7 +6824,7 @@
       </c>
     </row>
     <row r="28" spans="2:3">
-      <c r="B28" s="84" t="s">
+      <c r="B28" s="83" t="s">
         <v>81</v>
       </c>
       <c r="C28" t="s">
@@ -6848,7 +6862,7 @@
       </c>
     </row>
     <row r="35" spans="2:3">
-      <c r="B35" s="84" t="s">
+      <c r="B35" s="83" t="s">
         <v>80</v>
       </c>
       <c r="C35" t="s">
@@ -6901,7 +6915,7 @@
       </c>
     </row>
     <row r="45" spans="2:3">
-      <c r="B45" s="84" t="s">
+      <c r="B45" s="83" t="s">
         <v>84</v>
       </c>
       <c r="C45" t="s">
@@ -7053,12 +7067,12 @@
         <v>132</v>
       </c>
       <c r="C74" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="75" spans="2:3">
       <c r="C75" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/IG/7日版/AI Native-生成AI_IG.xlsx
+++ b/IG/7日版/AI Native-生成AI_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3D6FD9-0D6B-4144-A7AC-ED8B039FDDBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60224589-74D9-47BE-8256-95BA988DD336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -663,11 +663,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t xml:space="preserve">・AI-01
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>5-2. 例①：顧客提案向けの企画提案書を作りたい</t>
     <rPh sb="17" eb="19">
       <t>テイアン</t>
@@ -698,13 +693,6 @@
     <t>4-2. プロンプトを構成する4つの要素</t>
     <rPh sb="11" eb="13">
       <t>コウセイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>2-2. AIの変化</t>
-    <rPh sb="8" eb="10">
-      <t>ヘンカ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -832,76 +820,8 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>以下の内容を伝える。
-■学習項目
-　・ソフトウェア開発
-　・企画提案
-■実施構成
-　バイブコーディングフェーズ
-　企画提案フェーズ
-■各フェーズの概要の説明
-　バイブコーディングフェーズ⇒生成AIを活用し、システムを生成する
-　企画提案フェーズ⇒生成AIを活用し、企画提案書とプロトタイプを生成する</t>
-    <rPh sb="12" eb="14">
-      <t>ガクシュウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>コウセイ</t>
-    </rPh>
-    <rPh sb="69" eb="70">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="75" eb="77">
-      <t>ガイヨウ</t>
-    </rPh>
-    <rPh sb="78" eb="80">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="96" eb="98">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="101" eb="103">
-      <t>カツヨウ</t>
-    </rPh>
-    <rPh sb="110" eb="112">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="116" eb="118">
-      <t>キカク</t>
-    </rPh>
-    <rPh sb="118" eb="120">
-      <t>テイアン</t>
-    </rPh>
-    <rPh sb="134" eb="136">
-      <t>キカク</t>
-    </rPh>
-    <rPh sb="136" eb="139">
-      <t>テイアンショ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">・AI-01
 </t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">以下の内容を伝える。
-■生成AIとは
-　・自らデータを「生成」するAI
-　・自然言語インターフェース
-■AI時代の働き方の変化
-　・人間が手を動かす時代から、AIにどう指示を出すかを考える時代へ変化している。
-</t>
-    <rPh sb="12" eb="14">
-      <t>セイセイ</t>
-    </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -2364,6 +2284,72 @@
     <rPh sb="96" eb="97">
       <t>ツク</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-01
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を伝える。
+■研修の内容
+　・生成AIと協働しながら業務を自走する力を養い、AI時代の基盤となる人材を育成する研修
+■実施構成
+　バイブコーディングフェーズ
+　企画提案フェーズ
+■各フェーズの概要の説明
+　バイブコーディングフェーズ⇒生成AIを活用し、Java AP開発・単体テストをAIと実践する
+　企画提案フェーズ⇒生成AIを活用し、企画・モック・提案・改善をチームで実践する</t>
+    <rPh sb="12" eb="14">
+      <t>ケンシュウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="102" eb="104">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="105" eb="107">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="123" eb="125">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="128" eb="130">
+      <t>カツヨウ</t>
+    </rPh>
+    <rPh sb="157" eb="159">
+      <t>キカク</t>
+    </rPh>
+    <rPh sb="159" eb="161">
+      <t>テイアンキカク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">以下の内容を伝える。
+■生成AIとは
+　・自らデータを「生成」するAIのこと
+　　学習した膨大なデータをもとに、テキスト、画像、音声などを新しく生み出す
+　・自然言語インターフェース
+　　人間が普段使っている言葉（日本語や英語）で指示を出すだけで、高度な処理を実行できる
+■AI時代の働き方の変化
+　・人間が手を動かす時代から、AIにどう指示を出すかを考える時代へ変化している。
+</t>
+    <rPh sb="12" eb="14">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>2-2. 従来型AIと生成AIの比較</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -3047,6 +3033,9 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="20" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -3098,6 +3087,60 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3106,63 +3149,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3536,15 +3522,15 @@
   <sheetData>
     <row r="2" spans="1:8" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="91" t="str">
+      <c r="B2" s="92" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!B1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-生成AI_IG」</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
     </row>
     <row r="3" spans="1:8" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -3557,10 +3543,10 @@
     </row>
     <row r="4" spans="1:8" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="93"/>
+      <c r="C4" s="94"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -3568,18 +3554,18 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="94"/>
-      <c r="C5" s="95"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="96"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
     <row r="7" spans="1:8" ht="16.2">
-      <c r="B7" s="96" t="s">
+      <c r="B7" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="96"/>
+      <c r="C7" s="97"/>
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="24"/>
@@ -3639,7 +3625,7 @@
         <f>master!B5</f>
         <v>モジュール1：オリエンテーションとマインドセット変革</v>
       </c>
-      <c r="F14" s="90"/>
+      <c r="F14" s="91"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8">
@@ -3651,7 +3637,7 @@
         <f>master!B8</f>
         <v>モジュール2：AI・LLMの基礎理解</v>
       </c>
-      <c r="F15" s="90"/>
+      <c r="F15" s="91"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8">
@@ -3665,21 +3651,21 @@
         <f>master!B13</f>
         <v>モジュール3：NTTデータが目指すAIビジネス（Vision）</v>
       </c>
-      <c r="F16" s="90"/>
+      <c r="F16" s="91"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="38"/>
       <c r="B17" s="69"/>
       <c r="C17" s="73"/>
-      <c r="F17" s="90"/>
+      <c r="F17" s="91"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="38"/>
       <c r="B18" s="41"/>
       <c r="C18" s="74"/>
-      <c r="F18" s="90"/>
+      <c r="F18" s="91"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8">
@@ -3691,7 +3677,7 @@
         <f>master!B28</f>
         <v>モジュール4：プロンプトエンジニアリング</v>
       </c>
-      <c r="F19" s="90"/>
+      <c r="F19" s="91"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8">
@@ -3700,7 +3686,7 @@
       </c>
       <c r="B20" s="42"/>
       <c r="C20" s="74"/>
-      <c r="F20" s="90"/>
+      <c r="F20" s="91"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8">
@@ -3708,10 +3694,10 @@
       <c r="B21" s="17">
         <v>0.51041666666666663</v>
       </c>
-      <c r="C21" s="128" t="s">
+      <c r="C21" s="90" t="s">
         <v>51</v>
       </c>
-      <c r="F21" s="90"/>
+      <c r="F21" s="91"/>
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8">
@@ -3767,7 +3753,7 @@
         <f>master!B35</f>
         <v>モジュール5：ハンズオン（ChatGPT）</v>
       </c>
-      <c r="F26" s="90"/>
+      <c r="F26" s="91"/>
       <c r="G26" s="14"/>
       <c r="H26" s="6"/>
     </row>
@@ -3775,7 +3761,7 @@
       <c r="A27" s="39"/>
       <c r="B27" s="42"/>
       <c r="C27" s="58"/>
-      <c r="F27" s="90"/>
+      <c r="F27" s="91"/>
       <c r="G27" s="14"/>
       <c r="H27" s="6"/>
     </row>
@@ -3785,7 +3771,7 @@
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="58"/>
-      <c r="F28" s="90"/>
+      <c r="F28" s="91"/>
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8">
@@ -3794,7 +3780,7 @@
       <c r="C29" s="59"/>
       <c r="D29" s="55"/>
       <c r="E29" s="52"/>
-      <c r="F29" s="90"/>
+      <c r="F29" s="91"/>
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8">
@@ -3808,7 +3794,7 @@
       </c>
       <c r="D30" s="55"/>
       <c r="E30" s="52"/>
-      <c r="F30" s="90"/>
+      <c r="F30" s="91"/>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8">
@@ -3817,7 +3803,7 @@
       <c r="C31" s="58"/>
       <c r="D31" s="55"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="90"/>
+      <c r="F31" s="91"/>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8">
@@ -3828,7 +3814,7 @@
       <c r="C32" s="58"/>
       <c r="D32" s="55"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="90"/>
+      <c r="F32" s="91"/>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8">
@@ -3837,7 +3823,7 @@
       <c r="C33" s="58"/>
       <c r="D33" s="55"/>
       <c r="E33" s="52"/>
-      <c r="F33" s="90"/>
+      <c r="F33" s="91"/>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8">
@@ -3846,7 +3832,7 @@
       <c r="C34" s="58"/>
       <c r="D34" s="55"/>
       <c r="E34" s="52"/>
-      <c r="F34" s="90"/>
+      <c r="F34" s="91"/>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8">
@@ -3855,7 +3841,7 @@
       <c r="C35" s="58"/>
       <c r="D35" s="55"/>
       <c r="E35" s="52"/>
-      <c r="F35" s="90"/>
+      <c r="F35" s="91"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8">
@@ -3866,7 +3852,7 @@
       <c r="C36" s="58"/>
       <c r="D36" s="55"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="90"/>
+      <c r="F36" s="91"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8">
@@ -3875,7 +3861,7 @@
       <c r="C37" s="58"/>
       <c r="D37" s="55"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="90"/>
+      <c r="F37" s="91"/>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8">
@@ -3884,7 +3870,7 @@
       <c r="C38" s="58"/>
       <c r="D38" s="55"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="90"/>
+      <c r="F38" s="91"/>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8">
@@ -3893,7 +3879,7 @@
       <c r="C39" s="58"/>
       <c r="D39" s="55"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="90"/>
+      <c r="F39" s="91"/>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8">
@@ -3904,7 +3890,7 @@
       <c r="C40" s="59"/>
       <c r="D40" s="55"/>
       <c r="E40" s="52"/>
-      <c r="F40" s="90"/>
+      <c r="F40" s="91"/>
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8">
@@ -3918,7 +3904,7 @@
       </c>
       <c r="D41" s="57"/>
       <c r="E41" s="53"/>
-      <c r="F41" s="90"/>
+      <c r="F41" s="91"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8">
@@ -3927,7 +3913,7 @@
       <c r="C42" s="59"/>
       <c r="D42" s="55"/>
       <c r="E42" s="53"/>
-      <c r="F42" s="90"/>
+      <c r="F42" s="91"/>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1">
@@ -4014,10 +4000,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="102"/>
+      <c r="C4" s="103"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -4028,16 +4014,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -4052,10 +4038,10 @@
       <c r="C7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="104" t="s">
+      <c r="D7" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="104"/>
+      <c r="E7" s="105"/>
       <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
@@ -4087,46 +4073,46 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="10"/>
-      <c r="B10" s="98"/>
-      <c r="C10" s="98" t="s">
+      <c r="B10" s="99"/>
+      <c r="C10" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="98" t="s">
+      <c r="D10" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98" t="s">
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="105" t="s">
+      <c r="H10" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="97" t="s">
+      <c r="I10" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="97"/>
-      <c r="K10" s="97" t="s">
+      <c r="J10" s="98"/>
+      <c r="K10" s="98" t="s">
         <v>31</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="98"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="106"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="107"/>
       <c r="I11" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J11" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="98"/>
+      <c r="K11" s="99"/>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="63">
@@ -4135,11 +4121,11 @@
       <c r="C12" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="99" t="s">
+      <c r="D12" s="100" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="100"/>
-      <c r="F12" s="101"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="102"/>
       <c r="G12" s="82" t="s">
         <v>50</v>
       </c>
@@ -4238,12 +4224,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -4254,18 +4240,18 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="125" t="s">
-        <v>199</v>
-      </c>
-      <c r="C5" s="125"/>
-      <c r="D5" s="125"/>
-      <c r="E5" s="125"/>
-      <c r="F5" s="125"/>
-      <c r="G5" s="125"/>
-      <c r="H5" s="125"/>
-      <c r="I5" s="125"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="125"/>
+      <c r="B5" s="108" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" s="108"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
       <c r="L5" s="29"/>
       <c r="M5" s="30"/>
     </row>
@@ -4285,10 +4271,10 @@
       <c r="C7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="104" t="s">
+      <c r="D7" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="104"/>
+      <c r="E7" s="105"/>
       <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
@@ -4307,7 +4293,7 @@
         <v>34</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D8" s="45" t="s">
         <v>20</v>
@@ -4326,28 +4312,28 @@
     </row>
     <row r="10" spans="1:14" ht="24" customHeight="1">
       <c r="A10" s="10"/>
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="98" t="s">
+      <c r="C10" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="98" t="s">
+      <c r="D10" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98" t="s">
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="97" t="s">
+      <c r="H10" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="126" t="s">
+      <c r="I10" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="127"/>
-      <c r="K10" s="97" t="s">
+      <c r="J10" s="110"/>
+      <c r="K10" s="98" t="s">
         <v>33</v>
       </c>
       <c r="L10" s="6"/>
@@ -4356,27 +4342,27 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="10"/>
-      <c r="B11" s="98"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="97"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="98"/>
       <c r="I11" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J11" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="98"/>
+      <c r="K11" s="99"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
     </row>
     <row r="12" spans="1:14" ht="88.2">
       <c r="A12" s="10"/>
-      <c r="B12" s="123" t="str">
+      <c r="B12" s="111" t="str">
         <f>master!B3</f>
         <v>自己紹介</v>
       </c>
@@ -4384,11 +4370,11 @@
         <f>master!C3</f>
         <v>講師の自己紹介</v>
       </c>
-      <c r="D12" s="119" t="s">
-        <v>208</v>
-      </c>
-      <c r="E12" s="120"/>
-      <c r="F12" s="121"/>
+      <c r="D12" s="113" t="s">
+        <v>204</v>
+      </c>
+      <c r="E12" s="114"/>
+      <c r="F12" s="115"/>
       <c r="G12" s="51" t="s">
         <v>49</v>
       </c>
@@ -4406,18 +4392,18 @@
     </row>
     <row r="13" spans="1:14" ht="126">
       <c r="A13" s="10"/>
-      <c r="B13" s="124"/>
+      <c r="B13" s="112"/>
       <c r="C13" s="84" t="str">
         <f>master!C4</f>
         <v>受講生の自己紹介</v>
       </c>
-      <c r="D13" s="110" t="s">
-        <v>210</v>
-      </c>
-      <c r="E13" s="111"/>
-      <c r="F13" s="112"/>
+      <c r="D13" s="116" t="s">
+        <v>206</v>
+      </c>
+      <c r="E13" s="117"/>
+      <c r="F13" s="118"/>
       <c r="G13" s="84" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H13" s="85"/>
       <c r="I13" s="86" t="s">
@@ -4427,15 +4413,15 @@
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="K13" s="88" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14" ht="163.80000000000001">
+    <row r="14" spans="1:14" ht="151.19999999999999">
       <c r="A14" s="11"/>
-      <c r="B14" s="122" t="str">
+      <c r="B14" s="119" t="str">
         <f>master!B5</f>
         <v>モジュール1：オリエンテーションとマインドセット変革</v>
       </c>
@@ -4443,13 +4429,13 @@
         <f>master!C5</f>
         <v>1-1. 研修概要</v>
       </c>
-      <c r="D14" s="119" t="s">
-        <v>136</v>
-      </c>
-      <c r="E14" s="120"/>
-      <c r="F14" s="121"/>
+      <c r="D14" s="113" t="s">
+        <v>208</v>
+      </c>
+      <c r="E14" s="114"/>
+      <c r="F14" s="115"/>
       <c r="G14" s="51" t="s">
-        <v>104</v>
+        <v>207</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="49" t="s">
@@ -4465,16 +4451,16 @@
     </row>
     <row r="15" spans="1:14" ht="100.8">
       <c r="A15" s="11"/>
-      <c r="B15" s="122"/>
+      <c r="B15" s="119"/>
       <c r="C15" s="51" t="str">
         <f>master!C6</f>
         <v>1-2. 背景・目的</v>
       </c>
-      <c r="D15" s="119" t="s">
-        <v>135</v>
-      </c>
-      <c r="E15" s="120"/>
-      <c r="F15" s="121"/>
+      <c r="D15" s="113" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" s="114"/>
+      <c r="F15" s="115"/>
       <c r="G15" s="51" t="s">
         <v>47</v>
       </c>
@@ -4492,18 +4478,18 @@
     </row>
     <row r="16" spans="1:14" ht="214.2">
       <c r="A16" s="11"/>
-      <c r="B16" s="122"/>
+      <c r="B16" s="119"/>
       <c r="C16" s="51" t="str">
         <f>master!C7</f>
         <v>1-3. 研修ゴールと獲得可能な経験背景・目的</v>
       </c>
-      <c r="D16" s="119" t="s">
-        <v>175</v>
-      </c>
-      <c r="E16" s="120"/>
-      <c r="F16" s="121"/>
+      <c r="D16" s="113" t="s">
+        <v>171</v>
+      </c>
+      <c r="E16" s="114"/>
+      <c r="F16" s="115"/>
       <c r="G16" s="51" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="49" t="s">
@@ -4517,9 +4503,9 @@
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:14" ht="88.2">
+    <row r="17" spans="1:14" ht="113.4">
       <c r="A17" s="11"/>
-      <c r="B17" s="115" t="str">
+      <c r="B17" s="120" t="str">
         <f>master!B8</f>
         <v>モジュール2：AI・LLMの基礎理解</v>
       </c>
@@ -4527,13 +4513,13 @@
         <f>master!C8</f>
         <v>2-1. 生成AI（Generative AI）とは？</v>
       </c>
-      <c r="D17" s="119" t="s">
-        <v>138</v>
-      </c>
-      <c r="E17" s="120"/>
-      <c r="F17" s="121"/>
+      <c r="D17" s="113" t="s">
+        <v>209</v>
+      </c>
+      <c r="E17" s="114"/>
+      <c r="F17" s="115"/>
       <c r="G17" s="51" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="49" t="s">
@@ -4549,16 +4535,16 @@
     </row>
     <row r="18" spans="1:14" ht="113.4">
       <c r="A18" s="11"/>
-      <c r="B18" s="116"/>
+      <c r="B18" s="121"/>
       <c r="C18" s="51" t="str">
         <f>master!C9</f>
-        <v>2-2. AIの変化</v>
-      </c>
-      <c r="D18" s="119" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18" s="120"/>
-      <c r="F18" s="121"/>
+        <v>2-2. 従来型AIと生成AIの比較</v>
+      </c>
+      <c r="D18" s="113" t="s">
+        <v>135</v>
+      </c>
+      <c r="E18" s="114"/>
+      <c r="F18" s="115"/>
       <c r="G18" s="51" t="s">
         <v>43</v>
       </c>
@@ -4576,16 +4562,16 @@
     </row>
     <row r="19" spans="1:14" ht="113.4">
       <c r="A19" s="11"/>
-      <c r="B19" s="116"/>
+      <c r="B19" s="121"/>
       <c r="C19" s="51" t="str">
         <f>master!C10</f>
         <v>2-3. LLM（大規模言語モデル）の仕組み</v>
       </c>
-      <c r="D19" s="119" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19" s="120"/>
-      <c r="F19" s="121"/>
+      <c r="D19" s="113" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="114"/>
+      <c r="F19" s="115"/>
       <c r="G19" s="51" t="s">
         <v>43</v>
       </c>
@@ -4603,16 +4589,16 @@
     </row>
     <row r="20" spans="1:14" ht="126">
       <c r="A20" s="11"/>
-      <c r="B20" s="116"/>
+      <c r="B20" s="121"/>
       <c r="C20" s="51" t="str">
         <f>master!C11</f>
         <v>2-4. 生成AIの「苦手なこと」（弱み）</v>
       </c>
-      <c r="D20" s="119" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" s="120"/>
-      <c r="F20" s="121"/>
+      <c r="D20" s="113" t="s">
+        <v>137</v>
+      </c>
+      <c r="E20" s="114"/>
+      <c r="F20" s="115"/>
       <c r="G20" s="51" t="s">
         <v>44</v>
       </c>
@@ -4630,18 +4616,18 @@
     </row>
     <row r="21" spans="1:14" ht="239.4">
       <c r="A21" s="11"/>
-      <c r="B21" s="117"/>
+      <c r="B21" s="122"/>
       <c r="C21" s="51" t="str">
         <f>master!C12</f>
         <v>2-5. 生成AIを使う心得８条</v>
       </c>
-      <c r="D21" s="119" t="s">
-        <v>176</v>
-      </c>
-      <c r="E21" s="120"/>
-      <c r="F21" s="121"/>
+      <c r="D21" s="113" t="s">
+        <v>172</v>
+      </c>
+      <c r="E21" s="114"/>
+      <c r="F21" s="115"/>
       <c r="G21" s="51" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="49" t="s">
@@ -4657,7 +4643,7 @@
     </row>
     <row r="22" spans="1:14" ht="25.2">
       <c r="A22" s="11"/>
-      <c r="B22" s="122" t="str">
+      <c r="B22" s="119" t="str">
         <f>master!B13</f>
         <v>モジュール3：NTTデータが目指すAIビジネス（Vision）</v>
       </c>
@@ -4665,9 +4651,9 @@
         <f>master!C13</f>
         <v>3-1. 本モジュールで学ぶこと①</v>
       </c>
-      <c r="D22" s="119"/>
-      <c r="E22" s="120"/>
-      <c r="F22" s="121"/>
+      <c r="D22" s="113"/>
+      <c r="E22" s="114"/>
+      <c r="F22" s="115"/>
       <c r="G22" s="51" t="s">
         <v>46</v>
       </c>
@@ -4685,14 +4671,14 @@
     </row>
     <row r="23" spans="1:14" ht="25.2">
       <c r="A23" s="11"/>
-      <c r="B23" s="122"/>
+      <c r="B23" s="119"/>
       <c r="C23" s="51" t="str">
         <f>master!C14</f>
         <v>3-2. NTTデータのAI戦略：Quality Growthとは</v>
       </c>
-      <c r="D23" s="119"/>
-      <c r="E23" s="120"/>
-      <c r="F23" s="121"/>
+      <c r="D23" s="113"/>
+      <c r="E23" s="114"/>
+      <c r="F23" s="115"/>
       <c r="G23" s="51" t="s">
         <v>46</v>
       </c>
@@ -4710,14 +4696,14 @@
     </row>
     <row r="24" spans="1:14" ht="25.2">
       <c r="A24" s="11"/>
-      <c r="B24" s="122"/>
+      <c r="B24" s="119"/>
       <c r="C24" s="51" t="str">
         <f>master!C15</f>
         <v>3-3. なぜ今、AIが重要なのか</v>
       </c>
-      <c r="D24" s="119"/>
-      <c r="E24" s="120"/>
-      <c r="F24" s="121"/>
+      <c r="D24" s="113"/>
+      <c r="E24" s="114"/>
+      <c r="F24" s="115"/>
       <c r="G24" s="51" t="s">
         <v>46</v>
       </c>
@@ -4735,14 +4721,14 @@
     </row>
     <row r="25" spans="1:14" ht="25.2">
       <c r="A25" s="11"/>
-      <c r="B25" s="122"/>
+      <c r="B25" s="119"/>
       <c r="C25" s="51" t="str">
         <f>master!C16</f>
         <v>3-4. 生成AIの進化：今、どこにいるか</v>
       </c>
-      <c r="D25" s="119"/>
-      <c r="E25" s="120"/>
-      <c r="F25" s="121"/>
+      <c r="D25" s="113"/>
+      <c r="E25" s="114"/>
+      <c r="F25" s="115"/>
       <c r="G25" s="51" t="s">
         <v>46</v>
       </c>
@@ -4760,14 +4746,14 @@
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
       <c r="A26" s="11"/>
-      <c r="B26" s="122"/>
+      <c r="B26" s="119"/>
       <c r="C26" s="51" t="str">
         <f>master!C17</f>
         <v>3-5. 本モジュールで学ぶこと②</v>
       </c>
-      <c r="D26" s="119"/>
-      <c r="E26" s="120"/>
-      <c r="F26" s="121"/>
+      <c r="D26" s="113"/>
+      <c r="E26" s="114"/>
+      <c r="F26" s="115"/>
       <c r="G26" s="51" t="s">
         <v>37</v>
       </c>
@@ -4785,16 +4771,16 @@
     </row>
     <row r="27" spans="1:14" ht="63">
       <c r="A27" s="11"/>
-      <c r="B27" s="122"/>
+      <c r="B27" s="119"/>
       <c r="C27" s="51" t="str">
         <f>master!C18</f>
         <v>3-6. エージェントAI（Agentic AI）とは何か</v>
       </c>
-      <c r="D27" s="119" t="s">
-        <v>177</v>
-      </c>
-      <c r="E27" s="120"/>
-      <c r="F27" s="121"/>
+      <c r="D27" s="113" t="s">
+        <v>173</v>
+      </c>
+      <c r="E27" s="114"/>
+      <c r="F27" s="115"/>
       <c r="G27" s="51" t="s">
         <v>39</v>
       </c>
@@ -4812,16 +4798,16 @@
     </row>
     <row r="28" spans="1:14" ht="63">
       <c r="A28" s="11"/>
-      <c r="B28" s="122"/>
+      <c r="B28" s="119"/>
       <c r="C28" s="51" t="str">
         <f>master!C19</f>
         <v>3-7. エージェントの処理</v>
       </c>
-      <c r="D28" s="119" t="s">
-        <v>143</v>
-      </c>
-      <c r="E28" s="120"/>
-      <c r="F28" s="121"/>
+      <c r="D28" s="113" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" s="114"/>
+      <c r="F28" s="115"/>
       <c r="G28" s="51" t="s">
         <v>39</v>
       </c>
@@ -4839,14 +4825,14 @@
     </row>
     <row r="29" spans="1:14" ht="37.799999999999997">
       <c r="A29" s="11"/>
-      <c r="B29" s="122"/>
+      <c r="B29" s="119"/>
       <c r="C29" s="51" t="str">
         <f>master!C20</f>
         <v>3-8. 本モジュールで学ぶこと③</v>
       </c>
-      <c r="D29" s="119"/>
-      <c r="E29" s="120"/>
-      <c r="F29" s="121"/>
+      <c r="D29" s="113"/>
+      <c r="E29" s="114"/>
+      <c r="F29" s="115"/>
       <c r="G29" s="51" t="s">
         <v>40</v>
       </c>
@@ -4864,14 +4850,14 @@
     </row>
     <row r="30" spans="1:14" ht="37.799999999999997">
       <c r="A30" s="11"/>
-      <c r="B30" s="122"/>
+      <c r="B30" s="119"/>
       <c r="C30" s="51" t="str">
         <f>master!C21</f>
         <v>3-9. NTTデータが描く未来：Smart AI Agent®</v>
       </c>
-      <c r="D30" s="119"/>
-      <c r="E30" s="120"/>
-      <c r="F30" s="121"/>
+      <c r="D30" s="113"/>
+      <c r="E30" s="114"/>
+      <c r="F30" s="115"/>
       <c r="G30" s="51" t="s">
         <v>40</v>
       </c>
@@ -4889,14 +4875,14 @@
     </row>
     <row r="31" spans="1:14" ht="37.799999999999997">
       <c r="A31" s="11"/>
-      <c r="B31" s="122"/>
+      <c r="B31" s="119"/>
       <c r="C31" s="51" t="str">
         <f>master!C22</f>
         <v>3-10. AIの強みを生かした業務変革の進め方</v>
       </c>
-      <c r="D31" s="119"/>
-      <c r="E31" s="120"/>
-      <c r="F31" s="121"/>
+      <c r="D31" s="113"/>
+      <c r="E31" s="114"/>
+      <c r="F31" s="115"/>
       <c r="G31" s="51" t="s">
         <v>40</v>
       </c>
@@ -4914,14 +4900,14 @@
     </row>
     <row r="32" spans="1:14" ht="37.799999999999997">
       <c r="A32" s="11"/>
-      <c r="B32" s="122"/>
+      <c r="B32" s="119"/>
       <c r="C32" s="51" t="str">
         <f>master!C23</f>
         <v>3-11. AIの強みを生かすポイント：人とAIとの役割分担</v>
       </c>
-      <c r="D32" s="119"/>
-      <c r="E32" s="120"/>
-      <c r="F32" s="121"/>
+      <c r="D32" s="113"/>
+      <c r="E32" s="114"/>
+      <c r="F32" s="115"/>
       <c r="G32" s="51" t="s">
         <v>40</v>
       </c>
@@ -4939,14 +4925,14 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="122"/>
+      <c r="B33" s="119"/>
       <c r="C33" s="51" t="str">
         <f>master!C24</f>
         <v>3-12. AIの強みを生かすポイント：プロセス自体をAI前提で再設計</v>
       </c>
-      <c r="D33" s="119"/>
-      <c r="E33" s="120"/>
-      <c r="F33" s="121"/>
+      <c r="D33" s="113"/>
+      <c r="E33" s="114"/>
+      <c r="F33" s="115"/>
       <c r="G33" s="51" t="s">
         <v>40</v>
       </c>
@@ -4964,14 +4950,14 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="122"/>
+      <c r="B34" s="119"/>
       <c r="C34" s="51" t="str">
         <f>master!C25</f>
         <v>3-13. JALカード様 -  AIバーチャル顧客を活用したマーケティング高度化</v>
       </c>
-      <c r="D34" s="119"/>
-      <c r="E34" s="120"/>
-      <c r="F34" s="121"/>
+      <c r="D34" s="113"/>
+      <c r="E34" s="114"/>
+      <c r="F34" s="115"/>
       <c r="G34" s="51" t="s">
         <v>40</v>
       </c>
@@ -4989,14 +4975,14 @@
     </row>
     <row r="35" spans="1:14" ht="37.799999999999997">
       <c r="A35" s="11"/>
-      <c r="B35" s="122"/>
+      <c r="B35" s="119"/>
       <c r="C35" s="51" t="str">
         <f>master!C26</f>
         <v>3-14. 大手メディアサービス会社 - AI-BPOによるオペレーション変革</v>
       </c>
-      <c r="D35" s="119"/>
-      <c r="E35" s="120"/>
-      <c r="F35" s="121"/>
+      <c r="D35" s="113"/>
+      <c r="E35" s="114"/>
+      <c r="F35" s="115"/>
       <c r="G35" s="51" t="s">
         <v>40</v>
       </c>
@@ -5014,14 +5000,14 @@
     </row>
     <row r="36" spans="1:14" ht="37.799999999999997">
       <c r="A36" s="11"/>
-      <c r="B36" s="122"/>
+      <c r="B36" s="119"/>
       <c r="C36" s="51" t="str">
         <f>master!C27</f>
         <v>Appendix：りそな様 - AI CoEと生成AI人財育成アカデミーの推進</v>
       </c>
-      <c r="D36" s="119"/>
-      <c r="E36" s="120"/>
-      <c r="F36" s="121"/>
+      <c r="D36" s="113"/>
+      <c r="E36" s="114"/>
+      <c r="F36" s="115"/>
       <c r="G36" s="51" t="s">
         <v>40</v>
       </c>
@@ -5039,7 +5025,7 @@
     </row>
     <row r="37" spans="1:14" ht="88.2">
       <c r="A37" s="11"/>
-      <c r="B37" s="115" t="str">
+      <c r="B37" s="120" t="str">
         <f>master!B28</f>
         <v>モジュール4：プロンプトエンジニアリング</v>
       </c>
@@ -5047,11 +5033,11 @@
         <f>master!C28</f>
         <v>4-1. プロンプトとは?</v>
       </c>
-      <c r="D37" s="119" t="s">
-        <v>178</v>
-      </c>
-      <c r="E37" s="120"/>
-      <c r="F37" s="121"/>
+      <c r="D37" s="113" t="s">
+        <v>174</v>
+      </c>
+      <c r="E37" s="114"/>
+      <c r="F37" s="115"/>
       <c r="G37" s="51" t="s">
         <v>45</v>
       </c>
@@ -5069,16 +5055,16 @@
     </row>
     <row r="38" spans="1:14" ht="37.799999999999997">
       <c r="A38" s="11"/>
-      <c r="B38" s="116"/>
+      <c r="B38" s="121"/>
       <c r="C38" s="51" t="str">
         <f>master!C29</f>
         <v>4-2. プロンプトを構成する4つの要素</v>
       </c>
-      <c r="D38" s="119" t="s">
-        <v>144</v>
-      </c>
-      <c r="E38" s="120"/>
-      <c r="F38" s="121"/>
+      <c r="D38" s="113" t="s">
+        <v>140</v>
+      </c>
+      <c r="E38" s="114"/>
+      <c r="F38" s="115"/>
       <c r="G38" s="51" t="s">
         <v>40</v>
       </c>
@@ -5096,16 +5082,16 @@
     </row>
     <row r="39" spans="1:14" ht="63">
       <c r="A39" s="11"/>
-      <c r="B39" s="116"/>
+      <c r="B39" s="121"/>
       <c r="C39" s="51" t="str">
         <f>master!C30</f>
         <v>4-3. 悪いプロンプト vs 良いプロンプト</v>
       </c>
-      <c r="D39" s="119" t="s">
-        <v>145</v>
-      </c>
-      <c r="E39" s="120"/>
-      <c r="F39" s="121"/>
+      <c r="D39" s="113" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" s="114"/>
+      <c r="F39" s="115"/>
       <c r="G39" s="51" t="s">
         <v>39</v>
       </c>
@@ -5123,14 +5109,14 @@
     </row>
     <row r="40" spans="1:14" ht="37.799999999999997">
       <c r="A40" s="11"/>
-      <c r="B40" s="116"/>
+      <c r="B40" s="121"/>
       <c r="C40" s="51" t="str">
         <f>master!C31</f>
         <v>4-4. テクニック①：Role Prompting（役割の付与）</v>
       </c>
-      <c r="D40" s="119"/>
-      <c r="E40" s="120"/>
-      <c r="F40" s="121"/>
+      <c r="D40" s="113"/>
+      <c r="E40" s="114"/>
+      <c r="F40" s="115"/>
       <c r="G40" s="51" t="s">
         <v>40</v>
       </c>
@@ -5148,14 +5134,14 @@
     </row>
     <row r="41" spans="1:14" ht="37.799999999999997">
       <c r="A41" s="11"/>
-      <c r="B41" s="116"/>
+      <c r="B41" s="121"/>
       <c r="C41" s="51" t="str">
         <f>master!C32</f>
         <v>4-5. テクニック②：区切り文字の活用</v>
       </c>
-      <c r="D41" s="119"/>
-      <c r="E41" s="120"/>
-      <c r="F41" s="121"/>
+      <c r="D41" s="113"/>
+      <c r="E41" s="114"/>
+      <c r="F41" s="115"/>
       <c r="G41" s="51" t="s">
         <v>40</v>
       </c>
@@ -5173,14 +5159,14 @@
     </row>
     <row r="42" spans="1:14" ht="37.799999999999997">
       <c r="A42" s="11"/>
-      <c r="B42" s="116"/>
+      <c r="B42" s="121"/>
       <c r="C42" s="51" t="str">
         <f>master!C33</f>
         <v>4-6. テクニック③：Zero-shot vs Few-shot</v>
       </c>
-      <c r="D42" s="119"/>
-      <c r="E42" s="120"/>
-      <c r="F42" s="121"/>
+      <c r="D42" s="113"/>
+      <c r="E42" s="114"/>
+      <c r="F42" s="115"/>
       <c r="G42" s="51" t="s">
         <v>40</v>
       </c>
@@ -5198,14 +5184,14 @@
     </row>
     <row r="43" spans="1:14" ht="50.4">
       <c r="A43" s="11"/>
-      <c r="B43" s="117"/>
+      <c r="B43" s="122"/>
       <c r="C43" s="51" t="str">
         <f>master!C34</f>
         <v>4-7. テクニック④：Chain of Thought（思考の連鎖）</v>
       </c>
-      <c r="D43" s="119"/>
-      <c r="E43" s="120"/>
-      <c r="F43" s="121"/>
+      <c r="D43" s="113"/>
+      <c r="E43" s="114"/>
+      <c r="F43" s="115"/>
       <c r="G43" s="51" t="s">
         <v>41</v>
       </c>
@@ -5223,7 +5209,7 @@
     </row>
     <row r="44" spans="1:14" ht="75.599999999999994">
       <c r="A44" s="11"/>
-      <c r="B44" s="113" t="str">
+      <c r="B44" s="123" t="str">
         <f>master!B35</f>
         <v>モジュール5：ハンズオン（ChatGPT）</v>
       </c>
@@ -5231,11 +5217,11 @@
         <f>master!C35</f>
         <v>5-1. ChatGPTの使い方（一般チャット）</v>
       </c>
-      <c r="D44" s="107" t="s">
-        <v>179</v>
-      </c>
-      <c r="E44" s="108"/>
-      <c r="F44" s="109"/>
+      <c r="D44" s="126" t="s">
+        <v>175</v>
+      </c>
+      <c r="E44" s="127"/>
+      <c r="F44" s="128"/>
       <c r="G44" s="64" t="s">
         <v>42</v>
       </c>
@@ -5253,16 +5239,16 @@
     </row>
     <row r="45" spans="1:14" ht="126">
       <c r="A45" s="11"/>
-      <c r="B45" s="118"/>
+      <c r="B45" s="124"/>
       <c r="C45" s="64" t="str">
         <f>master!C36</f>
         <v>5-2. 例①：顧客提案向けの企画提案書を作りたい</v>
       </c>
-      <c r="D45" s="107" t="s">
-        <v>187</v>
-      </c>
-      <c r="E45" s="108"/>
-      <c r="F45" s="109"/>
+      <c r="D45" s="126" t="s">
+        <v>183</v>
+      </c>
+      <c r="E45" s="127"/>
+      <c r="F45" s="128"/>
       <c r="G45" s="64" t="s">
         <v>44</v>
       </c>
@@ -5280,16 +5266,16 @@
     </row>
     <row r="46" spans="1:14" ht="126">
       <c r="A46" s="11"/>
-      <c r="B46" s="118"/>
+      <c r="B46" s="124"/>
       <c r="C46" s="64" t="str">
         <f>master!C37</f>
         <v>5-3. 例①：顧客提案向けの企画提案書を作りたい - プロンプト例</v>
       </c>
-      <c r="D46" s="107" t="s">
-        <v>147</v>
-      </c>
-      <c r="E46" s="108"/>
-      <c r="F46" s="109"/>
+      <c r="D46" s="126" t="s">
+        <v>143</v>
+      </c>
+      <c r="E46" s="127"/>
+      <c r="F46" s="128"/>
       <c r="G46" s="64" t="s">
         <v>44</v>
       </c>
@@ -5307,16 +5293,16 @@
     </row>
     <row r="47" spans="1:14" ht="37.799999999999997">
       <c r="A47" s="11"/>
-      <c r="B47" s="118"/>
+      <c r="B47" s="124"/>
       <c r="C47" s="64" t="str">
         <f>master!C38</f>
         <v>5-4. 例①：顧客提案向けの企画提案書を作りたい - 実行例</v>
       </c>
-      <c r="D47" s="107" t="s">
-        <v>146</v>
-      </c>
-      <c r="E47" s="108"/>
-      <c r="F47" s="109"/>
+      <c r="D47" s="126" t="s">
+        <v>142</v>
+      </c>
+      <c r="E47" s="127"/>
+      <c r="F47" s="128"/>
       <c r="G47" s="64" t="s">
         <v>40</v>
       </c>
@@ -5334,13 +5320,13 @@
     </row>
     <row r="48" spans="1:14" ht="88.2">
       <c r="A48" s="11"/>
-      <c r="B48" s="118"/>
+      <c r="B48" s="124"/>
       <c r="C48" s="84"/>
-      <c r="D48" s="110" t="s">
-        <v>186</v>
-      </c>
-      <c r="E48" s="111"/>
-      <c r="F48" s="112"/>
+      <c r="D48" s="116" t="s">
+        <v>182</v>
+      </c>
+      <c r="E48" s="117"/>
+      <c r="F48" s="118"/>
       <c r="G48" s="84" t="s">
         <v>45</v>
       </c>
@@ -5352,7 +5338,7 @@
         <v>1.3888888888888888E-2</v>
       </c>
       <c r="K48" s="88" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
@@ -5360,16 +5346,16 @@
     </row>
     <row r="49" spans="1:14" ht="50.4">
       <c r="A49" s="11"/>
-      <c r="B49" s="118"/>
+      <c r="B49" s="124"/>
       <c r="C49" s="64" t="str">
         <f>master!C39</f>
         <v>5-5. 例②：100本ノックを作ってみる</v>
       </c>
-      <c r="D49" s="107" t="s">
-        <v>194</v>
-      </c>
-      <c r="E49" s="108"/>
-      <c r="F49" s="109"/>
+      <c r="D49" s="126" t="s">
+        <v>190</v>
+      </c>
+      <c r="E49" s="127"/>
+      <c r="F49" s="128"/>
       <c r="G49" s="64" t="s">
         <v>41</v>
       </c>
@@ -5387,16 +5373,16 @@
     </row>
     <row r="50" spans="1:14" ht="75.599999999999994">
       <c r="A50" s="11"/>
-      <c r="B50" s="118"/>
+      <c r="B50" s="124"/>
       <c r="C50" s="64" t="str">
         <f>master!C40</f>
         <v>5-6. 例②：100本ノックを作ってみる -プロンプト例</v>
       </c>
-      <c r="D50" s="107" t="s">
-        <v>180</v>
-      </c>
-      <c r="E50" s="108"/>
-      <c r="F50" s="109"/>
+      <c r="D50" s="126" t="s">
+        <v>176</v>
+      </c>
+      <c r="E50" s="127"/>
+      <c r="F50" s="128"/>
       <c r="G50" s="64" t="s">
         <v>42</v>
       </c>
@@ -5414,25 +5400,25 @@
     </row>
     <row r="51" spans="1:14" ht="88.2">
       <c r="A51" s="11"/>
-      <c r="B51" s="118"/>
+      <c r="B51" s="124"/>
       <c r="C51" s="84"/>
-      <c r="D51" s="110" t="s">
-        <v>188</v>
-      </c>
-      <c r="E51" s="111"/>
-      <c r="F51" s="112"/>
+      <c r="D51" s="116" t="s">
+        <v>184</v>
+      </c>
+      <c r="E51" s="117"/>
+      <c r="F51" s="118"/>
       <c r="G51" s="84" t="s">
         <v>45</v>
       </c>
       <c r="H51" s="85"/>
       <c r="I51" s="86" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J51" s="87">
         <v>1.3888888888888888E-2</v>
       </c>
       <c r="K51" s="88" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
@@ -5440,16 +5426,16 @@
     </row>
     <row r="52" spans="1:14" ht="50.4">
       <c r="A52" s="11"/>
-      <c r="B52" s="118"/>
+      <c r="B52" s="124"/>
       <c r="C52" s="64" t="str">
         <f>master!C41</f>
         <v>5-7. 例②：100本ノックを作ってみる - 実行結果①</v>
       </c>
-      <c r="D52" s="107" t="s">
-        <v>157</v>
-      </c>
-      <c r="E52" s="108"/>
-      <c r="F52" s="109"/>
+      <c r="D52" s="126" t="s">
+        <v>153</v>
+      </c>
+      <c r="E52" s="127"/>
+      <c r="F52" s="128"/>
       <c r="G52" s="64" t="s">
         <v>41</v>
       </c>
@@ -5467,16 +5453,16 @@
     </row>
     <row r="53" spans="1:14" ht="50.4">
       <c r="A53" s="11"/>
-      <c r="B53" s="118"/>
+      <c r="B53" s="124"/>
       <c r="C53" s="64" t="str">
         <f>master!C42</f>
         <v>5-8. 例②：100本ノックを作ってみる - 実行結果②</v>
       </c>
-      <c r="D53" s="107" t="s">
-        <v>158</v>
-      </c>
-      <c r="E53" s="108"/>
-      <c r="F53" s="109"/>
+      <c r="D53" s="126" t="s">
+        <v>154</v>
+      </c>
+      <c r="E53" s="127"/>
+      <c r="F53" s="128"/>
       <c r="G53" s="64" t="s">
         <v>41</v>
       </c>
@@ -5494,16 +5480,16 @@
     </row>
     <row r="54" spans="1:14" ht="50.4">
       <c r="A54" s="11"/>
-      <c r="B54" s="118"/>
+      <c r="B54" s="124"/>
       <c r="C54" s="64" t="str">
         <f>master!C43</f>
         <v>5-9. 例②：100本ノックを作ってみる - 実行結果③</v>
       </c>
-      <c r="D54" s="107" t="s">
-        <v>159</v>
-      </c>
-      <c r="E54" s="108"/>
-      <c r="F54" s="109"/>
+      <c r="D54" s="126" t="s">
+        <v>155</v>
+      </c>
+      <c r="E54" s="127"/>
+      <c r="F54" s="128"/>
       <c r="G54" s="64" t="s">
         <v>41</v>
       </c>
@@ -5521,16 +5507,16 @@
     </row>
     <row r="55" spans="1:14" ht="63">
       <c r="A55" s="11"/>
-      <c r="B55" s="114"/>
+      <c r="B55" s="125"/>
       <c r="C55" s="64" t="str">
         <f>master!C44</f>
         <v>5-10. ChatGPT まとめ</v>
       </c>
-      <c r="D55" s="107" t="s">
-        <v>148</v>
-      </c>
-      <c r="E55" s="108"/>
-      <c r="F55" s="109"/>
+      <c r="D55" s="126" t="s">
+        <v>144</v>
+      </c>
+      <c r="E55" s="127"/>
+      <c r="F55" s="128"/>
       <c r="G55" s="64" t="s">
         <v>39</v>
       </c>
@@ -5548,7 +5534,7 @@
     </row>
     <row r="56" spans="1:14" ht="50.4" customHeight="1">
       <c r="A56" s="11"/>
-      <c r="B56" s="118" t="str">
+      <c r="B56" s="124" t="str">
         <f>master!B45</f>
         <v>モジュール6：ハンズオン（ GitHub Copilot ）</v>
       </c>
@@ -5556,11 +5542,11 @@
         <f>master!C45</f>
         <v>6-1. Visual Studio Code を開く</v>
       </c>
-      <c r="D56" s="107" t="s">
-        <v>149</v>
-      </c>
-      <c r="E56" s="108"/>
-      <c r="F56" s="109"/>
+      <c r="D56" s="126" t="s">
+        <v>145</v>
+      </c>
+      <c r="E56" s="127"/>
+      <c r="F56" s="128"/>
       <c r="G56" s="64" t="s">
         <v>41</v>
       </c>
@@ -5578,16 +5564,16 @@
     </row>
     <row r="57" spans="1:14" ht="63">
       <c r="A57" s="11"/>
-      <c r="B57" s="118"/>
+      <c r="B57" s="124"/>
       <c r="C57" s="64" t="str">
         <f>master!C46</f>
         <v>6-2. コード補完機能</v>
       </c>
-      <c r="D57" s="107" t="s">
-        <v>150</v>
-      </c>
-      <c r="E57" s="108"/>
-      <c r="F57" s="109"/>
+      <c r="D57" s="126" t="s">
+        <v>146</v>
+      </c>
+      <c r="E57" s="127"/>
+      <c r="F57" s="128"/>
       <c r="G57" s="64" t="s">
         <v>39</v>
       </c>
@@ -5605,16 +5591,16 @@
     </row>
     <row r="58" spans="1:14" ht="75.599999999999994">
       <c r="A58" s="11"/>
-      <c r="B58" s="118"/>
+      <c r="B58" s="124"/>
       <c r="C58" s="64" t="str">
         <f>master!C47</f>
         <v>6-3. チャット機能</v>
       </c>
-      <c r="D58" s="107" t="s">
-        <v>204</v>
-      </c>
-      <c r="E58" s="108"/>
-      <c r="F58" s="109"/>
+      <c r="D58" s="126" t="s">
+        <v>200</v>
+      </c>
+      <c r="E58" s="127"/>
+      <c r="F58" s="128"/>
       <c r="G58" s="64" t="s">
         <v>42</v>
       </c>
@@ -5632,16 +5618,16 @@
     </row>
     <row r="59" spans="1:14" ht="88.2">
       <c r="A59" s="11"/>
-      <c r="B59" s="118"/>
+      <c r="B59" s="124"/>
       <c r="C59" s="64" t="str">
         <f>master!C48</f>
         <v>6-4. チャット機能 - コマンド</v>
       </c>
-      <c r="D59" s="107" t="s">
-        <v>203</v>
-      </c>
-      <c r="E59" s="108"/>
-      <c r="F59" s="109"/>
+      <c r="D59" s="126" t="s">
+        <v>199</v>
+      </c>
+      <c r="E59" s="127"/>
+      <c r="F59" s="128"/>
       <c r="G59" s="64" t="s">
         <v>45</v>
       </c>
@@ -5659,16 +5645,16 @@
     </row>
     <row r="60" spans="1:14" ht="50.4">
       <c r="A60" s="11"/>
-      <c r="B60" s="118"/>
+      <c r="B60" s="124"/>
       <c r="C60" s="64" t="str">
         <f>master!C49</f>
         <v>6-5. 簡単なアプリやゲームを作ってみましょう</v>
       </c>
-      <c r="D60" s="107" t="s">
-        <v>171</v>
-      </c>
-      <c r="E60" s="108"/>
-      <c r="F60" s="109"/>
+      <c r="D60" s="126" t="s">
+        <v>167</v>
+      </c>
+      <c r="E60" s="127"/>
+      <c r="F60" s="128"/>
       <c r="G60" s="64" t="s">
         <v>41</v>
       </c>
@@ -5686,16 +5672,16 @@
     </row>
     <row r="61" spans="1:14" ht="50.4">
       <c r="A61" s="11"/>
-      <c r="B61" s="118"/>
+      <c r="B61" s="124"/>
       <c r="C61" s="64" t="str">
         <f>master!C50</f>
         <v>6-6. 例①：高級志向テトリス</v>
       </c>
-      <c r="D61" s="107" t="s">
-        <v>174</v>
-      </c>
-      <c r="E61" s="108"/>
-      <c r="F61" s="109"/>
+      <c r="D61" s="126" t="s">
+        <v>170</v>
+      </c>
+      <c r="E61" s="127"/>
+      <c r="F61" s="128"/>
       <c r="G61" s="64" t="s">
         <v>41</v>
       </c>
@@ -5713,16 +5699,16 @@
     </row>
     <row r="62" spans="1:14" ht="50.4">
       <c r="A62" s="11"/>
-      <c r="B62" s="118"/>
+      <c r="B62" s="124"/>
       <c r="C62" s="64" t="str">
         <f>master!C51</f>
         <v>6-7. 例②：わくわく！にっぽんダーツの旅</v>
       </c>
-      <c r="D62" s="107" t="s">
-        <v>172</v>
-      </c>
-      <c r="E62" s="108"/>
-      <c r="F62" s="109"/>
+      <c r="D62" s="126" t="s">
+        <v>168</v>
+      </c>
+      <c r="E62" s="127"/>
+      <c r="F62" s="128"/>
       <c r="G62" s="64" t="s">
         <v>41</v>
       </c>
@@ -5740,16 +5726,16 @@
     </row>
     <row r="63" spans="1:14" ht="50.4">
       <c r="A63" s="11"/>
-      <c r="B63" s="118"/>
+      <c r="B63" s="124"/>
       <c r="C63" s="64" t="str">
         <f>master!C52</f>
         <v>6-8. 例③：タスク管理ツール</v>
       </c>
-      <c r="D63" s="107" t="s">
-        <v>173</v>
-      </c>
-      <c r="E63" s="108"/>
-      <c r="F63" s="109"/>
+      <c r="D63" s="126" t="s">
+        <v>169</v>
+      </c>
+      <c r="E63" s="127"/>
+      <c r="F63" s="128"/>
       <c r="G63" s="64" t="s">
         <v>41</v>
       </c>
@@ -5767,19 +5753,19 @@
     </row>
     <row r="64" spans="1:14" ht="138.6">
       <c r="A64" s="11"/>
-      <c r="B64" s="118"/>
+      <c r="B64" s="124"/>
       <c r="C64" s="84"/>
-      <c r="D64" s="110" t="s">
-        <v>185</v>
-      </c>
-      <c r="E64" s="111"/>
-      <c r="F64" s="112"/>
+      <c r="D64" s="116" t="s">
+        <v>181</v>
+      </c>
+      <c r="E64" s="117"/>
+      <c r="F64" s="118"/>
       <c r="G64" s="84" t="s">
         <v>38</v>
       </c>
       <c r="H64" s="85"/>
       <c r="I64" s="86" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J64" s="87">
         <v>2.0833333333333332E-2</v>
@@ -5791,16 +5777,16 @@
     </row>
     <row r="65" spans="1:14" ht="75.599999999999994">
       <c r="A65" s="11"/>
-      <c r="B65" s="118"/>
+      <c r="B65" s="124"/>
       <c r="C65" s="64" t="str">
         <f>master!C53</f>
         <v>6-9. ディレクトリ作成とファイル配置</v>
       </c>
-      <c r="D65" s="107" t="s">
-        <v>189</v>
-      </c>
-      <c r="E65" s="108"/>
-      <c r="F65" s="109"/>
+      <c r="D65" s="126" t="s">
+        <v>185</v>
+      </c>
+      <c r="E65" s="127"/>
+      <c r="F65" s="128"/>
       <c r="G65" s="64" t="s">
         <v>42</v>
       </c>
@@ -5818,19 +5804,19 @@
     </row>
     <row r="66" spans="1:14" ht="88.2">
       <c r="A66" s="11"/>
-      <c r="B66" s="118"/>
+      <c r="B66" s="124"/>
       <c r="C66" s="84"/>
-      <c r="D66" s="110" t="s">
-        <v>205</v>
-      </c>
-      <c r="E66" s="111"/>
-      <c r="F66" s="112"/>
+      <c r="D66" s="116" t="s">
+        <v>201</v>
+      </c>
+      <c r="E66" s="117"/>
+      <c r="F66" s="118"/>
       <c r="G66" s="84" t="s">
         <v>45</v>
       </c>
       <c r="H66" s="85"/>
       <c r="I66" s="86" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J66" s="87">
         <v>3.472222222222222E-3</v>
@@ -5842,16 +5828,16 @@
     </row>
     <row r="67" spans="1:14" ht="50.4">
       <c r="A67" s="11"/>
-      <c r="B67" s="118"/>
+      <c r="B67" s="124"/>
       <c r="C67" s="64" t="str">
         <f>master!C54</f>
         <v>6-10. チャット機能 - Askモード</v>
       </c>
-      <c r="D67" s="107" t="s">
-        <v>200</v>
-      </c>
-      <c r="E67" s="108"/>
-      <c r="F67" s="109"/>
+      <c r="D67" s="126" t="s">
+        <v>196</v>
+      </c>
+      <c r="E67" s="127"/>
+      <c r="F67" s="128"/>
       <c r="G67" s="64" t="s">
         <v>41</v>
       </c>
@@ -5869,16 +5855,16 @@
     </row>
     <row r="68" spans="1:14" ht="100.8">
       <c r="A68" s="11"/>
-      <c r="B68" s="118"/>
+      <c r="B68" s="124"/>
       <c r="C68" s="64" t="str">
         <f>master!C55</f>
         <v>6-11. Askモードについて</v>
       </c>
-      <c r="D68" s="107" t="s">
-        <v>152</v>
-      </c>
-      <c r="E68" s="108"/>
-      <c r="F68" s="109"/>
+      <c r="D68" s="126" t="s">
+        <v>148</v>
+      </c>
+      <c r="E68" s="127"/>
+      <c r="F68" s="128"/>
       <c r="G68" s="64" t="s">
         <v>47</v>
       </c>
@@ -5896,16 +5882,16 @@
     </row>
     <row r="69" spans="1:14" ht="50.4">
       <c r="A69" s="11"/>
-      <c r="B69" s="118"/>
+      <c r="B69" s="124"/>
       <c r="C69" s="64" t="str">
         <f>master!C56</f>
         <v>6-12. 実行例①</v>
       </c>
-      <c r="D69" s="107" t="s">
-        <v>156</v>
-      </c>
-      <c r="E69" s="108"/>
-      <c r="F69" s="109"/>
+      <c r="D69" s="126" t="s">
+        <v>152</v>
+      </c>
+      <c r="E69" s="127"/>
+      <c r="F69" s="128"/>
       <c r="G69" s="64" t="s">
         <v>41</v>
       </c>
@@ -5923,16 +5909,16 @@
     </row>
     <row r="70" spans="1:14" ht="50.4">
       <c r="A70" s="11"/>
-      <c r="B70" s="118"/>
+      <c r="B70" s="124"/>
       <c r="C70" s="64" t="str">
         <f>master!C57</f>
         <v>6-13. 実行例②</v>
       </c>
-      <c r="D70" s="107" t="s">
-        <v>154</v>
-      </c>
-      <c r="E70" s="108"/>
-      <c r="F70" s="109"/>
+      <c r="D70" s="126" t="s">
+        <v>150</v>
+      </c>
+      <c r="E70" s="127"/>
+      <c r="F70" s="128"/>
       <c r="G70" s="64" t="s">
         <v>41</v>
       </c>
@@ -5950,16 +5936,16 @@
     </row>
     <row r="71" spans="1:14" ht="50.4">
       <c r="A71" s="11"/>
-      <c r="B71" s="118"/>
+      <c r="B71" s="124"/>
       <c r="C71" s="64" t="str">
         <f>master!C58</f>
         <v>6-14. 実行例③</v>
       </c>
-      <c r="D71" s="107" t="s">
-        <v>155</v>
-      </c>
-      <c r="E71" s="108"/>
-      <c r="F71" s="109"/>
+      <c r="D71" s="126" t="s">
+        <v>151</v>
+      </c>
+      <c r="E71" s="127"/>
+      <c r="F71" s="128"/>
       <c r="G71" s="64" t="s">
         <v>41</v>
       </c>
@@ -5977,19 +5963,19 @@
     </row>
     <row r="72" spans="1:14" ht="138.6">
       <c r="A72" s="11"/>
-      <c r="B72" s="118"/>
+      <c r="B72" s="124"/>
       <c r="C72" s="84"/>
-      <c r="D72" s="110" t="s">
-        <v>184</v>
-      </c>
-      <c r="E72" s="111"/>
-      <c r="F72" s="112"/>
+      <c r="D72" s="116" t="s">
+        <v>180</v>
+      </c>
+      <c r="E72" s="117"/>
+      <c r="F72" s="118"/>
       <c r="G72" s="84" t="s">
         <v>38</v>
       </c>
       <c r="H72" s="85"/>
       <c r="I72" s="86" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J72" s="87">
         <v>2.0833333333333332E-2</v>
@@ -6001,16 +5987,16 @@
     </row>
     <row r="73" spans="1:14" ht="63">
       <c r="A73" s="11"/>
-      <c r="B73" s="118"/>
+      <c r="B73" s="124"/>
       <c r="C73" s="64" t="str">
         <f>master!C59</f>
         <v>6-15. Askモードまとめ</v>
       </c>
-      <c r="D73" s="107" t="s">
-        <v>151</v>
-      </c>
-      <c r="E73" s="108"/>
-      <c r="F73" s="109"/>
+      <c r="D73" s="126" t="s">
+        <v>147</v>
+      </c>
+      <c r="E73" s="127"/>
+      <c r="F73" s="128"/>
       <c r="G73" s="64" t="s">
         <v>39</v>
       </c>
@@ -6028,16 +6014,16 @@
     </row>
     <row r="74" spans="1:14" ht="50.4">
       <c r="A74" s="11"/>
-      <c r="B74" s="118"/>
+      <c r="B74" s="124"/>
       <c r="C74" s="64" t="str">
         <f>master!C60</f>
         <v>6-16. チャット機能 - Agentモード</v>
       </c>
-      <c r="D74" s="107" t="s">
-        <v>201</v>
-      </c>
-      <c r="E74" s="108"/>
-      <c r="F74" s="109"/>
+      <c r="D74" s="126" t="s">
+        <v>197</v>
+      </c>
+      <c r="E74" s="127"/>
+      <c r="F74" s="128"/>
       <c r="G74" s="64" t="s">
         <v>41</v>
       </c>
@@ -6055,16 +6041,16 @@
     </row>
     <row r="75" spans="1:14" ht="63">
       <c r="A75" s="11"/>
-      <c r="B75" s="118"/>
+      <c r="B75" s="124"/>
       <c r="C75" s="64" t="str">
         <f>master!C61</f>
         <v>6-17. Agentモード</v>
       </c>
-      <c r="D75" s="107" t="s">
-        <v>160</v>
-      </c>
-      <c r="E75" s="108"/>
-      <c r="F75" s="109"/>
+      <c r="D75" s="126" t="s">
+        <v>156</v>
+      </c>
+      <c r="E75" s="127"/>
+      <c r="F75" s="128"/>
       <c r="G75" s="64" t="s">
         <v>39</v>
       </c>
@@ -6082,16 +6068,16 @@
     </row>
     <row r="76" spans="1:14" ht="50.4">
       <c r="A76" s="11"/>
-      <c r="B76" s="118"/>
+      <c r="B76" s="124"/>
       <c r="C76" s="64" t="str">
         <f>master!C62</f>
         <v>6-18. 実行例</v>
       </c>
-      <c r="D76" s="107" t="s">
-        <v>161</v>
-      </c>
-      <c r="E76" s="108"/>
-      <c r="F76" s="109"/>
+      <c r="D76" s="126" t="s">
+        <v>157</v>
+      </c>
+      <c r="E76" s="127"/>
+      <c r="F76" s="128"/>
       <c r="G76" s="64" t="s">
         <v>41</v>
       </c>
@@ -6109,16 +6095,16 @@
     </row>
     <row r="77" spans="1:14" ht="37.799999999999997">
       <c r="A77" s="11"/>
-      <c r="B77" s="118"/>
+      <c r="B77" s="124"/>
       <c r="C77" s="64" t="str">
         <f>master!C63</f>
         <v>6-19. READMEの内容を確認しましょう①</v>
       </c>
-      <c r="D77" s="107" t="s">
-        <v>207</v>
-      </c>
-      <c r="E77" s="108"/>
-      <c r="F77" s="109"/>
+      <c r="D77" s="126" t="s">
+        <v>203</v>
+      </c>
+      <c r="E77" s="127"/>
+      <c r="F77" s="128"/>
       <c r="G77" s="64" t="s">
         <v>40</v>
       </c>
@@ -6136,16 +6122,16 @@
     </row>
     <row r="78" spans="1:14" ht="37.799999999999997">
       <c r="A78" s="11"/>
-      <c r="B78" s="118"/>
+      <c r="B78" s="124"/>
       <c r="C78" s="64" t="str">
         <f>master!C64</f>
         <v>6-20. READMEの内容を確認しましょう②</v>
       </c>
-      <c r="D78" s="107" t="s">
-        <v>206</v>
-      </c>
-      <c r="E78" s="108"/>
-      <c r="F78" s="109"/>
+      <c r="D78" s="126" t="s">
+        <v>202</v>
+      </c>
+      <c r="E78" s="127"/>
+      <c r="F78" s="128"/>
       <c r="G78" s="64" t="s">
         <v>40</v>
       </c>
@@ -6163,25 +6149,25 @@
     </row>
     <row r="79" spans="1:14" ht="126">
       <c r="A79" s="11"/>
-      <c r="B79" s="118"/>
+      <c r="B79" s="124"/>
       <c r="C79" s="84"/>
-      <c r="D79" s="110" t="s">
-        <v>183</v>
-      </c>
-      <c r="E79" s="111"/>
-      <c r="F79" s="112"/>
+      <c r="D79" s="116" t="s">
+        <v>179</v>
+      </c>
+      <c r="E79" s="117"/>
+      <c r="F79" s="118"/>
       <c r="G79" s="84" t="s">
         <v>44</v>
       </c>
       <c r="H79" s="85"/>
       <c r="I79" s="86" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J79" s="87">
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="K79" s="88" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
@@ -6189,16 +6175,16 @@
     </row>
     <row r="80" spans="1:14" ht="50.4">
       <c r="A80" s="11"/>
-      <c r="B80" s="118"/>
+      <c r="B80" s="124"/>
       <c r="C80" s="64" t="str">
         <f>master!C65</f>
         <v>6-21. Changeログを作ってみましょう</v>
       </c>
-      <c r="D80" s="107" t="s">
-        <v>162</v>
-      </c>
-      <c r="E80" s="108"/>
-      <c r="F80" s="109"/>
+      <c r="D80" s="126" t="s">
+        <v>158</v>
+      </c>
+      <c r="E80" s="127"/>
+      <c r="F80" s="128"/>
       <c r="G80" s="64" t="s">
         <v>41</v>
       </c>
@@ -6216,25 +6202,25 @@
     </row>
     <row r="81" spans="1:14" ht="113.4">
       <c r="A81" s="11"/>
-      <c r="B81" s="118"/>
+      <c r="B81" s="124"/>
       <c r="C81" s="89"/>
-      <c r="D81" s="110" t="s">
-        <v>182</v>
-      </c>
-      <c r="E81" s="111"/>
-      <c r="F81" s="112"/>
+      <c r="D81" s="116" t="s">
+        <v>178</v>
+      </c>
+      <c r="E81" s="117"/>
+      <c r="F81" s="118"/>
       <c r="G81" s="84" t="s">
         <v>43</v>
       </c>
       <c r="H81" s="85"/>
       <c r="I81" s="86" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J81" s="87">
         <v>6.9444444444444441E-3</v>
       </c>
       <c r="K81" s="88" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
@@ -6242,16 +6228,16 @@
     </row>
     <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="118"/>
+      <c r="B82" s="124"/>
       <c r="C82" s="64" t="str">
         <f>master!C66</f>
         <v>6-22. チャット機能 - Planモード</v>
       </c>
-      <c r="D82" s="107" t="s">
-        <v>202</v>
-      </c>
-      <c r="E82" s="108"/>
-      <c r="F82" s="109"/>
+      <c r="D82" s="126" t="s">
+        <v>198</v>
+      </c>
+      <c r="E82" s="127"/>
+      <c r="F82" s="128"/>
       <c r="G82" s="64" t="s">
         <v>41</v>
       </c>
@@ -6269,16 +6255,16 @@
     </row>
     <row r="83" spans="1:14" ht="63">
       <c r="A83" s="11"/>
-      <c r="B83" s="118"/>
+      <c r="B83" s="124"/>
       <c r="C83" s="64" t="str">
         <f>master!C67</f>
         <v>6-23. Planモードで機能追加してみましょう</v>
       </c>
-      <c r="D83" s="107" t="s">
-        <v>166</v>
-      </c>
-      <c r="E83" s="108"/>
-      <c r="F83" s="109"/>
+      <c r="D83" s="126" t="s">
+        <v>162</v>
+      </c>
+      <c r="E83" s="127"/>
+      <c r="F83" s="128"/>
       <c r="G83" s="64" t="s">
         <v>39</v>
       </c>
@@ -6296,16 +6282,16 @@
     </row>
     <row r="84" spans="1:14" ht="63">
       <c r="A84" s="11"/>
-      <c r="B84" s="118"/>
+      <c r="B84" s="124"/>
       <c r="C84" s="64" t="str">
         <f>master!C68</f>
         <v>6-24. 実行例①</v>
       </c>
-      <c r="D84" s="107" t="s">
-        <v>163</v>
-      </c>
-      <c r="E84" s="108"/>
-      <c r="F84" s="109"/>
+      <c r="D84" s="126" t="s">
+        <v>159</v>
+      </c>
+      <c r="E84" s="127"/>
+      <c r="F84" s="128"/>
       <c r="G84" s="64" t="s">
         <v>39</v>
       </c>
@@ -6323,16 +6309,16 @@
     </row>
     <row r="85" spans="1:14" ht="50.4">
       <c r="A85" s="11"/>
-      <c r="B85" s="118"/>
+      <c r="B85" s="124"/>
       <c r="C85" s="64" t="str">
         <f>master!C69</f>
         <v>6-25. 実行例②</v>
       </c>
-      <c r="D85" s="107" t="s">
-        <v>164</v>
-      </c>
-      <c r="E85" s="108"/>
-      <c r="F85" s="109"/>
+      <c r="D85" s="126" t="s">
+        <v>160</v>
+      </c>
+      <c r="E85" s="127"/>
+      <c r="F85" s="128"/>
       <c r="G85" s="64" t="s">
         <v>41</v>
       </c>
@@ -6350,16 +6336,16 @@
     </row>
     <row r="86" spans="1:14" ht="50.4">
       <c r="A86" s="11"/>
-      <c r="B86" s="118"/>
+      <c r="B86" s="124"/>
       <c r="C86" s="64" t="str">
         <f>master!C70</f>
         <v>6-26. 実行例③</v>
       </c>
-      <c r="D86" s="107" t="s">
-        <v>165</v>
-      </c>
-      <c r="E86" s="108"/>
-      <c r="F86" s="109"/>
+      <c r="D86" s="126" t="s">
+        <v>161</v>
+      </c>
+      <c r="E86" s="127"/>
+      <c r="F86" s="128"/>
       <c r="G86" s="64" t="s">
         <v>41</v>
       </c>
@@ -6377,13 +6363,13 @@
     </row>
     <row r="87" spans="1:14" ht="126">
       <c r="A87" s="11"/>
-      <c r="B87" s="118"/>
+      <c r="B87" s="124"/>
       <c r="C87" s="84"/>
-      <c r="D87" s="110" t="s">
-        <v>181</v>
-      </c>
-      <c r="E87" s="111"/>
-      <c r="F87" s="112"/>
+      <c r="D87" s="116" t="s">
+        <v>177</v>
+      </c>
+      <c r="E87" s="117"/>
+      <c r="F87" s="118"/>
       <c r="G87" s="84" t="s">
         <v>44</v>
       </c>
@@ -6401,16 +6387,16 @@
     </row>
     <row r="88" spans="1:14" ht="50.4">
       <c r="A88" s="11"/>
-      <c r="B88" s="118"/>
+      <c r="B88" s="124"/>
       <c r="C88" s="64" t="str">
         <f>master!C71</f>
         <v>6-27. 実行結果①</v>
       </c>
-      <c r="D88" s="107" t="s">
-        <v>167</v>
-      </c>
-      <c r="E88" s="108"/>
-      <c r="F88" s="109"/>
+      <c r="D88" s="126" t="s">
+        <v>163</v>
+      </c>
+      <c r="E88" s="127"/>
+      <c r="F88" s="128"/>
       <c r="G88" s="64" t="s">
         <v>41</v>
       </c>
@@ -6428,16 +6414,16 @@
     </row>
     <row r="89" spans="1:14" ht="50.4">
       <c r="A89" s="11"/>
-      <c r="B89" s="118"/>
+      <c r="B89" s="124"/>
       <c r="C89" s="64" t="str">
         <f>master!C72</f>
         <v>6-28. 実行結果②</v>
       </c>
-      <c r="D89" s="107" t="s">
-        <v>168</v>
-      </c>
-      <c r="E89" s="108"/>
-      <c r="F89" s="109"/>
+      <c r="D89" s="126" t="s">
+        <v>164</v>
+      </c>
+      <c r="E89" s="127"/>
+      <c r="F89" s="128"/>
       <c r="G89" s="64" t="s">
         <v>41</v>
       </c>
@@ -6455,16 +6441,16 @@
     </row>
     <row r="90" spans="1:14" ht="113.4">
       <c r="A90" s="11"/>
-      <c r="B90" s="114"/>
+      <c r="B90" s="125"/>
       <c r="C90" s="64" t="str">
         <f>master!C73</f>
         <v>6-29. Planモード＆Agentモードまとめ</v>
       </c>
-      <c r="D90" s="107" t="s">
-        <v>169</v>
-      </c>
-      <c r="E90" s="108"/>
-      <c r="F90" s="109"/>
+      <c r="D90" s="126" t="s">
+        <v>165</v>
+      </c>
+      <c r="E90" s="127"/>
+      <c r="F90" s="128"/>
       <c r="G90" s="64" t="s">
         <v>43</v>
       </c>
@@ -6482,7 +6468,7 @@
     </row>
     <row r="91" spans="1:14" ht="102" customHeight="1">
       <c r="A91" s="11"/>
-      <c r="B91" s="113" t="str">
+      <c r="B91" s="123" t="str">
         <f>master!B74</f>
         <v>成果物のプレゼン</v>
       </c>
@@ -6490,11 +6476,11 @@
         <f>master!C74</f>
         <v>開発した成果物のプレゼン（グループ）</v>
       </c>
-      <c r="D91" s="110" t="s">
-        <v>197</v>
-      </c>
-      <c r="E91" s="111"/>
-      <c r="F91" s="112"/>
+      <c r="D91" s="116" t="s">
+        <v>193</v>
+      </c>
+      <c r="E91" s="117"/>
+      <c r="F91" s="118"/>
       <c r="G91" s="84" t="s">
         <v>47</v>
       </c>
@@ -6512,16 +6498,16 @@
     </row>
     <row r="92" spans="1:14" ht="88.2">
       <c r="A92" s="11"/>
-      <c r="B92" s="114"/>
+      <c r="B92" s="125"/>
       <c r="C92" s="84" t="str">
         <f>master!C75</f>
         <v>開発した成果物のプレゼン（全体）</v>
       </c>
-      <c r="D92" s="110" t="s">
-        <v>192</v>
-      </c>
-      <c r="E92" s="111"/>
-      <c r="F92" s="112"/>
+      <c r="D92" s="116" t="s">
+        <v>188</v>
+      </c>
+      <c r="E92" s="117"/>
+      <c r="F92" s="118"/>
       <c r="G92" s="84" t="s">
         <v>45</v>
       </c>
@@ -6533,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="K92" s="88" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
@@ -6545,61 +6531,34 @@
     <row r="94" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="B22:B36"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="B44:B55"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D70:F70"/>
     <mergeCell ref="B37:B43"/>
     <mergeCell ref="D60:F60"/>
     <mergeCell ref="D78:F78"/>
@@ -6616,34 +6575,61 @@
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="B56:B90"/>
     <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="B44:B55"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="B22:B36"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:K11"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6691,12 +6677,12 @@
         <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="C4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="2:3">
@@ -6727,7 +6713,7 @@
     </row>
     <row r="9" spans="2:3">
       <c r="C9" t="s">
-        <v>112</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="2:3">
@@ -6747,7 +6733,7 @@
     </row>
     <row r="13" spans="2:3">
       <c r="B13" s="83" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C13" t="s">
         <v>63</v>
@@ -6828,12 +6814,12 @@
         <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="C29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="2:3">
@@ -6843,22 +6829,22 @@
     </row>
     <row r="31" spans="2:3">
       <c r="C31" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="2:3">
       <c r="C32" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="C33" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="2:3">
       <c r="C34" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="2:3">
@@ -6871,17 +6857,17 @@
     </row>
     <row r="36" spans="2:3">
       <c r="C36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="2:3">
       <c r="C37" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="2:3">
       <c r="C38" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="2:3">
@@ -6891,22 +6877,22 @@
     </row>
     <row r="40" spans="2:3">
       <c r="C40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="2:3">
       <c r="C41" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="C42" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="2:3">
       <c r="C43" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="2:3">
@@ -6934,7 +6920,7 @@
     </row>
     <row r="48" spans="2:3">
       <c r="C48" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="3:3">
@@ -6964,7 +6950,7 @@
     </row>
     <row r="54" spans="3:3">
       <c r="C54" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55" spans="3:3">
@@ -6994,7 +6980,7 @@
     </row>
     <row r="60" spans="3:3">
       <c r="C60" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61" spans="3:3">
@@ -7009,12 +6995,12 @@
     </row>
     <row r="63" spans="3:3">
       <c r="C63" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="64" spans="3:3">
       <c r="C64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65" spans="2:3">
@@ -7024,7 +7010,7 @@
     </row>
     <row r="66" spans="2:3">
       <c r="C66" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="2:3">
@@ -7034,27 +7020,27 @@
     </row>
     <row r="68" spans="2:3">
       <c r="C68" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69" spans="2:3">
       <c r="C69" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="70" spans="2:3">
       <c r="C70" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="71" spans="2:3">
       <c r="C71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="72" spans="2:3">
       <c r="C72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73" spans="2:3">
@@ -7064,15 +7050,15 @@
     </row>
     <row r="74" spans="2:3">
       <c r="B74" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C74" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" spans="2:3">
       <c r="C75" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/IG/7日版/AI Native-生成AI_IG.xlsx
+++ b/IG/7日版/AI Native-生成AI_IG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60224589-74D9-47BE-8256-95BA988DD336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2510544F-998C-457F-BD9C-6FFA57BA40B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール（1日）" sheetId="33" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="209">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -969,29 +969,6 @@
     </rPh>
     <rPh sb="85" eb="87">
       <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>以下の内容を説明する。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">以下の内容を説明する。
-■悪いプロンプト
-■良いプロンプト
-</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ヨ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -3087,6 +3064,60 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3095,60 +3126,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4240,18 +4217,18 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="108" t="s">
-        <v>195</v>
-      </c>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
+      <c r="B5" s="126" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="126"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
       <c r="L5" s="29"/>
       <c r="M5" s="30"/>
     </row>
@@ -4293,7 +4270,7 @@
         <v>34</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D8" s="45" t="s">
         <v>20</v>
@@ -4329,10 +4306,10 @@
       <c r="H10" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="109" t="s">
+      <c r="I10" s="127" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="110"/>
+      <c r="J10" s="128"/>
       <c r="K10" s="98" t="s">
         <v>33</v>
       </c>
@@ -4362,7 +4339,7 @@
     </row>
     <row r="12" spans="1:14" ht="88.2">
       <c r="A12" s="10"/>
-      <c r="B12" s="111" t="str">
+      <c r="B12" s="124" t="str">
         <f>master!B3</f>
         <v>自己紹介</v>
       </c>
@@ -4370,11 +4347,11 @@
         <f>master!C3</f>
         <v>講師の自己紹介</v>
       </c>
-      <c r="D12" s="113" t="s">
-        <v>204</v>
-      </c>
-      <c r="E12" s="114"/>
-      <c r="F12" s="115"/>
+      <c r="D12" s="120" t="s">
+        <v>202</v>
+      </c>
+      <c r="E12" s="121"/>
+      <c r="F12" s="122"/>
       <c r="G12" s="51" t="s">
         <v>49</v>
       </c>
@@ -4392,18 +4369,18 @@
     </row>
     <row r="13" spans="1:14" ht="126">
       <c r="A13" s="10"/>
-      <c r="B13" s="112"/>
+      <c r="B13" s="125"/>
       <c r="C13" s="84" t="str">
         <f>master!C4</f>
         <v>受講生の自己紹介</v>
       </c>
-      <c r="D13" s="116" t="s">
-        <v>206</v>
-      </c>
-      <c r="E13" s="117"/>
-      <c r="F13" s="118"/>
+      <c r="D13" s="111" t="s">
+        <v>204</v>
+      </c>
+      <c r="E13" s="112"/>
+      <c r="F13" s="113"/>
       <c r="G13" s="84" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H13" s="85"/>
       <c r="I13" s="86" t="s">
@@ -4413,7 +4390,7 @@
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="K13" s="88" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
@@ -4421,7 +4398,7 @@
     </row>
     <row r="14" spans="1:14" ht="151.19999999999999">
       <c r="A14" s="11"/>
-      <c r="B14" s="119" t="str">
+      <c r="B14" s="123" t="str">
         <f>master!B5</f>
         <v>モジュール1：オリエンテーションとマインドセット変革</v>
       </c>
@@ -4429,13 +4406,13 @@
         <f>master!C5</f>
         <v>1-1. 研修概要</v>
       </c>
-      <c r="D14" s="113" t="s">
-        <v>208</v>
-      </c>
-      <c r="E14" s="114"/>
-      <c r="F14" s="115"/>
+      <c r="D14" s="120" t="s">
+        <v>206</v>
+      </c>
+      <c r="E14" s="121"/>
+      <c r="F14" s="122"/>
       <c r="G14" s="51" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="49" t="s">
@@ -4451,16 +4428,16 @@
     </row>
     <row r="15" spans="1:14" ht="100.8">
       <c r="A15" s="11"/>
-      <c r="B15" s="119"/>
+      <c r="B15" s="123"/>
       <c r="C15" s="51" t="str">
         <f>master!C6</f>
         <v>1-2. 背景・目的</v>
       </c>
-      <c r="D15" s="113" t="s">
+      <c r="D15" s="120" t="s">
         <v>133</v>
       </c>
-      <c r="E15" s="114"/>
-      <c r="F15" s="115"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="122"/>
       <c r="G15" s="51" t="s">
         <v>47</v>
       </c>
@@ -4478,16 +4455,16 @@
     </row>
     <row r="16" spans="1:14" ht="214.2">
       <c r="A16" s="11"/>
-      <c r="B16" s="119"/>
+      <c r="B16" s="123"/>
       <c r="C16" s="51" t="str">
         <f>master!C7</f>
         <v>1-3. 研修ゴールと獲得可能な経験背景・目的</v>
       </c>
-      <c r="D16" s="113" t="s">
-        <v>171</v>
-      </c>
-      <c r="E16" s="114"/>
-      <c r="F16" s="115"/>
+      <c r="D16" s="120" t="s">
+        <v>169</v>
+      </c>
+      <c r="E16" s="121"/>
+      <c r="F16" s="122"/>
       <c r="G16" s="51" t="s">
         <v>134</v>
       </c>
@@ -4505,7 +4482,7 @@
     </row>
     <row r="17" spans="1:14" ht="113.4">
       <c r="A17" s="11"/>
-      <c r="B17" s="120" t="str">
+      <c r="B17" s="116" t="str">
         <f>master!B8</f>
         <v>モジュール2：AI・LLMの基礎理解</v>
       </c>
@@ -4513,11 +4490,11 @@
         <f>master!C8</f>
         <v>2-1. 生成AI（Generative AI）とは？</v>
       </c>
-      <c r="D17" s="113" t="s">
-        <v>209</v>
-      </c>
-      <c r="E17" s="114"/>
-      <c r="F17" s="115"/>
+      <c r="D17" s="120" t="s">
+        <v>207</v>
+      </c>
+      <c r="E17" s="121"/>
+      <c r="F17" s="122"/>
       <c r="G17" s="51" t="s">
         <v>43</v>
       </c>
@@ -4535,16 +4512,16 @@
     </row>
     <row r="18" spans="1:14" ht="113.4">
       <c r="A18" s="11"/>
-      <c r="B18" s="121"/>
+      <c r="B18" s="117"/>
       <c r="C18" s="51" t="str">
         <f>master!C9</f>
         <v>2-2. 従来型AIと生成AIの比較</v>
       </c>
-      <c r="D18" s="113" t="s">
+      <c r="D18" s="120" t="s">
         <v>135</v>
       </c>
-      <c r="E18" s="114"/>
-      <c r="F18" s="115"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="122"/>
       <c r="G18" s="51" t="s">
         <v>43</v>
       </c>
@@ -4562,16 +4539,16 @@
     </row>
     <row r="19" spans="1:14" ht="113.4">
       <c r="A19" s="11"/>
-      <c r="B19" s="121"/>
+      <c r="B19" s="117"/>
       <c r="C19" s="51" t="str">
         <f>master!C10</f>
         <v>2-3. LLM（大規模言語モデル）の仕組み</v>
       </c>
-      <c r="D19" s="113" t="s">
+      <c r="D19" s="120" t="s">
         <v>136</v>
       </c>
-      <c r="E19" s="114"/>
-      <c r="F19" s="115"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="122"/>
       <c r="G19" s="51" t="s">
         <v>43</v>
       </c>
@@ -4589,16 +4566,16 @@
     </row>
     <row r="20" spans="1:14" ht="126">
       <c r="A20" s="11"/>
-      <c r="B20" s="121"/>
+      <c r="B20" s="117"/>
       <c r="C20" s="51" t="str">
         <f>master!C11</f>
         <v>2-4. 生成AIの「苦手なこと」（弱み）</v>
       </c>
-      <c r="D20" s="113" t="s">
+      <c r="D20" s="120" t="s">
         <v>137</v>
       </c>
-      <c r="E20" s="114"/>
-      <c r="F20" s="115"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="122"/>
       <c r="G20" s="51" t="s">
         <v>44</v>
       </c>
@@ -4616,16 +4593,16 @@
     </row>
     <row r="21" spans="1:14" ht="239.4">
       <c r="A21" s="11"/>
-      <c r="B21" s="122"/>
+      <c r="B21" s="118"/>
       <c r="C21" s="51" t="str">
         <f>master!C12</f>
         <v>2-5. 生成AIを使う心得８条</v>
       </c>
-      <c r="D21" s="113" t="s">
-        <v>172</v>
-      </c>
-      <c r="E21" s="114"/>
-      <c r="F21" s="115"/>
+      <c r="D21" s="120" t="s">
+        <v>170</v>
+      </c>
+      <c r="E21" s="121"/>
+      <c r="F21" s="122"/>
       <c r="G21" s="51" t="s">
         <v>138</v>
       </c>
@@ -4643,7 +4620,7 @@
     </row>
     <row r="22" spans="1:14" ht="25.2">
       <c r="A22" s="11"/>
-      <c r="B22" s="119" t="str">
+      <c r="B22" s="123" t="str">
         <f>master!B13</f>
         <v>モジュール3：NTTデータが目指すAIビジネス（Vision）</v>
       </c>
@@ -4651,9 +4628,9 @@
         <f>master!C13</f>
         <v>3-1. 本モジュールで学ぶこと①</v>
       </c>
-      <c r="D22" s="113"/>
-      <c r="E22" s="114"/>
-      <c r="F22" s="115"/>
+      <c r="D22" s="120"/>
+      <c r="E22" s="121"/>
+      <c r="F22" s="122"/>
       <c r="G22" s="51" t="s">
         <v>46</v>
       </c>
@@ -4671,14 +4648,14 @@
     </row>
     <row r="23" spans="1:14" ht="25.2">
       <c r="A23" s="11"/>
-      <c r="B23" s="119"/>
+      <c r="B23" s="123"/>
       <c r="C23" s="51" t="str">
         <f>master!C14</f>
         <v>3-2. NTTデータのAI戦略：Quality Growthとは</v>
       </c>
-      <c r="D23" s="113"/>
-      <c r="E23" s="114"/>
-      <c r="F23" s="115"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="122"/>
       <c r="G23" s="51" t="s">
         <v>46</v>
       </c>
@@ -4696,14 +4673,14 @@
     </row>
     <row r="24" spans="1:14" ht="25.2">
       <c r="A24" s="11"/>
-      <c r="B24" s="119"/>
+      <c r="B24" s="123"/>
       <c r="C24" s="51" t="str">
         <f>master!C15</f>
         <v>3-3. なぜ今、AIが重要なのか</v>
       </c>
-      <c r="D24" s="113"/>
-      <c r="E24" s="114"/>
-      <c r="F24" s="115"/>
+      <c r="D24" s="120"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="122"/>
       <c r="G24" s="51" t="s">
         <v>46</v>
       </c>
@@ -4721,14 +4698,14 @@
     </row>
     <row r="25" spans="1:14" ht="25.2">
       <c r="A25" s="11"/>
-      <c r="B25" s="119"/>
+      <c r="B25" s="123"/>
       <c r="C25" s="51" t="str">
         <f>master!C16</f>
         <v>3-4. 生成AIの進化：今、どこにいるか</v>
       </c>
-      <c r="D25" s="113"/>
-      <c r="E25" s="114"/>
-      <c r="F25" s="115"/>
+      <c r="D25" s="120"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="122"/>
       <c r="G25" s="51" t="s">
         <v>46</v>
       </c>
@@ -4746,14 +4723,14 @@
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
       <c r="A26" s="11"/>
-      <c r="B26" s="119"/>
+      <c r="B26" s="123"/>
       <c r="C26" s="51" t="str">
         <f>master!C17</f>
         <v>3-5. 本モジュールで学ぶこと②</v>
       </c>
-      <c r="D26" s="113"/>
-      <c r="E26" s="114"/>
-      <c r="F26" s="115"/>
+      <c r="D26" s="120"/>
+      <c r="E26" s="121"/>
+      <c r="F26" s="122"/>
       <c r="G26" s="51" t="s">
         <v>37</v>
       </c>
@@ -4771,16 +4748,16 @@
     </row>
     <row r="27" spans="1:14" ht="63">
       <c r="A27" s="11"/>
-      <c r="B27" s="119"/>
+      <c r="B27" s="123"/>
       <c r="C27" s="51" t="str">
         <f>master!C18</f>
         <v>3-6. エージェントAI（Agentic AI）とは何か</v>
       </c>
-      <c r="D27" s="113" t="s">
-        <v>173</v>
-      </c>
-      <c r="E27" s="114"/>
-      <c r="F27" s="115"/>
+      <c r="D27" s="120" t="s">
+        <v>171</v>
+      </c>
+      <c r="E27" s="121"/>
+      <c r="F27" s="122"/>
       <c r="G27" s="51" t="s">
         <v>39</v>
       </c>
@@ -4798,16 +4775,16 @@
     </row>
     <row r="28" spans="1:14" ht="63">
       <c r="A28" s="11"/>
-      <c r="B28" s="119"/>
+      <c r="B28" s="123"/>
       <c r="C28" s="51" t="str">
         <f>master!C19</f>
         <v>3-7. エージェントの処理</v>
       </c>
-      <c r="D28" s="113" t="s">
+      <c r="D28" s="120" t="s">
         <v>139</v>
       </c>
-      <c r="E28" s="114"/>
-      <c r="F28" s="115"/>
+      <c r="E28" s="121"/>
+      <c r="F28" s="122"/>
       <c r="G28" s="51" t="s">
         <v>39</v>
       </c>
@@ -4825,14 +4802,14 @@
     </row>
     <row r="29" spans="1:14" ht="37.799999999999997">
       <c r="A29" s="11"/>
-      <c r="B29" s="119"/>
+      <c r="B29" s="123"/>
       <c r="C29" s="51" t="str">
         <f>master!C20</f>
         <v>3-8. 本モジュールで学ぶこと③</v>
       </c>
-      <c r="D29" s="113"/>
-      <c r="E29" s="114"/>
-      <c r="F29" s="115"/>
+      <c r="D29" s="120"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="122"/>
       <c r="G29" s="51" t="s">
         <v>40</v>
       </c>
@@ -4850,14 +4827,14 @@
     </row>
     <row r="30" spans="1:14" ht="37.799999999999997">
       <c r="A30" s="11"/>
-      <c r="B30" s="119"/>
+      <c r="B30" s="123"/>
       <c r="C30" s="51" t="str">
         <f>master!C21</f>
         <v>3-9. NTTデータが描く未来：Smart AI Agent®</v>
       </c>
-      <c r="D30" s="113"/>
-      <c r="E30" s="114"/>
-      <c r="F30" s="115"/>
+      <c r="D30" s="120"/>
+      <c r="E30" s="121"/>
+      <c r="F30" s="122"/>
       <c r="G30" s="51" t="s">
         <v>40</v>
       </c>
@@ -4875,14 +4852,14 @@
     </row>
     <row r="31" spans="1:14" ht="37.799999999999997">
       <c r="A31" s="11"/>
-      <c r="B31" s="119"/>
+      <c r="B31" s="123"/>
       <c r="C31" s="51" t="str">
         <f>master!C22</f>
         <v>3-10. AIの強みを生かした業務変革の進め方</v>
       </c>
-      <c r="D31" s="113"/>
-      <c r="E31" s="114"/>
-      <c r="F31" s="115"/>
+      <c r="D31" s="120"/>
+      <c r="E31" s="121"/>
+      <c r="F31" s="122"/>
       <c r="G31" s="51" t="s">
         <v>40</v>
       </c>
@@ -4900,14 +4877,14 @@
     </row>
     <row r="32" spans="1:14" ht="37.799999999999997">
       <c r="A32" s="11"/>
-      <c r="B32" s="119"/>
+      <c r="B32" s="123"/>
       <c r="C32" s="51" t="str">
         <f>master!C23</f>
         <v>3-11. AIの強みを生かすポイント：人とAIとの役割分担</v>
       </c>
-      <c r="D32" s="113"/>
-      <c r="E32" s="114"/>
-      <c r="F32" s="115"/>
+      <c r="D32" s="120"/>
+      <c r="E32" s="121"/>
+      <c r="F32" s="122"/>
       <c r="G32" s="51" t="s">
         <v>40</v>
       </c>
@@ -4925,14 +4902,14 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="119"/>
+      <c r="B33" s="123"/>
       <c r="C33" s="51" t="str">
         <f>master!C24</f>
         <v>3-12. AIの強みを生かすポイント：プロセス自体をAI前提で再設計</v>
       </c>
-      <c r="D33" s="113"/>
-      <c r="E33" s="114"/>
-      <c r="F33" s="115"/>
+      <c r="D33" s="120"/>
+      <c r="E33" s="121"/>
+      <c r="F33" s="122"/>
       <c r="G33" s="51" t="s">
         <v>40</v>
       </c>
@@ -4950,14 +4927,14 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="119"/>
+      <c r="B34" s="123"/>
       <c r="C34" s="51" t="str">
         <f>master!C25</f>
         <v>3-13. JALカード様 -  AIバーチャル顧客を活用したマーケティング高度化</v>
       </c>
-      <c r="D34" s="113"/>
-      <c r="E34" s="114"/>
-      <c r="F34" s="115"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="121"/>
+      <c r="F34" s="122"/>
       <c r="G34" s="51" t="s">
         <v>40</v>
       </c>
@@ -4975,14 +4952,14 @@
     </row>
     <row r="35" spans="1:14" ht="37.799999999999997">
       <c r="A35" s="11"/>
-      <c r="B35" s="119"/>
+      <c r="B35" s="123"/>
       <c r="C35" s="51" t="str">
         <f>master!C26</f>
         <v>3-14. 大手メディアサービス会社 - AI-BPOによるオペレーション変革</v>
       </c>
-      <c r="D35" s="113"/>
-      <c r="E35" s="114"/>
-      <c r="F35" s="115"/>
+      <c r="D35" s="120"/>
+      <c r="E35" s="121"/>
+      <c r="F35" s="122"/>
       <c r="G35" s="51" t="s">
         <v>40</v>
       </c>
@@ -5000,14 +4977,14 @@
     </row>
     <row r="36" spans="1:14" ht="37.799999999999997">
       <c r="A36" s="11"/>
-      <c r="B36" s="119"/>
+      <c r="B36" s="123"/>
       <c r="C36" s="51" t="str">
         <f>master!C27</f>
         <v>Appendix：りそな様 - AI CoEと生成AI人財育成アカデミーの推進</v>
       </c>
-      <c r="D36" s="113"/>
-      <c r="E36" s="114"/>
-      <c r="F36" s="115"/>
+      <c r="D36" s="120"/>
+      <c r="E36" s="121"/>
+      <c r="F36" s="122"/>
       <c r="G36" s="51" t="s">
         <v>40</v>
       </c>
@@ -5025,7 +5002,7 @@
     </row>
     <row r="37" spans="1:14" ht="88.2">
       <c r="A37" s="11"/>
-      <c r="B37" s="120" t="str">
+      <c r="B37" s="116" t="str">
         <f>master!B28</f>
         <v>モジュール4：プロンプトエンジニアリング</v>
       </c>
@@ -5033,11 +5010,11 @@
         <f>master!C28</f>
         <v>4-1. プロンプトとは?</v>
       </c>
-      <c r="D37" s="113" t="s">
-        <v>174</v>
-      </c>
-      <c r="E37" s="114"/>
-      <c r="F37" s="115"/>
+      <c r="D37" s="120" t="s">
+        <v>172</v>
+      </c>
+      <c r="E37" s="121"/>
+      <c r="F37" s="122"/>
       <c r="G37" s="51" t="s">
         <v>45</v>
       </c>
@@ -5055,16 +5032,14 @@
     </row>
     <row r="38" spans="1:14" ht="37.799999999999997">
       <c r="A38" s="11"/>
-      <c r="B38" s="121"/>
+      <c r="B38" s="117"/>
       <c r="C38" s="51" t="str">
         <f>master!C29</f>
         <v>4-2. プロンプトを構成する4つの要素</v>
       </c>
-      <c r="D38" s="113" t="s">
-        <v>140</v>
-      </c>
-      <c r="E38" s="114"/>
-      <c r="F38" s="115"/>
+      <c r="D38" s="120"/>
+      <c r="E38" s="121"/>
+      <c r="F38" s="122"/>
       <c r="G38" s="51" t="s">
         <v>40</v>
       </c>
@@ -5080,20 +5055,18 @@
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
     </row>
-    <row r="39" spans="1:14" ht="63">
+    <row r="39" spans="1:14" ht="37.799999999999997">
       <c r="A39" s="11"/>
-      <c r="B39" s="121"/>
+      <c r="B39" s="117"/>
       <c r="C39" s="51" t="str">
         <f>master!C30</f>
         <v>4-3. 悪いプロンプト vs 良いプロンプト</v>
       </c>
-      <c r="D39" s="113" t="s">
-        <v>141</v>
-      </c>
-      <c r="E39" s="114"/>
-      <c r="F39" s="115"/>
+      <c r="D39" s="120"/>
+      <c r="E39" s="121"/>
+      <c r="F39" s="122"/>
       <c r="G39" s="51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="49" t="s">
@@ -5109,14 +5082,14 @@
     </row>
     <row r="40" spans="1:14" ht="37.799999999999997">
       <c r="A40" s="11"/>
-      <c r="B40" s="121"/>
+      <c r="B40" s="117"/>
       <c r="C40" s="51" t="str">
         <f>master!C31</f>
         <v>4-4. テクニック①：Role Prompting（役割の付与）</v>
       </c>
-      <c r="D40" s="113"/>
-      <c r="E40" s="114"/>
-      <c r="F40" s="115"/>
+      <c r="D40" s="120"/>
+      <c r="E40" s="121"/>
+      <c r="F40" s="122"/>
       <c r="G40" s="51" t="s">
         <v>40</v>
       </c>
@@ -5134,14 +5107,14 @@
     </row>
     <row r="41" spans="1:14" ht="37.799999999999997">
       <c r="A41" s="11"/>
-      <c r="B41" s="121"/>
+      <c r="B41" s="117"/>
       <c r="C41" s="51" t="str">
         <f>master!C32</f>
         <v>4-5. テクニック②：区切り文字の活用</v>
       </c>
-      <c r="D41" s="113"/>
-      <c r="E41" s="114"/>
-      <c r="F41" s="115"/>
+      <c r="D41" s="120"/>
+      <c r="E41" s="121"/>
+      <c r="F41" s="122"/>
       <c r="G41" s="51" t="s">
         <v>40</v>
       </c>
@@ -5159,14 +5132,14 @@
     </row>
     <row r="42" spans="1:14" ht="37.799999999999997">
       <c r="A42" s="11"/>
-      <c r="B42" s="121"/>
+      <c r="B42" s="117"/>
       <c r="C42" s="51" t="str">
         <f>master!C33</f>
         <v>4-6. テクニック③：Zero-shot vs Few-shot</v>
       </c>
-      <c r="D42" s="113"/>
-      <c r="E42" s="114"/>
-      <c r="F42" s="115"/>
+      <c r="D42" s="120"/>
+      <c r="E42" s="121"/>
+      <c r="F42" s="122"/>
       <c r="G42" s="51" t="s">
         <v>40</v>
       </c>
@@ -5184,14 +5157,14 @@
     </row>
     <row r="43" spans="1:14" ht="50.4">
       <c r="A43" s="11"/>
-      <c r="B43" s="122"/>
+      <c r="B43" s="118"/>
       <c r="C43" s="51" t="str">
         <f>master!C34</f>
         <v>4-7. テクニック④：Chain of Thought（思考の連鎖）</v>
       </c>
-      <c r="D43" s="113"/>
-      <c r="E43" s="114"/>
-      <c r="F43" s="115"/>
+      <c r="D43" s="120"/>
+      <c r="E43" s="121"/>
+      <c r="F43" s="122"/>
       <c r="G43" s="51" t="s">
         <v>41</v>
       </c>
@@ -5209,7 +5182,7 @@
     </row>
     <row r="44" spans="1:14" ht="75.599999999999994">
       <c r="A44" s="11"/>
-      <c r="B44" s="123" t="str">
+      <c r="B44" s="114" t="str">
         <f>master!B35</f>
         <v>モジュール5：ハンズオン（ChatGPT）</v>
       </c>
@@ -5217,11 +5190,11 @@
         <f>master!C35</f>
         <v>5-1. ChatGPTの使い方（一般チャット）</v>
       </c>
-      <c r="D44" s="126" t="s">
-        <v>175</v>
-      </c>
-      <c r="E44" s="127"/>
-      <c r="F44" s="128"/>
+      <c r="D44" s="108" t="s">
+        <v>173</v>
+      </c>
+      <c r="E44" s="109"/>
+      <c r="F44" s="110"/>
       <c r="G44" s="64" t="s">
         <v>42</v>
       </c>
@@ -5239,16 +5212,16 @@
     </row>
     <row r="45" spans="1:14" ht="126">
       <c r="A45" s="11"/>
-      <c r="B45" s="124"/>
+      <c r="B45" s="119"/>
       <c r="C45" s="64" t="str">
         <f>master!C36</f>
         <v>5-2. 例①：顧客提案向けの企画提案書を作りたい</v>
       </c>
-      <c r="D45" s="126" t="s">
-        <v>183</v>
-      </c>
-      <c r="E45" s="127"/>
-      <c r="F45" s="128"/>
+      <c r="D45" s="108" t="s">
+        <v>181</v>
+      </c>
+      <c r="E45" s="109"/>
+      <c r="F45" s="110"/>
       <c r="G45" s="64" t="s">
         <v>44</v>
       </c>
@@ -5266,16 +5239,16 @@
     </row>
     <row r="46" spans="1:14" ht="126">
       <c r="A46" s="11"/>
-      <c r="B46" s="124"/>
+      <c r="B46" s="119"/>
       <c r="C46" s="64" t="str">
         <f>master!C37</f>
         <v>5-3. 例①：顧客提案向けの企画提案書を作りたい - プロンプト例</v>
       </c>
-      <c r="D46" s="126" t="s">
-        <v>143</v>
-      </c>
-      <c r="E46" s="127"/>
-      <c r="F46" s="128"/>
+      <c r="D46" s="108" t="s">
+        <v>141</v>
+      </c>
+      <c r="E46" s="109"/>
+      <c r="F46" s="110"/>
       <c r="G46" s="64" t="s">
         <v>44</v>
       </c>
@@ -5293,16 +5266,16 @@
     </row>
     <row r="47" spans="1:14" ht="37.799999999999997">
       <c r="A47" s="11"/>
-      <c r="B47" s="124"/>
+      <c r="B47" s="119"/>
       <c r="C47" s="64" t="str">
         <f>master!C38</f>
         <v>5-4. 例①：顧客提案向けの企画提案書を作りたい - 実行例</v>
       </c>
-      <c r="D47" s="126" t="s">
-        <v>142</v>
-      </c>
-      <c r="E47" s="127"/>
-      <c r="F47" s="128"/>
+      <c r="D47" s="108" t="s">
+        <v>140</v>
+      </c>
+      <c r="E47" s="109"/>
+      <c r="F47" s="110"/>
       <c r="G47" s="64" t="s">
         <v>40</v>
       </c>
@@ -5320,13 +5293,13 @@
     </row>
     <row r="48" spans="1:14" ht="88.2">
       <c r="A48" s="11"/>
-      <c r="B48" s="124"/>
+      <c r="B48" s="119"/>
       <c r="C48" s="84"/>
-      <c r="D48" s="116" t="s">
-        <v>182</v>
-      </c>
-      <c r="E48" s="117"/>
-      <c r="F48" s="118"/>
+      <c r="D48" s="111" t="s">
+        <v>180</v>
+      </c>
+      <c r="E48" s="112"/>
+      <c r="F48" s="113"/>
       <c r="G48" s="84" t="s">
         <v>45</v>
       </c>
@@ -5346,16 +5319,16 @@
     </row>
     <row r="49" spans="1:14" ht="50.4">
       <c r="A49" s="11"/>
-      <c r="B49" s="124"/>
+      <c r="B49" s="119"/>
       <c r="C49" s="64" t="str">
         <f>master!C39</f>
         <v>5-5. 例②：100本ノックを作ってみる</v>
       </c>
-      <c r="D49" s="126" t="s">
-        <v>190</v>
-      </c>
-      <c r="E49" s="127"/>
-      <c r="F49" s="128"/>
+      <c r="D49" s="108" t="s">
+        <v>188</v>
+      </c>
+      <c r="E49" s="109"/>
+      <c r="F49" s="110"/>
       <c r="G49" s="64" t="s">
         <v>41</v>
       </c>
@@ -5373,16 +5346,16 @@
     </row>
     <row r="50" spans="1:14" ht="75.599999999999994">
       <c r="A50" s="11"/>
-      <c r="B50" s="124"/>
+      <c r="B50" s="119"/>
       <c r="C50" s="64" t="str">
         <f>master!C40</f>
         <v>5-6. 例②：100本ノックを作ってみる -プロンプト例</v>
       </c>
-      <c r="D50" s="126" t="s">
-        <v>176</v>
-      </c>
-      <c r="E50" s="127"/>
-      <c r="F50" s="128"/>
+      <c r="D50" s="108" t="s">
+        <v>174</v>
+      </c>
+      <c r="E50" s="109"/>
+      <c r="F50" s="110"/>
       <c r="G50" s="64" t="s">
         <v>42</v>
       </c>
@@ -5400,19 +5373,19 @@
     </row>
     <row r="51" spans="1:14" ht="88.2">
       <c r="A51" s="11"/>
-      <c r="B51" s="124"/>
+      <c r="B51" s="119"/>
       <c r="C51" s="84"/>
-      <c r="D51" s="116" t="s">
-        <v>184</v>
-      </c>
-      <c r="E51" s="117"/>
-      <c r="F51" s="118"/>
+      <c r="D51" s="111" t="s">
+        <v>182</v>
+      </c>
+      <c r="E51" s="112"/>
+      <c r="F51" s="113"/>
       <c r="G51" s="84" t="s">
         <v>45</v>
       </c>
       <c r="H51" s="85"/>
       <c r="I51" s="86" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J51" s="87">
         <v>1.3888888888888888E-2</v>
@@ -5426,16 +5399,16 @@
     </row>
     <row r="52" spans="1:14" ht="50.4">
       <c r="A52" s="11"/>
-      <c r="B52" s="124"/>
+      <c r="B52" s="119"/>
       <c r="C52" s="64" t="str">
         <f>master!C41</f>
         <v>5-7. 例②：100本ノックを作ってみる - 実行結果①</v>
       </c>
-      <c r="D52" s="126" t="s">
-        <v>153</v>
-      </c>
-      <c r="E52" s="127"/>
-      <c r="F52" s="128"/>
+      <c r="D52" s="108" t="s">
+        <v>151</v>
+      </c>
+      <c r="E52" s="109"/>
+      <c r="F52" s="110"/>
       <c r="G52" s="64" t="s">
         <v>41</v>
       </c>
@@ -5453,16 +5426,16 @@
     </row>
     <row r="53" spans="1:14" ht="50.4">
       <c r="A53" s="11"/>
-      <c r="B53" s="124"/>
+      <c r="B53" s="119"/>
       <c r="C53" s="64" t="str">
         <f>master!C42</f>
         <v>5-8. 例②：100本ノックを作ってみる - 実行結果②</v>
       </c>
-      <c r="D53" s="126" t="s">
-        <v>154</v>
-      </c>
-      <c r="E53" s="127"/>
-      <c r="F53" s="128"/>
+      <c r="D53" s="108" t="s">
+        <v>152</v>
+      </c>
+      <c r="E53" s="109"/>
+      <c r="F53" s="110"/>
       <c r="G53" s="64" t="s">
         <v>41</v>
       </c>
@@ -5480,16 +5453,16 @@
     </row>
     <row r="54" spans="1:14" ht="50.4">
       <c r="A54" s="11"/>
-      <c r="B54" s="124"/>
+      <c r="B54" s="119"/>
       <c r="C54" s="64" t="str">
         <f>master!C43</f>
         <v>5-9. 例②：100本ノックを作ってみる - 実行結果③</v>
       </c>
-      <c r="D54" s="126" t="s">
-        <v>155</v>
-      </c>
-      <c r="E54" s="127"/>
-      <c r="F54" s="128"/>
+      <c r="D54" s="108" t="s">
+        <v>153</v>
+      </c>
+      <c r="E54" s="109"/>
+      <c r="F54" s="110"/>
       <c r="G54" s="64" t="s">
         <v>41</v>
       </c>
@@ -5507,16 +5480,16 @@
     </row>
     <row r="55" spans="1:14" ht="63">
       <c r="A55" s="11"/>
-      <c r="B55" s="125"/>
+      <c r="B55" s="115"/>
       <c r="C55" s="64" t="str">
         <f>master!C44</f>
         <v>5-10. ChatGPT まとめ</v>
       </c>
-      <c r="D55" s="126" t="s">
-        <v>144</v>
-      </c>
-      <c r="E55" s="127"/>
-      <c r="F55" s="128"/>
+      <c r="D55" s="108" t="s">
+        <v>142</v>
+      </c>
+      <c r="E55" s="109"/>
+      <c r="F55" s="110"/>
       <c r="G55" s="64" t="s">
         <v>39</v>
       </c>
@@ -5534,7 +5507,7 @@
     </row>
     <row r="56" spans="1:14" ht="50.4" customHeight="1">
       <c r="A56" s="11"/>
-      <c r="B56" s="124" t="str">
+      <c r="B56" s="119" t="str">
         <f>master!B45</f>
         <v>モジュール6：ハンズオン（ GitHub Copilot ）</v>
       </c>
@@ -5542,11 +5515,11 @@
         <f>master!C45</f>
         <v>6-1. Visual Studio Code を開く</v>
       </c>
-      <c r="D56" s="126" t="s">
-        <v>145</v>
-      </c>
-      <c r="E56" s="127"/>
-      <c r="F56" s="128"/>
+      <c r="D56" s="108" t="s">
+        <v>143</v>
+      </c>
+      <c r="E56" s="109"/>
+      <c r="F56" s="110"/>
       <c r="G56" s="64" t="s">
         <v>41</v>
       </c>
@@ -5564,16 +5537,16 @@
     </row>
     <row r="57" spans="1:14" ht="63">
       <c r="A57" s="11"/>
-      <c r="B57" s="124"/>
+      <c r="B57" s="119"/>
       <c r="C57" s="64" t="str">
         <f>master!C46</f>
         <v>6-2. コード補完機能</v>
       </c>
-      <c r="D57" s="126" t="s">
-        <v>146</v>
-      </c>
-      <c r="E57" s="127"/>
-      <c r="F57" s="128"/>
+      <c r="D57" s="108" t="s">
+        <v>144</v>
+      </c>
+      <c r="E57" s="109"/>
+      <c r="F57" s="110"/>
       <c r="G57" s="64" t="s">
         <v>39</v>
       </c>
@@ -5591,16 +5564,16 @@
     </row>
     <row r="58" spans="1:14" ht="75.599999999999994">
       <c r="A58" s="11"/>
-      <c r="B58" s="124"/>
+      <c r="B58" s="119"/>
       <c r="C58" s="64" t="str">
         <f>master!C47</f>
         <v>6-3. チャット機能</v>
       </c>
-      <c r="D58" s="126" t="s">
-        <v>200</v>
-      </c>
-      <c r="E58" s="127"/>
-      <c r="F58" s="128"/>
+      <c r="D58" s="108" t="s">
+        <v>198</v>
+      </c>
+      <c r="E58" s="109"/>
+      <c r="F58" s="110"/>
       <c r="G58" s="64" t="s">
         <v>42</v>
       </c>
@@ -5618,16 +5591,16 @@
     </row>
     <row r="59" spans="1:14" ht="88.2">
       <c r="A59" s="11"/>
-      <c r="B59" s="124"/>
+      <c r="B59" s="119"/>
       <c r="C59" s="64" t="str">
         <f>master!C48</f>
         <v>6-4. チャット機能 - コマンド</v>
       </c>
-      <c r="D59" s="126" t="s">
-        <v>199</v>
-      </c>
-      <c r="E59" s="127"/>
-      <c r="F59" s="128"/>
+      <c r="D59" s="108" t="s">
+        <v>197</v>
+      </c>
+      <c r="E59" s="109"/>
+      <c r="F59" s="110"/>
       <c r="G59" s="64" t="s">
         <v>45</v>
       </c>
@@ -5645,16 +5618,16 @@
     </row>
     <row r="60" spans="1:14" ht="50.4">
       <c r="A60" s="11"/>
-      <c r="B60" s="124"/>
+      <c r="B60" s="119"/>
       <c r="C60" s="64" t="str">
         <f>master!C49</f>
         <v>6-5. 簡単なアプリやゲームを作ってみましょう</v>
       </c>
-      <c r="D60" s="126" t="s">
-        <v>167</v>
-      </c>
-      <c r="E60" s="127"/>
-      <c r="F60" s="128"/>
+      <c r="D60" s="108" t="s">
+        <v>165</v>
+      </c>
+      <c r="E60" s="109"/>
+      <c r="F60" s="110"/>
       <c r="G60" s="64" t="s">
         <v>41</v>
       </c>
@@ -5672,16 +5645,16 @@
     </row>
     <row r="61" spans="1:14" ht="50.4">
       <c r="A61" s="11"/>
-      <c r="B61" s="124"/>
+      <c r="B61" s="119"/>
       <c r="C61" s="64" t="str">
         <f>master!C50</f>
         <v>6-6. 例①：高級志向テトリス</v>
       </c>
-      <c r="D61" s="126" t="s">
-        <v>170</v>
-      </c>
-      <c r="E61" s="127"/>
-      <c r="F61" s="128"/>
+      <c r="D61" s="108" t="s">
+        <v>168</v>
+      </c>
+      <c r="E61" s="109"/>
+      <c r="F61" s="110"/>
       <c r="G61" s="64" t="s">
         <v>41</v>
       </c>
@@ -5699,16 +5672,16 @@
     </row>
     <row r="62" spans="1:14" ht="50.4">
       <c r="A62" s="11"/>
-      <c r="B62" s="124"/>
+      <c r="B62" s="119"/>
       <c r="C62" s="64" t="str">
         <f>master!C51</f>
         <v>6-7. 例②：わくわく！にっぽんダーツの旅</v>
       </c>
-      <c r="D62" s="126" t="s">
-        <v>168</v>
-      </c>
-      <c r="E62" s="127"/>
-      <c r="F62" s="128"/>
+      <c r="D62" s="108" t="s">
+        <v>166</v>
+      </c>
+      <c r="E62" s="109"/>
+      <c r="F62" s="110"/>
       <c r="G62" s="64" t="s">
         <v>41</v>
       </c>
@@ -5726,16 +5699,16 @@
     </row>
     <row r="63" spans="1:14" ht="50.4">
       <c r="A63" s="11"/>
-      <c r="B63" s="124"/>
+      <c r="B63" s="119"/>
       <c r="C63" s="64" t="str">
         <f>master!C52</f>
         <v>6-8. 例③：タスク管理ツール</v>
       </c>
-      <c r="D63" s="126" t="s">
-        <v>169</v>
-      </c>
-      <c r="E63" s="127"/>
-      <c r="F63" s="128"/>
+      <c r="D63" s="108" t="s">
+        <v>167</v>
+      </c>
+      <c r="E63" s="109"/>
+      <c r="F63" s="110"/>
       <c r="G63" s="64" t="s">
         <v>41</v>
       </c>
@@ -5753,13 +5726,13 @@
     </row>
     <row r="64" spans="1:14" ht="138.6">
       <c r="A64" s="11"/>
-      <c r="B64" s="124"/>
+      <c r="B64" s="119"/>
       <c r="C64" s="84"/>
-      <c r="D64" s="116" t="s">
-        <v>181</v>
-      </c>
-      <c r="E64" s="117"/>
-      <c r="F64" s="118"/>
+      <c r="D64" s="111" t="s">
+        <v>179</v>
+      </c>
+      <c r="E64" s="112"/>
+      <c r="F64" s="113"/>
       <c r="G64" s="84" t="s">
         <v>38</v>
       </c>
@@ -5777,16 +5750,16 @@
     </row>
     <row r="65" spans="1:14" ht="75.599999999999994">
       <c r="A65" s="11"/>
-      <c r="B65" s="124"/>
+      <c r="B65" s="119"/>
       <c r="C65" s="64" t="str">
         <f>master!C53</f>
         <v>6-9. ディレクトリ作成とファイル配置</v>
       </c>
-      <c r="D65" s="126" t="s">
-        <v>185</v>
-      </c>
-      <c r="E65" s="127"/>
-      <c r="F65" s="128"/>
+      <c r="D65" s="108" t="s">
+        <v>183</v>
+      </c>
+      <c r="E65" s="109"/>
+      <c r="F65" s="110"/>
       <c r="G65" s="64" t="s">
         <v>42</v>
       </c>
@@ -5804,13 +5777,13 @@
     </row>
     <row r="66" spans="1:14" ht="88.2">
       <c r="A66" s="11"/>
-      <c r="B66" s="124"/>
+      <c r="B66" s="119"/>
       <c r="C66" s="84"/>
-      <c r="D66" s="116" t="s">
-        <v>201</v>
-      </c>
-      <c r="E66" s="117"/>
-      <c r="F66" s="118"/>
+      <c r="D66" s="111" t="s">
+        <v>199</v>
+      </c>
+      <c r="E66" s="112"/>
+      <c r="F66" s="113"/>
       <c r="G66" s="84" t="s">
         <v>45</v>
       </c>
@@ -5828,16 +5801,16 @@
     </row>
     <row r="67" spans="1:14" ht="50.4">
       <c r="A67" s="11"/>
-      <c r="B67" s="124"/>
+      <c r="B67" s="119"/>
       <c r="C67" s="64" t="str">
         <f>master!C54</f>
         <v>6-10. チャット機能 - Askモード</v>
       </c>
-      <c r="D67" s="126" t="s">
-        <v>196</v>
-      </c>
-      <c r="E67" s="127"/>
-      <c r="F67" s="128"/>
+      <c r="D67" s="108" t="s">
+        <v>194</v>
+      </c>
+      <c r="E67" s="109"/>
+      <c r="F67" s="110"/>
       <c r="G67" s="64" t="s">
         <v>41</v>
       </c>
@@ -5855,16 +5828,16 @@
     </row>
     <row r="68" spans="1:14" ht="100.8">
       <c r="A68" s="11"/>
-      <c r="B68" s="124"/>
+      <c r="B68" s="119"/>
       <c r="C68" s="64" t="str">
         <f>master!C55</f>
         <v>6-11. Askモードについて</v>
       </c>
-      <c r="D68" s="126" t="s">
-        <v>148</v>
-      </c>
-      <c r="E68" s="127"/>
-      <c r="F68" s="128"/>
+      <c r="D68" s="108" t="s">
+        <v>146</v>
+      </c>
+      <c r="E68" s="109"/>
+      <c r="F68" s="110"/>
       <c r="G68" s="64" t="s">
         <v>47</v>
       </c>
@@ -5882,16 +5855,16 @@
     </row>
     <row r="69" spans="1:14" ht="50.4">
       <c r="A69" s="11"/>
-      <c r="B69" s="124"/>
+      <c r="B69" s="119"/>
       <c r="C69" s="64" t="str">
         <f>master!C56</f>
         <v>6-12. 実行例①</v>
       </c>
-      <c r="D69" s="126" t="s">
-        <v>152</v>
-      </c>
-      <c r="E69" s="127"/>
-      <c r="F69" s="128"/>
+      <c r="D69" s="108" t="s">
+        <v>150</v>
+      </c>
+      <c r="E69" s="109"/>
+      <c r="F69" s="110"/>
       <c r="G69" s="64" t="s">
         <v>41</v>
       </c>
@@ -5909,16 +5882,16 @@
     </row>
     <row r="70" spans="1:14" ht="50.4">
       <c r="A70" s="11"/>
-      <c r="B70" s="124"/>
+      <c r="B70" s="119"/>
       <c r="C70" s="64" t="str">
         <f>master!C57</f>
         <v>6-13. 実行例②</v>
       </c>
-      <c r="D70" s="126" t="s">
-        <v>150</v>
-      </c>
-      <c r="E70" s="127"/>
-      <c r="F70" s="128"/>
+      <c r="D70" s="108" t="s">
+        <v>148</v>
+      </c>
+      <c r="E70" s="109"/>
+      <c r="F70" s="110"/>
       <c r="G70" s="64" t="s">
         <v>41</v>
       </c>
@@ -5936,16 +5909,16 @@
     </row>
     <row r="71" spans="1:14" ht="50.4">
       <c r="A71" s="11"/>
-      <c r="B71" s="124"/>
+      <c r="B71" s="119"/>
       <c r="C71" s="64" t="str">
         <f>master!C58</f>
         <v>6-14. 実行例③</v>
       </c>
-      <c r="D71" s="126" t="s">
-        <v>151</v>
-      </c>
-      <c r="E71" s="127"/>
-      <c r="F71" s="128"/>
+      <c r="D71" s="108" t="s">
+        <v>149</v>
+      </c>
+      <c r="E71" s="109"/>
+      <c r="F71" s="110"/>
       <c r="G71" s="64" t="s">
         <v>41</v>
       </c>
@@ -5963,13 +5936,13 @@
     </row>
     <row r="72" spans="1:14" ht="138.6">
       <c r="A72" s="11"/>
-      <c r="B72" s="124"/>
+      <c r="B72" s="119"/>
       <c r="C72" s="84"/>
-      <c r="D72" s="116" t="s">
-        <v>180</v>
-      </c>
-      <c r="E72" s="117"/>
-      <c r="F72" s="118"/>
+      <c r="D72" s="111" t="s">
+        <v>178</v>
+      </c>
+      <c r="E72" s="112"/>
+      <c r="F72" s="113"/>
       <c r="G72" s="84" t="s">
         <v>38</v>
       </c>
@@ -5987,16 +5960,16 @@
     </row>
     <row r="73" spans="1:14" ht="63">
       <c r="A73" s="11"/>
-      <c r="B73" s="124"/>
+      <c r="B73" s="119"/>
       <c r="C73" s="64" t="str">
         <f>master!C59</f>
         <v>6-15. Askモードまとめ</v>
       </c>
-      <c r="D73" s="126" t="s">
-        <v>147</v>
-      </c>
-      <c r="E73" s="127"/>
-      <c r="F73" s="128"/>
+      <c r="D73" s="108" t="s">
+        <v>145</v>
+      </c>
+      <c r="E73" s="109"/>
+      <c r="F73" s="110"/>
       <c r="G73" s="64" t="s">
         <v>39</v>
       </c>
@@ -6014,16 +5987,16 @@
     </row>
     <row r="74" spans="1:14" ht="50.4">
       <c r="A74" s="11"/>
-      <c r="B74" s="124"/>
+      <c r="B74" s="119"/>
       <c r="C74" s="64" t="str">
         <f>master!C60</f>
         <v>6-16. チャット機能 - Agentモード</v>
       </c>
-      <c r="D74" s="126" t="s">
-        <v>197</v>
-      </c>
-      <c r="E74" s="127"/>
-      <c r="F74" s="128"/>
+      <c r="D74" s="108" t="s">
+        <v>195</v>
+      </c>
+      <c r="E74" s="109"/>
+      <c r="F74" s="110"/>
       <c r="G74" s="64" t="s">
         <v>41</v>
       </c>
@@ -6041,16 +6014,16 @@
     </row>
     <row r="75" spans="1:14" ht="63">
       <c r="A75" s="11"/>
-      <c r="B75" s="124"/>
+      <c r="B75" s="119"/>
       <c r="C75" s="64" t="str">
         <f>master!C61</f>
         <v>6-17. Agentモード</v>
       </c>
-      <c r="D75" s="126" t="s">
-        <v>156</v>
-      </c>
-      <c r="E75" s="127"/>
-      <c r="F75" s="128"/>
+      <c r="D75" s="108" t="s">
+        <v>154</v>
+      </c>
+      <c r="E75" s="109"/>
+      <c r="F75" s="110"/>
       <c r="G75" s="64" t="s">
         <v>39</v>
       </c>
@@ -6068,16 +6041,16 @@
     </row>
     <row r="76" spans="1:14" ht="50.4">
       <c r="A76" s="11"/>
-      <c r="B76" s="124"/>
+      <c r="B76" s="119"/>
       <c r="C76" s="64" t="str">
         <f>master!C62</f>
         <v>6-18. 実行例</v>
       </c>
-      <c r="D76" s="126" t="s">
-        <v>157</v>
-      </c>
-      <c r="E76" s="127"/>
-      <c r="F76" s="128"/>
+      <c r="D76" s="108" t="s">
+        <v>155</v>
+      </c>
+      <c r="E76" s="109"/>
+      <c r="F76" s="110"/>
       <c r="G76" s="64" t="s">
         <v>41</v>
       </c>
@@ -6095,16 +6068,16 @@
     </row>
     <row r="77" spans="1:14" ht="37.799999999999997">
       <c r="A77" s="11"/>
-      <c r="B77" s="124"/>
+      <c r="B77" s="119"/>
       <c r="C77" s="64" t="str">
         <f>master!C63</f>
         <v>6-19. READMEの内容を確認しましょう①</v>
       </c>
-      <c r="D77" s="126" t="s">
-        <v>203</v>
-      </c>
-      <c r="E77" s="127"/>
-      <c r="F77" s="128"/>
+      <c r="D77" s="108" t="s">
+        <v>201</v>
+      </c>
+      <c r="E77" s="109"/>
+      <c r="F77" s="110"/>
       <c r="G77" s="64" t="s">
         <v>40</v>
       </c>
@@ -6122,16 +6095,16 @@
     </row>
     <row r="78" spans="1:14" ht="37.799999999999997">
       <c r="A78" s="11"/>
-      <c r="B78" s="124"/>
+      <c r="B78" s="119"/>
       <c r="C78" s="64" t="str">
         <f>master!C64</f>
         <v>6-20. READMEの内容を確認しましょう②</v>
       </c>
-      <c r="D78" s="126" t="s">
-        <v>202</v>
-      </c>
-      <c r="E78" s="127"/>
-      <c r="F78" s="128"/>
+      <c r="D78" s="108" t="s">
+        <v>200</v>
+      </c>
+      <c r="E78" s="109"/>
+      <c r="F78" s="110"/>
       <c r="G78" s="64" t="s">
         <v>40</v>
       </c>
@@ -6149,13 +6122,13 @@
     </row>
     <row r="79" spans="1:14" ht="126">
       <c r="A79" s="11"/>
-      <c r="B79" s="124"/>
+      <c r="B79" s="119"/>
       <c r="C79" s="84"/>
-      <c r="D79" s="116" t="s">
-        <v>179</v>
-      </c>
-      <c r="E79" s="117"/>
-      <c r="F79" s="118"/>
+      <c r="D79" s="111" t="s">
+        <v>177</v>
+      </c>
+      <c r="E79" s="112"/>
+      <c r="F79" s="113"/>
       <c r="G79" s="84" t="s">
         <v>44</v>
       </c>
@@ -6167,7 +6140,7 @@
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="K79" s="88" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
@@ -6175,16 +6148,16 @@
     </row>
     <row r="80" spans="1:14" ht="50.4">
       <c r="A80" s="11"/>
-      <c r="B80" s="124"/>
+      <c r="B80" s="119"/>
       <c r="C80" s="64" t="str">
         <f>master!C65</f>
         <v>6-21. Changeログを作ってみましょう</v>
       </c>
-      <c r="D80" s="126" t="s">
-        <v>158</v>
-      </c>
-      <c r="E80" s="127"/>
-      <c r="F80" s="128"/>
+      <c r="D80" s="108" t="s">
+        <v>156</v>
+      </c>
+      <c r="E80" s="109"/>
+      <c r="F80" s="110"/>
       <c r="G80" s="64" t="s">
         <v>41</v>
       </c>
@@ -6202,19 +6175,19 @@
     </row>
     <row r="81" spans="1:14" ht="113.4">
       <c r="A81" s="11"/>
-      <c r="B81" s="124"/>
+      <c r="B81" s="119"/>
       <c r="C81" s="89"/>
-      <c r="D81" s="116" t="s">
-        <v>178</v>
-      </c>
-      <c r="E81" s="117"/>
-      <c r="F81" s="118"/>
+      <c r="D81" s="111" t="s">
+        <v>176</v>
+      </c>
+      <c r="E81" s="112"/>
+      <c r="F81" s="113"/>
       <c r="G81" s="84" t="s">
         <v>43</v>
       </c>
       <c r="H81" s="85"/>
       <c r="I81" s="86" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J81" s="87">
         <v>6.9444444444444441E-3</v>
@@ -6228,16 +6201,16 @@
     </row>
     <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="124"/>
+      <c r="B82" s="119"/>
       <c r="C82" s="64" t="str">
         <f>master!C66</f>
         <v>6-22. チャット機能 - Planモード</v>
       </c>
-      <c r="D82" s="126" t="s">
-        <v>198</v>
-      </c>
-      <c r="E82" s="127"/>
-      <c r="F82" s="128"/>
+      <c r="D82" s="108" t="s">
+        <v>196</v>
+      </c>
+      <c r="E82" s="109"/>
+      <c r="F82" s="110"/>
       <c r="G82" s="64" t="s">
         <v>41</v>
       </c>
@@ -6255,16 +6228,16 @@
     </row>
     <row r="83" spans="1:14" ht="63">
       <c r="A83" s="11"/>
-      <c r="B83" s="124"/>
+      <c r="B83" s="119"/>
       <c r="C83" s="64" t="str">
         <f>master!C67</f>
         <v>6-23. Planモードで機能追加してみましょう</v>
       </c>
-      <c r="D83" s="126" t="s">
-        <v>162</v>
-      </c>
-      <c r="E83" s="127"/>
-      <c r="F83" s="128"/>
+      <c r="D83" s="108" t="s">
+        <v>160</v>
+      </c>
+      <c r="E83" s="109"/>
+      <c r="F83" s="110"/>
       <c r="G83" s="64" t="s">
         <v>39</v>
       </c>
@@ -6282,16 +6255,16 @@
     </row>
     <row r="84" spans="1:14" ht="63">
       <c r="A84" s="11"/>
-      <c r="B84" s="124"/>
+      <c r="B84" s="119"/>
       <c r="C84" s="64" t="str">
         <f>master!C68</f>
         <v>6-24. 実行例①</v>
       </c>
-      <c r="D84" s="126" t="s">
-        <v>159</v>
-      </c>
-      <c r="E84" s="127"/>
-      <c r="F84" s="128"/>
+      <c r="D84" s="108" t="s">
+        <v>157</v>
+      </c>
+      <c r="E84" s="109"/>
+      <c r="F84" s="110"/>
       <c r="G84" s="64" t="s">
         <v>39</v>
       </c>
@@ -6309,16 +6282,16 @@
     </row>
     <row r="85" spans="1:14" ht="50.4">
       <c r="A85" s="11"/>
-      <c r="B85" s="124"/>
+      <c r="B85" s="119"/>
       <c r="C85" s="64" t="str">
         <f>master!C69</f>
         <v>6-25. 実行例②</v>
       </c>
-      <c r="D85" s="126" t="s">
-        <v>160</v>
-      </c>
-      <c r="E85" s="127"/>
-      <c r="F85" s="128"/>
+      <c r="D85" s="108" t="s">
+        <v>158</v>
+      </c>
+      <c r="E85" s="109"/>
+      <c r="F85" s="110"/>
       <c r="G85" s="64" t="s">
         <v>41</v>
       </c>
@@ -6336,16 +6309,16 @@
     </row>
     <row r="86" spans="1:14" ht="50.4">
       <c r="A86" s="11"/>
-      <c r="B86" s="124"/>
+      <c r="B86" s="119"/>
       <c r="C86" s="64" t="str">
         <f>master!C70</f>
         <v>6-26. 実行例③</v>
       </c>
-      <c r="D86" s="126" t="s">
-        <v>161</v>
-      </c>
-      <c r="E86" s="127"/>
-      <c r="F86" s="128"/>
+      <c r="D86" s="108" t="s">
+        <v>159</v>
+      </c>
+      <c r="E86" s="109"/>
+      <c r="F86" s="110"/>
       <c r="G86" s="64" t="s">
         <v>41</v>
       </c>
@@ -6363,13 +6336,13 @@
     </row>
     <row r="87" spans="1:14" ht="126">
       <c r="A87" s="11"/>
-      <c r="B87" s="124"/>
+      <c r="B87" s="119"/>
       <c r="C87" s="84"/>
-      <c r="D87" s="116" t="s">
-        <v>177</v>
-      </c>
-      <c r="E87" s="117"/>
-      <c r="F87" s="118"/>
+      <c r="D87" s="111" t="s">
+        <v>175</v>
+      </c>
+      <c r="E87" s="112"/>
+      <c r="F87" s="113"/>
       <c r="G87" s="84" t="s">
         <v>44</v>
       </c>
@@ -6387,16 +6360,16 @@
     </row>
     <row r="88" spans="1:14" ht="50.4">
       <c r="A88" s="11"/>
-      <c r="B88" s="124"/>
+      <c r="B88" s="119"/>
       <c r="C88" s="64" t="str">
         <f>master!C71</f>
         <v>6-27. 実行結果①</v>
       </c>
-      <c r="D88" s="126" t="s">
-        <v>163</v>
-      </c>
-      <c r="E88" s="127"/>
-      <c r="F88" s="128"/>
+      <c r="D88" s="108" t="s">
+        <v>161</v>
+      </c>
+      <c r="E88" s="109"/>
+      <c r="F88" s="110"/>
       <c r="G88" s="64" t="s">
         <v>41</v>
       </c>
@@ -6414,16 +6387,16 @@
     </row>
     <row r="89" spans="1:14" ht="50.4">
       <c r="A89" s="11"/>
-      <c r="B89" s="124"/>
+      <c r="B89" s="119"/>
       <c r="C89" s="64" t="str">
         <f>master!C72</f>
         <v>6-28. 実行結果②</v>
       </c>
-      <c r="D89" s="126" t="s">
-        <v>164</v>
-      </c>
-      <c r="E89" s="127"/>
-      <c r="F89" s="128"/>
+      <c r="D89" s="108" t="s">
+        <v>162</v>
+      </c>
+      <c r="E89" s="109"/>
+      <c r="F89" s="110"/>
       <c r="G89" s="64" t="s">
         <v>41</v>
       </c>
@@ -6441,16 +6414,16 @@
     </row>
     <row r="90" spans="1:14" ht="113.4">
       <c r="A90" s="11"/>
-      <c r="B90" s="125"/>
+      <c r="B90" s="115"/>
       <c r="C90" s="64" t="str">
         <f>master!C73</f>
         <v>6-29. Planモード＆Agentモードまとめ</v>
       </c>
-      <c r="D90" s="126" t="s">
-        <v>165</v>
-      </c>
-      <c r="E90" s="127"/>
-      <c r="F90" s="128"/>
+      <c r="D90" s="108" t="s">
+        <v>163</v>
+      </c>
+      <c r="E90" s="109"/>
+      <c r="F90" s="110"/>
       <c r="G90" s="64" t="s">
         <v>43</v>
       </c>
@@ -6468,7 +6441,7 @@
     </row>
     <row r="91" spans="1:14" ht="102" customHeight="1">
       <c r="A91" s="11"/>
-      <c r="B91" s="123" t="str">
+      <c r="B91" s="114" t="str">
         <f>master!B74</f>
         <v>成果物のプレゼン</v>
       </c>
@@ -6476,11 +6449,11 @@
         <f>master!C74</f>
         <v>開発した成果物のプレゼン（グループ）</v>
       </c>
-      <c r="D91" s="116" t="s">
-        <v>193</v>
-      </c>
-      <c r="E91" s="117"/>
-      <c r="F91" s="118"/>
+      <c r="D91" s="111" t="s">
+        <v>191</v>
+      </c>
+      <c r="E91" s="112"/>
+      <c r="F91" s="113"/>
       <c r="G91" s="84" t="s">
         <v>47</v>
       </c>
@@ -6498,16 +6471,16 @@
     </row>
     <row r="92" spans="1:14" ht="88.2">
       <c r="A92" s="11"/>
-      <c r="B92" s="125"/>
+      <c r="B92" s="115"/>
       <c r="C92" s="84" t="str">
         <f>master!C75</f>
         <v>開発した成果物のプレゼン（全体）</v>
       </c>
-      <c r="D92" s="116" t="s">
-        <v>188</v>
-      </c>
-      <c r="E92" s="117"/>
-      <c r="F92" s="118"/>
+      <c r="D92" s="111" t="s">
+        <v>186</v>
+      </c>
+      <c r="E92" s="112"/>
+      <c r="F92" s="113"/>
       <c r="G92" s="84" t="s">
         <v>45</v>
       </c>
@@ -6519,7 +6492,7 @@
         <v>36</v>
       </c>
       <c r="K92" s="88" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
@@ -6531,34 +6504,61 @@
     <row r="94" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="B22:B36"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="B44:B55"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
     <mergeCell ref="B37:B43"/>
     <mergeCell ref="D60:F60"/>
     <mergeCell ref="D78:F78"/>
@@ -6575,61 +6575,34 @@
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="B56:B90"/>
     <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="B44:B55"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="B22:B36"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="D79:F79"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6713,7 +6686,7 @@
     </row>
     <row r="9" spans="2:3">
       <c r="C9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="2:3">
@@ -6733,7 +6706,7 @@
     </row>
     <row r="13" spans="2:3">
       <c r="B13" s="83" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C13" t="s">
         <v>63</v>
@@ -7053,12 +7026,12 @@
         <v>130</v>
       </c>
       <c r="C74" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="75" spans="2:3">
       <c r="C75" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/IG/7日版/AI Native-生成AI_IG.xlsx
+++ b/IG/7日版/AI Native-生成AI_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2510544F-998C-457F-BD9C-6FFA57BA40B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E673F16-9D83-48F5-AD19-A4A8BBEE2A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2739,7 +2739,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3007,9 +3007,6 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3064,6 +3061,60 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3073,59 +3124,11 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3499,15 +3502,15 @@
   <sheetData>
     <row r="2" spans="1:8" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="92" t="str">
+      <c r="B2" s="91" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!B1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-生成AI_IG」</v>
       </c>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
     </row>
     <row r="3" spans="1:8" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -3520,10 +3523,10 @@
     </row>
     <row r="4" spans="1:8" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="93" t="s">
+      <c r="B4" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="94"/>
+      <c r="C4" s="93"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -3531,18 +3534,18 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="95"/>
-      <c r="C5" s="96"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="95"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
     <row r="7" spans="1:8" ht="16.2">
-      <c r="B7" s="97" t="s">
+      <c r="B7" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="97"/>
+      <c r="C7" s="96"/>
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="24"/>
@@ -3602,7 +3605,7 @@
         <f>master!B5</f>
         <v>モジュール1：オリエンテーションとマインドセット変革</v>
       </c>
-      <c r="F14" s="91"/>
+      <c r="F14" s="90"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8">
@@ -3614,7 +3617,7 @@
         <f>master!B8</f>
         <v>モジュール2：AI・LLMの基礎理解</v>
       </c>
-      <c r="F15" s="91"/>
+      <c r="F15" s="90"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8">
@@ -3628,21 +3631,21 @@
         <f>master!B13</f>
         <v>モジュール3：NTTデータが目指すAIビジネス（Vision）</v>
       </c>
-      <c r="F16" s="91"/>
+      <c r="F16" s="90"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="38"/>
       <c r="B17" s="69"/>
       <c r="C17" s="73"/>
-      <c r="F17" s="91"/>
+      <c r="F17" s="90"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="38"/>
       <c r="B18" s="41"/>
       <c r="C18" s="74"/>
-      <c r="F18" s="91"/>
+      <c r="F18" s="90"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8">
@@ -3654,7 +3657,7 @@
         <f>master!B28</f>
         <v>モジュール4：プロンプトエンジニアリング</v>
       </c>
-      <c r="F19" s="91"/>
+      <c r="F19" s="90"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8">
@@ -3663,7 +3666,7 @@
       </c>
       <c r="B20" s="42"/>
       <c r="C20" s="74"/>
-      <c r="F20" s="91"/>
+      <c r="F20" s="90"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8">
@@ -3671,10 +3674,10 @@
       <c r="B21" s="17">
         <v>0.51041666666666663</v>
       </c>
-      <c r="C21" s="90" t="s">
+      <c r="C21" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="F21" s="91"/>
+      <c r="F21" s="90"/>
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8">
@@ -3730,7 +3733,7 @@
         <f>master!B35</f>
         <v>モジュール5：ハンズオン（ChatGPT）</v>
       </c>
-      <c r="F26" s="91"/>
+      <c r="F26" s="90"/>
       <c r="G26" s="14"/>
       <c r="H26" s="6"/>
     </row>
@@ -3738,7 +3741,7 @@
       <c r="A27" s="39"/>
       <c r="B27" s="42"/>
       <c r="C27" s="58"/>
-      <c r="F27" s="91"/>
+      <c r="F27" s="90"/>
       <c r="G27" s="14"/>
       <c r="H27" s="6"/>
     </row>
@@ -3748,7 +3751,7 @@
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="58"/>
-      <c r="F28" s="91"/>
+      <c r="F28" s="90"/>
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8">
@@ -3757,7 +3760,7 @@
       <c r="C29" s="59"/>
       <c r="D29" s="55"/>
       <c r="E29" s="52"/>
-      <c r="F29" s="91"/>
+      <c r="F29" s="90"/>
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8">
@@ -3771,7 +3774,7 @@
       </c>
       <c r="D30" s="55"/>
       <c r="E30" s="52"/>
-      <c r="F30" s="91"/>
+      <c r="F30" s="90"/>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8">
@@ -3780,7 +3783,7 @@
       <c r="C31" s="58"/>
       <c r="D31" s="55"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="91"/>
+      <c r="F31" s="90"/>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8">
@@ -3791,7 +3794,7 @@
       <c r="C32" s="58"/>
       <c r="D32" s="55"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="91"/>
+      <c r="F32" s="90"/>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8">
@@ -3800,7 +3803,7 @@
       <c r="C33" s="58"/>
       <c r="D33" s="55"/>
       <c r="E33" s="52"/>
-      <c r="F33" s="91"/>
+      <c r="F33" s="90"/>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8">
@@ -3809,7 +3812,7 @@
       <c r="C34" s="58"/>
       <c r="D34" s="55"/>
       <c r="E34" s="52"/>
-      <c r="F34" s="91"/>
+      <c r="F34" s="90"/>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8">
@@ -3818,7 +3821,7 @@
       <c r="C35" s="58"/>
       <c r="D35" s="55"/>
       <c r="E35" s="52"/>
-      <c r="F35" s="91"/>
+      <c r="F35" s="90"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8">
@@ -3829,7 +3832,7 @@
       <c r="C36" s="58"/>
       <c r="D36" s="55"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="91"/>
+      <c r="F36" s="90"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8">
@@ -3838,7 +3841,7 @@
       <c r="C37" s="58"/>
       <c r="D37" s="55"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="91"/>
+      <c r="F37" s="90"/>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8">
@@ -3847,7 +3850,7 @@
       <c r="C38" s="58"/>
       <c r="D38" s="55"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="91"/>
+      <c r="F38" s="90"/>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8">
@@ -3856,7 +3859,7 @@
       <c r="C39" s="58"/>
       <c r="D39" s="55"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="91"/>
+      <c r="F39" s="90"/>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8">
@@ -3867,7 +3870,7 @@
       <c r="C40" s="59"/>
       <c r="D40" s="55"/>
       <c r="E40" s="52"/>
-      <c r="F40" s="91"/>
+      <c r="F40" s="90"/>
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8">
@@ -3881,7 +3884,7 @@
       </c>
       <c r="D41" s="57"/>
       <c r="E41" s="53"/>
-      <c r="F41" s="91"/>
+      <c r="F41" s="90"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8">
@@ -3890,7 +3893,7 @@
       <c r="C42" s="59"/>
       <c r="D42" s="55"/>
       <c r="E42" s="53"/>
-      <c r="F42" s="91"/>
+      <c r="F42" s="90"/>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1">
@@ -3977,10 +3980,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="103" t="s">
+      <c r="B4" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="103"/>
+      <c r="C4" s="102"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -3991,16 +3994,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="104"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -4015,10 +4018,10 @@
       <c r="C7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="105" t="s">
+      <c r="D7" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="105"/>
+      <c r="E7" s="104"/>
       <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
@@ -4050,46 +4053,46 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="10"/>
-      <c r="B10" s="99"/>
-      <c r="C10" s="99" t="s">
+      <c r="B10" s="98"/>
+      <c r="C10" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="99" t="s">
+      <c r="D10" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99" t="s">
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="106" t="s">
+      <c r="H10" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="98" t="s">
+      <c r="I10" s="97" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="98"/>
-      <c r="K10" s="98" t="s">
+      <c r="J10" s="97"/>
+      <c r="K10" s="97" t="s">
         <v>31</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="107"/>
+      <c r="B11" s="98"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="106"/>
       <c r="I11" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J11" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="99"/>
+      <c r="K11" s="98"/>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="63">
@@ -4098,11 +4101,11 @@
       <c r="C12" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="100" t="s">
+      <c r="D12" s="99" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="101"/>
-      <c r="F12" s="102"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="101"/>
       <c r="G12" s="82" t="s">
         <v>50</v>
       </c>
@@ -4201,12 +4204,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="103" t="s">
+      <c r="B4" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -4217,18 +4220,18 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="126" t="s">
+      <c r="B5" s="107" t="s">
         <v>193</v>
       </c>
-      <c r="C5" s="126"/>
-      <c r="D5" s="126"/>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="126"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
       <c r="L5" s="29"/>
       <c r="M5" s="30"/>
     </row>
@@ -4248,10 +4251,10 @@
       <c r="C7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="105" t="s">
+      <c r="D7" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="105"/>
+      <c r="E7" s="104"/>
       <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
@@ -4289,28 +4292,28 @@
     </row>
     <row r="10" spans="1:14" ht="24" customHeight="1">
       <c r="A10" s="10"/>
-      <c r="B10" s="99" t="s">
+      <c r="B10" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="99" t="s">
+      <c r="C10" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="99" t="s">
+      <c r="D10" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99" t="s">
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="98" t="s">
+      <c r="H10" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="127" t="s">
+      <c r="I10" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="128"/>
-      <c r="K10" s="98" t="s">
+      <c r="J10" s="109"/>
+      <c r="K10" s="97" t="s">
         <v>33</v>
       </c>
       <c r="L10" s="6"/>
@@ -4319,27 +4322,27 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="10"/>
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="98"/>
+      <c r="B11" s="98"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="97"/>
       <c r="I11" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J11" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="99"/>
+      <c r="K11" s="98"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
     </row>
     <row r="12" spans="1:14" ht="88.2">
       <c r="A12" s="10"/>
-      <c r="B12" s="124" t="str">
+      <c r="B12" s="110" t="str">
         <f>master!B3</f>
         <v>自己紹介</v>
       </c>
@@ -4347,11 +4350,11 @@
         <f>master!C3</f>
         <v>講師の自己紹介</v>
       </c>
-      <c r="D12" s="120" t="s">
+      <c r="D12" s="112" t="s">
         <v>202</v>
       </c>
-      <c r="E12" s="121"/>
-      <c r="F12" s="122"/>
+      <c r="E12" s="113"/>
+      <c r="F12" s="114"/>
       <c r="G12" s="51" t="s">
         <v>49</v>
       </c>
@@ -4369,16 +4372,16 @@
     </row>
     <row r="13" spans="1:14" ht="126">
       <c r="A13" s="10"/>
-      <c r="B13" s="125"/>
+      <c r="B13" s="111"/>
       <c r="C13" s="84" t="str">
         <f>master!C4</f>
         <v>受講生の自己紹介</v>
       </c>
-      <c r="D13" s="111" t="s">
+      <c r="D13" s="115" t="s">
         <v>204</v>
       </c>
-      <c r="E13" s="112"/>
-      <c r="F13" s="113"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="117"/>
       <c r="G13" s="84" t="s">
         <v>203</v>
       </c>
@@ -4398,7 +4401,7 @@
     </row>
     <row r="14" spans="1:14" ht="151.19999999999999">
       <c r="A14" s="11"/>
-      <c r="B14" s="123" t="str">
+      <c r="B14" s="118" t="str">
         <f>master!B5</f>
         <v>モジュール1：オリエンテーションとマインドセット変革</v>
       </c>
@@ -4406,11 +4409,11 @@
         <f>master!C5</f>
         <v>1-1. 研修概要</v>
       </c>
-      <c r="D14" s="120" t="s">
+      <c r="D14" s="112" t="s">
         <v>206</v>
       </c>
-      <c r="E14" s="121"/>
-      <c r="F14" s="122"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="114"/>
       <c r="G14" s="51" t="s">
         <v>205</v>
       </c>
@@ -4428,16 +4431,16 @@
     </row>
     <row r="15" spans="1:14" ht="100.8">
       <c r="A15" s="11"/>
-      <c r="B15" s="123"/>
+      <c r="B15" s="118"/>
       <c r="C15" s="51" t="str">
         <f>master!C6</f>
         <v>1-2. 背景・目的</v>
       </c>
-      <c r="D15" s="120" t="s">
+      <c r="D15" s="112" t="s">
         <v>133</v>
       </c>
-      <c r="E15" s="121"/>
-      <c r="F15" s="122"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="114"/>
       <c r="G15" s="51" t="s">
         <v>47</v>
       </c>
@@ -4455,16 +4458,16 @@
     </row>
     <row r="16" spans="1:14" ht="214.2">
       <c r="A16" s="11"/>
-      <c r="B16" s="123"/>
+      <c r="B16" s="118"/>
       <c r="C16" s="51" t="str">
         <f>master!C7</f>
         <v>1-3. 研修ゴールと獲得可能な経験背景・目的</v>
       </c>
-      <c r="D16" s="120" t="s">
+      <c r="D16" s="112" t="s">
         <v>169</v>
       </c>
-      <c r="E16" s="121"/>
-      <c r="F16" s="122"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="114"/>
       <c r="G16" s="51" t="s">
         <v>134</v>
       </c>
@@ -4482,7 +4485,7 @@
     </row>
     <row r="17" spans="1:14" ht="113.4">
       <c r="A17" s="11"/>
-      <c r="B17" s="116" t="str">
+      <c r="B17" s="119" t="str">
         <f>master!B8</f>
         <v>モジュール2：AI・LLMの基礎理解</v>
       </c>
@@ -4490,11 +4493,11 @@
         <f>master!C8</f>
         <v>2-1. 生成AI（Generative AI）とは？</v>
       </c>
-      <c r="D17" s="120" t="s">
+      <c r="D17" s="112" t="s">
         <v>207</v>
       </c>
-      <c r="E17" s="121"/>
-      <c r="F17" s="122"/>
+      <c r="E17" s="113"/>
+      <c r="F17" s="114"/>
       <c r="G17" s="51" t="s">
         <v>43</v>
       </c>
@@ -4512,16 +4515,16 @@
     </row>
     <row r="18" spans="1:14" ht="113.4">
       <c r="A18" s="11"/>
-      <c r="B18" s="117"/>
+      <c r="B18" s="120"/>
       <c r="C18" s="51" t="str">
         <f>master!C9</f>
         <v>2-2. 従来型AIと生成AIの比較</v>
       </c>
-      <c r="D18" s="120" t="s">
+      <c r="D18" s="112" t="s">
         <v>135</v>
       </c>
-      <c r="E18" s="121"/>
-      <c r="F18" s="122"/>
+      <c r="E18" s="113"/>
+      <c r="F18" s="114"/>
       <c r="G18" s="51" t="s">
         <v>43</v>
       </c>
@@ -4539,16 +4542,16 @@
     </row>
     <row r="19" spans="1:14" ht="113.4">
       <c r="A19" s="11"/>
-      <c r="B19" s="117"/>
+      <c r="B19" s="120"/>
       <c r="C19" s="51" t="str">
         <f>master!C10</f>
         <v>2-3. LLM（大規模言語モデル）の仕組み</v>
       </c>
-      <c r="D19" s="120" t="s">
+      <c r="D19" s="112" t="s">
         <v>136</v>
       </c>
-      <c r="E19" s="121"/>
-      <c r="F19" s="122"/>
+      <c r="E19" s="113"/>
+      <c r="F19" s="114"/>
       <c r="G19" s="51" t="s">
         <v>43</v>
       </c>
@@ -4566,16 +4569,16 @@
     </row>
     <row r="20" spans="1:14" ht="126">
       <c r="A20" s="11"/>
-      <c r="B20" s="117"/>
+      <c r="B20" s="120"/>
       <c r="C20" s="51" t="str">
         <f>master!C11</f>
         <v>2-4. 生成AIの「苦手なこと」（弱み）</v>
       </c>
-      <c r="D20" s="120" t="s">
+      <c r="D20" s="112" t="s">
         <v>137</v>
       </c>
-      <c r="E20" s="121"/>
-      <c r="F20" s="122"/>
+      <c r="E20" s="113"/>
+      <c r="F20" s="114"/>
       <c r="G20" s="51" t="s">
         <v>44</v>
       </c>
@@ -4593,16 +4596,16 @@
     </row>
     <row r="21" spans="1:14" ht="239.4">
       <c r="A21" s="11"/>
-      <c r="B21" s="118"/>
+      <c r="B21" s="121"/>
       <c r="C21" s="51" t="str">
         <f>master!C12</f>
         <v>2-5. 生成AIを使う心得８条</v>
       </c>
-      <c r="D21" s="120" t="s">
+      <c r="D21" s="112" t="s">
         <v>170</v>
       </c>
-      <c r="E21" s="121"/>
-      <c r="F21" s="122"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="114"/>
       <c r="G21" s="51" t="s">
         <v>138</v>
       </c>
@@ -4620,7 +4623,7 @@
     </row>
     <row r="22" spans="1:14" ht="25.2">
       <c r="A22" s="11"/>
-      <c r="B22" s="123" t="str">
+      <c r="B22" s="118" t="str">
         <f>master!B13</f>
         <v>モジュール3：NTTデータが目指すAIビジネス（Vision）</v>
       </c>
@@ -4628,9 +4631,9 @@
         <f>master!C13</f>
         <v>3-1. 本モジュールで学ぶこと①</v>
       </c>
-      <c r="D22" s="120"/>
-      <c r="E22" s="121"/>
-      <c r="F22" s="122"/>
+      <c r="D22" s="112"/>
+      <c r="E22" s="113"/>
+      <c r="F22" s="114"/>
       <c r="G22" s="51" t="s">
         <v>46</v>
       </c>
@@ -4648,14 +4651,14 @@
     </row>
     <row r="23" spans="1:14" ht="25.2">
       <c r="A23" s="11"/>
-      <c r="B23" s="123"/>
+      <c r="B23" s="118"/>
       <c r="C23" s="51" t="str">
         <f>master!C14</f>
         <v>3-2. NTTデータのAI戦略：Quality Growthとは</v>
       </c>
-      <c r="D23" s="120"/>
-      <c r="E23" s="121"/>
-      <c r="F23" s="122"/>
+      <c r="D23" s="112"/>
+      <c r="E23" s="113"/>
+      <c r="F23" s="114"/>
       <c r="G23" s="51" t="s">
         <v>46</v>
       </c>
@@ -4673,14 +4676,14 @@
     </row>
     <row r="24" spans="1:14" ht="25.2">
       <c r="A24" s="11"/>
-      <c r="B24" s="123"/>
+      <c r="B24" s="118"/>
       <c r="C24" s="51" t="str">
         <f>master!C15</f>
         <v>3-3. なぜ今、AIが重要なのか</v>
       </c>
-      <c r="D24" s="120"/>
-      <c r="E24" s="121"/>
-      <c r="F24" s="122"/>
+      <c r="D24" s="112"/>
+      <c r="E24" s="113"/>
+      <c r="F24" s="114"/>
       <c r="G24" s="51" t="s">
         <v>46</v>
       </c>
@@ -4698,14 +4701,14 @@
     </row>
     <row r="25" spans="1:14" ht="25.2">
       <c r="A25" s="11"/>
-      <c r="B25" s="123"/>
+      <c r="B25" s="118"/>
       <c r="C25" s="51" t="str">
         <f>master!C16</f>
         <v>3-4. 生成AIの進化：今、どこにいるか</v>
       </c>
-      <c r="D25" s="120"/>
-      <c r="E25" s="121"/>
-      <c r="F25" s="122"/>
+      <c r="D25" s="112"/>
+      <c r="E25" s="113"/>
+      <c r="F25" s="114"/>
       <c r="G25" s="51" t="s">
         <v>46</v>
       </c>
@@ -4723,14 +4726,14 @@
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
       <c r="A26" s="11"/>
-      <c r="B26" s="123"/>
+      <c r="B26" s="118"/>
       <c r="C26" s="51" t="str">
         <f>master!C17</f>
         <v>3-5. 本モジュールで学ぶこと②</v>
       </c>
-      <c r="D26" s="120"/>
-      <c r="E26" s="121"/>
-      <c r="F26" s="122"/>
+      <c r="D26" s="112"/>
+      <c r="E26" s="113"/>
+      <c r="F26" s="114"/>
       <c r="G26" s="51" t="s">
         <v>37</v>
       </c>
@@ -4748,16 +4751,16 @@
     </row>
     <row r="27" spans="1:14" ht="63">
       <c r="A27" s="11"/>
-      <c r="B27" s="123"/>
+      <c r="B27" s="118"/>
       <c r="C27" s="51" t="str">
         <f>master!C18</f>
         <v>3-6. エージェントAI（Agentic AI）とは何か</v>
       </c>
-      <c r="D27" s="120" t="s">
+      <c r="D27" s="112" t="s">
         <v>171</v>
       </c>
-      <c r="E27" s="121"/>
-      <c r="F27" s="122"/>
+      <c r="E27" s="113"/>
+      <c r="F27" s="114"/>
       <c r="G27" s="51" t="s">
         <v>39</v>
       </c>
@@ -4775,16 +4778,16 @@
     </row>
     <row r="28" spans="1:14" ht="63">
       <c r="A28" s="11"/>
-      <c r="B28" s="123"/>
+      <c r="B28" s="118"/>
       <c r="C28" s="51" t="str">
         <f>master!C19</f>
         <v>3-7. エージェントの処理</v>
       </c>
-      <c r="D28" s="120" t="s">
+      <c r="D28" s="112" t="s">
         <v>139</v>
       </c>
-      <c r="E28" s="121"/>
-      <c r="F28" s="122"/>
+      <c r="E28" s="113"/>
+      <c r="F28" s="114"/>
       <c r="G28" s="51" t="s">
         <v>39</v>
       </c>
@@ -4802,14 +4805,14 @@
     </row>
     <row r="29" spans="1:14" ht="37.799999999999997">
       <c r="A29" s="11"/>
-      <c r="B29" s="123"/>
+      <c r="B29" s="118"/>
       <c r="C29" s="51" t="str">
         <f>master!C20</f>
         <v>3-8. 本モジュールで学ぶこと③</v>
       </c>
-      <c r="D29" s="120"/>
-      <c r="E29" s="121"/>
-      <c r="F29" s="122"/>
+      <c r="D29" s="112"/>
+      <c r="E29" s="113"/>
+      <c r="F29" s="114"/>
       <c r="G29" s="51" t="s">
         <v>40</v>
       </c>
@@ -4827,14 +4830,14 @@
     </row>
     <row r="30" spans="1:14" ht="37.799999999999997">
       <c r="A30" s="11"/>
-      <c r="B30" s="123"/>
+      <c r="B30" s="118"/>
       <c r="C30" s="51" t="str">
         <f>master!C21</f>
         <v>3-9. NTTデータが描く未来：Smart AI Agent®</v>
       </c>
-      <c r="D30" s="120"/>
-      <c r="E30" s="121"/>
-      <c r="F30" s="122"/>
+      <c r="D30" s="112"/>
+      <c r="E30" s="113"/>
+      <c r="F30" s="114"/>
       <c r="G30" s="51" t="s">
         <v>40</v>
       </c>
@@ -4852,14 +4855,14 @@
     </row>
     <row r="31" spans="1:14" ht="37.799999999999997">
       <c r="A31" s="11"/>
-      <c r="B31" s="123"/>
+      <c r="B31" s="118"/>
       <c r="C31" s="51" t="str">
         <f>master!C22</f>
         <v>3-10. AIの強みを生かした業務変革の進め方</v>
       </c>
-      <c r="D31" s="120"/>
-      <c r="E31" s="121"/>
-      <c r="F31" s="122"/>
+      <c r="D31" s="112"/>
+      <c r="E31" s="113"/>
+      <c r="F31" s="114"/>
       <c r="G31" s="51" t="s">
         <v>40</v>
       </c>
@@ -4877,14 +4880,14 @@
     </row>
     <row r="32" spans="1:14" ht="37.799999999999997">
       <c r="A32" s="11"/>
-      <c r="B32" s="123"/>
+      <c r="B32" s="118"/>
       <c r="C32" s="51" t="str">
         <f>master!C23</f>
         <v>3-11. AIの強みを生かすポイント：人とAIとの役割分担</v>
       </c>
-      <c r="D32" s="120"/>
-      <c r="E32" s="121"/>
-      <c r="F32" s="122"/>
+      <c r="D32" s="112"/>
+      <c r="E32" s="113"/>
+      <c r="F32" s="114"/>
       <c r="G32" s="51" t="s">
         <v>40</v>
       </c>
@@ -4902,14 +4905,14 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="123"/>
+      <c r="B33" s="118"/>
       <c r="C33" s="51" t="str">
         <f>master!C24</f>
         <v>3-12. AIの強みを生かすポイント：プロセス自体をAI前提で再設計</v>
       </c>
-      <c r="D33" s="120"/>
-      <c r="E33" s="121"/>
-      <c r="F33" s="122"/>
+      <c r="D33" s="112"/>
+      <c r="E33" s="113"/>
+      <c r="F33" s="114"/>
       <c r="G33" s="51" t="s">
         <v>40</v>
       </c>
@@ -4927,14 +4930,14 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="123"/>
+      <c r="B34" s="118"/>
       <c r="C34" s="51" t="str">
         <f>master!C25</f>
         <v>3-13. JALカード様 -  AIバーチャル顧客を活用したマーケティング高度化</v>
       </c>
-      <c r="D34" s="120"/>
-      <c r="E34" s="121"/>
-      <c r="F34" s="122"/>
+      <c r="D34" s="112"/>
+      <c r="E34" s="113"/>
+      <c r="F34" s="114"/>
       <c r="G34" s="51" t="s">
         <v>40</v>
       </c>
@@ -4952,14 +4955,14 @@
     </row>
     <row r="35" spans="1:14" ht="37.799999999999997">
       <c r="A35" s="11"/>
-      <c r="B35" s="123"/>
+      <c r="B35" s="118"/>
       <c r="C35" s="51" t="str">
         <f>master!C26</f>
         <v>3-14. 大手メディアサービス会社 - AI-BPOによるオペレーション変革</v>
       </c>
-      <c r="D35" s="120"/>
-      <c r="E35" s="121"/>
-      <c r="F35" s="122"/>
+      <c r="D35" s="112"/>
+      <c r="E35" s="113"/>
+      <c r="F35" s="114"/>
       <c r="G35" s="51" t="s">
         <v>40</v>
       </c>
@@ -4977,14 +4980,14 @@
     </row>
     <row r="36" spans="1:14" ht="37.799999999999997">
       <c r="A36" s="11"/>
-      <c r="B36" s="123"/>
+      <c r="B36" s="118"/>
       <c r="C36" s="51" t="str">
         <f>master!C27</f>
         <v>Appendix：りそな様 - AI CoEと生成AI人財育成アカデミーの推進</v>
       </c>
-      <c r="D36" s="120"/>
-      <c r="E36" s="121"/>
-      <c r="F36" s="122"/>
+      <c r="D36" s="112"/>
+      <c r="E36" s="113"/>
+      <c r="F36" s="114"/>
       <c r="G36" s="51" t="s">
         <v>40</v>
       </c>
@@ -5002,7 +5005,7 @@
     </row>
     <row r="37" spans="1:14" ht="88.2">
       <c r="A37" s="11"/>
-      <c r="B37" s="116" t="str">
+      <c r="B37" s="119" t="str">
         <f>master!B28</f>
         <v>モジュール4：プロンプトエンジニアリング</v>
       </c>
@@ -5010,11 +5013,11 @@
         <f>master!C28</f>
         <v>4-1. プロンプトとは?</v>
       </c>
-      <c r="D37" s="120" t="s">
+      <c r="D37" s="112" t="s">
         <v>172</v>
       </c>
-      <c r="E37" s="121"/>
-      <c r="F37" s="122"/>
+      <c r="E37" s="113"/>
+      <c r="F37" s="114"/>
       <c r="G37" s="51" t="s">
         <v>45</v>
       </c>
@@ -5032,14 +5035,14 @@
     </row>
     <row r="38" spans="1:14" ht="37.799999999999997">
       <c r="A38" s="11"/>
-      <c r="B38" s="117"/>
+      <c r="B38" s="120"/>
       <c r="C38" s="51" t="str">
         <f>master!C29</f>
         <v>4-2. プロンプトを構成する4つの要素</v>
       </c>
-      <c r="D38" s="120"/>
-      <c r="E38" s="121"/>
-      <c r="F38" s="122"/>
+      <c r="D38" s="112"/>
+      <c r="E38" s="113"/>
+      <c r="F38" s="114"/>
       <c r="G38" s="51" t="s">
         <v>40</v>
       </c>
@@ -5057,14 +5060,14 @@
     </row>
     <row r="39" spans="1:14" ht="37.799999999999997">
       <c r="A39" s="11"/>
-      <c r="B39" s="117"/>
+      <c r="B39" s="120"/>
       <c r="C39" s="51" t="str">
         <f>master!C30</f>
         <v>4-3. 悪いプロンプト vs 良いプロンプト</v>
       </c>
-      <c r="D39" s="120"/>
-      <c r="E39" s="121"/>
-      <c r="F39" s="122"/>
+      <c r="D39" s="112"/>
+      <c r="E39" s="113"/>
+      <c r="F39" s="114"/>
       <c r="G39" s="51" t="s">
         <v>40</v>
       </c>
@@ -5082,14 +5085,14 @@
     </row>
     <row r="40" spans="1:14" ht="37.799999999999997">
       <c r="A40" s="11"/>
-      <c r="B40" s="117"/>
+      <c r="B40" s="120"/>
       <c r="C40" s="51" t="str">
         <f>master!C31</f>
         <v>4-4. テクニック①：Role Prompting（役割の付与）</v>
       </c>
-      <c r="D40" s="120"/>
-      <c r="E40" s="121"/>
-      <c r="F40" s="122"/>
+      <c r="D40" s="112"/>
+      <c r="E40" s="113"/>
+      <c r="F40" s="114"/>
       <c r="G40" s="51" t="s">
         <v>40</v>
       </c>
@@ -5107,14 +5110,14 @@
     </row>
     <row r="41" spans="1:14" ht="37.799999999999997">
       <c r="A41" s="11"/>
-      <c r="B41" s="117"/>
+      <c r="B41" s="120"/>
       <c r="C41" s="51" t="str">
         <f>master!C32</f>
         <v>4-5. テクニック②：区切り文字の活用</v>
       </c>
-      <c r="D41" s="120"/>
-      <c r="E41" s="121"/>
-      <c r="F41" s="122"/>
+      <c r="D41" s="112"/>
+      <c r="E41" s="113"/>
+      <c r="F41" s="114"/>
       <c r="G41" s="51" t="s">
         <v>40</v>
       </c>
@@ -5132,14 +5135,14 @@
     </row>
     <row r="42" spans="1:14" ht="37.799999999999997">
       <c r="A42" s="11"/>
-      <c r="B42" s="117"/>
+      <c r="B42" s="120"/>
       <c r="C42" s="51" t="str">
         <f>master!C33</f>
         <v>4-6. テクニック③：Zero-shot vs Few-shot</v>
       </c>
-      <c r="D42" s="120"/>
-      <c r="E42" s="121"/>
-      <c r="F42" s="122"/>
+      <c r="D42" s="112"/>
+      <c r="E42" s="113"/>
+      <c r="F42" s="114"/>
       <c r="G42" s="51" t="s">
         <v>40</v>
       </c>
@@ -5157,14 +5160,14 @@
     </row>
     <row r="43" spans="1:14" ht="50.4">
       <c r="A43" s="11"/>
-      <c r="B43" s="118"/>
+      <c r="B43" s="121"/>
       <c r="C43" s="51" t="str">
         <f>master!C34</f>
         <v>4-7. テクニック④：Chain of Thought（思考の連鎖）</v>
       </c>
-      <c r="D43" s="120"/>
-      <c r="E43" s="121"/>
-      <c r="F43" s="122"/>
+      <c r="D43" s="112"/>
+      <c r="E43" s="113"/>
+      <c r="F43" s="114"/>
       <c r="G43" s="51" t="s">
         <v>41</v>
       </c>
@@ -5182,7 +5185,7 @@
     </row>
     <row r="44" spans="1:14" ht="75.599999999999994">
       <c r="A44" s="11"/>
-      <c r="B44" s="114" t="str">
+      <c r="B44" s="122" t="str">
         <f>master!B35</f>
         <v>モジュール5：ハンズオン（ChatGPT）</v>
       </c>
@@ -5190,11 +5193,11 @@
         <f>master!C35</f>
         <v>5-1. ChatGPTの使い方（一般チャット）</v>
       </c>
-      <c r="D44" s="108" t="s">
+      <c r="D44" s="125" t="s">
         <v>173</v>
       </c>
-      <c r="E44" s="109"/>
-      <c r="F44" s="110"/>
+      <c r="E44" s="126"/>
+      <c r="F44" s="127"/>
       <c r="G44" s="64" t="s">
         <v>42</v>
       </c>
@@ -5212,16 +5215,16 @@
     </row>
     <row r="45" spans="1:14" ht="126">
       <c r="A45" s="11"/>
-      <c r="B45" s="119"/>
+      <c r="B45" s="123"/>
       <c r="C45" s="64" t="str">
         <f>master!C36</f>
         <v>5-2. 例①：顧客提案向けの企画提案書を作りたい</v>
       </c>
-      <c r="D45" s="108" t="s">
+      <c r="D45" s="125" t="s">
         <v>181</v>
       </c>
-      <c r="E45" s="109"/>
-      <c r="F45" s="110"/>
+      <c r="E45" s="126"/>
+      <c r="F45" s="127"/>
       <c r="G45" s="64" t="s">
         <v>44</v>
       </c>
@@ -5239,16 +5242,16 @@
     </row>
     <row r="46" spans="1:14" ht="126">
       <c r="A46" s="11"/>
-      <c r="B46" s="119"/>
+      <c r="B46" s="123"/>
       <c r="C46" s="64" t="str">
         <f>master!C37</f>
         <v>5-3. 例①：顧客提案向けの企画提案書を作りたい - プロンプト例</v>
       </c>
-      <c r="D46" s="108" t="s">
+      <c r="D46" s="125" t="s">
         <v>141</v>
       </c>
-      <c r="E46" s="109"/>
-      <c r="F46" s="110"/>
+      <c r="E46" s="126"/>
+      <c r="F46" s="127"/>
       <c r="G46" s="64" t="s">
         <v>44</v>
       </c>
@@ -5266,16 +5269,16 @@
     </row>
     <row r="47" spans="1:14" ht="37.799999999999997">
       <c r="A47" s="11"/>
-      <c r="B47" s="119"/>
+      <c r="B47" s="123"/>
       <c r="C47" s="64" t="str">
         <f>master!C38</f>
         <v>5-4. 例①：顧客提案向けの企画提案書を作りたい - 実行例</v>
       </c>
-      <c r="D47" s="108" t="s">
+      <c r="D47" s="125" t="s">
         <v>140</v>
       </c>
-      <c r="E47" s="109"/>
-      <c r="F47" s="110"/>
+      <c r="E47" s="126"/>
+      <c r="F47" s="127"/>
       <c r="G47" s="64" t="s">
         <v>40</v>
       </c>
@@ -5293,13 +5296,13 @@
     </row>
     <row r="48" spans="1:14" ht="88.2">
       <c r="A48" s="11"/>
-      <c r="B48" s="119"/>
+      <c r="B48" s="123"/>
       <c r="C48" s="84"/>
-      <c r="D48" s="111" t="s">
+      <c r="D48" s="115" t="s">
         <v>180</v>
       </c>
-      <c r="E48" s="112"/>
-      <c r="F48" s="113"/>
+      <c r="E48" s="116"/>
+      <c r="F48" s="117"/>
       <c r="G48" s="84" t="s">
         <v>45</v>
       </c>
@@ -5319,16 +5322,16 @@
     </row>
     <row r="49" spans="1:14" ht="50.4">
       <c r="A49" s="11"/>
-      <c r="B49" s="119"/>
+      <c r="B49" s="123"/>
       <c r="C49" s="64" t="str">
         <f>master!C39</f>
         <v>5-5. 例②：100本ノックを作ってみる</v>
       </c>
-      <c r="D49" s="108" t="s">
+      <c r="D49" s="125" t="s">
         <v>188</v>
       </c>
-      <c r="E49" s="109"/>
-      <c r="F49" s="110"/>
+      <c r="E49" s="126"/>
+      <c r="F49" s="127"/>
       <c r="G49" s="64" t="s">
         <v>41</v>
       </c>
@@ -5346,16 +5349,16 @@
     </row>
     <row r="50" spans="1:14" ht="75.599999999999994">
       <c r="A50" s="11"/>
-      <c r="B50" s="119"/>
-      <c r="C50" s="64" t="str">
+      <c r="B50" s="123"/>
+      <c r="C50" s="128" t="str">
         <f>master!C40</f>
         <v>5-6. 例②：100本ノックを作ってみる -プロンプト例</v>
       </c>
-      <c r="D50" s="108" t="s">
+      <c r="D50" s="125" t="s">
         <v>174</v>
       </c>
-      <c r="E50" s="109"/>
-      <c r="F50" s="110"/>
+      <c r="E50" s="126"/>
+      <c r="F50" s="127"/>
       <c r="G50" s="64" t="s">
         <v>42</v>
       </c>
@@ -5373,13 +5376,13 @@
     </row>
     <row r="51" spans="1:14" ht="88.2">
       <c r="A51" s="11"/>
-      <c r="B51" s="119"/>
-      <c r="C51" s="84"/>
-      <c r="D51" s="111" t="s">
+      <c r="B51" s="123"/>
+      <c r="C51" s="129"/>
+      <c r="D51" s="115" t="s">
         <v>182</v>
       </c>
-      <c r="E51" s="112"/>
-      <c r="F51" s="113"/>
+      <c r="E51" s="116"/>
+      <c r="F51" s="117"/>
       <c r="G51" s="84" t="s">
         <v>45</v>
       </c>
@@ -5399,16 +5402,16 @@
     </row>
     <row r="52" spans="1:14" ht="50.4">
       <c r="A52" s="11"/>
-      <c r="B52" s="119"/>
+      <c r="B52" s="123"/>
       <c r="C52" s="64" t="str">
         <f>master!C41</f>
         <v>5-7. 例②：100本ノックを作ってみる - 実行結果①</v>
       </c>
-      <c r="D52" s="108" t="s">
+      <c r="D52" s="125" t="s">
         <v>151</v>
       </c>
-      <c r="E52" s="109"/>
-      <c r="F52" s="110"/>
+      <c r="E52" s="126"/>
+      <c r="F52" s="127"/>
       <c r="G52" s="64" t="s">
         <v>41</v>
       </c>
@@ -5426,16 +5429,16 @@
     </row>
     <row r="53" spans="1:14" ht="50.4">
       <c r="A53" s="11"/>
-      <c r="B53" s="119"/>
+      <c r="B53" s="123"/>
       <c r="C53" s="64" t="str">
         <f>master!C42</f>
         <v>5-8. 例②：100本ノックを作ってみる - 実行結果②</v>
       </c>
-      <c r="D53" s="108" t="s">
+      <c r="D53" s="125" t="s">
         <v>152</v>
       </c>
-      <c r="E53" s="109"/>
-      <c r="F53" s="110"/>
+      <c r="E53" s="126"/>
+      <c r="F53" s="127"/>
       <c r="G53" s="64" t="s">
         <v>41</v>
       </c>
@@ -5453,16 +5456,16 @@
     </row>
     <row r="54" spans="1:14" ht="50.4">
       <c r="A54" s="11"/>
-      <c r="B54" s="119"/>
+      <c r="B54" s="123"/>
       <c r="C54" s="64" t="str">
         <f>master!C43</f>
         <v>5-9. 例②：100本ノックを作ってみる - 実行結果③</v>
       </c>
-      <c r="D54" s="108" t="s">
+      <c r="D54" s="125" t="s">
         <v>153</v>
       </c>
-      <c r="E54" s="109"/>
-      <c r="F54" s="110"/>
+      <c r="E54" s="126"/>
+      <c r="F54" s="127"/>
       <c r="G54" s="64" t="s">
         <v>41</v>
       </c>
@@ -5480,16 +5483,16 @@
     </row>
     <row r="55" spans="1:14" ht="63">
       <c r="A55" s="11"/>
-      <c r="B55" s="115"/>
+      <c r="B55" s="124"/>
       <c r="C55" s="64" t="str">
         <f>master!C44</f>
         <v>5-10. ChatGPT まとめ</v>
       </c>
-      <c r="D55" s="108" t="s">
+      <c r="D55" s="125" t="s">
         <v>142</v>
       </c>
-      <c r="E55" s="109"/>
-      <c r="F55" s="110"/>
+      <c r="E55" s="126"/>
+      <c r="F55" s="127"/>
       <c r="G55" s="64" t="s">
         <v>39</v>
       </c>
@@ -5507,7 +5510,7 @@
     </row>
     <row r="56" spans="1:14" ht="50.4" customHeight="1">
       <c r="A56" s="11"/>
-      <c r="B56" s="119" t="str">
+      <c r="B56" s="123" t="str">
         <f>master!B45</f>
         <v>モジュール6：ハンズオン（ GitHub Copilot ）</v>
       </c>
@@ -5515,11 +5518,11 @@
         <f>master!C45</f>
         <v>6-1. Visual Studio Code を開く</v>
       </c>
-      <c r="D56" s="108" t="s">
+      <c r="D56" s="125" t="s">
         <v>143</v>
       </c>
-      <c r="E56" s="109"/>
-      <c r="F56" s="110"/>
+      <c r="E56" s="126"/>
+      <c r="F56" s="127"/>
       <c r="G56" s="64" t="s">
         <v>41</v>
       </c>
@@ -5537,16 +5540,16 @@
     </row>
     <row r="57" spans="1:14" ht="63">
       <c r="A57" s="11"/>
-      <c r="B57" s="119"/>
+      <c r="B57" s="123"/>
       <c r="C57" s="64" t="str">
         <f>master!C46</f>
         <v>6-2. コード補完機能</v>
       </c>
-      <c r="D57" s="108" t="s">
+      <c r="D57" s="125" t="s">
         <v>144</v>
       </c>
-      <c r="E57" s="109"/>
-      <c r="F57" s="110"/>
+      <c r="E57" s="126"/>
+      <c r="F57" s="127"/>
       <c r="G57" s="64" t="s">
         <v>39</v>
       </c>
@@ -5564,16 +5567,16 @@
     </row>
     <row r="58" spans="1:14" ht="75.599999999999994">
       <c r="A58" s="11"/>
-      <c r="B58" s="119"/>
+      <c r="B58" s="123"/>
       <c r="C58" s="64" t="str">
         <f>master!C47</f>
         <v>6-3. チャット機能</v>
       </c>
-      <c r="D58" s="108" t="s">
+      <c r="D58" s="125" t="s">
         <v>198</v>
       </c>
-      <c r="E58" s="109"/>
-      <c r="F58" s="110"/>
+      <c r="E58" s="126"/>
+      <c r="F58" s="127"/>
       <c r="G58" s="64" t="s">
         <v>42</v>
       </c>
@@ -5591,16 +5594,16 @@
     </row>
     <row r="59" spans="1:14" ht="88.2">
       <c r="A59" s="11"/>
-      <c r="B59" s="119"/>
+      <c r="B59" s="123"/>
       <c r="C59" s="64" t="str">
         <f>master!C48</f>
         <v>6-4. チャット機能 - コマンド</v>
       </c>
-      <c r="D59" s="108" t="s">
+      <c r="D59" s="125" t="s">
         <v>197</v>
       </c>
-      <c r="E59" s="109"/>
-      <c r="F59" s="110"/>
+      <c r="E59" s="126"/>
+      <c r="F59" s="127"/>
       <c r="G59" s="64" t="s">
         <v>45</v>
       </c>
@@ -5618,16 +5621,16 @@
     </row>
     <row r="60" spans="1:14" ht="50.4">
       <c r="A60" s="11"/>
-      <c r="B60" s="119"/>
+      <c r="B60" s="123"/>
       <c r="C60" s="64" t="str">
         <f>master!C49</f>
         <v>6-5. 簡単なアプリやゲームを作ってみましょう</v>
       </c>
-      <c r="D60" s="108" t="s">
+      <c r="D60" s="125" t="s">
         <v>165</v>
       </c>
-      <c r="E60" s="109"/>
-      <c r="F60" s="110"/>
+      <c r="E60" s="126"/>
+      <c r="F60" s="127"/>
       <c r="G60" s="64" t="s">
         <v>41</v>
       </c>
@@ -5645,16 +5648,16 @@
     </row>
     <row r="61" spans="1:14" ht="50.4">
       <c r="A61" s="11"/>
-      <c r="B61" s="119"/>
+      <c r="B61" s="123"/>
       <c r="C61" s="64" t="str">
         <f>master!C50</f>
         <v>6-6. 例①：高級志向テトリス</v>
       </c>
-      <c r="D61" s="108" t="s">
+      <c r="D61" s="125" t="s">
         <v>168</v>
       </c>
-      <c r="E61" s="109"/>
-      <c r="F61" s="110"/>
+      <c r="E61" s="126"/>
+      <c r="F61" s="127"/>
       <c r="G61" s="64" t="s">
         <v>41</v>
       </c>
@@ -5672,16 +5675,16 @@
     </row>
     <row r="62" spans="1:14" ht="50.4">
       <c r="A62" s="11"/>
-      <c r="B62" s="119"/>
+      <c r="B62" s="123"/>
       <c r="C62" s="64" t="str">
         <f>master!C51</f>
         <v>6-7. 例②：わくわく！にっぽんダーツの旅</v>
       </c>
-      <c r="D62" s="108" t="s">
+      <c r="D62" s="125" t="s">
         <v>166</v>
       </c>
-      <c r="E62" s="109"/>
-      <c r="F62" s="110"/>
+      <c r="E62" s="126"/>
+      <c r="F62" s="127"/>
       <c r="G62" s="64" t="s">
         <v>41</v>
       </c>
@@ -5699,16 +5702,16 @@
     </row>
     <row r="63" spans="1:14" ht="50.4">
       <c r="A63" s="11"/>
-      <c r="B63" s="119"/>
-      <c r="C63" s="64" t="str">
+      <c r="B63" s="123"/>
+      <c r="C63" s="128" t="str">
         <f>master!C52</f>
         <v>6-8. 例③：タスク管理ツール</v>
       </c>
-      <c r="D63" s="108" t="s">
+      <c r="D63" s="125" t="s">
         <v>167</v>
       </c>
-      <c r="E63" s="109"/>
-      <c r="F63" s="110"/>
+      <c r="E63" s="126"/>
+      <c r="F63" s="127"/>
       <c r="G63" s="64" t="s">
         <v>41</v>
       </c>
@@ -5726,13 +5729,13 @@
     </row>
     <row r="64" spans="1:14" ht="138.6">
       <c r="A64" s="11"/>
-      <c r="B64" s="119"/>
-      <c r="C64" s="84"/>
-      <c r="D64" s="111" t="s">
+      <c r="B64" s="123"/>
+      <c r="C64" s="129"/>
+      <c r="D64" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="E64" s="112"/>
-      <c r="F64" s="113"/>
+      <c r="E64" s="116"/>
+      <c r="F64" s="117"/>
       <c r="G64" s="84" t="s">
         <v>38</v>
       </c>
@@ -5750,16 +5753,16 @@
     </row>
     <row r="65" spans="1:14" ht="75.599999999999994">
       <c r="A65" s="11"/>
-      <c r="B65" s="119"/>
-      <c r="C65" s="64" t="str">
+      <c r="B65" s="123"/>
+      <c r="C65" s="128" t="str">
         <f>master!C53</f>
         <v>6-9. ディレクトリ作成とファイル配置</v>
       </c>
-      <c r="D65" s="108" t="s">
+      <c r="D65" s="125" t="s">
         <v>183</v>
       </c>
-      <c r="E65" s="109"/>
-      <c r="F65" s="110"/>
+      <c r="E65" s="126"/>
+      <c r="F65" s="127"/>
       <c r="G65" s="64" t="s">
         <v>42</v>
       </c>
@@ -5777,13 +5780,13 @@
     </row>
     <row r="66" spans="1:14" ht="88.2">
       <c r="A66" s="11"/>
-      <c r="B66" s="119"/>
-      <c r="C66" s="84"/>
-      <c r="D66" s="111" t="s">
+      <c r="B66" s="123"/>
+      <c r="C66" s="129"/>
+      <c r="D66" s="115" t="s">
         <v>199</v>
       </c>
-      <c r="E66" s="112"/>
-      <c r="F66" s="113"/>
+      <c r="E66" s="116"/>
+      <c r="F66" s="117"/>
       <c r="G66" s="84" t="s">
         <v>45</v>
       </c>
@@ -5801,16 +5804,16 @@
     </row>
     <row r="67" spans="1:14" ht="50.4">
       <c r="A67" s="11"/>
-      <c r="B67" s="119"/>
+      <c r="B67" s="123"/>
       <c r="C67" s="64" t="str">
         <f>master!C54</f>
         <v>6-10. チャット機能 - Askモード</v>
       </c>
-      <c r="D67" s="108" t="s">
+      <c r="D67" s="125" t="s">
         <v>194</v>
       </c>
-      <c r="E67" s="109"/>
-      <c r="F67" s="110"/>
+      <c r="E67" s="126"/>
+      <c r="F67" s="127"/>
       <c r="G67" s="64" t="s">
         <v>41</v>
       </c>
@@ -5828,16 +5831,16 @@
     </row>
     <row r="68" spans="1:14" ht="100.8">
       <c r="A68" s="11"/>
-      <c r="B68" s="119"/>
+      <c r="B68" s="123"/>
       <c r="C68" s="64" t="str">
         <f>master!C55</f>
         <v>6-11. Askモードについて</v>
       </c>
-      <c r="D68" s="108" t="s">
+      <c r="D68" s="125" t="s">
         <v>146</v>
       </c>
-      <c r="E68" s="109"/>
-      <c r="F68" s="110"/>
+      <c r="E68" s="126"/>
+      <c r="F68" s="127"/>
       <c r="G68" s="64" t="s">
         <v>47</v>
       </c>
@@ -5855,16 +5858,16 @@
     </row>
     <row r="69" spans="1:14" ht="50.4">
       <c r="A69" s="11"/>
-      <c r="B69" s="119"/>
+      <c r="B69" s="123"/>
       <c r="C69" s="64" t="str">
         <f>master!C56</f>
         <v>6-12. 実行例①</v>
       </c>
-      <c r="D69" s="108" t="s">
+      <c r="D69" s="125" t="s">
         <v>150</v>
       </c>
-      <c r="E69" s="109"/>
-      <c r="F69" s="110"/>
+      <c r="E69" s="126"/>
+      <c r="F69" s="127"/>
       <c r="G69" s="64" t="s">
         <v>41</v>
       </c>
@@ -5882,16 +5885,16 @@
     </row>
     <row r="70" spans="1:14" ht="50.4">
       <c r="A70" s="11"/>
-      <c r="B70" s="119"/>
+      <c r="B70" s="123"/>
       <c r="C70" s="64" t="str">
         <f>master!C57</f>
         <v>6-13. 実行例②</v>
       </c>
-      <c r="D70" s="108" t="s">
+      <c r="D70" s="125" t="s">
         <v>148</v>
       </c>
-      <c r="E70" s="109"/>
-      <c r="F70" s="110"/>
+      <c r="E70" s="126"/>
+      <c r="F70" s="127"/>
       <c r="G70" s="64" t="s">
         <v>41</v>
       </c>
@@ -5909,16 +5912,16 @@
     </row>
     <row r="71" spans="1:14" ht="50.4">
       <c r="A71" s="11"/>
-      <c r="B71" s="119"/>
-      <c r="C71" s="64" t="str">
+      <c r="B71" s="123"/>
+      <c r="C71" s="128" t="str">
         <f>master!C58</f>
         <v>6-14. 実行例③</v>
       </c>
-      <c r="D71" s="108" t="s">
+      <c r="D71" s="125" t="s">
         <v>149</v>
       </c>
-      <c r="E71" s="109"/>
-      <c r="F71" s="110"/>
+      <c r="E71" s="126"/>
+      <c r="F71" s="127"/>
       <c r="G71" s="64" t="s">
         <v>41</v>
       </c>
@@ -5936,13 +5939,13 @@
     </row>
     <row r="72" spans="1:14" ht="138.6">
       <c r="A72" s="11"/>
-      <c r="B72" s="119"/>
-      <c r="C72" s="84"/>
-      <c r="D72" s="111" t="s">
+      <c r="B72" s="123"/>
+      <c r="C72" s="129"/>
+      <c r="D72" s="115" t="s">
         <v>178</v>
       </c>
-      <c r="E72" s="112"/>
-      <c r="F72" s="113"/>
+      <c r="E72" s="116"/>
+      <c r="F72" s="117"/>
       <c r="G72" s="84" t="s">
         <v>38</v>
       </c>
@@ -5960,16 +5963,16 @@
     </row>
     <row r="73" spans="1:14" ht="63">
       <c r="A73" s="11"/>
-      <c r="B73" s="119"/>
+      <c r="B73" s="123"/>
       <c r="C73" s="64" t="str">
         <f>master!C59</f>
         <v>6-15. Askモードまとめ</v>
       </c>
-      <c r="D73" s="108" t="s">
+      <c r="D73" s="125" t="s">
         <v>145</v>
       </c>
-      <c r="E73" s="109"/>
-      <c r="F73" s="110"/>
+      <c r="E73" s="126"/>
+      <c r="F73" s="127"/>
       <c r="G73" s="64" t="s">
         <v>39</v>
       </c>
@@ -5987,16 +5990,16 @@
     </row>
     <row r="74" spans="1:14" ht="50.4">
       <c r="A74" s="11"/>
-      <c r="B74" s="119"/>
+      <c r="B74" s="123"/>
       <c r="C74" s="64" t="str">
         <f>master!C60</f>
         <v>6-16. チャット機能 - Agentモード</v>
       </c>
-      <c r="D74" s="108" t="s">
+      <c r="D74" s="125" t="s">
         <v>195</v>
       </c>
-      <c r="E74" s="109"/>
-      <c r="F74" s="110"/>
+      <c r="E74" s="126"/>
+      <c r="F74" s="127"/>
       <c r="G74" s="64" t="s">
         <v>41</v>
       </c>
@@ -6014,16 +6017,16 @@
     </row>
     <row r="75" spans="1:14" ht="63">
       <c r="A75" s="11"/>
-      <c r="B75" s="119"/>
+      <c r="B75" s="123"/>
       <c r="C75" s="64" t="str">
         <f>master!C61</f>
         <v>6-17. Agentモード</v>
       </c>
-      <c r="D75" s="108" t="s">
+      <c r="D75" s="125" t="s">
         <v>154</v>
       </c>
-      <c r="E75" s="109"/>
-      <c r="F75" s="110"/>
+      <c r="E75" s="126"/>
+      <c r="F75" s="127"/>
       <c r="G75" s="64" t="s">
         <v>39</v>
       </c>
@@ -6041,16 +6044,16 @@
     </row>
     <row r="76" spans="1:14" ht="50.4">
       <c r="A76" s="11"/>
-      <c r="B76" s="119"/>
+      <c r="B76" s="123"/>
       <c r="C76" s="64" t="str">
         <f>master!C62</f>
         <v>6-18. 実行例</v>
       </c>
-      <c r="D76" s="108" t="s">
+      <c r="D76" s="125" t="s">
         <v>155</v>
       </c>
-      <c r="E76" s="109"/>
-      <c r="F76" s="110"/>
+      <c r="E76" s="126"/>
+      <c r="F76" s="127"/>
       <c r="G76" s="64" t="s">
         <v>41</v>
       </c>
@@ -6068,16 +6071,16 @@
     </row>
     <row r="77" spans="1:14" ht="37.799999999999997">
       <c r="A77" s="11"/>
-      <c r="B77" s="119"/>
+      <c r="B77" s="123"/>
       <c r="C77" s="64" t="str">
         <f>master!C63</f>
         <v>6-19. READMEの内容を確認しましょう①</v>
       </c>
-      <c r="D77" s="108" t="s">
+      <c r="D77" s="125" t="s">
         <v>201</v>
       </c>
-      <c r="E77" s="109"/>
-      <c r="F77" s="110"/>
+      <c r="E77" s="126"/>
+      <c r="F77" s="127"/>
       <c r="G77" s="64" t="s">
         <v>40</v>
       </c>
@@ -6095,16 +6098,16 @@
     </row>
     <row r="78" spans="1:14" ht="37.799999999999997">
       <c r="A78" s="11"/>
-      <c r="B78" s="119"/>
-      <c r="C78" s="64" t="str">
+      <c r="B78" s="123"/>
+      <c r="C78" s="128" t="str">
         <f>master!C64</f>
         <v>6-20. READMEの内容を確認しましょう②</v>
       </c>
-      <c r="D78" s="108" t="s">
+      <c r="D78" s="125" t="s">
         <v>200</v>
       </c>
-      <c r="E78" s="109"/>
-      <c r="F78" s="110"/>
+      <c r="E78" s="126"/>
+      <c r="F78" s="127"/>
       <c r="G78" s="64" t="s">
         <v>40</v>
       </c>
@@ -6122,13 +6125,13 @@
     </row>
     <row r="79" spans="1:14" ht="126">
       <c r="A79" s="11"/>
-      <c r="B79" s="119"/>
-      <c r="C79" s="84"/>
-      <c r="D79" s="111" t="s">
+      <c r="B79" s="123"/>
+      <c r="C79" s="129"/>
+      <c r="D79" s="115" t="s">
         <v>177</v>
       </c>
-      <c r="E79" s="112"/>
-      <c r="F79" s="113"/>
+      <c r="E79" s="116"/>
+      <c r="F79" s="117"/>
       <c r="G79" s="84" t="s">
         <v>44</v>
       </c>
@@ -6148,16 +6151,16 @@
     </row>
     <row r="80" spans="1:14" ht="50.4">
       <c r="A80" s="11"/>
-      <c r="B80" s="119"/>
-      <c r="C80" s="64" t="str">
+      <c r="B80" s="123"/>
+      <c r="C80" s="128" t="str">
         <f>master!C65</f>
         <v>6-21. Changeログを作ってみましょう</v>
       </c>
-      <c r="D80" s="108" t="s">
+      <c r="D80" s="125" t="s">
         <v>156</v>
       </c>
-      <c r="E80" s="109"/>
-      <c r="F80" s="110"/>
+      <c r="E80" s="126"/>
+      <c r="F80" s="127"/>
       <c r="G80" s="64" t="s">
         <v>41</v>
       </c>
@@ -6175,13 +6178,13 @@
     </row>
     <row r="81" spans="1:14" ht="113.4">
       <c r="A81" s="11"/>
-      <c r="B81" s="119"/>
-      <c r="C81" s="89"/>
-      <c r="D81" s="111" t="s">
+      <c r="B81" s="123"/>
+      <c r="C81" s="129"/>
+      <c r="D81" s="115" t="s">
         <v>176</v>
       </c>
-      <c r="E81" s="112"/>
-      <c r="F81" s="113"/>
+      <c r="E81" s="116"/>
+      <c r="F81" s="117"/>
       <c r="G81" s="84" t="s">
         <v>43</v>
       </c>
@@ -6201,16 +6204,16 @@
     </row>
     <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="119"/>
+      <c r="B82" s="123"/>
       <c r="C82" s="64" t="str">
         <f>master!C66</f>
         <v>6-22. チャット機能 - Planモード</v>
       </c>
-      <c r="D82" s="108" t="s">
+      <c r="D82" s="125" t="s">
         <v>196</v>
       </c>
-      <c r="E82" s="109"/>
-      <c r="F82" s="110"/>
+      <c r="E82" s="126"/>
+      <c r="F82" s="127"/>
       <c r="G82" s="64" t="s">
         <v>41</v>
       </c>
@@ -6228,16 +6231,16 @@
     </row>
     <row r="83" spans="1:14" ht="63">
       <c r="A83" s="11"/>
-      <c r="B83" s="119"/>
+      <c r="B83" s="123"/>
       <c r="C83" s="64" t="str">
         <f>master!C67</f>
         <v>6-23. Planモードで機能追加してみましょう</v>
       </c>
-      <c r="D83" s="108" t="s">
+      <c r="D83" s="125" t="s">
         <v>160</v>
       </c>
-      <c r="E83" s="109"/>
-      <c r="F83" s="110"/>
+      <c r="E83" s="126"/>
+      <c r="F83" s="127"/>
       <c r="G83" s="64" t="s">
         <v>39</v>
       </c>
@@ -6255,16 +6258,16 @@
     </row>
     <row r="84" spans="1:14" ht="63">
       <c r="A84" s="11"/>
-      <c r="B84" s="119"/>
+      <c r="B84" s="123"/>
       <c r="C84" s="64" t="str">
         <f>master!C68</f>
         <v>6-24. 実行例①</v>
       </c>
-      <c r="D84" s="108" t="s">
+      <c r="D84" s="125" t="s">
         <v>157</v>
       </c>
-      <c r="E84" s="109"/>
-      <c r="F84" s="110"/>
+      <c r="E84" s="126"/>
+      <c r="F84" s="127"/>
       <c r="G84" s="64" t="s">
         <v>39</v>
       </c>
@@ -6282,16 +6285,16 @@
     </row>
     <row r="85" spans="1:14" ht="50.4">
       <c r="A85" s="11"/>
-      <c r="B85" s="119"/>
+      <c r="B85" s="123"/>
       <c r="C85" s="64" t="str">
         <f>master!C69</f>
         <v>6-25. 実行例②</v>
       </c>
-      <c r="D85" s="108" t="s">
+      <c r="D85" s="125" t="s">
         <v>158</v>
       </c>
-      <c r="E85" s="109"/>
-      <c r="F85" s="110"/>
+      <c r="E85" s="126"/>
+      <c r="F85" s="127"/>
       <c r="G85" s="64" t="s">
         <v>41</v>
       </c>
@@ -6309,16 +6312,16 @@
     </row>
     <row r="86" spans="1:14" ht="50.4">
       <c r="A86" s="11"/>
-      <c r="B86" s="119"/>
-      <c r="C86" s="64" t="str">
+      <c r="B86" s="123"/>
+      <c r="C86" s="128" t="str">
         <f>master!C70</f>
         <v>6-26. 実行例③</v>
       </c>
-      <c r="D86" s="108" t="s">
+      <c r="D86" s="125" t="s">
         <v>159</v>
       </c>
-      <c r="E86" s="109"/>
-      <c r="F86" s="110"/>
+      <c r="E86" s="126"/>
+      <c r="F86" s="127"/>
       <c r="G86" s="64" t="s">
         <v>41</v>
       </c>
@@ -6336,13 +6339,13 @@
     </row>
     <row r="87" spans="1:14" ht="126">
       <c r="A87" s="11"/>
-      <c r="B87" s="119"/>
-      <c r="C87" s="84"/>
-      <c r="D87" s="111" t="s">
+      <c r="B87" s="123"/>
+      <c r="C87" s="129"/>
+      <c r="D87" s="115" t="s">
         <v>175</v>
       </c>
-      <c r="E87" s="112"/>
-      <c r="F87" s="113"/>
+      <c r="E87" s="116"/>
+      <c r="F87" s="117"/>
       <c r="G87" s="84" t="s">
         <v>44</v>
       </c>
@@ -6360,16 +6363,16 @@
     </row>
     <row r="88" spans="1:14" ht="50.4">
       <c r="A88" s="11"/>
-      <c r="B88" s="119"/>
+      <c r="B88" s="123"/>
       <c r="C88" s="64" t="str">
         <f>master!C71</f>
         <v>6-27. 実行結果①</v>
       </c>
-      <c r="D88" s="108" t="s">
+      <c r="D88" s="125" t="s">
         <v>161</v>
       </c>
-      <c r="E88" s="109"/>
-      <c r="F88" s="110"/>
+      <c r="E88" s="126"/>
+      <c r="F88" s="127"/>
       <c r="G88" s="64" t="s">
         <v>41</v>
       </c>
@@ -6387,16 +6390,16 @@
     </row>
     <row r="89" spans="1:14" ht="50.4">
       <c r="A89" s="11"/>
-      <c r="B89" s="119"/>
+      <c r="B89" s="123"/>
       <c r="C89" s="64" t="str">
         <f>master!C72</f>
         <v>6-28. 実行結果②</v>
       </c>
-      <c r="D89" s="108" t="s">
+      <c r="D89" s="125" t="s">
         <v>162</v>
       </c>
-      <c r="E89" s="109"/>
-      <c r="F89" s="110"/>
+      <c r="E89" s="126"/>
+      <c r="F89" s="127"/>
       <c r="G89" s="64" t="s">
         <v>41</v>
       </c>
@@ -6414,16 +6417,16 @@
     </row>
     <row r="90" spans="1:14" ht="113.4">
       <c r="A90" s="11"/>
-      <c r="B90" s="115"/>
+      <c r="B90" s="124"/>
       <c r="C90" s="64" t="str">
         <f>master!C73</f>
         <v>6-29. Planモード＆Agentモードまとめ</v>
       </c>
-      <c r="D90" s="108" t="s">
+      <c r="D90" s="125" t="s">
         <v>163</v>
       </c>
-      <c r="E90" s="109"/>
-      <c r="F90" s="110"/>
+      <c r="E90" s="126"/>
+      <c r="F90" s="127"/>
       <c r="G90" s="64" t="s">
         <v>43</v>
       </c>
@@ -6441,7 +6444,7 @@
     </row>
     <row r="91" spans="1:14" ht="102" customHeight="1">
       <c r="A91" s="11"/>
-      <c r="B91" s="114" t="str">
+      <c r="B91" s="122" t="str">
         <f>master!B74</f>
         <v>成果物のプレゼン</v>
       </c>
@@ -6449,11 +6452,11 @@
         <f>master!C74</f>
         <v>開発した成果物のプレゼン（グループ）</v>
       </c>
-      <c r="D91" s="111" t="s">
+      <c r="D91" s="115" t="s">
         <v>191</v>
       </c>
-      <c r="E91" s="112"/>
-      <c r="F91" s="113"/>
+      <c r="E91" s="116"/>
+      <c r="F91" s="117"/>
       <c r="G91" s="84" t="s">
         <v>47</v>
       </c>
@@ -6471,16 +6474,16 @@
     </row>
     <row r="92" spans="1:14" ht="88.2">
       <c r="A92" s="11"/>
-      <c r="B92" s="115"/>
+      <c r="B92" s="124"/>
       <c r="C92" s="84" t="str">
         <f>master!C75</f>
         <v>開発した成果物のプレゼン（全体）</v>
       </c>
-      <c r="D92" s="111" t="s">
+      <c r="D92" s="115" t="s">
         <v>186</v>
       </c>
-      <c r="E92" s="112"/>
-      <c r="F92" s="113"/>
+      <c r="E92" s="116"/>
+      <c r="F92" s="117"/>
       <c r="G92" s="84" t="s">
         <v>45</v>
       </c>
@@ -6504,23 +6507,72 @@
     <row r="94" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="B37:B43"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="B56:B90"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="B44:B55"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D51:F51"/>
     <mergeCell ref="B17:B21"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="D18:F18"/>
@@ -6537,72 +6589,23 @@
     <mergeCell ref="D19:F19"/>
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="D32:F32"/>
-    <mergeCell ref="B44:B55"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="B37:B43"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="B56:B90"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:K11"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/IG/7日版/AI Native-生成AI_IG.xlsx
+++ b/IG/7日版/AI Native-生成AI_IG.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\レビュー後\SF修正後\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E673F16-9D83-48F5-AD19-A4A8BBEE2A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F15CC6B-14FA-4517-8DB6-FDFC67809830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（1日）'!$A$1:$H$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$93</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$94</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -63,7 +63,7 @@
     <author>ishida</author>
   </authors>
   <commentList>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{340225FA-055B-46D0-A70B-4D76CC80D05D}">
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="230">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -421,19 +421,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t xml:space="preserve">
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・共通1
-</t>
-    <rPh sb="1" eb="3">
-      <t>キョウツウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>予備</t>
     <rPh sb="0" eb="2">
       <t>ヨビ</t>
@@ -461,25 +448,12 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>・教材のダウンロード
-・本科目の概要説明
-　科目の位置づけや目的、全体の説明</t>
-    <rPh sb="1" eb="3">
-      <t>キョウザイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>1-1. 研修概要</t>
   </si>
   <si>
     <t>1-2. 背景・目的</t>
   </si>
   <si>
-    <t>モジュール1：オリエンテーションとマインドセット変革</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>1-3. 研修ゴールと獲得可能な経験背景・目的</t>
   </si>
   <si>
@@ -567,14 +541,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>モジュール5：ハンズオン（ChatGPT）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>モジュール4：プロンプトエンジニアリング</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>5-5. 例②：100本ノックを作ってみる</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -583,10 +549,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>モジュール6：ハンズオン（ GitHub Copilot ）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>6-1. Visual Studio Code を開く</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -656,10 +618,6 @@
   </si>
   <si>
     <t>6-29. Planモード＆Agentモードまとめ</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>モジュール2：AI・LLMの基礎理解</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1435,19 +1393,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>※時間が不足しそうな場合、生成AIを利用しない自己紹介をしてください。</t>
-    <rPh sb="13" eb="15">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>リヨウ</t>
-    </rPh>
-    <rPh sb="23" eb="27">
-      <t>ジコショウカイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>以下の内容を説明する。
 ■実施内容
 　・生成AIを活用して、アプリやゲームを作成する。</t>
@@ -1507,24 +1452,6 @@
     </rPh>
     <rPh sb="26" eb="27">
       <t>ヨ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>以下の内容を伝える。
-■研修ゴール
-　・ 生成AI（ChatGPT / GitHub Copilot）を活用し、要件定義～設計～実装～テストまでの開発プロセスを一通り実行できる
-　・ プロンプトの選択・修正・改善を通じて、成果物の品質を向上させるサイクルを実践できる
-　・ AIを前提とした開発の進め方を理解し、実務における再現可能な状態の「とっかかり」を獲得する
-■獲得可能な経験
-　・ ChatGPT を用いた 「調査・整理」、「叩き台資料作成」、「モックアプリ開発」、「企画・提案書骨子作成」、「成果物RV」の経験
-　・ GitHub Copilot を用いた AIエージェント への作業指示および上述の成果物作成・修正・RVの経験
-　・ GitHub Copilot を用いる際の 各種ハーネスエンジニアリング に向けたAI動作環境の改善経験
-　・ 生産性向上および品質向上を実現するための開発プロセスの改善経験
-■目標
-　・高度な自走ではなく、生成AIを活用して実務に取り組めるレベルへの到達</t>
-    <rPh sb="414" eb="416">
-      <t>モクヒョウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1937,10 +1864,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>モジュール3：NTTデータが目指すAIビジネス（Vision）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>※時間に余裕がある場合、実施してください。</t>
     <rPh sb="1" eb="3">
       <t>ジカン</t>
@@ -2000,31 +1923,6 @@
     <t>【AI Native研修】 生成AIの基礎.pptx</t>
     <rPh sb="19" eb="21">
       <t>キソ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>生成AIを活用して、自己紹介文を事前に作成する。</t>
-    <rPh sb="0" eb="2">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カツヨウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジコ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ショウカイ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>サクセイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -2143,127 +2041,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>以下の内容を実施する。
-■講師による自己紹介 (3分)
-　・氏名
-　・経歴
-　・その他
-　※生成AIを使った、自己紹介文を読む（1分）</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>コウシ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ジコ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ショウカイ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>プン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ケイレキ</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="55" eb="59">
-      <t>ジコショウカイ</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="61" eb="62">
-      <t>ヨ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">以下の内容を実施してもらう。
-■グループ内での自己紹介（5分*人数）
-　1. 生成AIを使って自己紹介文を作成する（2分）
-　　・部署
-　　・氏名
-　　・その他の特徴
-　2. 生成AIで作った自己紹介文を読む（2分）
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>※「1分以内」や「簡潔に」といった、分量や長さを具体的に指定するキーワードを指定した方が良いかもしれません。</t>
-    </r>
-    <rPh sb="20" eb="21">
-      <t>ナイ</t>
-    </rPh>
-    <rPh sb="23" eb="27">
-      <t>ジコショウカイ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>フン</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="50" eb="54">
-      <t>ジコショウカイ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="62" eb="63">
-      <t>フン</t>
-    </rPh>
-    <rPh sb="68" eb="70">
-      <t>ブショ</t>
-    </rPh>
-    <rPh sb="74" eb="76">
-      <t>シメイ</t>
-    </rPh>
-    <rPh sb="82" eb="83">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>トクチョウ</t>
-    </rPh>
-    <rPh sb="96" eb="97">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">・AI-01
 </t>
     <phoneticPr fontId="3"/>
@@ -2327,6 +2104,362 @@
   </si>
   <si>
     <t>2-2. 従来型AIと生成AIの比較</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■本モジュールで学ぶこと
+　① NTTデータのAI戦略
+　　・NTTデータが「Quality Growth」を掲げ、AIをどのように事業の中核に据えているかを理解する。
+　② 生成AIの進化とAgentic AI
+　　・生成AIがチャットボットからエージェントへ進化する中で、何が変わるのかを理解する。
+　③ NTTデータが描く未来と社員として知っておくべきこと
+　　・NTTデータが描くAI活用の未来像と、その実現に向けて必要な考え方や事例を学ぶ。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■Quality Growthとは
+　・「顧客への価値提供を最大化し、持続的な成長と両立する質を伴った成長」を目指す考え方である。
+■AI戦略
+　・AIを全事業に組み込んだ「AI-empowered New Value &amp; Productivity」を中核戦略としている。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■AIが重要となる背景
+　・生成AI活用による競争激化により、提供価値の劣後や価格競争が生じる可能性がある。
+　・国内労働人口の減少により、人財確保やノウハウ継承が課題となっている。
+■求められる変革
+　・AIによる変革を推進できる人財の拡充と、AIを前提としたシステム・データの整備が必要である。
+　・競争領域では価値創造、非競争領域では効率化を進めることが重要である。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■生成AIの進化
+　・現在はLevel1～2の段階であり、チャットボットや推論を中心に活用されている。
+　・今後はLevel3のエージェントへ移行し、AIが自律的に業務を遂行する世界へ進化していく。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■本モジュールで学ぶこと
+　・生成AIの進化とAgentic AIについて学ぶ。
+　・Agentic AIが目標に基づいて計画・実行・評価・改善を行う仕組みを理解する。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■本モジュールで学ぶこと
+　・NTTデータが描くAI活用の未来像を理解する。
+　・Smart AI Agent®、AIを起点とした業務変革、人とAIの役割分担について学ぶ。
+　・具体的な事例を通じて、AIによる価値創出の考え方を理解する。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■人とAIの役割分担
+　・AIを前提に業務を再設計する際は、人とAIの役割分担を再定義する。
+　・AIの強みを最大限に活用し、人間だけでは実現できない価値の創出を図る。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■AI前提のプロセス再設計
+　・AIを補助的に利用して既存業務を効率化するだけではなく、プロセス自体をAI前提で再設計する。
+　・業務全体を見直し、AIの活用効果を最大化することが重要である。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■AIバーチャル顧客の活用事例
+　・AIバーチャル顧客との会話から、JALカード会員への効果的なマーケティング施策を導出した事例である。
+■成果
+　・AI上のグループインタビューから得た示唆をもとにターゲットを選定し、販促プロモーションの購買率が3.0％向上した。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■AI-BPOによるオペレーション変革事例
+　・生成AIを活用し、従来は人手で行っていた校閲作業や文化的適合性確認などを効率化した事例である。
+■成果
+　・校閲ミスを96％削減し、作業期間を1/3に短縮した。
+　・1日あたりの処理量が5倍に増加した。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■AI CoEと生成AI人財育成の事例
+　・りそなグループでは、NTTデータの支援のもと、AIドリブンの企画・推進組織「AI CoE」を設置している。
+　・生成AI人財育成アカデミーを推進している。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■Smart AI Agent®とは
+　・複数のAIエージェントが自律的に協働する構想である。
+　・業務の抜本的変革によるP/Lインパクトの創出と、新たなビジネス価値の創造を目指している。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■AIを起点とした業務変革
+　・AIの強みや業務適用の発想を踏まえ、従来の考え方を転換することが重要である。
+　・AIを起点として、顧客企業の変革を提言・実現する。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■プロンプトを構成する4つの要素
+　・Role（役割）：AIに役割を与え、視点と専門性を定める。
+　・Context（背景）：依頼の目的や対象者などの前提条件を共有する。
+　・Task（指示）：実行してほしい具体的なアクションを明確にする。
+　・Format（形式）：表形式、箇条書き、文字数などの出力形式を指定する。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■プロンプトによる回答品質の違い
+　・対象者、目的、条件、出力形式が不明確なプロンプトでは、期待する回答を得にくい。
+　・役割、背景、具体的な指示、出力形式を明確にすることで、回答品質を高めることができる。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■Role Promptingとは
+　・AIに「プロのコンサルタント」や「新入社員のメンター」などの役割を与える手法である。
+■効果
+　・期待する視点や専門性、トーンで回答を生成しやすくなる。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■区切り文字の活用
+　・###、---、【指示】【データ】などを使い、指示文と参照データを明確に分離する。
+■効果
+　・AIが命令と処理対象を認識しやすくなり、意図しない解釈やハルシネーションを減らすことができる。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■Zero-shot Prompting
+　・例示を与えず、AIへ直接タスクを指示する方法である。
+■Few-shot Prompting
+　・事前に入力と出力の例を提示する方法である。
+　・出力形式を厳密に守らせたい場合に有効である。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を説明する。
+■Chain of Thought（思考の連鎖）
+　・複雑な問題や業務フローの設計において、考える順序やプロセスを分解して指示する手法である。
+■実践のポイント
+　・「まずAを考え、次にBを評価し、最後にCを出力する」のように、処理の流れを明確に指示する。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>01. オリエンテーションとマインドセット変革</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を伝える。
+■研修ゴール
+　・生成AIを活用して成果物を作成できる
+　・AIとの試行錯誤により成果物の品質を高めることができる
+　・AIを活用した開発の進め方を理解できるようになる_x000B_　・AIを活用した企画・提案の進め方を理解できるようになる
+　・AI時代の働き方の基礎を習得できる
+■獲得可能な経験
+　・ ChatGPT を用いた 「調査・整理」、「叩き台資料作成」、「モックアプリ開発」、「企画・提案書骨子作成」、「成果物RV」の経験
+　・ GitHub Copilot を用いた AIエージェント への作業指示および上述の成果物作成・修正・RVの経験
+　・ GitHub Copilot を用いる際の 各種ハーネスエンジニアリング に向けたAI動作環境の改善経験
+　・ 生産性向上および品質向上を実現するための開発プロセスの改善経験
+■目標
+　・高度な自走ではなく、生成AIを活用して実務に取り組めるレベルへの到達</t>
+    <rPh sb="376" eb="378">
+      <t>モクヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>02. AI・LLMの基礎理解</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>03. NTTデータが目指すAIビジネス（Vision）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>04. プロンプトエンジニアリング</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>05. ハンズオン（ChatGPT）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>06. ハンズオン（ GitHub Copilot ）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を実施する。
+■講師による自己紹介 (3分)
+　・氏名
+　・経歴
+　・その他</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウシ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジコ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>プン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ケイレキ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の内容を実施してもらう。
+■グループ内での自己紹介（2分*人数）
+　・氏名
+　・部署
+　・その他</t>
+    <rPh sb="20" eb="21">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>ジコショウカイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ブショ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>特になし</t>
+    <rPh sb="0" eb="1">
+      <t>トク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>環境確認</t>
+    <rPh sb="0" eb="2">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>・教材のダウンロード
+・本科目の概要説明
+　科目の位置づけや目的、全体の説明</t>
+    <rPh sb="1" eb="3">
+      <t>キョウザイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・共通1
+</t>
+    <rPh sb="1" eb="3">
+      <t>キョウツウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>研修環境の確認</t>
+    <rPh sb="0" eb="2">
+      <t>ケンシュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">以下の内容を実施してもらう。
+■以下を実施し、問題がないかを確認する。
+　・ChatGPTのログイン
+　・環境へのログイン
+　・VS Codeの起動
+　・GitHub Copilotへのログイン
+　　受講生は各自のメールアドレスでGitHubにログインするため、複数の組織が表示さる可能性があります。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">　　必ず、研修用の組織を選択するようにアナウンスをお願いします。
+　　組織を間違えると、研修で必要なGitHub Copilotを利用できない場合があります。
+</t>
+    </r>
+    <rPh sb="16" eb="18">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="141" eb="144">
+      <t>カノウセイ</t>
+    </rPh>
+    <rPh sb="153" eb="154">
+      <t>カナラ</t>
+    </rPh>
+    <rPh sb="177" eb="178">
+      <t>ネガ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -3007,9 +3140,15 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="20" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -3123,12 +3262,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3502,15 +3635,15 @@
   <sheetData>
     <row r="2" spans="1:8" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="91" t="str">
+      <c r="B2" s="93" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!B1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-生成AI_IG」</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
     </row>
     <row r="3" spans="1:8" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -3523,10 +3656,10 @@
     </row>
     <row r="4" spans="1:8" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="93"/>
+      <c r="C4" s="95"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -3534,18 +3667,18 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="94"/>
-      <c r="C5" s="95"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="97"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
     <row r="7" spans="1:8" ht="16.2">
-      <c r="B7" s="96" t="s">
+      <c r="B7" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="96"/>
+      <c r="C7" s="98"/>
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="24"/>
@@ -3583,8 +3716,13 @@
       <c r="A12" s="37">
         <v>0.41666666666666669</v>
       </c>
-      <c r="B12" s="69"/>
-      <c r="C12" s="73"/>
+      <c r="B12" s="62">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C12" s="72" t="str">
+        <f>master!B5</f>
+        <v>環境確認</v>
+      </c>
       <c r="G12" s="14" t="s">
         <v>12</v>
       </c>
@@ -3602,10 +3740,10 @@
         <v>0.4375</v>
       </c>
       <c r="C14" s="72" t="str">
-        <f>master!B5</f>
-        <v>モジュール1：オリエンテーションとマインドセット変革</v>
-      </c>
-      <c r="F14" s="90"/>
+        <f>master!B6</f>
+        <v>01. オリエンテーションとマインドセット変革</v>
+      </c>
+      <c r="F14" s="92"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8">
@@ -3614,10 +3752,10 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C15" s="71" t="str">
-        <f>master!B8</f>
-        <v>モジュール2：AI・LLMの基礎理解</v>
-      </c>
-      <c r="F15" s="90"/>
+        <f>master!B9</f>
+        <v>02. AI・LLMの基礎理解</v>
+      </c>
+      <c r="F15" s="92"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8">
@@ -3628,24 +3766,24 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C16" s="72" t="str">
-        <f>master!B13</f>
-        <v>モジュール3：NTTデータが目指すAIビジネス（Vision）</v>
-      </c>
-      <c r="F16" s="90"/>
+        <f>master!B14</f>
+        <v>03. NTTデータが目指すAIビジネス（Vision）</v>
+      </c>
+      <c r="F16" s="92"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="38"/>
       <c r="B17" s="69"/>
       <c r="C17" s="73"/>
-      <c r="F17" s="90"/>
+      <c r="F17" s="92"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="38"/>
       <c r="B18" s="41"/>
       <c r="C18" s="74"/>
-      <c r="F18" s="90"/>
+      <c r="F18" s="92"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8">
@@ -3654,10 +3792,10 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="C19" s="72" t="str">
-        <f>master!B28</f>
-        <v>モジュール4：プロンプトエンジニアリング</v>
-      </c>
-      <c r="F19" s="90"/>
+        <f>master!B29</f>
+        <v>04. プロンプトエンジニアリング</v>
+      </c>
+      <c r="F19" s="92"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8">
@@ -3666,7 +3804,7 @@
       </c>
       <c r="B20" s="42"/>
       <c r="C20" s="74"/>
-      <c r="F20" s="90"/>
+      <c r="F20" s="92"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8">
@@ -3674,10 +3812,10 @@
       <c r="B21" s="17">
         <v>0.51041666666666663</v>
       </c>
-      <c r="C21" s="89" t="s">
-        <v>51</v>
-      </c>
-      <c r="F21" s="90"/>
+      <c r="C21" s="90" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" s="92"/>
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8">
@@ -3730,10 +3868,10 @@
         <v>0.5625</v>
       </c>
       <c r="C26" s="58" t="str">
-        <f>master!B35</f>
-        <v>モジュール5：ハンズオン（ChatGPT）</v>
-      </c>
-      <c r="F26" s="90"/>
+        <f>master!B36</f>
+        <v>05. ハンズオン（ChatGPT）</v>
+      </c>
+      <c r="F26" s="92"/>
       <c r="G26" s="14"/>
       <c r="H26" s="6"/>
     </row>
@@ -3741,7 +3879,7 @@
       <c r="A27" s="39"/>
       <c r="B27" s="42"/>
       <c r="C27" s="58"/>
-      <c r="F27" s="90"/>
+      <c r="F27" s="92"/>
       <c r="G27" s="14"/>
       <c r="H27" s="6"/>
     </row>
@@ -3751,7 +3889,7 @@
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="58"/>
-      <c r="F28" s="90"/>
+      <c r="F28" s="92"/>
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8">
@@ -3760,7 +3898,7 @@
       <c r="C29" s="59"/>
       <c r="D29" s="55"/>
       <c r="E29" s="52"/>
-      <c r="F29" s="90"/>
+      <c r="F29" s="92"/>
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8">
@@ -3769,12 +3907,12 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="C30" s="58" t="str">
-        <f>master!B45</f>
-        <v>モジュール6：ハンズオン（ GitHub Copilot ）</v>
+        <f>master!B46</f>
+        <v>06. ハンズオン（ GitHub Copilot ）</v>
       </c>
       <c r="D30" s="55"/>
       <c r="E30" s="52"/>
-      <c r="F30" s="90"/>
+      <c r="F30" s="92"/>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8">
@@ -3783,7 +3921,7 @@
       <c r="C31" s="58"/>
       <c r="D31" s="55"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="90"/>
+      <c r="F31" s="92"/>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8">
@@ -3794,7 +3932,7 @@
       <c r="C32" s="58"/>
       <c r="D32" s="55"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="90"/>
+      <c r="F32" s="92"/>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8">
@@ -3803,7 +3941,7 @@
       <c r="C33" s="58"/>
       <c r="D33" s="55"/>
       <c r="E33" s="52"/>
-      <c r="F33" s="90"/>
+      <c r="F33" s="92"/>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8">
@@ -3812,7 +3950,7 @@
       <c r="C34" s="58"/>
       <c r="D34" s="55"/>
       <c r="E34" s="52"/>
-      <c r="F34" s="90"/>
+      <c r="F34" s="92"/>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8">
@@ -3821,7 +3959,7 @@
       <c r="C35" s="58"/>
       <c r="D35" s="55"/>
       <c r="E35" s="52"/>
-      <c r="F35" s="90"/>
+      <c r="F35" s="92"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8">
@@ -3832,7 +3970,7 @@
       <c r="C36" s="58"/>
       <c r="D36" s="55"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="90"/>
+      <c r="F36" s="92"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8">
@@ -3841,7 +3979,7 @@
       <c r="C37" s="58"/>
       <c r="D37" s="55"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="90"/>
+      <c r="F37" s="92"/>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8">
@@ -3850,7 +3988,7 @@
       <c r="C38" s="58"/>
       <c r="D38" s="55"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="90"/>
+      <c r="F38" s="92"/>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8">
@@ -3859,7 +3997,7 @@
       <c r="C39" s="58"/>
       <c r="D39" s="55"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="90"/>
+      <c r="F39" s="92"/>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8">
@@ -3870,7 +4008,7 @@
       <c r="C40" s="59"/>
       <c r="D40" s="55"/>
       <c r="E40" s="52"/>
-      <c r="F40" s="90"/>
+      <c r="F40" s="92"/>
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8">
@@ -3879,12 +4017,12 @@
         <v>0.71875</v>
       </c>
       <c r="C41" s="58" t="str">
-        <f>master!B74</f>
+        <f>master!B75</f>
         <v>成果物のプレゼン</v>
       </c>
       <c r="D41" s="57"/>
       <c r="E41" s="53"/>
-      <c r="F41" s="90"/>
+      <c r="F41" s="92"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8">
@@ -3893,7 +4031,7 @@
       <c r="C42" s="59"/>
       <c r="D42" s="55"/>
       <c r="E42" s="53"/>
-      <c r="F42" s="90"/>
+      <c r="F42" s="92"/>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1">
@@ -3902,7 +4040,7 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="C43" s="79" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D43" s="56"/>
       <c r="E43" s="54"/>
@@ -3980,10 +4118,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="102"/>
+      <c r="C4" s="104"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -3994,16 +4132,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
+      <c r="B5" s="105"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -4018,10 +4156,10 @@
       <c r="C7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="104" t="s">
+      <c r="D7" s="106" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="104"/>
+      <c r="E7" s="106"/>
       <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
@@ -4036,7 +4174,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D8" s="45" t="s">
         <v>20</v>
@@ -4053,46 +4191,46 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="10"/>
-      <c r="B10" s="98"/>
-      <c r="C10" s="98" t="s">
+      <c r="B10" s="100"/>
+      <c r="C10" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="98" t="s">
+      <c r="D10" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98" t="s">
+      <c r="E10" s="100"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="105" t="s">
+      <c r="H10" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="97" t="s">
+      <c r="I10" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="97"/>
-      <c r="K10" s="97" t="s">
+      <c r="J10" s="99"/>
+      <c r="K10" s="99" t="s">
         <v>31</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="98"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="106"/>
+      <c r="B11" s="100"/>
+      <c r="C11" s="100"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="100"/>
+      <c r="H11" s="108"/>
       <c r="I11" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J11" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="98"/>
+      <c r="K11" s="100"/>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="63">
@@ -4101,13 +4239,13 @@
       <c r="C12" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="99" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="100"/>
-      <c r="F12" s="101"/>
+      <c r="D12" s="101" t="s">
+        <v>225</v>
+      </c>
+      <c r="E12" s="102"/>
+      <c r="F12" s="103"/>
       <c r="G12" s="82" t="s">
-        <v>50</v>
+        <v>226</v>
       </c>
       <c r="H12" s="20"/>
       <c r="I12" s="50" t="s">
@@ -4153,8 +4291,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF8DE2F-88F4-47C2-84DC-4E7D3D9288E2}">
-  <dimension ref="A2:N94"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A2:N95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -4204,12 +4342,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -4220,18 +4358,18 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="107" t="s">
-        <v>193</v>
-      </c>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="107"/>
-      <c r="I5" s="107"/>
-      <c r="J5" s="107"/>
-      <c r="K5" s="107"/>
+      <c r="B5" s="109" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
+      <c r="H5" s="109"/>
+      <c r="I5" s="109"/>
+      <c r="J5" s="109"/>
+      <c r="K5" s="109"/>
       <c r="L5" s="29"/>
       <c r="M5" s="30"/>
     </row>
@@ -4251,10 +4389,10 @@
       <c r="C7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="104" t="s">
+      <c r="D7" s="106" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="104"/>
+      <c r="E7" s="106"/>
       <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
@@ -4273,7 +4411,7 @@
         <v>34</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D8" s="45" t="s">
         <v>20</v>
@@ -4292,28 +4430,28 @@
     </row>
     <row r="10" spans="1:14" ht="24" customHeight="1">
       <c r="A10" s="10"/>
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="98" t="s">
+      <c r="C10" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="98" t="s">
+      <c r="D10" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98" t="s">
+      <c r="E10" s="100"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="97" t="s">
+      <c r="H10" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="108" t="s">
+      <c r="I10" s="110" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="109"/>
-      <c r="K10" s="97" t="s">
+      <c r="J10" s="111"/>
+      <c r="K10" s="99" t="s">
         <v>33</v>
       </c>
       <c r="L10" s="6"/>
@@ -4322,27 +4460,27 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="10"/>
-      <c r="B11" s="98"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="97"/>
+      <c r="B11" s="100"/>
+      <c r="C11" s="100"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="100"/>
+      <c r="H11" s="99"/>
       <c r="I11" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J11" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="98"/>
+      <c r="K11" s="100"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:14" ht="88.2">
+    <row r="12" spans="1:14" ht="75.599999999999994">
       <c r="A12" s="10"/>
-      <c r="B12" s="110" t="str">
+      <c r="B12" s="112" t="str">
         <f>master!B3</f>
         <v>自己紹介</v>
       </c>
@@ -4350,13 +4488,13 @@
         <f>master!C3</f>
         <v>講師の自己紹介</v>
       </c>
-      <c r="D12" s="112" t="s">
-        <v>202</v>
-      </c>
-      <c r="E12" s="113"/>
-      <c r="F12" s="114"/>
+      <c r="D12" s="114" t="s">
+        <v>220</v>
+      </c>
+      <c r="E12" s="115"/>
+      <c r="F12" s="116"/>
       <c r="G12" s="51" t="s">
-        <v>49</v>
+        <v>221</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="49" t="s">
@@ -4370,79 +4508,80 @@
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
     </row>
-    <row r="13" spans="1:14" ht="126">
+    <row r="13" spans="1:14" ht="75.599999999999994">
       <c r="A13" s="10"/>
-      <c r="B13" s="111"/>
+      <c r="B13" s="113"/>
       <c r="C13" s="84" t="str">
         <f>master!C4</f>
         <v>受講生の自己紹介</v>
       </c>
-      <c r="D13" s="115" t="s">
-        <v>204</v>
-      </c>
-      <c r="E13" s="116"/>
-      <c r="F13" s="117"/>
+      <c r="D13" s="117" t="s">
+        <v>222</v>
+      </c>
+      <c r="E13" s="118"/>
+      <c r="F13" s="119"/>
       <c r="G13" s="84" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="H13" s="85"/>
       <c r="I13" s="86" t="s">
         <v>25</v>
       </c>
       <c r="J13" s="87">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K13" s="88" t="s">
-        <v>164</v>
-      </c>
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K13" s="88"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14" ht="151.19999999999999">
-      <c r="A14" s="11"/>
-      <c r="B14" s="118" t="str">
+    <row r="14" spans="1:14" ht="126">
+      <c r="A14" s="10"/>
+      <c r="B14" s="91" t="str">
         <f>master!B5</f>
-        <v>モジュール1：オリエンテーションとマインドセット変革</v>
+        <v>環境確認</v>
       </c>
       <c r="C14" s="51" t="str">
         <f>master!C5</f>
-        <v>1-1. 研修概要</v>
-      </c>
-      <c r="D14" s="112" t="s">
-        <v>206</v>
-      </c>
-      <c r="E14" s="113"/>
-      <c r="F14" s="114"/>
+        <v>研修環境の確認</v>
+      </c>
+      <c r="D14" s="114" t="s">
+        <v>229</v>
+      </c>
+      <c r="E14" s="115"/>
+      <c r="F14" s="116"/>
       <c r="G14" s="51" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J14" s="47">
-        <v>1.3888888888888889E-3</v>
+        <v>1.3888888888888888E-2</v>
       </c>
       <c r="K14" s="43"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:14" ht="100.8">
+    <row r="15" spans="1:14" ht="151.19999999999999">
       <c r="A15" s="11"/>
-      <c r="B15" s="118"/>
+      <c r="B15" s="120" t="str">
+        <f>master!B6</f>
+        <v>01. オリエンテーションとマインドセット変革</v>
+      </c>
       <c r="C15" s="51" t="str">
         <f>master!C6</f>
-        <v>1-2. 背景・目的</v>
-      </c>
-      <c r="D15" s="112" t="s">
-        <v>133</v>
-      </c>
-      <c r="E15" s="113"/>
-      <c r="F15" s="114"/>
+        <v>1-1. 研修概要</v>
+      </c>
+      <c r="D15" s="114" t="s">
+        <v>191</v>
+      </c>
+      <c r="E15" s="115"/>
+      <c r="F15" s="116"/>
       <c r="G15" s="51" t="s">
-        <v>47</v>
+        <v>190</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="49" t="s">
@@ -4456,57 +4595,54 @@
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
-    <row r="16" spans="1:14" ht="214.2">
+    <row r="16" spans="1:14" ht="100.8">
       <c r="A16" s="11"/>
-      <c r="B16" s="118"/>
+      <c r="B16" s="120"/>
       <c r="C16" s="51" t="str">
         <f>master!C7</f>
-        <v>1-3. 研修ゴールと獲得可能な経験背景・目的</v>
-      </c>
-      <c r="D16" s="112" t="s">
-        <v>169</v>
-      </c>
-      <c r="E16" s="113"/>
-      <c r="F16" s="114"/>
+        <v>1-2. 背景・目的</v>
+      </c>
+      <c r="D16" s="114" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" s="115"/>
+      <c r="F16" s="116"/>
       <c r="G16" s="51" t="s">
-        <v>134</v>
+        <v>47</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J16" s="47">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K16" s="43"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:14" ht="113.4">
+    <row r="17" spans="1:14" ht="214.2">
       <c r="A17" s="11"/>
-      <c r="B17" s="119" t="str">
-        <f>master!B8</f>
-        <v>モジュール2：AI・LLMの基礎理解</v>
-      </c>
+      <c r="B17" s="120"/>
       <c r="C17" s="51" t="str">
         <f>master!C8</f>
-        <v>2-1. 生成AI（Generative AI）とは？</v>
-      </c>
-      <c r="D17" s="112" t="s">
-        <v>207</v>
-      </c>
-      <c r="E17" s="113"/>
-      <c r="F17" s="114"/>
+        <v>1-3. 研修ゴールと獲得可能な経験背景・目的</v>
+      </c>
+      <c r="D17" s="114" t="s">
+        <v>214</v>
+      </c>
+      <c r="E17" s="115"/>
+      <c r="F17" s="116"/>
       <c r="G17" s="51" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J17" s="47">
-        <v>1.3888888888888889E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K17" s="43"/>
       <c r="L17" s="6"/>
@@ -4515,16 +4651,19 @@
     </row>
     <row r="18" spans="1:14" ht="113.4">
       <c r="A18" s="11"/>
-      <c r="B18" s="120"/>
+      <c r="B18" s="121" t="str">
+        <f>master!B9</f>
+        <v>02. AI・LLMの基礎理解</v>
+      </c>
       <c r="C18" s="51" t="str">
         <f>master!C9</f>
-        <v>2-2. 従来型AIと生成AIの比較</v>
-      </c>
-      <c r="D18" s="112" t="s">
-        <v>135</v>
-      </c>
-      <c r="E18" s="113"/>
-      <c r="F18" s="114"/>
+        <v>2-1. 生成AI（Generative AI）とは？</v>
+      </c>
+      <c r="D18" s="114" t="s">
+        <v>192</v>
+      </c>
+      <c r="E18" s="115"/>
+      <c r="F18" s="116"/>
       <c r="G18" s="51" t="s">
         <v>43</v>
       </c>
@@ -4542,16 +4681,16 @@
     </row>
     <row r="19" spans="1:14" ht="113.4">
       <c r="A19" s="11"/>
-      <c r="B19" s="120"/>
+      <c r="B19" s="122"/>
       <c r="C19" s="51" t="str">
         <f>master!C10</f>
-        <v>2-3. LLM（大規模言語モデル）の仕組み</v>
-      </c>
-      <c r="D19" s="112" t="s">
-        <v>136</v>
-      </c>
-      <c r="E19" s="113"/>
-      <c r="F19" s="114"/>
+        <v>2-2. 従来型AIと生成AIの比較</v>
+      </c>
+      <c r="D19" s="114" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" s="115"/>
+      <c r="F19" s="116"/>
       <c r="G19" s="51" t="s">
         <v>43</v>
       </c>
@@ -4560,27 +4699,27 @@
         <v>25</v>
       </c>
       <c r="J19" s="47">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K19" s="43"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
     </row>
-    <row r="20" spans="1:14" ht="126">
+    <row r="20" spans="1:14" ht="113.4">
       <c r="A20" s="11"/>
-      <c r="B20" s="120"/>
+      <c r="B20" s="122"/>
       <c r="C20" s="51" t="str">
         <f>master!C11</f>
-        <v>2-4. 生成AIの「苦手なこと」（弱み）</v>
-      </c>
-      <c r="D20" s="112" t="s">
-        <v>137</v>
-      </c>
-      <c r="E20" s="113"/>
-      <c r="F20" s="114"/>
+        <v>2-3. LLM（大規模言語モデル）の仕組み</v>
+      </c>
+      <c r="D20" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" s="115"/>
+      <c r="F20" s="116"/>
       <c r="G20" s="51" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="49" t="s">
@@ -4594,71 +4733,75 @@
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
     </row>
-    <row r="21" spans="1:14" ht="239.4">
+    <row r="21" spans="1:14" ht="126">
       <c r="A21" s="11"/>
-      <c r="B21" s="121"/>
+      <c r="B21" s="122"/>
       <c r="C21" s="51" t="str">
         <f>master!C12</f>
-        <v>2-5. 生成AIを使う心得８条</v>
-      </c>
-      <c r="D21" s="112" t="s">
-        <v>170</v>
-      </c>
-      <c r="E21" s="113"/>
-      <c r="F21" s="114"/>
+        <v>2-4. 生成AIの「苦手なこと」（弱み）</v>
+      </c>
+      <c r="D21" s="114" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="115"/>
+      <c r="F21" s="116"/>
       <c r="G21" s="51" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J21" s="47">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K21" s="43"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:14" ht="25.2">
+    <row r="22" spans="1:14" ht="239.4">
       <c r="A22" s="11"/>
-      <c r="B22" s="118" t="str">
-        <f>master!B13</f>
-        <v>モジュール3：NTTデータが目指すAIビジネス（Vision）</v>
-      </c>
+      <c r="B22" s="123"/>
       <c r="C22" s="51" t="str">
         <f>master!C13</f>
-        <v>3-1. 本モジュールで学ぶこと①</v>
-      </c>
-      <c r="D22" s="112"/>
-      <c r="E22" s="113"/>
-      <c r="F22" s="114"/>
+        <v>2-5. 生成AIを使う心得８条</v>
+      </c>
+      <c r="D22" s="114" t="s">
+        <v>160</v>
+      </c>
+      <c r="E22" s="115"/>
+      <c r="F22" s="116"/>
       <c r="G22" s="51" t="s">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J22" s="47">
-        <v>6.9444444444444447E-4</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K22" s="43"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:14" ht="25.2">
+    <row r="23" spans="1:14" ht="106.8" customHeight="1">
       <c r="A23" s="11"/>
-      <c r="B23" s="118"/>
+      <c r="B23" s="120" t="str">
+        <f>master!B14</f>
+        <v>03. NTTデータが目指すAIビジネス（Vision）</v>
+      </c>
       <c r="C23" s="51" t="str">
         <f>master!C14</f>
-        <v>3-2. NTTデータのAI戦略：Quality Growthとは</v>
-      </c>
-      <c r="D23" s="112"/>
-      <c r="E23" s="113"/>
-      <c r="F23" s="114"/>
+        <v>3-1. 本モジュールで学ぶこと①</v>
+      </c>
+      <c r="D23" s="114" t="s">
+        <v>194</v>
+      </c>
+      <c r="E23" s="115"/>
+      <c r="F23" s="116"/>
       <c r="G23" s="51" t="s">
         <v>46</v>
       </c>
@@ -4667,23 +4810,25 @@
         <v>25</v>
       </c>
       <c r="J23" s="47">
-        <v>2.0833333333333333E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K23" s="43"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:14" ht="25.2">
+    <row r="24" spans="1:14" ht="64.8" customHeight="1">
       <c r="A24" s="11"/>
-      <c r="B24" s="118"/>
+      <c r="B24" s="120"/>
       <c r="C24" s="51" t="str">
         <f>master!C15</f>
-        <v>3-3. なぜ今、AIが重要なのか</v>
-      </c>
-      <c r="D24" s="112"/>
-      <c r="E24" s="113"/>
-      <c r="F24" s="114"/>
+        <v>3-2. NTTデータのAI戦略：Quality Growthとは</v>
+      </c>
+      <c r="D24" s="114" t="s">
+        <v>195</v>
+      </c>
+      <c r="E24" s="115"/>
+      <c r="F24" s="116"/>
       <c r="G24" s="51" t="s">
         <v>46</v>
       </c>
@@ -4699,16 +4844,18 @@
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="1:14" ht="25.2">
+    <row r="25" spans="1:14" ht="97.2" customHeight="1">
       <c r="A25" s="11"/>
-      <c r="B25" s="118"/>
+      <c r="B25" s="120"/>
       <c r="C25" s="51" t="str">
         <f>master!C16</f>
-        <v>3-4. 生成AIの進化：今、どこにいるか</v>
-      </c>
-      <c r="D25" s="112"/>
-      <c r="E25" s="113"/>
-      <c r="F25" s="114"/>
+        <v>3-3. なぜ今、AIが重要なのか</v>
+      </c>
+      <c r="D25" s="114" t="s">
+        <v>196</v>
+      </c>
+      <c r="E25" s="115"/>
+      <c r="F25" s="116"/>
       <c r="G25" s="51" t="s">
         <v>46</v>
       </c>
@@ -4724,70 +4871,72 @@
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
     </row>
-    <row r="26" spans="1:14" ht="15" customHeight="1">
+    <row r="26" spans="1:14" ht="55.8" customHeight="1">
       <c r="A26" s="11"/>
-      <c r="B26" s="118"/>
+      <c r="B26" s="120"/>
       <c r="C26" s="51" t="str">
         <f>master!C17</f>
-        <v>3-5. 本モジュールで学ぶこと②</v>
-      </c>
-      <c r="D26" s="112"/>
-      <c r="E26" s="113"/>
-      <c r="F26" s="114"/>
+        <v>3-4. 生成AIの進化：今、どこにいるか</v>
+      </c>
+      <c r="D26" s="114" t="s">
+        <v>197</v>
+      </c>
+      <c r="E26" s="115"/>
+      <c r="F26" s="116"/>
       <c r="G26" s="51" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J26" s="47">
-        <v>6.9444444444444447E-4</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K26" s="43"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
     </row>
-    <row r="27" spans="1:14" ht="63">
+    <row r="27" spans="1:14" ht="59.4" customHeight="1">
       <c r="A27" s="11"/>
-      <c r="B27" s="118"/>
+      <c r="B27" s="120"/>
       <c r="C27" s="51" t="str">
         <f>master!C18</f>
-        <v>3-6. エージェントAI（Agentic AI）とは何か</v>
-      </c>
-      <c r="D27" s="112" t="s">
-        <v>171</v>
-      </c>
-      <c r="E27" s="113"/>
-      <c r="F27" s="114"/>
+        <v>3-5. 本モジュールで学ぶこと②</v>
+      </c>
+      <c r="D27" s="114" t="s">
+        <v>198</v>
+      </c>
+      <c r="E27" s="115"/>
+      <c r="F27" s="116"/>
       <c r="G27" s="51" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J27" s="47">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K27" s="43"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
     </row>
-    <row r="28" spans="1:14" ht="63">
+    <row r="28" spans="1:14" ht="63" customHeight="1">
       <c r="A28" s="11"/>
-      <c r="B28" s="118"/>
+      <c r="B28" s="120"/>
       <c r="C28" s="51" t="str">
         <f>master!C19</f>
-        <v>3-7. エージェントの処理</v>
-      </c>
-      <c r="D28" s="112" t="s">
-        <v>139</v>
-      </c>
-      <c r="E28" s="113"/>
-      <c r="F28" s="114"/>
+        <v>3-6. エージェントAI（Agentic AI）とは何か</v>
+      </c>
+      <c r="D28" s="114" t="s">
+        <v>161</v>
+      </c>
+      <c r="E28" s="115"/>
+      <c r="F28" s="116"/>
       <c r="G28" s="51" t="s">
         <v>39</v>
       </c>
@@ -4796,48 +4945,52 @@
         <v>25</v>
       </c>
       <c r="J28" s="47">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K28" s="43"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
     </row>
-    <row r="29" spans="1:14" ht="37.799999999999997">
+    <row r="29" spans="1:14" ht="63" customHeight="1">
       <c r="A29" s="11"/>
-      <c r="B29" s="118"/>
+      <c r="B29" s="120"/>
       <c r="C29" s="51" t="str">
         <f>master!C20</f>
-        <v>3-8. 本モジュールで学ぶこと③</v>
-      </c>
-      <c r="D29" s="112"/>
-      <c r="E29" s="113"/>
-      <c r="F29" s="114"/>
+        <v>3-7. エージェントの処理</v>
+      </c>
+      <c r="D29" s="114" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" s="115"/>
+      <c r="F29" s="116"/>
       <c r="G29" s="51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J29" s="47">
-        <v>6.9444444444444447E-4</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K29" s="43"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
     </row>
-    <row r="30" spans="1:14" ht="37.799999999999997">
+    <row r="30" spans="1:14" ht="74.400000000000006" customHeight="1">
       <c r="A30" s="11"/>
-      <c r="B30" s="118"/>
+      <c r="B30" s="120"/>
       <c r="C30" s="51" t="str">
         <f>master!C21</f>
-        <v>3-9. NTTデータが描く未来：Smart AI Agent®</v>
-      </c>
-      <c r="D30" s="112"/>
-      <c r="E30" s="113"/>
-      <c r="F30" s="114"/>
+        <v>3-8. 本モジュールで学ぶこと③</v>
+      </c>
+      <c r="D30" s="114" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" s="115"/>
+      <c r="F30" s="116"/>
       <c r="G30" s="51" t="s">
         <v>40</v>
       </c>
@@ -4846,23 +4999,25 @@
         <v>25</v>
       </c>
       <c r="J30" s="47">
-        <v>2.0833333333333333E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K30" s="43"/>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
     </row>
-    <row r="31" spans="1:14" ht="37.799999999999997">
+    <row r="31" spans="1:14" ht="55.2" customHeight="1">
       <c r="A31" s="11"/>
-      <c r="B31" s="118"/>
+      <c r="B31" s="120"/>
       <c r="C31" s="51" t="str">
         <f>master!C22</f>
-        <v>3-10. AIの強みを生かした業務変革の進め方</v>
-      </c>
-      <c r="D31" s="112"/>
-      <c r="E31" s="113"/>
-      <c r="F31" s="114"/>
+        <v>3-9. NTTデータが描く未来：Smart AI Agent®</v>
+      </c>
+      <c r="D31" s="114" t="s">
+        <v>205</v>
+      </c>
+      <c r="E31" s="115"/>
+      <c r="F31" s="116"/>
       <c r="G31" s="51" t="s">
         <v>40</v>
       </c>
@@ -4878,16 +5033,18 @@
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="1:14" ht="37.799999999999997">
+    <row r="32" spans="1:14" ht="66" customHeight="1">
       <c r="A32" s="11"/>
-      <c r="B32" s="118"/>
+      <c r="B32" s="120"/>
       <c r="C32" s="51" t="str">
         <f>master!C23</f>
-        <v>3-11. AIの強みを生かすポイント：人とAIとの役割分担</v>
-      </c>
-      <c r="D32" s="112"/>
-      <c r="E32" s="113"/>
-      <c r="F32" s="114"/>
+        <v>3-10. AIの強みを生かした業務変革の進め方</v>
+      </c>
+      <c r="D32" s="114" t="s">
+        <v>206</v>
+      </c>
+      <c r="E32" s="115"/>
+      <c r="F32" s="116"/>
       <c r="G32" s="51" t="s">
         <v>40</v>
       </c>
@@ -4903,16 +5060,18 @@
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
     </row>
-    <row r="33" spans="1:14" ht="37.799999999999997">
+    <row r="33" spans="1:14" ht="37.799999999999997" customHeight="1">
       <c r="A33" s="11"/>
-      <c r="B33" s="118"/>
+      <c r="B33" s="120"/>
       <c r="C33" s="51" t="str">
         <f>master!C24</f>
-        <v>3-12. AIの強みを生かすポイント：プロセス自体をAI前提で再設計</v>
-      </c>
-      <c r="D33" s="112"/>
-      <c r="E33" s="113"/>
-      <c r="F33" s="114"/>
+        <v>3-11. AIの強みを生かすポイント：人とAIとの役割分担</v>
+      </c>
+      <c r="D33" s="114" t="s">
+        <v>200</v>
+      </c>
+      <c r="E33" s="115"/>
+      <c r="F33" s="116"/>
       <c r="G33" s="51" t="s">
         <v>40</v>
       </c>
@@ -4930,14 +5089,16 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="118"/>
+      <c r="B34" s="120"/>
       <c r="C34" s="51" t="str">
         <f>master!C25</f>
-        <v>3-13. JALカード様 -  AIバーチャル顧客を活用したマーケティング高度化</v>
-      </c>
-      <c r="D34" s="112"/>
-      <c r="E34" s="113"/>
-      <c r="F34" s="114"/>
+        <v>3-12. AIの強みを生かすポイント：プロセス自体をAI前提で再設計</v>
+      </c>
+      <c r="D34" s="114" t="s">
+        <v>201</v>
+      </c>
+      <c r="E34" s="115"/>
+      <c r="F34" s="116"/>
       <c r="G34" s="51" t="s">
         <v>40</v>
       </c>
@@ -4946,23 +5107,25 @@
         <v>25</v>
       </c>
       <c r="J34" s="47">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K34" s="43"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="1:14" ht="37.799999999999997">
+    <row r="35" spans="1:14" ht="93.6" customHeight="1">
       <c r="A35" s="11"/>
-      <c r="B35" s="118"/>
+      <c r="B35" s="120"/>
       <c r="C35" s="51" t="str">
         <f>master!C26</f>
-        <v>3-14. 大手メディアサービス会社 - AI-BPOによるオペレーション変革</v>
-      </c>
-      <c r="D35" s="112"/>
-      <c r="E35" s="113"/>
-      <c r="F35" s="114"/>
+        <v>3-13. JALカード様 -  AIバーチャル顧客を活用したマーケティング高度化</v>
+      </c>
+      <c r="D35" s="114" t="s">
+        <v>202</v>
+      </c>
+      <c r="E35" s="115"/>
+      <c r="F35" s="116"/>
       <c r="G35" s="51" t="s">
         <v>40</v>
       </c>
@@ -4978,16 +5141,18 @@
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
-    <row r="36" spans="1:14" ht="37.799999999999997">
+    <row r="36" spans="1:14" ht="93.6" customHeight="1">
       <c r="A36" s="11"/>
-      <c r="B36" s="118"/>
+      <c r="B36" s="120"/>
       <c r="C36" s="51" t="str">
         <f>master!C27</f>
-        <v>Appendix：りそな様 - AI CoEと生成AI人財育成アカデミーの推進</v>
-      </c>
-      <c r="D36" s="112"/>
-      <c r="E36" s="113"/>
-      <c r="F36" s="114"/>
+        <v>3-14. 大手メディアサービス会社 - AI-BPOによるオペレーション変革</v>
+      </c>
+      <c r="D36" s="114" t="s">
+        <v>203</v>
+      </c>
+      <c r="E36" s="115"/>
+      <c r="F36" s="116"/>
       <c r="G36" s="51" t="s">
         <v>40</v>
       </c>
@@ -5003,48 +5168,50 @@
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
-    <row r="37" spans="1:14" ht="88.2">
+    <row r="37" spans="1:14" ht="59.4" customHeight="1">
       <c r="A37" s="11"/>
-      <c r="B37" s="119" t="str">
-        <f>master!B28</f>
-        <v>モジュール4：プロンプトエンジニアリング</v>
-      </c>
+      <c r="B37" s="120"/>
       <c r="C37" s="51" t="str">
         <f>master!C28</f>
-        <v>4-1. プロンプトとは?</v>
-      </c>
-      <c r="D37" s="112" t="s">
-        <v>172</v>
-      </c>
-      <c r="E37" s="113"/>
-      <c r="F37" s="114"/>
+        <v>Appendix：りそな様 - AI CoEと生成AI人財育成アカデミーの推進</v>
+      </c>
+      <c r="D37" s="114" t="s">
+        <v>204</v>
+      </c>
+      <c r="E37" s="115"/>
+      <c r="F37" s="116"/>
       <c r="G37" s="51" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J37" s="47">
-        <v>1.3888888888888889E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K37" s="43"/>
       <c r="L37" s="6"/>
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
-    <row r="38" spans="1:14" ht="37.799999999999997">
+    <row r="38" spans="1:14" ht="88.2" customHeight="1">
       <c r="A38" s="11"/>
-      <c r="B38" s="120"/>
+      <c r="B38" s="121" t="str">
+        <f>master!B29</f>
+        <v>04. プロンプトエンジニアリング</v>
+      </c>
       <c r="C38" s="51" t="str">
         <f>master!C29</f>
-        <v>4-2. プロンプトを構成する4つの要素</v>
-      </c>
-      <c r="D38" s="112"/>
-      <c r="E38" s="113"/>
-      <c r="F38" s="114"/>
+        <v>4-1. プロンプトとは?</v>
+      </c>
+      <c r="D38" s="114" t="s">
+        <v>162</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="116"/>
       <c r="G38" s="51" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="49" t="s">
@@ -5058,16 +5225,18 @@
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
     </row>
-    <row r="39" spans="1:14" ht="37.799999999999997">
+    <row r="39" spans="1:14" ht="88.8" customHeight="1">
       <c r="A39" s="11"/>
-      <c r="B39" s="120"/>
+      <c r="B39" s="122"/>
       <c r="C39" s="51" t="str">
         <f>master!C30</f>
-        <v>4-3. 悪いプロンプト vs 良いプロンプト</v>
-      </c>
-      <c r="D39" s="112"/>
-      <c r="E39" s="113"/>
-      <c r="F39" s="114"/>
+        <v>4-2. プロンプトを構成する4つの要素</v>
+      </c>
+      <c r="D39" s="114" t="s">
+        <v>207</v>
+      </c>
+      <c r="E39" s="115"/>
+      <c r="F39" s="116"/>
       <c r="G39" s="51" t="s">
         <v>40</v>
       </c>
@@ -5083,16 +5252,18 @@
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
-    <row r="40" spans="1:14" ht="37.799999999999997">
+    <row r="40" spans="1:14" ht="58.8" customHeight="1">
       <c r="A40" s="11"/>
-      <c r="B40" s="120"/>
+      <c r="B40" s="122"/>
       <c r="C40" s="51" t="str">
         <f>master!C31</f>
-        <v>4-4. テクニック①：Role Prompting（役割の付与）</v>
-      </c>
-      <c r="D40" s="112"/>
-      <c r="E40" s="113"/>
-      <c r="F40" s="114"/>
+        <v>4-3. 悪いプロンプト vs 良いプロンプト</v>
+      </c>
+      <c r="D40" s="114" t="s">
+        <v>208</v>
+      </c>
+      <c r="E40" s="115"/>
+      <c r="F40" s="116"/>
       <c r="G40" s="51" t="s">
         <v>40</v>
       </c>
@@ -5101,23 +5272,25 @@
         <v>25</v>
       </c>
       <c r="J40" s="47">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K40" s="43"/>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:14" ht="37.799999999999997">
+    <row r="41" spans="1:14" ht="75.599999999999994" customHeight="1">
       <c r="A41" s="11"/>
-      <c r="B41" s="120"/>
+      <c r="B41" s="122"/>
       <c r="C41" s="51" t="str">
         <f>master!C32</f>
-        <v>4-5. テクニック②：区切り文字の活用</v>
-      </c>
-      <c r="D41" s="112"/>
-      <c r="E41" s="113"/>
-      <c r="F41" s="114"/>
+        <v>4-4. テクニック①：Role Prompting（役割の付与）</v>
+      </c>
+      <c r="D41" s="114" t="s">
+        <v>209</v>
+      </c>
+      <c r="E41" s="115"/>
+      <c r="F41" s="116"/>
       <c r="G41" s="51" t="s">
         <v>40</v>
       </c>
@@ -5133,16 +5306,18 @@
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
-    <row r="42" spans="1:14" ht="37.799999999999997">
+    <row r="42" spans="1:14" ht="64.8" customHeight="1">
       <c r="A42" s="11"/>
-      <c r="B42" s="120"/>
+      <c r="B42" s="122"/>
       <c r="C42" s="51" t="str">
         <f>master!C33</f>
-        <v>4-6. テクニック③：Zero-shot vs Few-shot</v>
-      </c>
-      <c r="D42" s="112"/>
-      <c r="E42" s="113"/>
-      <c r="F42" s="114"/>
+        <v>4-5. テクニック②：区切り文字の活用</v>
+      </c>
+      <c r="D42" s="114" t="s">
+        <v>210</v>
+      </c>
+      <c r="E42" s="115"/>
+      <c r="F42" s="116"/>
       <c r="G42" s="51" t="s">
         <v>40</v>
       </c>
@@ -5158,18 +5333,20 @@
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:14" ht="50.4">
+    <row r="43" spans="1:14" ht="78" customHeight="1">
       <c r="A43" s="11"/>
-      <c r="B43" s="121"/>
+      <c r="B43" s="122"/>
       <c r="C43" s="51" t="str">
         <f>master!C34</f>
-        <v>4-7. テクニック④：Chain of Thought（思考の連鎖）</v>
-      </c>
-      <c r="D43" s="112"/>
-      <c r="E43" s="113"/>
-      <c r="F43" s="114"/>
+        <v>4-6. テクニック③：Zero-shot vs Few-shot</v>
+      </c>
+      <c r="D43" s="114" t="s">
+        <v>211</v>
+      </c>
+      <c r="E43" s="115"/>
+      <c r="F43" s="116"/>
       <c r="G43" s="51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H43" s="12"/>
       <c r="I43" s="49" t="s">
@@ -5183,57 +5360,57 @@
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
     </row>
-    <row r="44" spans="1:14" ht="75.599999999999994">
+    <row r="44" spans="1:14" ht="69.599999999999994" customHeight="1">
       <c r="A44" s="11"/>
-      <c r="B44" s="122" t="str">
-        <f>master!B35</f>
-        <v>モジュール5：ハンズオン（ChatGPT）</v>
-      </c>
-      <c r="C44" s="64" t="str">
+      <c r="B44" s="123"/>
+      <c r="C44" s="51" t="str">
         <f>master!C35</f>
-        <v>5-1. ChatGPTの使い方（一般チャット）</v>
-      </c>
-      <c r="D44" s="125" t="s">
-        <v>173</v>
-      </c>
-      <c r="E44" s="126"/>
-      <c r="F44" s="127"/>
-      <c r="G44" s="64" t="s">
-        <v>42</v>
-      </c>
-      <c r="H44" s="65"/>
-      <c r="I44" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="J44" s="67">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K44" s="68"/>
+        <v>4-7. テクニック④：Chain of Thought（思考の連鎖）</v>
+      </c>
+      <c r="D44" s="114" t="s">
+        <v>212</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="116"/>
+      <c r="G44" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="H44" s="12"/>
+      <c r="I44" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" s="47">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K44" s="43"/>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
     </row>
-    <row r="45" spans="1:14" ht="126">
+    <row r="45" spans="1:14" ht="75.599999999999994">
       <c r="A45" s="11"/>
-      <c r="B45" s="123"/>
+      <c r="B45" s="124" t="str">
+        <f>master!B36</f>
+        <v>05. ハンズオン（ChatGPT）</v>
+      </c>
       <c r="C45" s="64" t="str">
         <f>master!C36</f>
-        <v>5-2. 例①：顧客提案向けの企画提案書を作りたい</v>
-      </c>
-      <c r="D45" s="125" t="s">
-        <v>181</v>
-      </c>
-      <c r="E45" s="126"/>
-      <c r="F45" s="127"/>
+        <v>5-1. ChatGPTの使い方（一般チャット）</v>
+      </c>
+      <c r="D45" s="127" t="s">
+        <v>163</v>
+      </c>
+      <c r="E45" s="128"/>
+      <c r="F45" s="129"/>
       <c r="G45" s="64" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H45" s="65"/>
       <c r="I45" s="66" t="s">
         <v>25</v>
       </c>
       <c r="J45" s="67">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K45" s="68"/>
       <c r="L45" s="6"/>
@@ -5242,16 +5419,16 @@
     </row>
     <row r="46" spans="1:14" ht="126">
       <c r="A46" s="11"/>
-      <c r="B46" s="123"/>
+      <c r="B46" s="125"/>
       <c r="C46" s="64" t="str">
         <f>master!C37</f>
-        <v>5-3. 例①：顧客提案向けの企画提案書を作りたい - プロンプト例</v>
-      </c>
-      <c r="D46" s="125" t="s">
-        <v>141</v>
-      </c>
-      <c r="E46" s="126"/>
-      <c r="F46" s="127"/>
+        <v>5-2. 例①：顧客提案向けの企画提案書を作りたい</v>
+      </c>
+      <c r="D46" s="127" t="s">
+        <v>171</v>
+      </c>
+      <c r="E46" s="128"/>
+      <c r="F46" s="129"/>
       <c r="G46" s="64" t="s">
         <v>44</v>
       </c>
@@ -5260,107 +5437,107 @@
         <v>25</v>
       </c>
       <c r="J46" s="67">
-        <v>3.472222222222222E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K46" s="68"/>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
-    <row r="47" spans="1:14" ht="37.799999999999997">
+    <row r="47" spans="1:14" ht="126">
       <c r="A47" s="11"/>
-      <c r="B47" s="123"/>
+      <c r="B47" s="125"/>
       <c r="C47" s="64" t="str">
         <f>master!C38</f>
-        <v>5-4. 例①：顧客提案向けの企画提案書を作りたい - 実行例</v>
-      </c>
-      <c r="D47" s="125" t="s">
-        <v>140</v>
-      </c>
-      <c r="E47" s="126"/>
-      <c r="F47" s="127"/>
+        <v>5-3. 例①：顧客提案向けの企画提案書を作りたい - プロンプト例</v>
+      </c>
+      <c r="D47" s="127" t="s">
+        <v>133</v>
+      </c>
+      <c r="E47" s="128"/>
+      <c r="F47" s="129"/>
       <c r="G47" s="64" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H47" s="65"/>
       <c r="I47" s="66" t="s">
         <v>25</v>
       </c>
       <c r="J47" s="67">
-        <v>6.9444444444444447E-4</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K47" s="68"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
-    <row r="48" spans="1:14" ht="88.2">
+    <row r="48" spans="1:14" ht="37.799999999999997">
       <c r="A48" s="11"/>
-      <c r="B48" s="123"/>
-      <c r="C48" s="84"/>
-      <c r="D48" s="115" t="s">
-        <v>180</v>
-      </c>
-      <c r="E48" s="116"/>
-      <c r="F48" s="117"/>
-      <c r="G48" s="84" t="s">
-        <v>45</v>
-      </c>
-      <c r="H48" s="85"/>
-      <c r="I48" s="86" t="s">
-        <v>25</v>
-      </c>
-      <c r="J48" s="87">
-        <v>1.3888888888888888E-2</v>
-      </c>
-      <c r="K48" s="88" t="s">
-        <v>128</v>
-      </c>
+      <c r="B48" s="125"/>
+      <c r="C48" s="64" t="str">
+        <f>master!C39</f>
+        <v>5-4. 例①：顧客提案向けの企画提案書を作りたい - 実行例</v>
+      </c>
+      <c r="D48" s="127" t="s">
+        <v>132</v>
+      </c>
+      <c r="E48" s="128"/>
+      <c r="F48" s="129"/>
+      <c r="G48" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H48" s="65"/>
+      <c r="I48" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" s="67">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K48" s="68"/>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
-    <row r="49" spans="1:14" ht="50.4">
+    <row r="49" spans="1:14" ht="88.2">
       <c r="A49" s="11"/>
-      <c r="B49" s="123"/>
-      <c r="C49" s="64" t="str">
-        <f>master!C39</f>
-        <v>5-5. 例②：100本ノックを作ってみる</v>
-      </c>
-      <c r="D49" s="125" t="s">
-        <v>188</v>
-      </c>
-      <c r="E49" s="126"/>
-      <c r="F49" s="127"/>
-      <c r="G49" s="64" t="s">
-        <v>41</v>
-      </c>
-      <c r="H49" s="65"/>
-      <c r="I49" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="J49" s="67">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K49" s="68"/>
+      <c r="B49" s="125"/>
+      <c r="C49" s="84"/>
+      <c r="D49" s="117" t="s">
+        <v>170</v>
+      </c>
+      <c r="E49" s="118"/>
+      <c r="F49" s="119"/>
+      <c r="G49" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="H49" s="85"/>
+      <c r="I49" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="J49" s="87">
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="K49" s="88" t="s">
+        <v>120</v>
+      </c>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
-    <row r="50" spans="1:14" ht="75.599999999999994">
+    <row r="50" spans="1:14" ht="50.4">
       <c r="A50" s="11"/>
-      <c r="B50" s="123"/>
-      <c r="C50" s="128" t="str">
+      <c r="B50" s="125"/>
+      <c r="C50" s="64" t="str">
         <f>master!C40</f>
-        <v>5-6. 例②：100本ノックを作ってみる -プロンプト例</v>
-      </c>
-      <c r="D50" s="125" t="s">
-        <v>174</v>
-      </c>
-      <c r="E50" s="126"/>
-      <c r="F50" s="127"/>
+        <v>5-5. 例②：100本ノックを作ってみる</v>
+      </c>
+      <c r="D50" s="127" t="s">
+        <v>178</v>
+      </c>
+      <c r="E50" s="128"/>
+      <c r="F50" s="129"/>
       <c r="G50" s="64" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H50" s="65"/>
       <c r="I50" s="66" t="s">
@@ -5374,71 +5551,71 @@
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
-    <row r="51" spans="1:14" ht="88.2">
+    <row r="51" spans="1:14" ht="75.599999999999994">
       <c r="A51" s="11"/>
-      <c r="B51" s="123"/>
-      <c r="C51" s="129"/>
-      <c r="D51" s="115" t="s">
-        <v>182</v>
-      </c>
-      <c r="E51" s="116"/>
-      <c r="F51" s="117"/>
-      <c r="G51" s="84" t="s">
-        <v>45</v>
-      </c>
-      <c r="H51" s="85"/>
-      <c r="I51" s="86" t="s">
-        <v>187</v>
-      </c>
-      <c r="J51" s="87">
-        <v>1.3888888888888888E-2</v>
-      </c>
-      <c r="K51" s="88" t="s">
-        <v>128</v>
-      </c>
+      <c r="B51" s="125"/>
+      <c r="C51" s="64" t="str">
+        <f>master!C41</f>
+        <v>5-6. 例②：100本ノックを作ってみる -プロンプト例</v>
+      </c>
+      <c r="D51" s="127" t="s">
+        <v>164</v>
+      </c>
+      <c r="E51" s="128"/>
+      <c r="F51" s="129"/>
+      <c r="G51" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="H51" s="65"/>
+      <c r="I51" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J51" s="67">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K51" s="68"/>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
-    <row r="52" spans="1:14" ht="50.4">
+    <row r="52" spans="1:14" ht="88.2">
       <c r="A52" s="11"/>
-      <c r="B52" s="123"/>
-      <c r="C52" s="64" t="str">
-        <f>master!C41</f>
-        <v>5-7. 例②：100本ノックを作ってみる - 実行結果①</v>
-      </c>
-      <c r="D52" s="125" t="s">
-        <v>151</v>
-      </c>
-      <c r="E52" s="126"/>
-      <c r="F52" s="127"/>
-      <c r="G52" s="64" t="s">
-        <v>41</v>
-      </c>
-      <c r="H52" s="65"/>
-      <c r="I52" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="J52" s="67">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K52" s="68"/>
+      <c r="B52" s="125"/>
+      <c r="C52" s="84"/>
+      <c r="D52" s="117" t="s">
+        <v>172</v>
+      </c>
+      <c r="E52" s="118"/>
+      <c r="F52" s="119"/>
+      <c r="G52" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="H52" s="85"/>
+      <c r="I52" s="86" t="s">
+        <v>177</v>
+      </c>
+      <c r="J52" s="87">
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="K52" s="88" t="s">
+        <v>120</v>
+      </c>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
     <row r="53" spans="1:14" ht="50.4">
       <c r="A53" s="11"/>
-      <c r="B53" s="123"/>
+      <c r="B53" s="125"/>
       <c r="C53" s="64" t="str">
         <f>master!C42</f>
-        <v>5-8. 例②：100本ノックを作ってみる - 実行結果②</v>
-      </c>
-      <c r="D53" s="125" t="s">
-        <v>152</v>
-      </c>
-      <c r="E53" s="126"/>
-      <c r="F53" s="127"/>
+        <v>5-7. 例②：100本ノックを作ってみる - 実行結果①</v>
+      </c>
+      <c r="D53" s="127" t="s">
+        <v>143</v>
+      </c>
+      <c r="E53" s="128"/>
+      <c r="F53" s="129"/>
       <c r="G53" s="64" t="s">
         <v>41</v>
       </c>
@@ -5456,16 +5633,16 @@
     </row>
     <row r="54" spans="1:14" ht="50.4">
       <c r="A54" s="11"/>
-      <c r="B54" s="123"/>
+      <c r="B54" s="125"/>
       <c r="C54" s="64" t="str">
         <f>master!C43</f>
-        <v>5-9. 例②：100本ノックを作ってみる - 実行結果③</v>
-      </c>
-      <c r="D54" s="125" t="s">
-        <v>153</v>
-      </c>
-      <c r="E54" s="126"/>
-      <c r="F54" s="127"/>
+        <v>5-8. 例②：100本ノックを作ってみる - 実行結果②</v>
+      </c>
+      <c r="D54" s="127" t="s">
+        <v>144</v>
+      </c>
+      <c r="E54" s="128"/>
+      <c r="F54" s="129"/>
       <c r="G54" s="64" t="s">
         <v>41</v>
       </c>
@@ -5481,131 +5658,131 @@
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
     </row>
-    <row r="55" spans="1:14" ht="63">
+    <row r="55" spans="1:14" ht="50.4">
       <c r="A55" s="11"/>
-      <c r="B55" s="124"/>
+      <c r="B55" s="125"/>
       <c r="C55" s="64" t="str">
         <f>master!C44</f>
-        <v>5-10. ChatGPT まとめ</v>
-      </c>
-      <c r="D55" s="125" t="s">
-        <v>142</v>
-      </c>
-      <c r="E55" s="126"/>
-      <c r="F55" s="127"/>
+        <v>5-9. 例②：100本ノックを作ってみる - 実行結果③</v>
+      </c>
+      <c r="D55" s="127" t="s">
+        <v>145</v>
+      </c>
+      <c r="E55" s="128"/>
+      <c r="F55" s="129"/>
       <c r="G55" s="64" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H55" s="65"/>
       <c r="I55" s="66" t="s">
         <v>25</v>
       </c>
       <c r="J55" s="67">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K55" s="68"/>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
-    <row r="56" spans="1:14" ht="50.4" customHeight="1">
+    <row r="56" spans="1:14" ht="63">
       <c r="A56" s="11"/>
-      <c r="B56" s="123" t="str">
-        <f>master!B45</f>
-        <v>モジュール6：ハンズオン（ GitHub Copilot ）</v>
-      </c>
+      <c r="B56" s="126"/>
       <c r="C56" s="64" t="str">
         <f>master!C45</f>
-        <v>6-1. Visual Studio Code を開く</v>
-      </c>
-      <c r="D56" s="125" t="s">
-        <v>143</v>
-      </c>
-      <c r="E56" s="126"/>
-      <c r="F56" s="127"/>
+        <v>5-10. ChatGPT まとめ</v>
+      </c>
+      <c r="D56" s="127" t="s">
+        <v>134</v>
+      </c>
+      <c r="E56" s="128"/>
+      <c r="F56" s="129"/>
       <c r="G56" s="64" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H56" s="65"/>
       <c r="I56" s="66" t="s">
         <v>25</v>
       </c>
       <c r="J56" s="67">
-        <v>6.9444444444444447E-4</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K56" s="68"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
-    <row r="57" spans="1:14" ht="63">
+    <row r="57" spans="1:14" ht="50.4" customHeight="1">
       <c r="A57" s="11"/>
-      <c r="B57" s="123"/>
+      <c r="B57" s="125" t="str">
+        <f>master!B46</f>
+        <v>06. ハンズオン（ GitHub Copilot ）</v>
+      </c>
       <c r="C57" s="64" t="str">
         <f>master!C46</f>
-        <v>6-2. コード補完機能</v>
-      </c>
-      <c r="D57" s="125" t="s">
-        <v>144</v>
-      </c>
-      <c r="E57" s="126"/>
-      <c r="F57" s="127"/>
+        <v>6-1. Visual Studio Code を開く</v>
+      </c>
+      <c r="D57" s="127" t="s">
+        <v>135</v>
+      </c>
+      <c r="E57" s="128"/>
+      <c r="F57" s="129"/>
       <c r="G57" s="64" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H57" s="65"/>
       <c r="I57" s="66" t="s">
         <v>25</v>
       </c>
       <c r="J57" s="67">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K57" s="68"/>
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
-    <row r="58" spans="1:14" ht="75.599999999999994">
+    <row r="58" spans="1:14" ht="63">
       <c r="A58" s="11"/>
-      <c r="B58" s="123"/>
+      <c r="B58" s="125"/>
       <c r="C58" s="64" t="str">
         <f>master!C47</f>
-        <v>6-3. チャット機能</v>
-      </c>
-      <c r="D58" s="125" t="s">
-        <v>198</v>
-      </c>
-      <c r="E58" s="126"/>
-      <c r="F58" s="127"/>
+        <v>6-2. コード補完機能</v>
+      </c>
+      <c r="D58" s="127" t="s">
+        <v>136</v>
+      </c>
+      <c r="E58" s="128"/>
+      <c r="F58" s="129"/>
       <c r="G58" s="64" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H58" s="65"/>
       <c r="I58" s="66" t="s">
         <v>25</v>
       </c>
       <c r="J58" s="67">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K58" s="68"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
-    <row r="59" spans="1:14" ht="88.2">
+    <row r="59" spans="1:14" ht="75.599999999999994">
       <c r="A59" s="11"/>
-      <c r="B59" s="123"/>
+      <c r="B59" s="125"/>
       <c r="C59" s="64" t="str">
         <f>master!C48</f>
-        <v>6-4. チャット機能 - コマンド</v>
-      </c>
-      <c r="D59" s="125" t="s">
-        <v>197</v>
-      </c>
-      <c r="E59" s="126"/>
-      <c r="F59" s="127"/>
+        <v>6-3. チャット機能</v>
+      </c>
+      <c r="D59" s="127" t="s">
+        <v>186</v>
+      </c>
+      <c r="E59" s="128"/>
+      <c r="F59" s="129"/>
       <c r="G59" s="64" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H59" s="65"/>
       <c r="I59" s="66" t="s">
@@ -5619,27 +5796,27 @@
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
-    <row r="60" spans="1:14" ht="50.4">
+    <row r="60" spans="1:14" ht="88.2">
       <c r="A60" s="11"/>
-      <c r="B60" s="123"/>
+      <c r="B60" s="125"/>
       <c r="C60" s="64" t="str">
         <f>master!C49</f>
-        <v>6-5. 簡単なアプリやゲームを作ってみましょう</v>
-      </c>
-      <c r="D60" s="125" t="s">
-        <v>165</v>
-      </c>
-      <c r="E60" s="126"/>
-      <c r="F60" s="127"/>
+        <v>6-4. チャット機能 - コマンド</v>
+      </c>
+      <c r="D60" s="127" t="s">
+        <v>185</v>
+      </c>
+      <c r="E60" s="128"/>
+      <c r="F60" s="129"/>
       <c r="G60" s="64" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H60" s="65"/>
       <c r="I60" s="66" t="s">
         <v>25</v>
       </c>
       <c r="J60" s="67">
-        <v>6.9444444444444447E-4</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K60" s="68"/>
       <c r="L60" s="6"/>
@@ -5648,16 +5825,16 @@
     </row>
     <row r="61" spans="1:14" ht="50.4">
       <c r="A61" s="11"/>
-      <c r="B61" s="123"/>
+      <c r="B61" s="125"/>
       <c r="C61" s="64" t="str">
         <f>master!C50</f>
-        <v>6-6. 例①：高級志向テトリス</v>
-      </c>
-      <c r="D61" s="125" t="s">
-        <v>168</v>
-      </c>
-      <c r="E61" s="126"/>
-      <c r="F61" s="127"/>
+        <v>6-5. 簡単なアプリやゲームを作ってみましょう</v>
+      </c>
+      <c r="D61" s="127" t="s">
+        <v>156</v>
+      </c>
+      <c r="E61" s="128"/>
+      <c r="F61" s="129"/>
       <c r="G61" s="64" t="s">
         <v>41</v>
       </c>
@@ -5675,16 +5852,16 @@
     </row>
     <row r="62" spans="1:14" ht="50.4">
       <c r="A62" s="11"/>
-      <c r="B62" s="123"/>
+      <c r="B62" s="125"/>
       <c r="C62" s="64" t="str">
         <f>master!C51</f>
-        <v>6-7. 例②：わくわく！にっぽんダーツの旅</v>
-      </c>
-      <c r="D62" s="125" t="s">
-        <v>166</v>
-      </c>
-      <c r="E62" s="126"/>
-      <c r="F62" s="127"/>
+        <v>6-6. 例①：高級志向テトリス</v>
+      </c>
+      <c r="D62" s="127" t="s">
+        <v>159</v>
+      </c>
+      <c r="E62" s="128"/>
+      <c r="F62" s="129"/>
       <c r="G62" s="64" t="s">
         <v>41</v>
       </c>
@@ -5702,16 +5879,16 @@
     </row>
     <row r="63" spans="1:14" ht="50.4">
       <c r="A63" s="11"/>
-      <c r="B63" s="123"/>
-      <c r="C63" s="128" t="str">
+      <c r="B63" s="125"/>
+      <c r="C63" s="64" t="str">
         <f>master!C52</f>
-        <v>6-8. 例③：タスク管理ツール</v>
-      </c>
-      <c r="D63" s="125" t="s">
-        <v>167</v>
-      </c>
-      <c r="E63" s="126"/>
-      <c r="F63" s="127"/>
+        <v>6-7. 例②：わくわく！にっぽんダーツの旅</v>
+      </c>
+      <c r="D63" s="127" t="s">
+        <v>157</v>
+      </c>
+      <c r="E63" s="128"/>
+      <c r="F63" s="129"/>
       <c r="G63" s="64" t="s">
         <v>41</v>
       </c>
@@ -5727,149 +5904,149 @@
       <c r="M63" s="6"/>
       <c r="N63" s="6"/>
     </row>
-    <row r="64" spans="1:14" ht="138.6">
+    <row r="64" spans="1:14" ht="50.4">
       <c r="A64" s="11"/>
-      <c r="B64" s="123"/>
-      <c r="C64" s="129"/>
-      <c r="D64" s="115" t="s">
-        <v>179</v>
-      </c>
-      <c r="E64" s="116"/>
-      <c r="F64" s="117"/>
-      <c r="G64" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="H64" s="85"/>
-      <c r="I64" s="86" t="s">
-        <v>129</v>
-      </c>
-      <c r="J64" s="87">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K64" s="88"/>
+      <c r="B64" s="125"/>
+      <c r="C64" s="64" t="str">
+        <f>master!C53</f>
+        <v>6-8. 例③：タスク管理ツール</v>
+      </c>
+      <c r="D64" s="127" t="s">
+        <v>158</v>
+      </c>
+      <c r="E64" s="128"/>
+      <c r="F64" s="129"/>
+      <c r="G64" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="H64" s="65"/>
+      <c r="I64" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J64" s="67">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K64" s="68"/>
       <c r="L64" s="6"/>
       <c r="M64" s="6"/>
       <c r="N64" s="6"/>
     </row>
-    <row r="65" spans="1:14" ht="75.599999999999994">
+    <row r="65" spans="1:14" ht="138.6">
       <c r="A65" s="11"/>
-      <c r="B65" s="123"/>
-      <c r="C65" s="128" t="str">
-        <f>master!C53</f>
-        <v>6-9. ディレクトリ作成とファイル配置</v>
-      </c>
-      <c r="D65" s="125" t="s">
-        <v>183</v>
-      </c>
-      <c r="E65" s="126"/>
-      <c r="F65" s="127"/>
-      <c r="G65" s="64" t="s">
-        <v>42</v>
-      </c>
-      <c r="H65" s="65"/>
-      <c r="I65" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="J65" s="67">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K65" s="68"/>
+      <c r="B65" s="125"/>
+      <c r="C65" s="84"/>
+      <c r="D65" s="117" t="s">
+        <v>169</v>
+      </c>
+      <c r="E65" s="118"/>
+      <c r="F65" s="119"/>
+      <c r="G65" s="84" t="s">
+        <v>38</v>
+      </c>
+      <c r="H65" s="85"/>
+      <c r="I65" s="86" t="s">
+        <v>121</v>
+      </c>
+      <c r="J65" s="87">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="K65" s="88"/>
       <c r="L65" s="6"/>
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
     </row>
-    <row r="66" spans="1:14" ht="88.2">
+    <row r="66" spans="1:14" ht="75.599999999999994">
       <c r="A66" s="11"/>
-      <c r="B66" s="123"/>
-      <c r="C66" s="129"/>
-      <c r="D66" s="115" t="s">
-        <v>199</v>
-      </c>
-      <c r="E66" s="116"/>
-      <c r="F66" s="117"/>
-      <c r="G66" s="84" t="s">
-        <v>45</v>
-      </c>
-      <c r="H66" s="85"/>
-      <c r="I66" s="86" t="s">
-        <v>129</v>
-      </c>
-      <c r="J66" s="87">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K66" s="88"/>
+      <c r="B66" s="125"/>
+      <c r="C66" s="64" t="str">
+        <f>master!C54</f>
+        <v>6-9. ディレクトリ作成とファイル配置</v>
+      </c>
+      <c r="D66" s="127" t="s">
+        <v>173</v>
+      </c>
+      <c r="E66" s="128"/>
+      <c r="F66" s="129"/>
+      <c r="G66" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="H66" s="65"/>
+      <c r="I66" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J66" s="67">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K66" s="68"/>
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
     </row>
-    <row r="67" spans="1:14" ht="50.4">
+    <row r="67" spans="1:14" ht="88.2">
       <c r="A67" s="11"/>
-      <c r="B67" s="123"/>
-      <c r="C67" s="64" t="str">
-        <f>master!C54</f>
-        <v>6-10. チャット機能 - Askモード</v>
-      </c>
-      <c r="D67" s="125" t="s">
-        <v>194</v>
-      </c>
-      <c r="E67" s="126"/>
-      <c r="F67" s="127"/>
-      <c r="G67" s="64" t="s">
-        <v>41</v>
-      </c>
-      <c r="H67" s="65"/>
-      <c r="I67" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="J67" s="67">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K67" s="68"/>
+      <c r="B67" s="125"/>
+      <c r="C67" s="84"/>
+      <c r="D67" s="117" t="s">
+        <v>187</v>
+      </c>
+      <c r="E67" s="118"/>
+      <c r="F67" s="119"/>
+      <c r="G67" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="H67" s="85"/>
+      <c r="I67" s="86" t="s">
+        <v>121</v>
+      </c>
+      <c r="J67" s="87">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K67" s="88"/>
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
     </row>
-    <row r="68" spans="1:14" ht="100.8">
+    <row r="68" spans="1:14" ht="50.4">
       <c r="A68" s="11"/>
-      <c r="B68" s="123"/>
+      <c r="B68" s="125"/>
       <c r="C68" s="64" t="str">
         <f>master!C55</f>
-        <v>6-11. Askモードについて</v>
-      </c>
-      <c r="D68" s="125" t="s">
-        <v>146</v>
-      </c>
-      <c r="E68" s="126"/>
-      <c r="F68" s="127"/>
+        <v>6-10. チャット機能 - Askモード</v>
+      </c>
+      <c r="D68" s="127" t="s">
+        <v>182</v>
+      </c>
+      <c r="E68" s="128"/>
+      <c r="F68" s="129"/>
       <c r="G68" s="64" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H68" s="65"/>
       <c r="I68" s="66" t="s">
         <v>25</v>
       </c>
       <c r="J68" s="67">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K68" s="68"/>
       <c r="L68" s="6"/>
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
     </row>
-    <row r="69" spans="1:14" ht="50.4">
+    <row r="69" spans="1:14" ht="100.8">
       <c r="A69" s="11"/>
-      <c r="B69" s="123"/>
+      <c r="B69" s="125"/>
       <c r="C69" s="64" t="str">
         <f>master!C56</f>
-        <v>6-12. 実行例①</v>
-      </c>
-      <c r="D69" s="125" t="s">
-        <v>150</v>
-      </c>
-      <c r="E69" s="126"/>
-      <c r="F69" s="127"/>
+        <v>6-11. Askモードについて</v>
+      </c>
+      <c r="D69" s="127" t="s">
+        <v>138</v>
+      </c>
+      <c r="E69" s="128"/>
+      <c r="F69" s="129"/>
       <c r="G69" s="64" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H69" s="65"/>
       <c r="I69" s="66" t="s">
@@ -5885,16 +6062,16 @@
     </row>
     <row r="70" spans="1:14" ht="50.4">
       <c r="A70" s="11"/>
-      <c r="B70" s="123"/>
+      <c r="B70" s="125"/>
       <c r="C70" s="64" t="str">
         <f>master!C57</f>
-        <v>6-13. 実行例②</v>
-      </c>
-      <c r="D70" s="125" t="s">
-        <v>148</v>
-      </c>
-      <c r="E70" s="126"/>
-      <c r="F70" s="127"/>
+        <v>6-12. 実行例①</v>
+      </c>
+      <c r="D70" s="127" t="s">
+        <v>142</v>
+      </c>
+      <c r="E70" s="128"/>
+      <c r="F70" s="129"/>
       <c r="G70" s="64" t="s">
         <v>41</v>
       </c>
@@ -5912,16 +6089,16 @@
     </row>
     <row r="71" spans="1:14" ht="50.4">
       <c r="A71" s="11"/>
-      <c r="B71" s="123"/>
-      <c r="C71" s="128" t="str">
+      <c r="B71" s="125"/>
+      <c r="C71" s="64" t="str">
         <f>master!C58</f>
-        <v>6-14. 実行例③</v>
-      </c>
-      <c r="D71" s="125" t="s">
-        <v>149</v>
-      </c>
-      <c r="E71" s="126"/>
-      <c r="F71" s="127"/>
+        <v>6-13. 実行例②</v>
+      </c>
+      <c r="D71" s="127" t="s">
+        <v>140</v>
+      </c>
+      <c r="E71" s="128"/>
+      <c r="F71" s="129"/>
       <c r="G71" s="64" t="s">
         <v>41</v>
       </c>
@@ -5937,125 +6114,125 @@
       <c r="M71" s="6"/>
       <c r="N71" s="6"/>
     </row>
-    <row r="72" spans="1:14" ht="138.6">
+    <row r="72" spans="1:14" ht="50.4">
       <c r="A72" s="11"/>
-      <c r="B72" s="123"/>
-      <c r="C72" s="129"/>
-      <c r="D72" s="115" t="s">
-        <v>178</v>
-      </c>
-      <c r="E72" s="116"/>
-      <c r="F72" s="117"/>
-      <c r="G72" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="H72" s="85"/>
-      <c r="I72" s="86" t="s">
-        <v>129</v>
-      </c>
-      <c r="J72" s="87">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K72" s="88"/>
+      <c r="B72" s="125"/>
+      <c r="C72" s="64" t="str">
+        <f>master!C59</f>
+        <v>6-14. 実行例③</v>
+      </c>
+      <c r="D72" s="127" t="s">
+        <v>141</v>
+      </c>
+      <c r="E72" s="128"/>
+      <c r="F72" s="129"/>
+      <c r="G72" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="H72" s="65"/>
+      <c r="I72" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J72" s="67">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K72" s="68"/>
       <c r="L72" s="6"/>
       <c r="M72" s="6"/>
       <c r="N72" s="6"/>
     </row>
-    <row r="73" spans="1:14" ht="63">
+    <row r="73" spans="1:14" ht="138.6">
       <c r="A73" s="11"/>
-      <c r="B73" s="123"/>
-      <c r="C73" s="64" t="str">
-        <f>master!C59</f>
-        <v>6-15. Askモードまとめ</v>
-      </c>
-      <c r="D73" s="125" t="s">
-        <v>145</v>
-      </c>
-      <c r="E73" s="126"/>
-      <c r="F73" s="127"/>
-      <c r="G73" s="64" t="s">
-        <v>39</v>
-      </c>
-      <c r="H73" s="65"/>
-      <c r="I73" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="J73" s="67">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K73" s="68"/>
+      <c r="B73" s="125"/>
+      <c r="C73" s="84"/>
+      <c r="D73" s="117" t="s">
+        <v>168</v>
+      </c>
+      <c r="E73" s="118"/>
+      <c r="F73" s="119"/>
+      <c r="G73" s="84" t="s">
+        <v>38</v>
+      </c>
+      <c r="H73" s="85"/>
+      <c r="I73" s="86" t="s">
+        <v>121</v>
+      </c>
+      <c r="J73" s="87">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="K73" s="88"/>
       <c r="L73" s="6"/>
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
     </row>
-    <row r="74" spans="1:14" ht="50.4">
+    <row r="74" spans="1:14" ht="63">
       <c r="A74" s="11"/>
-      <c r="B74" s="123"/>
+      <c r="B74" s="125"/>
       <c r="C74" s="64" t="str">
         <f>master!C60</f>
-        <v>6-16. チャット機能 - Agentモード</v>
-      </c>
-      <c r="D74" s="125" t="s">
-        <v>195</v>
-      </c>
-      <c r="E74" s="126"/>
-      <c r="F74" s="127"/>
+        <v>6-15. Askモードまとめ</v>
+      </c>
+      <c r="D74" s="127" t="s">
+        <v>137</v>
+      </c>
+      <c r="E74" s="128"/>
+      <c r="F74" s="129"/>
       <c r="G74" s="64" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H74" s="65"/>
       <c r="I74" s="66" t="s">
         <v>25</v>
       </c>
       <c r="J74" s="67">
-        <v>6.9444444444444447E-4</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K74" s="68"/>
       <c r="L74" s="6"/>
       <c r="M74" s="6"/>
       <c r="N74" s="6"/>
     </row>
-    <row r="75" spans="1:14" ht="63">
+    <row r="75" spans="1:14" ht="50.4">
       <c r="A75" s="11"/>
-      <c r="B75" s="123"/>
+      <c r="B75" s="125"/>
       <c r="C75" s="64" t="str">
         <f>master!C61</f>
-        <v>6-17. Agentモード</v>
-      </c>
-      <c r="D75" s="125" t="s">
-        <v>154</v>
-      </c>
-      <c r="E75" s="126"/>
-      <c r="F75" s="127"/>
+        <v>6-16. チャット機能 - Agentモード</v>
+      </c>
+      <c r="D75" s="127" t="s">
+        <v>183</v>
+      </c>
+      <c r="E75" s="128"/>
+      <c r="F75" s="129"/>
       <c r="G75" s="64" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H75" s="65"/>
       <c r="I75" s="66" t="s">
         <v>25</v>
       </c>
       <c r="J75" s="67">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K75" s="68"/>
       <c r="L75" s="6"/>
       <c r="M75" s="6"/>
       <c r="N75" s="6"/>
     </row>
-    <row r="76" spans="1:14" ht="50.4">
+    <row r="76" spans="1:14" ht="63">
       <c r="A76" s="11"/>
-      <c r="B76" s="123"/>
+      <c r="B76" s="125"/>
       <c r="C76" s="64" t="str">
         <f>master!C62</f>
-        <v>6-18. 実行例</v>
-      </c>
-      <c r="D76" s="125" t="s">
-        <v>155</v>
-      </c>
-      <c r="E76" s="126"/>
-      <c r="F76" s="127"/>
+        <v>6-17. Agentモード</v>
+      </c>
+      <c r="D76" s="127" t="s">
+        <v>146</v>
+      </c>
+      <c r="E76" s="128"/>
+      <c r="F76" s="129"/>
       <c r="G76" s="64" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H76" s="65"/>
       <c r="I76" s="66" t="s">
@@ -6069,20 +6246,20 @@
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
     </row>
-    <row r="77" spans="1:14" ht="37.799999999999997">
+    <row r="77" spans="1:14" ht="50.4">
       <c r="A77" s="11"/>
-      <c r="B77" s="123"/>
+      <c r="B77" s="125"/>
       <c r="C77" s="64" t="str">
         <f>master!C63</f>
-        <v>6-19. READMEの内容を確認しましょう①</v>
-      </c>
-      <c r="D77" s="125" t="s">
-        <v>201</v>
-      </c>
-      <c r="E77" s="126"/>
-      <c r="F77" s="127"/>
+        <v>6-18. 実行例</v>
+      </c>
+      <c r="D77" s="127" t="s">
+        <v>147</v>
+      </c>
+      <c r="E77" s="128"/>
+      <c r="F77" s="129"/>
       <c r="G77" s="64" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H77" s="65"/>
       <c r="I77" s="66" t="s">
@@ -6098,16 +6275,16 @@
     </row>
     <row r="78" spans="1:14" ht="37.799999999999997">
       <c r="A78" s="11"/>
-      <c r="B78" s="123"/>
-      <c r="C78" s="128" t="str">
+      <c r="B78" s="125"/>
+      <c r="C78" s="64" t="str">
         <f>master!C64</f>
-        <v>6-20. READMEの内容を確認しましょう②</v>
-      </c>
-      <c r="D78" s="125" t="s">
-        <v>200</v>
-      </c>
-      <c r="E78" s="126"/>
-      <c r="F78" s="127"/>
+        <v>6-19. READMEの内容を確認しましょう①</v>
+      </c>
+      <c r="D78" s="127" t="s">
+        <v>189</v>
+      </c>
+      <c r="E78" s="128"/>
+      <c r="F78" s="129"/>
       <c r="G78" s="64" t="s">
         <v>40</v>
       </c>
@@ -6123,133 +6300,133 @@
       <c r="M78" s="6"/>
       <c r="N78" s="6"/>
     </row>
-    <row r="79" spans="1:14" ht="126">
+    <row r="79" spans="1:14" ht="37.799999999999997">
       <c r="A79" s="11"/>
-      <c r="B79" s="123"/>
-      <c r="C79" s="129"/>
-      <c r="D79" s="115" t="s">
-        <v>177</v>
-      </c>
-      <c r="E79" s="116"/>
-      <c r="F79" s="117"/>
-      <c r="G79" s="84" t="s">
-        <v>44</v>
-      </c>
-      <c r="H79" s="85"/>
-      <c r="I79" s="86" t="s">
-        <v>129</v>
-      </c>
-      <c r="J79" s="87">
-        <v>1.0416666666666666E-2</v>
-      </c>
-      <c r="K79" s="88" t="s">
-        <v>147</v>
-      </c>
+      <c r="B79" s="125"/>
+      <c r="C79" s="64" t="str">
+        <f>master!C65</f>
+        <v>6-20. READMEの内容を確認しましょう②</v>
+      </c>
+      <c r="D79" s="127" t="s">
+        <v>188</v>
+      </c>
+      <c r="E79" s="128"/>
+      <c r="F79" s="129"/>
+      <c r="G79" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H79" s="65"/>
+      <c r="I79" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J79" s="67">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K79" s="68"/>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
       <c r="N79" s="6"/>
     </row>
-    <row r="80" spans="1:14" ht="50.4">
+    <row r="80" spans="1:14" ht="126">
       <c r="A80" s="11"/>
-      <c r="B80" s="123"/>
-      <c r="C80" s="128" t="str">
-        <f>master!C65</f>
-        <v>6-21. Changeログを作ってみましょう</v>
-      </c>
-      <c r="D80" s="125" t="s">
-        <v>156</v>
-      </c>
-      <c r="E80" s="126"/>
-      <c r="F80" s="127"/>
-      <c r="G80" s="64" t="s">
-        <v>41</v>
-      </c>
-      <c r="H80" s="65"/>
-      <c r="I80" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="J80" s="67">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K80" s="68"/>
+      <c r="B80" s="125"/>
+      <c r="C80" s="84"/>
+      <c r="D80" s="117" t="s">
+        <v>167</v>
+      </c>
+      <c r="E80" s="118"/>
+      <c r="F80" s="119"/>
+      <c r="G80" s="84" t="s">
+        <v>44</v>
+      </c>
+      <c r="H80" s="85"/>
+      <c r="I80" s="86" t="s">
+        <v>121</v>
+      </c>
+      <c r="J80" s="87">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="K80" s="88" t="s">
+        <v>139</v>
+      </c>
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
       <c r="N80" s="6"/>
     </row>
-    <row r="81" spans="1:14" ht="113.4">
+    <row r="81" spans="1:14" ht="50.4">
       <c r="A81" s="11"/>
-      <c r="B81" s="123"/>
-      <c r="C81" s="129"/>
-      <c r="D81" s="115" t="s">
-        <v>176</v>
-      </c>
-      <c r="E81" s="116"/>
-      <c r="F81" s="117"/>
-      <c r="G81" s="84" t="s">
-        <v>43</v>
-      </c>
-      <c r="H81" s="85"/>
-      <c r="I81" s="86" t="s">
-        <v>187</v>
-      </c>
-      <c r="J81" s="87">
-        <v>6.9444444444444441E-3</v>
-      </c>
-      <c r="K81" s="88" t="s">
-        <v>128</v>
-      </c>
+      <c r="B81" s="125"/>
+      <c r="C81" s="64" t="str">
+        <f>master!C66</f>
+        <v>6-21. Changeログを作ってみましょう</v>
+      </c>
+      <c r="D81" s="127" t="s">
+        <v>148</v>
+      </c>
+      <c r="E81" s="128"/>
+      <c r="F81" s="129"/>
+      <c r="G81" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="H81" s="65"/>
+      <c r="I81" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J81" s="67">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K81" s="68"/>
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
       <c r="N81" s="6"/>
     </row>
-    <row r="82" spans="1:14" ht="50.4">
+    <row r="82" spans="1:14" ht="113.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="123"/>
-      <c r="C82" s="64" t="str">
-        <f>master!C66</f>
-        <v>6-22. チャット機能 - Planモード</v>
-      </c>
-      <c r="D82" s="125" t="s">
-        <v>196</v>
-      </c>
-      <c r="E82" s="126"/>
-      <c r="F82" s="127"/>
-      <c r="G82" s="64" t="s">
-        <v>41</v>
-      </c>
-      <c r="H82" s="65"/>
-      <c r="I82" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="J82" s="67">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K82" s="68"/>
+      <c r="B82" s="125"/>
+      <c r="C82" s="89"/>
+      <c r="D82" s="117" t="s">
+        <v>166</v>
+      </c>
+      <c r="E82" s="118"/>
+      <c r="F82" s="119"/>
+      <c r="G82" s="84" t="s">
+        <v>43</v>
+      </c>
+      <c r="H82" s="85"/>
+      <c r="I82" s="86" t="s">
+        <v>177</v>
+      </c>
+      <c r="J82" s="87">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K82" s="88" t="s">
+        <v>120</v>
+      </c>
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
       <c r="N82" s="6"/>
     </row>
-    <row r="83" spans="1:14" ht="63">
+    <row r="83" spans="1:14" ht="50.4">
       <c r="A83" s="11"/>
-      <c r="B83" s="123"/>
+      <c r="B83" s="125"/>
       <c r="C83" s="64" t="str">
         <f>master!C67</f>
-        <v>6-23. Planモードで機能追加してみましょう</v>
-      </c>
-      <c r="D83" s="125" t="s">
-        <v>160</v>
-      </c>
-      <c r="E83" s="126"/>
-      <c r="F83" s="127"/>
+        <v>6-22. チャット機能 - Planモード</v>
+      </c>
+      <c r="D83" s="127" t="s">
+        <v>184</v>
+      </c>
+      <c r="E83" s="128"/>
+      <c r="F83" s="129"/>
       <c r="G83" s="64" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H83" s="65"/>
       <c r="I83" s="66" t="s">
         <v>25</v>
       </c>
       <c r="J83" s="67">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K83" s="68"/>
       <c r="L83" s="6"/>
@@ -6258,16 +6435,16 @@
     </row>
     <row r="84" spans="1:14" ht="63">
       <c r="A84" s="11"/>
-      <c r="B84" s="123"/>
+      <c r="B84" s="125"/>
       <c r="C84" s="64" t="str">
         <f>master!C68</f>
-        <v>6-24. 実行例①</v>
-      </c>
-      <c r="D84" s="125" t="s">
-        <v>157</v>
-      </c>
-      <c r="E84" s="126"/>
-      <c r="F84" s="127"/>
+        <v>6-23. Planモードで機能追加してみましょう</v>
+      </c>
+      <c r="D84" s="127" t="s">
+        <v>152</v>
+      </c>
+      <c r="E84" s="128"/>
+      <c r="F84" s="129"/>
       <c r="G84" s="64" t="s">
         <v>39</v>
       </c>
@@ -6283,20 +6460,20 @@
       <c r="M84" s="6"/>
       <c r="N84" s="6"/>
     </row>
-    <row r="85" spans="1:14" ht="50.4">
+    <row r="85" spans="1:14" ht="63">
       <c r="A85" s="11"/>
-      <c r="B85" s="123"/>
+      <c r="B85" s="125"/>
       <c r="C85" s="64" t="str">
         <f>master!C69</f>
-        <v>6-25. 実行例②</v>
-      </c>
-      <c r="D85" s="125" t="s">
-        <v>158</v>
-      </c>
-      <c r="E85" s="126"/>
-      <c r="F85" s="127"/>
+        <v>6-24. 実行例①</v>
+      </c>
+      <c r="D85" s="127" t="s">
+        <v>149</v>
+      </c>
+      <c r="E85" s="128"/>
+      <c r="F85" s="129"/>
       <c r="G85" s="64" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H85" s="65"/>
       <c r="I85" s="66" t="s">
@@ -6312,16 +6489,16 @@
     </row>
     <row r="86" spans="1:14" ht="50.4">
       <c r="A86" s="11"/>
-      <c r="B86" s="123"/>
-      <c r="C86" s="128" t="str">
+      <c r="B86" s="125"/>
+      <c r="C86" s="64" t="str">
         <f>master!C70</f>
-        <v>6-26. 実行例③</v>
-      </c>
-      <c r="D86" s="125" t="s">
-        <v>159</v>
-      </c>
-      <c r="E86" s="126"/>
-      <c r="F86" s="127"/>
+        <v>6-25. 実行例②</v>
+      </c>
+      <c r="D86" s="127" t="s">
+        <v>150</v>
+      </c>
+      <c r="E86" s="128"/>
+      <c r="F86" s="129"/>
       <c r="G86" s="64" t="s">
         <v>41</v>
       </c>
@@ -6337,69 +6514,69 @@
       <c r="M86" s="6"/>
       <c r="N86" s="6"/>
     </row>
-    <row r="87" spans="1:14" ht="126">
+    <row r="87" spans="1:14" ht="50.4">
       <c r="A87" s="11"/>
-      <c r="B87" s="123"/>
-      <c r="C87" s="129"/>
-      <c r="D87" s="115" t="s">
-        <v>175</v>
-      </c>
-      <c r="E87" s="116"/>
-      <c r="F87" s="117"/>
-      <c r="G87" s="84" t="s">
-        <v>44</v>
-      </c>
-      <c r="H87" s="85"/>
-      <c r="I87" s="86" t="s">
-        <v>25</v>
-      </c>
-      <c r="J87" s="87">
-        <v>1.0416666666666666E-2</v>
-      </c>
-      <c r="K87" s="88"/>
+      <c r="B87" s="125"/>
+      <c r="C87" s="64" t="str">
+        <f>master!C71</f>
+        <v>6-26. 実行例③</v>
+      </c>
+      <c r="D87" s="127" t="s">
+        <v>151</v>
+      </c>
+      <c r="E87" s="128"/>
+      <c r="F87" s="129"/>
+      <c r="G87" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="H87" s="65"/>
+      <c r="I87" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J87" s="67">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K87" s="68"/>
       <c r="L87" s="6"/>
       <c r="M87" s="6"/>
       <c r="N87" s="6"/>
     </row>
-    <row r="88" spans="1:14" ht="50.4">
+    <row r="88" spans="1:14" ht="126">
       <c r="A88" s="11"/>
-      <c r="B88" s="123"/>
-      <c r="C88" s="64" t="str">
-        <f>master!C71</f>
-        <v>6-27. 実行結果①</v>
-      </c>
-      <c r="D88" s="125" t="s">
-        <v>161</v>
-      </c>
-      <c r="E88" s="126"/>
-      <c r="F88" s="127"/>
-      <c r="G88" s="64" t="s">
-        <v>41</v>
-      </c>
-      <c r="H88" s="65"/>
-      <c r="I88" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="J88" s="67">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K88" s="68"/>
+      <c r="B88" s="125"/>
+      <c r="C88" s="84"/>
+      <c r="D88" s="117" t="s">
+        <v>165</v>
+      </c>
+      <c r="E88" s="118"/>
+      <c r="F88" s="119"/>
+      <c r="G88" s="84" t="s">
+        <v>44</v>
+      </c>
+      <c r="H88" s="85"/>
+      <c r="I88" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="J88" s="87">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="K88" s="88"/>
       <c r="L88" s="6"/>
       <c r="M88" s="6"/>
       <c r="N88" s="6"/>
     </row>
     <row r="89" spans="1:14" ht="50.4">
       <c r="A89" s="11"/>
-      <c r="B89" s="123"/>
+      <c r="B89" s="125"/>
       <c r="C89" s="64" t="str">
         <f>master!C72</f>
-        <v>6-28. 実行結果②</v>
-      </c>
-      <c r="D89" s="125" t="s">
-        <v>162</v>
-      </c>
-      <c r="E89" s="126"/>
-      <c r="F89" s="127"/>
+        <v>6-27. 実行結果①</v>
+      </c>
+      <c r="D89" s="127" t="s">
+        <v>153</v>
+      </c>
+      <c r="E89" s="128"/>
+      <c r="F89" s="129"/>
       <c r="G89" s="64" t="s">
         <v>41</v>
       </c>
@@ -6415,20 +6592,20 @@
       <c r="M89" s="6"/>
       <c r="N89" s="6"/>
     </row>
-    <row r="90" spans="1:14" ht="113.4">
+    <row r="90" spans="1:14" ht="50.4">
       <c r="A90" s="11"/>
-      <c r="B90" s="124"/>
+      <c r="B90" s="125"/>
       <c r="C90" s="64" t="str">
         <f>master!C73</f>
-        <v>6-29. Planモード＆Agentモードまとめ</v>
-      </c>
-      <c r="D90" s="125" t="s">
-        <v>163</v>
-      </c>
-      <c r="E90" s="126"/>
-      <c r="F90" s="127"/>
+        <v>6-28. 実行結果②</v>
+      </c>
+      <c r="D90" s="127" t="s">
+        <v>154</v>
+      </c>
+      <c r="E90" s="128"/>
+      <c r="F90" s="129"/>
       <c r="G90" s="64" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H90" s="65"/>
       <c r="I90" s="66" t="s">
@@ -6442,160 +6619,188 @@
       <c r="M90" s="6"/>
       <c r="N90" s="6"/>
     </row>
-    <row r="91" spans="1:14" ht="102" customHeight="1">
+    <row r="91" spans="1:14" ht="113.4">
       <c r="A91" s="11"/>
-      <c r="B91" s="122" t="str">
-        <f>master!B74</f>
-        <v>成果物のプレゼン</v>
-      </c>
-      <c r="C91" s="84" t="str">
+      <c r="B91" s="126"/>
+      <c r="C91" s="64" t="str">
         <f>master!C74</f>
-        <v>開発した成果物のプレゼン（グループ）</v>
-      </c>
-      <c r="D91" s="115" t="s">
-        <v>191</v>
-      </c>
-      <c r="E91" s="116"/>
-      <c r="F91" s="117"/>
-      <c r="G91" s="84" t="s">
-        <v>47</v>
-      </c>
-      <c r="H91" s="85"/>
-      <c r="I91" s="86" t="s">
-        <v>25</v>
-      </c>
-      <c r="J91" s="87">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K91" s="88"/>
+        <v>6-29. Planモード＆Agentモードまとめ</v>
+      </c>
+      <c r="D91" s="127" t="s">
+        <v>155</v>
+      </c>
+      <c r="E91" s="128"/>
+      <c r="F91" s="129"/>
+      <c r="G91" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="H91" s="65"/>
+      <c r="I91" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J91" s="67">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K91" s="68"/>
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="1:14" ht="88.2">
+    <row r="92" spans="1:14" ht="102" customHeight="1">
       <c r="A92" s="11"/>
-      <c r="B92" s="124"/>
+      <c r="B92" s="124" t="str">
+        <f>master!B75</f>
+        <v>成果物のプレゼン</v>
+      </c>
       <c r="C92" s="84" t="str">
         <f>master!C75</f>
-        <v>開発した成果物のプレゼン（全体）</v>
-      </c>
-      <c r="D92" s="115" t="s">
-        <v>186</v>
-      </c>
-      <c r="E92" s="116"/>
-      <c r="F92" s="117"/>
+        <v>開発した成果物のプレゼン（グループ）</v>
+      </c>
+      <c r="D92" s="117" t="s">
+        <v>180</v>
+      </c>
+      <c r="E92" s="118"/>
+      <c r="F92" s="119"/>
       <c r="G92" s="84" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H92" s="85"/>
       <c r="I92" s="86" t="s">
-        <v>48</v>
-      </c>
-      <c r="J92" s="87" t="s">
-        <v>36</v>
-      </c>
-      <c r="K92" s="88" t="s">
-        <v>190</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="J92" s="87">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="K92" s="88"/>
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
       <c r="N92" s="6"/>
     </row>
-    <row r="93" spans="1:14" ht="15" customHeight="1">
-      <c r="J93" s="46"/>
-    </row>
-    <row r="94" spans="1:14" ht="15" customHeight="1"/>
+    <row r="93" spans="1:14" ht="88.2">
+      <c r="A93" s="11"/>
+      <c r="B93" s="126"/>
+      <c r="C93" s="84" t="str">
+        <f>master!C76</f>
+        <v>開発した成果物のプレゼン（全体）</v>
+      </c>
+      <c r="D93" s="117" t="s">
+        <v>176</v>
+      </c>
+      <c r="E93" s="118"/>
+      <c r="F93" s="119"/>
+      <c r="G93" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="H93" s="85"/>
+      <c r="I93" s="86" t="s">
+        <v>48</v>
+      </c>
+      <c r="J93" s="87" t="s">
+        <v>36</v>
+      </c>
+      <c r="K93" s="88" t="s">
+        <v>179</v>
+      </c>
+      <c r="L93" s="6"/>
+      <c r="M93" s="6"/>
+      <c r="N93" s="6"/>
+    </row>
+    <row r="94" spans="1:14" ht="15" customHeight="1">
+      <c r="J94" s="46"/>
+    </row>
+    <row r="95" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="99">
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D87:F87"/>
+  <mergeCells count="100">
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D92:F92"/>
     <mergeCell ref="D91:F91"/>
     <mergeCell ref="D90:F90"/>
     <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D87:F87"/>
     <mergeCell ref="D82:F82"/>
     <mergeCell ref="D83:F83"/>
     <mergeCell ref="D84:F84"/>
     <mergeCell ref="D85:F85"/>
-    <mergeCell ref="B37:B43"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
     <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D73:F73"/>
     <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D73:F73"/>
     <mergeCell ref="D74:F74"/>
     <mergeCell ref="D75:F75"/>
     <mergeCell ref="D76:F76"/>
     <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="B56:B90"/>
-    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B57:B91"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D32:F32"/>
     <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D27:F27"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D30:F30"/>
     <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D44:F44"/>
     <mergeCell ref="D37:F37"/>
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="D39:F39"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="D41:F41"/>
-    <mergeCell ref="B44:B55"/>
-    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="B45:B56"/>
     <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D55:F55"/>
     <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D55:F55"/>
     <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D51:F51"/>
     <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D50:F50"/>
     <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B18:B22"/>
     <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="B22:B36"/>
+    <mergeCell ref="D19:F19"/>
     <mergeCell ref="D22:F22"/>
+    <mergeCell ref="B23:B37"/>
     <mergeCell ref="D23:F23"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
     <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D32:F32"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D13:F13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="B15:B17"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D14:F14"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:K5"/>
     <mergeCell ref="D7:E7"/>
@@ -6614,11 +6819,11 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{37C63177-3313-4E9D-87CD-3CDC1DBD7A44}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000000000000}">
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H12:H92</xm:sqref>
+          <xm:sqref>H12:H93</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6628,7 +6833,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:C75"/>
+  <dimension ref="B1:C76"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="4.6640625" customWidth="1"/>
@@ -6637,7 +6842,7 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="2:3">
@@ -6653,330 +6858,333 @@
         <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="C4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="2:3">
-      <c r="B5" s="83" t="s">
-        <v>57</v>
+      <c r="B5" t="s">
+        <v>224</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="2:3">
+      <c r="B6" s="83" t="s">
+        <v>213</v>
+      </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="2:3">
-      <c r="B8" s="83" t="s">
-        <v>103</v>
-      </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="2:3">
+      <c r="B9" s="83" t="s">
+        <v>215</v>
+      </c>
       <c r="C9" t="s">
-        <v>208</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="C10" t="s">
-        <v>62</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="2:3">
-      <c r="B13" s="83" t="s">
-        <v>189</v>
-      </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="2:3">
+      <c r="B14" s="83" t="s">
+        <v>216</v>
+      </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="C15" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="C16" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="2:3">
       <c r="C17" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="C18" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="C19" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="C20" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="C21" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="C22" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="C23" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="2:3">
       <c r="C24" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="C25" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="C26" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="2:3">
       <c r="C27" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="2:3">
-      <c r="B28" s="83" t="s">
-        <v>81</v>
-      </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="2:3">
+      <c r="B29" s="83" t="s">
+        <v>217</v>
+      </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="2:3">
       <c r="C30" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="2:3">
       <c r="C31" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="2:3">
       <c r="C32" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="C33" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="2:3">
       <c r="C34" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="2:3">
-      <c r="B35" s="83" t="s">
-        <v>80</v>
-      </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="2:3">
+      <c r="B36" s="83" t="s">
+        <v>218</v>
+      </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="2:3">
       <c r="C37" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="2:3">
       <c r="C38" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="2:3">
       <c r="C39" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="2:3">
       <c r="C40" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="2:3">
       <c r="C41" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="C42" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="2:3">
       <c r="C43" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="2:3">
       <c r="C44" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="2:3">
-      <c r="B45" s="83" t="s">
-        <v>84</v>
-      </c>
       <c r="C45" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="2:3">
+      <c r="B46" s="83" t="s">
+        <v>219</v>
+      </c>
       <c r="C46" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="2:3">
       <c r="C47" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="2:3">
       <c r="C48" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="3:3">
       <c r="C49" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="3:3">
       <c r="C51" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" spans="3:3">
       <c r="C52" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="3:3">
       <c r="C53" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="3:3">
       <c r="C54" t="s">
-        <v>125</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="3:3">
       <c r="C55" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="3:3">
       <c r="C56" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="3:3">
       <c r="C57" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="3:3">
       <c r="C58" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="3:3">
       <c r="C59" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="3:3">
       <c r="C60" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" spans="3:3">
       <c r="C61" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="3:3">
       <c r="C62" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63" spans="3:3">
       <c r="C63" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="64" spans="3:3">
       <c r="C64" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="2:3">
@@ -6986,55 +7194,60 @@
     </row>
     <row r="66" spans="2:3">
       <c r="C66" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="2:3">
       <c r="C67" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
     </row>
     <row r="68" spans="2:3">
       <c r="C68" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69" spans="2:3">
       <c r="C69" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" spans="2:3">
       <c r="C70" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="71" spans="2:3">
       <c r="C71" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="2:3">
       <c r="C72" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="73" spans="2:3">
       <c r="C73" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="74" spans="2:3">
-      <c r="B74" t="s">
-        <v>130</v>
-      </c>
       <c r="C74" t="s">
-        <v>185</v>
+        <v>95</v>
       </c>
     </row>
     <row r="75" spans="2:3">
+      <c r="B75" t="s">
+        <v>122</v>
+      </c>
       <c r="C75" t="s">
-        <v>184</v>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3">
+      <c r="C76" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
